--- a/code/goal19/nlp_demo/task0_vertjump_no_cvt_results.xlsx
+++ b/code/goal19/nlp_demo/task0_vertjump_no_cvt_results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T99"/>
+  <dimension ref="A1:T101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -523,61 +523,61 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.1461830129138172</v>
+        <v>0.1461830126705125</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.2967000344706324</v>
+        <v>-0.2967000339617897</v>
       </c>
       <c r="D2" t="n">
-        <v>-2.548192584648528</v>
+        <v>-2.548192585666214</v>
       </c>
       <c r="E2" t="n">
-        <v>3.889866461925354e-24</v>
+        <v>1.405343351662499e-25</v>
       </c>
       <c r="F2" t="n">
-        <v>2.103578522370098e-23</v>
+        <v>1.032175778623011e-23</v>
       </c>
       <c r="G2" t="n">
-        <v>3.870003122775076e-22</v>
+        <v>-3.19644665953929e-23</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.225067683469641</v>
+        <v>-1.048276159022536</v>
       </c>
       <c r="I2" t="n">
-        <v>8.404264366500868</v>
+        <v>8.11487625433203</v>
       </c>
       <c r="J2" t="n">
-        <v>-1.225067683469641</v>
+        <v>-1.048276159022536</v>
       </c>
       <c r="K2" t="n">
-        <v>8.404264366500868</v>
+        <v>8.11487625433203</v>
       </c>
       <c r="L2" t="n">
-        <v>9.886288349368478</v>
+        <v>9.88632007705316</v>
       </c>
       <c r="M2" t="n">
-        <v>32.95512539999962</v>
+        <v>32.95512540000004</v>
       </c>
       <c r="N2" t="n">
-        <v>28.01185658999967</v>
+        <v>28.01185659000003</v>
       </c>
       <c r="O2" t="n">
-        <v>-2.577026067396427e-23</v>
+        <v>-1.082005260651026e-23</v>
       </c>
       <c r="P2" t="n">
-        <v>3.252452934298566e-21</v>
+        <v>-2.593876909573432e-22</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.226682673624601e-21</v>
+        <v>-2.702077435638535e-22</v>
       </c>
       <c r="R2" t="n">
-        <v>2.577026067396427e-23</v>
+        <v>1.082005260651026e-23</v>
       </c>
       <c r="S2" t="n">
-        <v>3.252452934298566e-21</v>
+        <v>2.593876909573432e-22</v>
       </c>
       <c r="T2" t="n">
-        <v>3.226682673624601e-21</v>
+        <v>2.702077435638535e-22</v>
       </c>
     </row>
     <row r="3">
@@ -585,61 +585,61 @@
         <v>0.002</v>
       </c>
       <c r="B3" t="n">
-        <v>0.1463639350733554</v>
+        <v>0.1463450074372451</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.2970784474789943</v>
+        <v>-0.2970388560434017</v>
       </c>
       <c r="D3" t="n">
-        <v>-2.547435758631805</v>
+        <v>-2.54751494150299</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01434125854114599</v>
+        <v>0.01225214608800845</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.2297745760645653</v>
+        <v>-0.2015949650031156</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4595491521290533</v>
+        <v>0.4031899300062489</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.069508033613052</v>
+        <v>-0.9913382892612282</v>
       </c>
       <c r="I3" t="n">
-        <v>8.671330862617356</v>
+        <v>8.340509704685473</v>
       </c>
       <c r="J3" t="n">
-        <v>-1.069508033613052</v>
+        <v>-1.089716632182749</v>
       </c>
       <c r="K3" t="n">
-        <v>8.671330862617356</v>
+        <v>8.346194682698561</v>
       </c>
       <c r="L3" t="n">
-        <v>10.69488664192826</v>
+        <v>10.60181120998474</v>
       </c>
       <c r="M3" t="n">
-        <v>35.65174889270138</v>
+        <v>35.34462475805658</v>
       </c>
       <c r="N3" t="n">
-        <v>30.30398655879618</v>
+        <v>30.04293104434809</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2226236125377846</v>
+        <v>0.192035388060578</v>
       </c>
       <c r="P3" t="n">
-        <v>4.06429543634972</v>
+        <v>3.424735579464122</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.286919048887505</v>
+        <v>3.6167709675247</v>
       </c>
       <c r="R3" t="n">
-        <v>0.2226236125377846</v>
+        <v>0.192035388060578</v>
       </c>
       <c r="S3" t="n">
-        <v>4.06429543634972</v>
+        <v>3.424735579464122</v>
       </c>
       <c r="T3" t="n">
-        <v>4.286919048887505</v>
+        <v>3.6167709675247</v>
       </c>
     </row>
     <row r="4">
@@ -647,61 +647,61 @@
         <v>0.004</v>
       </c>
       <c r="B4" t="n">
-        <v>0.1466629581654667</v>
+        <v>0.146602243174131</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.2977040180493256</v>
+        <v>-0.2975769836724323</v>
       </c>
       <c r="D4" t="n">
-        <v>-2.546184617491142</v>
+        <v>-2.546438686244928</v>
       </c>
       <c r="E4" t="n">
-        <v>0.02877397474818754</v>
+        <v>0.0245674416530214</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.4473523714278799</v>
+        <v>-0.3930385780820428</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8947047428556967</v>
+        <v>0.786077156164123</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.9051945216579553</v>
+        <v>-0.9296868422867096</v>
       </c>
       <c r="I4" t="n">
-        <v>9.006133492514946</v>
+        <v>8.630127094616366</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.9051945216579553</v>
+        <v>-1.121489668390746</v>
       </c>
       <c r="K4" t="n">
-        <v>9.006133492514946</v>
+        <v>8.64121078251828</v>
       </c>
       <c r="L4" t="n">
-        <v>11.60102144194838</v>
+        <v>11.37701615412466</v>
       </c>
       <c r="M4" t="n">
-        <v>38.73549580179549</v>
+        <v>38.0451608286163</v>
       </c>
       <c r="N4" t="n">
-        <v>32.92517143152617</v>
+        <v>32.33838670432386</v>
       </c>
       <c r="O4" t="n">
-        <v>0.3888550963783793</v>
+        <v>0.360110507551188</v>
       </c>
       <c r="P4" t="n">
-        <v>8.139689567173994</v>
+        <v>6.846836669354487</v>
       </c>
       <c r="Q4" t="n">
-        <v>8.528544663552374</v>
+        <v>7.206947176905675</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3888550963783793</v>
+        <v>0.360110507551188</v>
       </c>
       <c r="S4" t="n">
-        <v>8.139689567173994</v>
+        <v>6.846836669354487</v>
       </c>
       <c r="T4" t="n">
-        <v>8.528544663552374</v>
+        <v>7.206947176905675</v>
       </c>
     </row>
     <row r="5">
@@ -709,61 +709,61 @@
         <v>0.006</v>
       </c>
       <c r="B5" t="n">
-        <v>0.1471783378239027</v>
+        <v>0.1470625250577804</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.2987823721860844</v>
+        <v>-0.298540014821102</v>
       </c>
       <c r="D5" t="n">
-        <v>-2.544027909217624</v>
+        <v>-2.544512623947589</v>
       </c>
       <c r="E5" t="n">
-        <v>0.04337423803657812</v>
+        <v>0.03701736686276877</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.6425861129785546</v>
+        <v>-0.5628403190829061</v>
       </c>
       <c r="G5" t="n">
-        <v>1.285172225957228</v>
+        <v>1.125680638165873</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.7248442561866273</v>
+        <v>-0.8579864249050759</v>
       </c>
       <c r="I5" t="n">
-        <v>9.465026229083872</v>
+        <v>9.056153136885099</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.7248442561866273</v>
+        <v>-1.132652500617534</v>
       </c>
       <c r="K5" t="n">
-        <v>9.465026229083872</v>
+        <v>9.072025233883238</v>
       </c>
       <c r="L5" t="n">
-        <v>12.68583953756695</v>
+        <v>12.27952617773733</v>
       </c>
       <c r="M5" t="n">
-        <v>42.5284385765754</v>
+        <v>41.40880234501677</v>
       </c>
       <c r="N5" t="n">
-        <v>36.14917279008909</v>
+        <v>35.19748199326425</v>
       </c>
       <c r="O5" t="n">
-        <v>0.451778273782824</v>
+        <v>0.4771042468256589</v>
       </c>
       <c r="P5" t="n">
-        <v>12.23541609821631</v>
+        <v>10.26332123774387</v>
       </c>
       <c r="Q5" t="n">
-        <v>12.68719437199913</v>
+        <v>10.74042548456953</v>
       </c>
       <c r="R5" t="n">
-        <v>0.451778273782824</v>
+        <v>0.4771042468256589</v>
       </c>
       <c r="S5" t="n">
-        <v>12.23541609821631</v>
+        <v>10.26332123774387</v>
       </c>
       <c r="T5" t="n">
-        <v>12.68719437199913</v>
+        <v>10.74042548456953</v>
       </c>
     </row>
     <row r="6">
@@ -771,61 +771,61 @@
         <v>0.008</v>
       </c>
       <c r="B6" t="n">
-        <v>0.1478885449239659</v>
+        <v>0.1476797978872671</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.3002691864806851</v>
+        <v>-0.2998321096263668</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.541054280628423</v>
+        <v>-2.54192843433706</v>
       </c>
       <c r="E6" t="n">
-        <v>0.05845728345758289</v>
+        <v>0.04998400824735147</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.810081781970684</v>
+        <v>-0.7115648948736895</v>
       </c>
       <c r="G6" t="n">
-        <v>1.62016356394144</v>
+        <v>1.42312978974726</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5149638561427047</v>
+        <v>-0.7496664755668619</v>
       </c>
       <c r="I6" t="n">
-        <v>9.978829099048824</v>
+        <v>9.533818588262791</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.5149638561427047</v>
+        <v>-1.096910144265222</v>
       </c>
       <c r="K6" t="n">
-        <v>9.978829099048824</v>
+        <v>9.553884718298228</v>
       </c>
       <c r="L6" t="n">
-        <v>13.84291318537866</v>
+        <v>13.26055863694993</v>
       </c>
       <c r="M6" t="n">
-        <v>46.84454382857908</v>
+        <v>45.20590108600094</v>
       </c>
       <c r="N6" t="n">
-        <v>39.81786225429222</v>
+        <v>38.4250159231008</v>
       </c>
       <c r="O6" t="n">
-        <v>0.3941454138030542</v>
+        <v>0.5216886758916832</v>
       </c>
       <c r="P6" t="n">
-        <v>16.27853381740939</v>
+        <v>13.66015130572234</v>
       </c>
       <c r="Q6" t="n">
-        <v>16.67267923121244</v>
+        <v>14.18183998161402</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3941454138030542</v>
+        <v>0.5216886758916832</v>
       </c>
       <c r="S6" t="n">
-        <v>16.27853381740939</v>
+        <v>13.66015130572234</v>
       </c>
       <c r="T6" t="n">
-        <v>16.67267923121244</v>
+        <v>14.18183998161402</v>
       </c>
     </row>
     <row r="7">
@@ -833,61 +833,61 @@
         <v>0.01</v>
       </c>
       <c r="B7" t="n">
-        <v>0.148692293721834</v>
+        <v>0.1483859213270266</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.3019521991251697</v>
+        <v>-0.3013104413292513</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.537688255339454</v>
+        <v>-2.538971770931291</v>
       </c>
       <c r="E7" t="n">
-        <v>0.07379386082665169</v>
+        <v>0.06324309036618904</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.9634925181930293</v>
+        <v>-0.8483606362864669</v>
       </c>
       <c r="G7" t="n">
-        <v>1.926985036385999</v>
+        <v>1.69672127257252</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.2923426616613936</v>
+        <v>-0.620621332524647</v>
       </c>
       <c r="I7" t="n">
-        <v>10.51985703506515</v>
+        <v>10.04070988441131</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.2923426616613936</v>
+        <v>-1.034621323032443</v>
       </c>
       <c r="K7" t="n">
-        <v>10.51985703506515</v>
+        <v>10.06463365435458</v>
       </c>
       <c r="L7" t="n">
-        <v>15.03340747228062</v>
+        <v>14.2860316611006</v>
       </c>
       <c r="M7" t="n">
-        <v>51.39980205693131</v>
+        <v>49.24831931803015</v>
       </c>
       <c r="N7" t="n">
-        <v>43.6898317483916</v>
+        <v>41.86107142032563</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2792222934593255</v>
+        <v>0.5252923250334167</v>
       </c>
       <c r="P7" t="n">
-        <v>20.28460921783937</v>
+        <v>17.04585771082453</v>
       </c>
       <c r="Q7" t="n">
-        <v>20.56383151129869</v>
+        <v>17.57115003585795</v>
       </c>
       <c r="R7" t="n">
-        <v>0.2851996450986483</v>
+        <v>0.5252923250334167</v>
       </c>
       <c r="S7" t="n">
-        <v>20.28460921783937</v>
+        <v>17.04585771082453</v>
       </c>
       <c r="T7" t="n">
-        <v>20.56383151129869</v>
+        <v>17.57115003585795</v>
       </c>
     </row>
     <row r="8">
@@ -895,61 +895,61 @@
         <v>0.012</v>
       </c>
       <c r="B8" t="n">
-        <v>0.1496941614153883</v>
+        <v>0.1492744130248635</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.3040519367886507</v>
+        <v>-0.303172155489029</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.533488780012492</v>
+        <v>-2.535248342611735</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0899659585064827</v>
+        <v>0.07753433851120492</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.076534503642863</v>
+        <v>-0.9511967314871428</v>
       </c>
       <c r="G8" t="n">
-        <v>2.153069007285723</v>
+        <v>1.90239346297455</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.06247968827440697</v>
+        <v>-0.4804509755794532</v>
       </c>
       <c r="I8" t="n">
-        <v>11.13037699544955</v>
+        <v>10.61563453019374</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.06247968827440697</v>
+        <v>-0.9446349805451788</v>
       </c>
       <c r="K8" t="n">
-        <v>11.13037699544955</v>
+        <v>10.64245827802168</v>
       </c>
       <c r="L8" t="n">
-        <v>16.27722661704827</v>
+        <v>15.36866048189103</v>
       </c>
       <c r="M8" t="n">
-        <v>56.29633294176671</v>
+        <v>53.63262463974404</v>
       </c>
       <c r="N8" t="n">
-        <v>47.8518830005017</v>
+        <v>45.58773094378243</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0510886007735159</v>
+        <v>0.4471336110964794</v>
       </c>
       <c r="P8" t="n">
-        <v>24.05038095179686</v>
+        <v>20.27621608104271</v>
       </c>
       <c r="Q8" t="n">
-        <v>24.10146955257037</v>
+        <v>20.72334969213919</v>
       </c>
       <c r="R8" t="n">
-        <v>0.1578036685484169</v>
+        <v>0.4471336110964794</v>
       </c>
       <c r="S8" t="n">
-        <v>24.05038095179686</v>
+        <v>20.27621608104271</v>
       </c>
       <c r="T8" t="n">
-        <v>24.10146955257037</v>
+        <v>20.72334969213919</v>
       </c>
     </row>
     <row r="9">
@@ -957,61 +957,61 @@
         <v>0.014</v>
       </c>
       <c r="B9" t="n">
-        <v>0.1507557018385417</v>
+        <v>0.1502084332773912</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.3062778980528282</v>
+        <v>-0.3051299667039215</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.529036857484137</v>
+        <v>-2.53133272018195</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1066525679716216</v>
+        <v>0.09227826466974175</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.172972375059671</v>
+        <v>-1.043506684501408</v>
       </c>
       <c r="G9" t="n">
-        <v>2.345944750119397</v>
+        <v>2.087013369003324</v>
       </c>
       <c r="H9" t="n">
-        <v>0.156589748877367</v>
+        <v>-0.3397234960015003</v>
       </c>
       <c r="I9" t="n">
-        <v>11.75073299702965</v>
+        <v>11.20277452564193</v>
       </c>
       <c r="J9" t="n">
-        <v>0.156589748877367</v>
+        <v>-0.8489547580381873</v>
       </c>
       <c r="K9" t="n">
-        <v>11.75073299702965</v>
+        <v>11.23220141414488</v>
       </c>
       <c r="L9" t="n">
-        <v>17.51360062806557</v>
+        <v>16.45979931219317</v>
       </c>
       <c r="M9" t="n">
-        <v>61.20717407950106</v>
+        <v>58.05424721679858</v>
       </c>
       <c r="N9" t="n">
-        <v>52.02609796757589</v>
+        <v>49.34611013427879</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.1912238515531869</v>
+        <v>0.3507350322142301</v>
       </c>
       <c r="P9" t="n">
-        <v>27.61358674886336</v>
+        <v>23.41303483738055</v>
       </c>
       <c r="Q9" t="n">
-        <v>27.42236289731017</v>
+        <v>23.76376986959478</v>
       </c>
       <c r="R9" t="n">
-        <v>0.1912238515531869</v>
+        <v>0.3507350322142301</v>
       </c>
       <c r="S9" t="n">
-        <v>27.61358674886336</v>
+        <v>23.41303483738055</v>
       </c>
       <c r="T9" t="n">
-        <v>27.42236289731017</v>
+        <v>23.76376986959478</v>
       </c>
     </row>
     <row r="10">
@@ -1019,61 +1019,61 @@
         <v>0.016</v>
       </c>
       <c r="B10" t="n">
-        <v>0.1519022490328865</v>
+        <v>0.1512402727017285</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.3086836711140435</v>
+        <v>-0.3072944215322459</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.524225311361707</v>
+        <v>-2.527003810525302</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1240721250646426</v>
+        <v>0.1080843511410948</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.245756860215741</v>
+        <v>-1.112260202893645</v>
       </c>
       <c r="G10" t="n">
-        <v>2.491513720431595</v>
+        <v>2.224520405786797</v>
       </c>
       <c r="H10" t="n">
-        <v>0.3602832568357515</v>
+        <v>-0.1988189179612083</v>
       </c>
       <c r="I10" t="n">
-        <v>12.38510092849745</v>
+        <v>11.81396872283974</v>
       </c>
       <c r="J10" t="n">
-        <v>0.3602832568357515</v>
+        <v>-0.7416018969733071</v>
       </c>
       <c r="K10" t="n">
-        <v>12.38510092849745</v>
+        <v>11.84533446056133</v>
       </c>
       <c r="L10" t="n">
-        <v>18.73936867576502</v>
+        <v>17.56657669889296</v>
       </c>
       <c r="M10" t="n">
-        <v>66.13840088422339</v>
+        <v>62.53398182093753</v>
       </c>
       <c r="N10" t="n">
-        <v>56.21764075158988</v>
+        <v>53.15388454779689</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.4537346521818325</v>
+        <v>0.2161454929426774</v>
       </c>
       <c r="P10" t="n">
-        <v>30.88822729402779</v>
+        <v>26.32372916520886</v>
       </c>
       <c r="Q10" t="n">
-        <v>30.43449264184595</v>
+        <v>26.53987465815154</v>
       </c>
       <c r="R10" t="n">
-        <v>0.4537346521818325</v>
+        <v>0.2161454929426774</v>
       </c>
       <c r="S10" t="n">
-        <v>30.88822729402779</v>
+        <v>26.32372916520886</v>
       </c>
       <c r="T10" t="n">
-        <v>30.43449264184595</v>
+        <v>26.53987465815154</v>
       </c>
     </row>
     <row r="11">
@@ -1081,61 +1081,61 @@
         <v>0.018</v>
       </c>
       <c r="B11" t="n">
-        <v>0.1531142170038921</v>
+        <v>0.1523237427491662</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.3112293179652024</v>
+        <v>-0.3095688711649115</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.519134017659389</v>
+        <v>-2.52245491125997</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1426926329339285</v>
+        <v>0.1249545214687733</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.292031793684386</v>
+        <v>-1.164441182494852</v>
       </c>
       <c r="G11" t="n">
-        <v>2.584063587368795</v>
+        <v>2.328882364989454</v>
       </c>
       <c r="H11" t="n">
-        <v>0.5401188640137533</v>
+        <v>-0.07000746216955059</v>
       </c>
       <c r="I11" t="n">
-        <v>13.01896318169449</v>
+        <v>12.42537302794652</v>
       </c>
       <c r="J11" t="n">
-        <v>0.5401188640137533</v>
+        <v>-0.6382547592270383</v>
       </c>
       <c r="K11" t="n">
-        <v>13.01896318169449</v>
+        <v>12.45821026929288</v>
       </c>
       <c r="L11" t="n">
-        <v>19.934021092179</v>
+        <v>18.65794902576715</v>
       </c>
       <c r="M11" t="n">
-        <v>70.88899755020799</v>
+        <v>66.92409413742709</v>
       </c>
       <c r="N11" t="n">
-        <v>60.25564791767679</v>
+        <v>56.88548001681302</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.7022924755237926</v>
+        <v>0.07832347083319938</v>
       </c>
       <c r="P11" t="n">
-        <v>33.67445799336949</v>
+        <v>28.96963808805511</v>
       </c>
       <c r="Q11" t="n">
-        <v>32.9721655178457</v>
+        <v>29.04796155888831</v>
       </c>
       <c r="R11" t="n">
-        <v>0.7022924755237926</v>
+        <v>0.1304780909803657</v>
       </c>
       <c r="S11" t="n">
-        <v>33.67445799336949</v>
+        <v>28.96963808805511</v>
       </c>
       <c r="T11" t="n">
-        <v>32.9721655178457</v>
+        <v>29.04796155888831</v>
       </c>
     </row>
     <row r="12">
@@ -1143,61 +1143,61 @@
         <v>0.02</v>
       </c>
       <c r="B12" t="n">
-        <v>0.1543505957367888</v>
+        <v>0.1534421432451628</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.3138274390102313</v>
+        <v>-0.311917737250916</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.51393777556933</v>
+        <v>-2.517757179087961</v>
       </c>
       <c r="E12" t="n">
-        <v>0.1618985022180014</v>
+        <v>0.142544592587377</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.32698586418685</v>
+        <v>-1.205410091062012</v>
       </c>
       <c r="G12" t="n">
-        <v>2.653971728373596</v>
+        <v>2.41082018212486</v>
       </c>
       <c r="H12" t="n">
-        <v>0.7063127190822732</v>
+        <v>0.05062245020351591</v>
       </c>
       <c r="I12" t="n">
-        <v>13.64812280617393</v>
+        <v>13.03691948054381</v>
       </c>
       <c r="J12" t="n">
-        <v>0.7063127190822732</v>
+        <v>-0.5376176742347459</v>
       </c>
       <c r="K12" t="n">
-        <v>13.64812280617393</v>
+        <v>13.07091204511177</v>
       </c>
       <c r="L12" t="n">
-        <v>21.1078684850798</v>
+        <v>19.73889913385963</v>
       </c>
       <c r="M12" t="n">
-        <v>75.53230869824215</v>
+        <v>71.2535729282976</v>
       </c>
       <c r="N12" t="n">
-        <v>64.20246239350583</v>
+        <v>60.56553698905296</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.9375083128074833</v>
+        <v>-0.06168547191964846</v>
       </c>
       <c r="P12" t="n">
-        <v>36.22414395801802</v>
+        <v>31.43640772470796</v>
       </c>
       <c r="Q12" t="n">
-        <v>35.28663564521054</v>
+        <v>31.37472225278831</v>
       </c>
       <c r="R12" t="n">
-        <v>0.9375083128074833</v>
+        <v>0.07790872460361446</v>
       </c>
       <c r="S12" t="n">
-        <v>36.22414395801802</v>
+        <v>31.43640772470796</v>
       </c>
       <c r="T12" t="n">
-        <v>35.28663564521054</v>
+        <v>31.37472225278831</v>
       </c>
     </row>
     <row r="13">
@@ -1205,61 +1205,61 @@
         <v>0.022</v>
       </c>
       <c r="B13" t="n">
-        <v>0.1556194785399623</v>
+        <v>0.1546033738544638</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.3164971533226981</v>
+        <v>-0.314359473764</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.508598346944397</v>
+        <v>-2.512873706061793</v>
       </c>
       <c r="E13" t="n">
-        <v>0.18272032566036</v>
+        <v>0.1619867671088955</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.338154422080981</v>
+        <v>-1.226600578546658</v>
       </c>
       <c r="G13" t="n">
-        <v>2.676308844161818</v>
+        <v>2.453201157093115</v>
       </c>
       <c r="H13" t="n">
-        <v>0.8254541014323133</v>
+        <v>0.1479688630632462</v>
       </c>
       <c r="I13" t="n">
-        <v>14.24350785950001</v>
+        <v>13.62595702025168</v>
       </c>
       <c r="J13" t="n">
-        <v>0.8254541014323133</v>
+        <v>-0.4506122192675227</v>
       </c>
       <c r="K13" t="n">
-        <v>14.24350785950001</v>
+        <v>13.66054715656669</v>
       </c>
       <c r="L13" t="n">
-        <v>22.197970655679</v>
+        <v>20.77483203038565</v>
       </c>
       <c r="M13" t="n">
-        <v>79.78965527293184</v>
+        <v>75.28451064525514</v>
       </c>
       <c r="N13" t="n">
-        <v>67.82120698199206</v>
+        <v>63.99183404846686</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.105371330750395</v>
+        <v>-0.1827905771822487</v>
       </c>
       <c r="P13" t="n">
-        <v>38.12788455499134</v>
+        <v>33.44314330273032</v>
       </c>
       <c r="Q13" t="n">
-        <v>37.02251322424095</v>
+        <v>33.26035272554807</v>
       </c>
       <c r="R13" t="n">
-        <v>1.105371330750395</v>
+        <v>0.1827905771822487</v>
       </c>
       <c r="S13" t="n">
-        <v>38.12788455499134</v>
+        <v>33.44314330273032</v>
       </c>
       <c r="T13" t="n">
-        <v>37.02251322424095</v>
+        <v>33.26035272554807</v>
       </c>
     </row>
     <row r="14">
@@ -1267,61 +1267,61 @@
         <v>0.024</v>
       </c>
       <c r="B14" t="n">
-        <v>0.1568888693748589</v>
+        <v>0.1557726187310537</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.3191697638300415</v>
+        <v>-0.3168191161272472</v>
       </c>
       <c r="D14" t="n">
-        <v>-2.503253125929711</v>
+        <v>-2.507954421335299</v>
       </c>
       <c r="E14" t="n">
-        <v>0.2044894031003579</v>
+        <v>0.1821066726952599</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.340543283603165</v>
+        <v>-1.242435846810195</v>
       </c>
       <c r="G14" t="n">
-        <v>2.681086567206411</v>
+        <v>2.484871693619615</v>
       </c>
       <c r="H14" t="n">
-        <v>0.9236670168493588</v>
+        <v>0.2348064866048855</v>
       </c>
       <c r="I14" t="n">
-        <v>14.81414439953601</v>
+        <v>14.20142885177641</v>
       </c>
       <c r="J14" t="n">
-        <v>0.9236670168493588</v>
+        <v>-0.3715022066384895</v>
       </c>
       <c r="K14" t="n">
-        <v>14.81414439953601</v>
+        <v>14.23646554265645</v>
       </c>
       <c r="L14" t="n">
-        <v>23.24385791106501</v>
+        <v>21.78798086059916</v>
       </c>
       <c r="M14" t="n">
-        <v>83.77751265415634</v>
+        <v>79.18272572939492</v>
       </c>
       <c r="N14" t="n">
-        <v>71.21088575603288</v>
+        <v>67.30531686998567</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.237907123705615</v>
+        <v>-0.2918196694477683</v>
       </c>
       <c r="P14" t="n">
-        <v>39.7135241083678</v>
+        <v>35.29031135242914</v>
       </c>
       <c r="Q14" t="n">
-        <v>38.47561698466218</v>
+        <v>34.99849168298137</v>
       </c>
       <c r="R14" t="n">
-        <v>1.237907123705615</v>
+        <v>0.2918196694477683</v>
       </c>
       <c r="S14" t="n">
-        <v>39.7135241083678</v>
+        <v>35.29031135242914</v>
       </c>
       <c r="T14" t="n">
-        <v>38.47561698466218</v>
+        <v>34.99849168298137</v>
       </c>
     </row>
     <row r="15">
@@ -1329,61 +1329,61 @@
         <v>0.026</v>
       </c>
       <c r="B15" t="n">
-        <v>0.1581588290103518</v>
+        <v>0.1569551228287347</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.3218456169643666</v>
+        <v>-0.3193092278922173</v>
       </c>
       <c r="D15" t="n">
-        <v>-2.49790141966106</v>
+        <v>-2.502974197805358</v>
       </c>
       <c r="E15" t="n">
-        <v>0.2273190415530456</v>
+        <v>0.2038777077206989</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.333102253988917</v>
+        <v>-1.246764315526081</v>
       </c>
       <c r="G15" t="n">
-        <v>2.666204507978442</v>
+        <v>2.49352863105295</v>
       </c>
       <c r="H15" t="n">
-        <v>0.9984480796272804</v>
+        <v>0.2944148605579441</v>
       </c>
       <c r="I15" t="n">
-        <v>15.35707210077807</v>
+        <v>14.73949109088955</v>
       </c>
       <c r="J15" t="n">
-        <v>0.9984480796272804</v>
+        <v>-0.3140061254187834</v>
       </c>
       <c r="K15" t="n">
-        <v>15.35707210077807</v>
+        <v>14.7746498445874</v>
       </c>
       <c r="L15" t="n">
-        <v>24.24024142682958</v>
+        <v>22.74045835383424</v>
       </c>
       <c r="M15" t="n">
-        <v>87.4636455426442</v>
+        <v>82.73838474562538</v>
       </c>
       <c r="N15" t="n">
-        <v>74.34409871124757</v>
+        <v>70.32762703378157</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.330889979854188</v>
+        <v>-0.3672079545916056</v>
       </c>
       <c r="P15" t="n">
-        <v>40.94301254939679</v>
+        <v>36.75590682827092</v>
       </c>
       <c r="Q15" t="n">
-        <v>39.61212256954261</v>
+        <v>36.38869887367932</v>
       </c>
       <c r="R15" t="n">
-        <v>1.330889979854188</v>
+        <v>0.3672079545916056</v>
       </c>
       <c r="S15" t="n">
-        <v>40.94301254939679</v>
+        <v>36.75590682827092</v>
       </c>
       <c r="T15" t="n">
-        <v>39.61212256954261</v>
+        <v>36.38869887367932</v>
       </c>
     </row>
     <row r="16">
@@ -1391,61 +1391,61 @@
         <v>0.028</v>
       </c>
       <c r="B16" t="n">
-        <v>0.1594109976242205</v>
+        <v>0.1581366926208119</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.324487154325214</v>
+        <v>-0.3217992879160035</v>
       </c>
       <c r="D16" t="n">
-        <v>-2.492618344939365</v>
+        <v>-2.497994077757786</v>
       </c>
       <c r="E16" t="n">
-        <v>0.2518673538341114</v>
+        <v>0.2268649260098548</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.317100630118101</v>
+        <v>-1.246263081926188</v>
       </c>
       <c r="G16" t="n">
-        <v>2.634201260235901</v>
+        <v>2.492526163852864</v>
       </c>
       <c r="H16" t="n">
-        <v>1.027050766486314</v>
+        <v>0.335610784217529</v>
       </c>
       <c r="I16" t="n">
-        <v>15.83721696622144</v>
+        <v>15.24355272988936</v>
       </c>
       <c r="J16" t="n">
-        <v>1.027050766486314</v>
+        <v>-0.2725655997624507</v>
       </c>
       <c r="K16" t="n">
-        <v>15.83721696622144</v>
+        <v>15.27869734879969</v>
       </c>
       <c r="L16" t="n">
-        <v>25.13223867807963</v>
+        <v>23.64555825980998</v>
       </c>
       <c r="M16" t="n">
-        <v>90.62126905303428</v>
+        <v>86.00608364960686</v>
       </c>
       <c r="N16" t="n">
-        <v>77.02807869507913</v>
+        <v>73.10517110216584</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.352502064284574</v>
+        <v>-0.4181870823382526</v>
       </c>
       <c r="P16" t="n">
-        <v>41.70713652742772</v>
+        <v>37.99234408155354</v>
       </c>
       <c r="Q16" t="n">
-        <v>40.35463446314315</v>
+        <v>37.57415699921529</v>
       </c>
       <c r="R16" t="n">
-        <v>1.352502064284574</v>
+        <v>0.4181870823382526</v>
       </c>
       <c r="S16" t="n">
-        <v>41.70713652742772</v>
+        <v>37.99234408155354</v>
       </c>
       <c r="T16" t="n">
-        <v>40.35463446314315</v>
+        <v>37.57415699921529</v>
       </c>
     </row>
     <row r="17">
@@ -1453,61 +1453,61 @@
         <v>0.03</v>
       </c>
       <c r="B17" t="n">
-        <v>0.1606537098736899</v>
+        <v>0.15931751129134</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.3271100862033756</v>
+        <v>-0.3242893063432091</v>
       </c>
       <c r="D17" t="n">
-        <v>-2.487372481183042</v>
+        <v>-2.493014040903375</v>
       </c>
       <c r="E17" t="n">
-        <v>0.2771475382693666</v>
+        <v>0.250829877337519</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.298751328930882</v>
+        <v>-1.241879078630989</v>
       </c>
       <c r="G17" t="n">
-        <v>2.597502657860759</v>
+        <v>2.483758157260669</v>
       </c>
       <c r="H17" t="n">
-        <v>1.038982131454963</v>
+        <v>0.362004283350398</v>
       </c>
       <c r="I17" t="n">
-        <v>16.29036382002196</v>
+        <v>15.72028007557031</v>
       </c>
       <c r="J17" t="n">
-        <v>1.038982131454963</v>
+        <v>-0.2440327070215247</v>
       </c>
       <c r="K17" t="n">
-        <v>16.29036382002196</v>
+        <v>15.75530106558769</v>
       </c>
       <c r="L17" t="n">
-        <v>25.98339705524361</v>
+        <v>24.51256963609596</v>
       </c>
       <c r="M17" t="n">
-        <v>93.5499993214781</v>
+        <v>89.0422811640215</v>
       </c>
       <c r="N17" t="n">
-        <v>79.51749942325638</v>
+        <v>75.68593898941828</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.349487032452553</v>
+        <v>-0.4495428191524768</v>
       </c>
       <c r="P17" t="n">
-        <v>42.31002122402524</v>
+        <v>39.04455287854479</v>
       </c>
       <c r="Q17" t="n">
-        <v>40.96053419157269</v>
+        <v>38.59501005939232</v>
       </c>
       <c r="R17" t="n">
-        <v>1.349487032452553</v>
+        <v>0.4495428191524768</v>
       </c>
       <c r="S17" t="n">
-        <v>42.31002122402524</v>
+        <v>39.04455287854479</v>
       </c>
       <c r="T17" t="n">
-        <v>40.96053419157269</v>
+        <v>38.59501005939232</v>
       </c>
     </row>
     <row r="18">
@@ -1515,61 +1515,61 @@
         <v>0.032</v>
       </c>
       <c r="B18" t="n">
-        <v>0.1618701943570368</v>
+        <v>0.160488670106283</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.3296807400963517</v>
+        <v>-0.3267619795783088</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.48223117339709</v>
+        <v>-2.488068694433176</v>
       </c>
       <c r="E18" t="n">
-        <v>0.3041226240462886</v>
+        <v>0.2766625931279135</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.277952414095075</v>
+        <v>-1.234834950028424</v>
       </c>
       <c r="G18" t="n">
-        <v>2.555904828190802</v>
+        <v>2.469669900056827</v>
       </c>
       <c r="H18" t="n">
-        <v>1.019195066789688</v>
+        <v>0.3559652860011956</v>
       </c>
       <c r="I18" t="n">
-        <v>16.68038243239525</v>
+        <v>16.13282358146893</v>
       </c>
       <c r="J18" t="n">
-        <v>1.019195066789688</v>
+        <v>-0.2466341696126751</v>
       </c>
       <c r="K18" t="n">
-        <v>16.68038243239525</v>
+        <v>16.16764592705974</v>
       </c>
       <c r="L18" t="n">
-        <v>26.74829459571701</v>
+        <v>25.29215879705997</v>
       </c>
       <c r="M18" t="n">
-        <v>95.93982032578636</v>
+        <v>91.60013206954135</v>
       </c>
       <c r="N18" t="n">
-        <v>81.54884727691839</v>
+        <v>77.86011225911014</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.30271011330182</v>
+        <v>-0.4396145803215375</v>
       </c>
       <c r="P18" t="n">
-        <v>42.62450879078402</v>
+        <v>39.8385242436111</v>
       </c>
       <c r="Q18" t="n">
-        <v>41.3217986774822</v>
+        <v>39.39890966328956</v>
       </c>
       <c r="R18" t="n">
-        <v>1.30271011330182</v>
+        <v>0.4396145803215375</v>
       </c>
       <c r="S18" t="n">
-        <v>42.62450879078402</v>
+        <v>39.8385242436111</v>
       </c>
       <c r="T18" t="n">
-        <v>41.3217986774822</v>
+        <v>39.39890966328956</v>
       </c>
     </row>
     <row r="19">
@@ -1577,61 +1577,61 @@
         <v>0.034</v>
       </c>
       <c r="B19" t="n">
-        <v>0.1630698401506707</v>
+        <v>0.1616560952107498</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.3322177219208012</v>
+        <v>-0.3292278754535332</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.477157209748191</v>
+        <v>-2.483136902682727</v>
       </c>
       <c r="E19" t="n">
-        <v>0.3321337046071152</v>
+        <v>0.3031524608703647</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.258801033443378</v>
+        <v>-1.227732835270322</v>
       </c>
       <c r="G19" t="n">
-        <v>2.51760206688727</v>
+        <v>2.455465670541697</v>
       </c>
       <c r="H19" t="n">
-        <v>0.9759097535626803</v>
+        <v>0.3394332849245827</v>
       </c>
       <c r="I19" t="n">
-        <v>17.02335765481725</v>
+        <v>16.5216834162065</v>
       </c>
       <c r="J19" t="n">
-        <v>0.9759097535626803</v>
+        <v>-0.2597003386873346</v>
       </c>
       <c r="K19" t="n">
-        <v>17.02335765481725</v>
+        <v>16.55630548216114</v>
       </c>
       <c r="L19" t="n">
-        <v>27.44829434757137</v>
+        <v>26.04127047511572</v>
       </c>
       <c r="M19" t="n">
-        <v>97.99617826069957</v>
+        <v>93.98460009874481</v>
       </c>
       <c r="N19" t="n">
-        <v>83.29675152159463</v>
+        <v>79.88691008393309</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.229147707680254</v>
+        <v>-0.4168005585863472</v>
       </c>
       <c r="P19" t="n">
-        <v>42.85171773741408</v>
+        <v>40.567344504327</v>
       </c>
       <c r="Q19" t="n">
-        <v>41.62257002973382</v>
+        <v>40.15054394574065</v>
       </c>
       <c r="R19" t="n">
-        <v>1.229147707680254</v>
+        <v>0.4168005585863472</v>
       </c>
       <c r="S19" t="n">
-        <v>42.85171773741408</v>
+        <v>40.567344504327</v>
       </c>
       <c r="T19" t="n">
-        <v>41.62257002973382</v>
+        <v>40.15054394574065</v>
       </c>
     </row>
     <row r="20">
@@ -1639,61 +1639,61 @@
         <v>0.036</v>
       </c>
       <c r="B20" t="n">
-        <v>0.1642546204762896</v>
+        <v>0.1628137461650647</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.3347249774977686</v>
+        <v>-0.3316759150035779</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.472142698594256</v>
+        <v>-2.478240823582638</v>
       </c>
       <c r="E20" t="n">
-        <v>0.3610593781431871</v>
+        <v>0.3312612306518148</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.241104122654535</v>
+        <v>-1.221997707151859</v>
       </c>
       <c r="G20" t="n">
-        <v>2.482208245307862</v>
+        <v>2.443995414303071</v>
       </c>
       <c r="H20" t="n">
-        <v>0.9118798059040867</v>
+        <v>0.2986303614960819</v>
       </c>
       <c r="I20" t="n">
-        <v>17.32480221062814</v>
+        <v>16.85030427796023</v>
       </c>
       <c r="J20" t="n">
-        <v>0.9118798059040867</v>
+        <v>-0.2977045195940252</v>
       </c>
       <c r="K20" t="n">
-        <v>17.32480221062814</v>
+        <v>16.8847646133019</v>
       </c>
       <c r="L20" t="n">
-        <v>28.09100128048296</v>
+        <v>26.7157838098677</v>
       </c>
       <c r="M20" t="n">
-        <v>99.7581495968473</v>
+        <v>95.93319758515322</v>
       </c>
       <c r="N20" t="n">
-        <v>84.7944271573202</v>
+        <v>81.54321794738024</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.131938640757533</v>
+        <v>-0.3650617837804264</v>
       </c>
       <c r="P20" t="n">
-        <v>43.00187570454212</v>
+        <v>41.17987305026563</v>
       </c>
       <c r="Q20" t="n">
-        <v>41.86993706378459</v>
+        <v>40.8148112664852</v>
       </c>
       <c r="R20" t="n">
-        <v>1.131938640757533</v>
+        <v>0.3650617837804264</v>
       </c>
       <c r="S20" t="n">
-        <v>43.00187570454212</v>
+        <v>41.17987305026563</v>
       </c>
       <c r="T20" t="n">
-        <v>41.86993706378459</v>
+        <v>40.8148112664852</v>
       </c>
     </row>
     <row r="21">
@@ -1701,61 +1701,61 @@
         <v>0.038</v>
       </c>
       <c r="B21" t="n">
-        <v>0.1654186910321664</v>
+        <v>0.1639680698973427</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.3371915038936382</v>
+        <v>-0.3341186898370312</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.467209645802517</v>
+        <v>-2.473355273915731</v>
       </c>
       <c r="E21" t="n">
-        <v>0.3915315992481593</v>
+        <v>0.3602994296153517</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.229972538557567</v>
+        <v>-1.219005458933033</v>
       </c>
       <c r="G21" t="n">
-        <v>2.459945077115199</v>
+        <v>2.438010917865533</v>
       </c>
       <c r="H21" t="n">
-        <v>0.8283863964818367</v>
+        <v>0.2421413012655994</v>
       </c>
       <c r="I21" t="n">
-        <v>17.55365455452864</v>
+        <v>17.13929564886921</v>
       </c>
       <c r="J21" t="n">
-        <v>0.8283863964818367</v>
+        <v>-0.3527333626937205</v>
       </c>
       <c r="K21" t="n">
-        <v>17.55365455452864</v>
+        <v>17.17367160281112</v>
       </c>
       <c r="L21" t="n">
-        <v>28.65583525590652</v>
+        <v>27.34101914194695</v>
       </c>
       <c r="M21" t="n">
-        <v>101.0140788589548</v>
+        <v>97.62269954749092</v>
       </c>
       <c r="N21" t="n">
-        <v>85.8619670301116</v>
+        <v>82.97929461536729</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.019488537095257</v>
+        <v>-0.2951878246550604</v>
       </c>
       <c r="P21" t="n">
-        <v>43.17798721998609</v>
+        <v>41.78567554688167</v>
       </c>
       <c r="Q21" t="n">
-        <v>42.15849868289084</v>
+        <v>41.49048772222661</v>
       </c>
       <c r="R21" t="n">
-        <v>1.019488537095257</v>
+        <v>0.2951878246550604</v>
       </c>
       <c r="S21" t="n">
-        <v>43.17798721998609</v>
+        <v>41.78567554688167</v>
       </c>
       <c r="T21" t="n">
-        <v>42.15849868289084</v>
+        <v>41.49048772222661</v>
       </c>
     </row>
     <row r="22">
@@ -1763,61 +1763,61 @@
         <v>0.04</v>
       </c>
       <c r="B22" t="n">
-        <v>0.1665777199034823</v>
+        <v>0.1651192251917341</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.3396485851218954</v>
+        <v>-0.3365564512005915</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.462295483346003</v>
+        <v>-2.46847975118861</v>
       </c>
       <c r="E22" t="n">
-        <v>0.4225572245851215</v>
+        <v>0.3902227028542811</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.222079277086947</v>
+        <v>-1.21862519287105</v>
       </c>
       <c r="G22" t="n">
-        <v>2.444158554174864</v>
+        <v>2.437250385743409</v>
       </c>
       <c r="H22" t="n">
-        <v>0.7358778328773297</v>
+        <v>0.1707146896527194</v>
       </c>
       <c r="I22" t="n">
-        <v>17.7526244001693</v>
+        <v>17.3905487567996</v>
       </c>
       <c r="J22" t="n">
-        <v>0.7358778328773297</v>
+        <v>-0.423974404468353</v>
       </c>
       <c r="K22" t="n">
-        <v>17.7526244001693</v>
+        <v>17.42491398723858</v>
       </c>
       <c r="L22" t="n">
-        <v>29.18693939508089</v>
+        <v>27.91932815263566</v>
       </c>
       <c r="M22" t="n">
-        <v>102.0847505607601</v>
+        <v>99.0654707339459</v>
       </c>
       <c r="N22" t="n">
-        <v>86.77203797664608</v>
+        <v>84.20565012385401</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.89931050988877</v>
+        <v>-0.2080441418864108</v>
       </c>
       <c r="P22" t="n">
-        <v>43.39020649360677</v>
+        <v>42.38507297967448</v>
       </c>
       <c r="Q22" t="n">
-        <v>42.490895983718</v>
+        <v>42.17702883778806</v>
       </c>
       <c r="R22" t="n">
-        <v>0.89931050988877</v>
+        <v>0.2080441418864108</v>
       </c>
       <c r="S22" t="n">
-        <v>43.39020649360677</v>
+        <v>42.38507297967448</v>
       </c>
       <c r="T22" t="n">
-        <v>42.490895983718</v>
+        <v>42.17702883778806</v>
       </c>
     </row>
     <row r="23">
@@ -1825,61 +1825,61 @@
         <v>0.042</v>
       </c>
       <c r="B23" t="n">
-        <v>0.167729260997043</v>
+        <v>0.1662736198712599</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.3420924510957395</v>
+        <v>-0.3390040010724412</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.457407751398314</v>
+        <v>-2.46358465144491</v>
       </c>
       <c r="E23" t="n">
-        <v>0.4547104677462341</v>
+        <v>0.4214520729936305</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.221829678140065</v>
+        <v>-1.224701362855879</v>
       </c>
       <c r="G23" t="n">
-        <v>2.443659356279561</v>
+        <v>2.449402725711856</v>
       </c>
       <c r="H23" t="n">
-        <v>0.622589177589367</v>
+        <v>0.08227638989779323</v>
       </c>
       <c r="I23" t="n">
-        <v>17.88611248392402</v>
+        <v>17.58104091757924</v>
       </c>
       <c r="J23" t="n">
-        <v>0.622589177589367</v>
+        <v>-0.515377875175876</v>
       </c>
       <c r="K23" t="n">
-        <v>17.88611248392402</v>
+        <v>17.61557749601177</v>
       </c>
       <c r="L23" t="n">
-        <v>29.64242072511166</v>
+        <v>28.43108115727134</v>
       </c>
       <c r="M23" t="n">
-        <v>102.7730271303394</v>
+        <v>100.12987143683</v>
       </c>
       <c r="N23" t="n">
-        <v>87.35707306078851</v>
+        <v>85.11039072130548</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.7607122636322381</v>
+        <v>-0.1002848949250411</v>
       </c>
       <c r="P23" t="n">
-        <v>43.70753235068437</v>
+        <v>43.06490769688701</v>
       </c>
       <c r="Q23" t="n">
-        <v>42.94682008705214</v>
+        <v>42.96462280196197</v>
       </c>
       <c r="R23" t="n">
-        <v>0.7607122636322381</v>
+        <v>0.1002848949250411</v>
       </c>
       <c r="S23" t="n">
-        <v>43.70753235068437</v>
+        <v>43.06490769688701</v>
       </c>
       <c r="T23" t="n">
-        <v>42.94682008705214</v>
+        <v>42.96462280196197</v>
       </c>
     </row>
     <row r="24">
@@ -1887,61 +1887,61 @@
         <v>0.044</v>
       </c>
       <c r="B24" t="n">
-        <v>0.1688838970882142</v>
+        <v>0.1674312584276098</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.3445449773500808</v>
+        <v>-0.3414595744548679</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.452502698889631</v>
+        <v>-2.458673504680057</v>
       </c>
       <c r="E24" t="n">
-        <v>0.4874765622046562</v>
+        <v>0.4531414634116908</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.227133405730392</v>
+        <v>-1.233452305533906</v>
       </c>
       <c r="G24" t="n">
-        <v>2.45426681146043</v>
+        <v>2.466904611066617</v>
       </c>
       <c r="H24" t="n">
-        <v>0.5130053660138342</v>
+        <v>-0.01273239272786142</v>
       </c>
       <c r="I24" t="n">
-        <v>17.96199220053905</v>
+        <v>17.74867905927334</v>
       </c>
       <c r="J24" t="n">
-        <v>0.5130053660138342</v>
+        <v>-0.6146571178284074</v>
       </c>
       <c r="K24" t="n">
-        <v>17.96199220053905</v>
+        <v>17.78346241428938</v>
       </c>
       <c r="L24" t="n">
-        <v>30.0619970754475</v>
+        <v>28.91742005070443</v>
       </c>
       <c r="M24" t="n">
-        <v>103.1989345506662</v>
+        <v>101.0579526134805</v>
       </c>
       <c r="N24" t="n">
-        <v>87.71909436806622</v>
+        <v>85.89925972145841</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.6289148619214217</v>
+        <v>0.01613203911631498</v>
       </c>
       <c r="P24" t="n">
-        <v>44.08393162869658</v>
+        <v>43.78511988809567</v>
       </c>
       <c r="Q24" t="n">
-        <v>43.45501676677516</v>
+        <v>43.80125192721199</v>
       </c>
       <c r="R24" t="n">
-        <v>0.6289148619214217</v>
+        <v>0.02565234500971721</v>
       </c>
       <c r="S24" t="n">
-        <v>44.08393162869658</v>
+        <v>43.78511988809567</v>
       </c>
       <c r="T24" t="n">
-        <v>43.45501676677516</v>
+        <v>43.80125192721199</v>
       </c>
     </row>
     <row r="25">
@@ -1949,61 +1949,61 @@
         <v>0.046</v>
       </c>
       <c r="B25" t="n">
-        <v>0.1700406798974233</v>
+        <v>0.1686034670413478</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.347003510452471</v>
+        <v>-0.3439491594205626</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.447585632684851</v>
+        <v>-2.453694334748667</v>
       </c>
       <c r="E25" t="n">
-        <v>0.520667735806948</v>
+        <v>0.4859309931123427</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.23628897030047</v>
+        <v>-1.249898182326363</v>
       </c>
       <c r="G25" t="n">
-        <v>2.472577940602017</v>
+        <v>2.499796364653278</v>
       </c>
       <c r="H25" t="n">
-        <v>0.4059912671897685</v>
+        <v>-0.1253294749937992</v>
       </c>
       <c r="I25" t="n">
-        <v>17.9979142382017</v>
+        <v>17.85695354137159</v>
       </c>
       <c r="J25" t="n">
-        <v>0.4059912671897685</v>
+        <v>-0.7352797879690642</v>
       </c>
       <c r="K25" t="n">
-        <v>17.9979142382017</v>
+        <v>17.8922006701132</v>
       </c>
       <c r="L25" t="n">
-        <v>30.45666941057381</v>
+        <v>29.3365915036102</v>
       </c>
       <c r="M25" t="n">
-        <v>103.4428603812799</v>
+        <v>101.6501331721379</v>
       </c>
       <c r="N25" t="n">
-        <v>87.9264313240879</v>
+        <v>86.40261319631723</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.5018345868443791</v>
+        <v>0.1577783069906202</v>
       </c>
       <c r="P25" t="n">
-        <v>44.50130476008326</v>
+        <v>44.6409192927287</v>
       </c>
       <c r="Q25" t="n">
-        <v>43.99947017323889</v>
+        <v>44.79869759971932</v>
       </c>
       <c r="R25" t="n">
-        <v>0.5018345868443791</v>
+        <v>0.1610757793632293</v>
       </c>
       <c r="S25" t="n">
-        <v>44.50130476008326</v>
+        <v>44.6409192927287</v>
       </c>
       <c r="T25" t="n">
-        <v>43.99947017323889</v>
+        <v>44.79869759971932</v>
       </c>
     </row>
     <row r="26">
@@ -2011,61 +2011,61 @@
         <v>0.048</v>
       </c>
       <c r="B26" t="n">
-        <v>0.1712166975136866</v>
+        <v>0.1697900945529388</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.3495064176911083</v>
+        <v>-0.3464712019652739</v>
       </c>
       <c r="D26" t="n">
-        <v>-2.442579818207577</v>
+        <v>-2.448650249659245</v>
       </c>
       <c r="E26" t="n">
-        <v>0.5545687139352565</v>
+        <v>0.5191507791003723</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.255110990798546</v>
+        <v>-1.270193467936519</v>
       </c>
       <c r="G26" t="n">
-        <v>2.5102219815968</v>
+        <v>2.54038693587372</v>
       </c>
       <c r="H26" t="n">
-        <v>0.2807505817030562</v>
+        <v>-0.2385900163220737</v>
       </c>
       <c r="I26" t="n">
-        <v>17.99995448914228</v>
+        <v>17.92801530231662</v>
       </c>
       <c r="J26" t="n">
-        <v>0.2807505817030562</v>
+        <v>-0.8584444286750952</v>
       </c>
       <c r="K26" t="n">
-        <v>17.99995448914228</v>
+        <v>17.96383475811244</v>
       </c>
       <c r="L26" t="n">
-        <v>30.67061603137505</v>
+        <v>29.72802051113145</v>
       </c>
       <c r="M26" t="n">
-        <v>103.3373688836383</v>
+        <v>102.0788626409346</v>
       </c>
       <c r="N26" t="n">
-        <v>87.83676355109252</v>
+        <v>86.76703324479438</v>
       </c>
       <c r="O26" t="n">
-        <v>-0.3507466907380273</v>
+        <v>0.304653830544622</v>
       </c>
       <c r="P26" t="n">
-        <v>45.1838817828575</v>
+        <v>45.54491223497331</v>
       </c>
       <c r="Q26" t="n">
-        <v>44.83313509211948</v>
+        <v>45.84956606551793</v>
       </c>
       <c r="R26" t="n">
-        <v>0.3507466907380273</v>
+        <v>0.304653830544622</v>
       </c>
       <c r="S26" t="n">
-        <v>45.1838817828575</v>
+        <v>45.54491223497331</v>
       </c>
       <c r="T26" t="n">
-        <v>44.83313509211948</v>
+        <v>45.84956606551793</v>
       </c>
     </row>
     <row r="27">
@@ -2073,61 +2073,61 @@
         <v>0.05</v>
       </c>
       <c r="B27" t="n">
-        <v>0.1724056622504632</v>
+        <v>0.170992975072246</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.3520382714591017</v>
+        <v>-0.3490298307517063</v>
       </c>
       <c r="D27" t="n">
-        <v>-2.43751611067159</v>
+        <v>-2.44353299208638</v>
       </c>
       <c r="E27" t="n">
-        <v>0.5887555246794424</v>
+        <v>0.552855550753044</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.278964926543203</v>
+        <v>-1.294827814122195</v>
       </c>
       <c r="G27" t="n">
-        <v>2.557929853085533</v>
+        <v>2.589655628243376</v>
       </c>
       <c r="H27" t="n">
-        <v>0.1565072092434274</v>
+        <v>-0.3525984099043412</v>
       </c>
       <c r="I27" t="n">
-        <v>17.99996489560006</v>
+        <v>17.95713081673121</v>
       </c>
       <c r="J27" t="n">
-        <v>0.1565072092434274</v>
+        <v>-0.9844743831959726</v>
       </c>
       <c r="K27" t="n">
-        <v>17.99996489560006</v>
+        <v>17.99364496108944</v>
       </c>
       <c r="L27" t="n">
-        <v>30.80941985620517</v>
+        <v>30.08817818408229</v>
       </c>
       <c r="M27" t="n">
-        <v>103.1386780508771</v>
+        <v>102.3233497458701</v>
       </c>
       <c r="N27" t="n">
-        <v>87.66787634324557</v>
+        <v>86.97484728398958</v>
       </c>
       <c r="O27" t="n">
-        <v>-0.1985227727586877</v>
+        <v>0.4574237805504869</v>
       </c>
       <c r="P27" t="n">
-        <v>46.04264762317771</v>
+        <v>46.50322901990351</v>
       </c>
       <c r="Q27" t="n">
-        <v>45.84412485041902</v>
+        <v>46.960652800454</v>
       </c>
       <c r="R27" t="n">
-        <v>0.2007031192012083</v>
+        <v>0.4574237805504869</v>
       </c>
       <c r="S27" t="n">
-        <v>46.04264762317771</v>
+        <v>46.50322901990351</v>
       </c>
       <c r="T27" t="n">
-        <v>45.84412485041902</v>
+        <v>46.960652800454</v>
       </c>
     </row>
     <row r="28">
@@ -2135,61 +2135,61 @@
         <v>0.052</v>
       </c>
       <c r="B28" t="n">
-        <v>0.1736225928533107</v>
+        <v>0.1722303190978648</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.3546324556909842</v>
+        <v>-0.3516651129960671</v>
       </c>
       <c r="D28" t="n">
-        <v>-2.432327742207825</v>
+        <v>-2.438262427597659</v>
       </c>
       <c r="E28" t="n">
-        <v>0.6235193047617655</v>
+        <v>0.5870832864035619</v>
       </c>
       <c r="F28" t="n">
-        <v>-1.313377208852065</v>
+        <v>-1.326177609486279</v>
       </c>
       <c r="G28" t="n">
-        <v>2.626754417704956</v>
+        <v>2.652355218972449</v>
       </c>
       <c r="H28" t="n">
-        <v>0.03721235271371801</v>
+        <v>-0.4783515173048836</v>
       </c>
       <c r="I28" t="n">
-        <v>17.99996715281744</v>
+        <v>17.96253990248105</v>
       </c>
       <c r="J28" t="n">
-        <v>0.03721235271371801</v>
+        <v>-1.125526190734188</v>
       </c>
       <c r="K28" t="n">
-        <v>17.99996715281744</v>
+        <v>17.99993811106856</v>
       </c>
       <c r="L28" t="n">
-        <v>30.7957106439681</v>
+        <v>30.33225372958709</v>
       </c>
       <c r="M28" t="n">
-        <v>102.7685862725551</v>
+        <v>102.3400800378955</v>
       </c>
       <c r="N28" t="n">
-        <v>87.35329833167182</v>
+        <v>86.98906803221118</v>
       </c>
       <c r="O28" t="n">
-        <v>-0.04700964469086436</v>
+        <v>0.6373844766935622</v>
       </c>
       <c r="P28" t="n">
-        <v>47.28149330775402</v>
+        <v>47.64299375337482</v>
       </c>
       <c r="Q28" t="n">
-        <v>47.23448366306315</v>
+        <v>48.28037823006838</v>
       </c>
       <c r="R28" t="n">
-        <v>0.05653916964110089</v>
+        <v>0.6373844766935622</v>
       </c>
       <c r="S28" t="n">
-        <v>47.28149330775402</v>
+        <v>47.64299375337482</v>
       </c>
       <c r="T28" t="n">
-        <v>47.23448366306315</v>
+        <v>48.28037823006838</v>
       </c>
     </row>
     <row r="29">
@@ -2197,61 +2197,61 @@
         <v>0.054</v>
       </c>
       <c r="B29" t="n">
-        <v>0.1748821540785204</v>
+        <v>0.1734833388776607</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.3573204172666173</v>
+        <v>-0.3543351656981921</v>
       </c>
       <c r="D29" t="n">
-        <v>-2.426951819056558</v>
+        <v>-2.432922322193409</v>
       </c>
       <c r="E29" t="n">
-        <v>0.6588888258356288</v>
+        <v>0.6215269591507254</v>
       </c>
       <c r="F29" t="n">
-        <v>-1.360010065632229</v>
+        <v>-1.360635032102857</v>
       </c>
       <c r="G29" t="n">
-        <v>2.720020131264804</v>
+        <v>2.721270064206858</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.08738263031384835</v>
+        <v>-0.60760191116186</v>
       </c>
       <c r="I29" t="n">
-        <v>17.99996628351695</v>
+        <v>17.96158529998867</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.08738263031384835</v>
+        <v>-1.271591806828054</v>
       </c>
       <c r="K29" t="n">
-        <v>17.99996628351695</v>
+        <v>17.99995520789398</v>
       </c>
       <c r="L29" t="n">
-        <v>30.70003546075815</v>
+        <v>30.52541763986686</v>
       </c>
       <c r="M29" t="n">
-        <v>102.3356849258754</v>
+        <v>102.2756254547529</v>
       </c>
       <c r="N29" t="n">
-        <v>86.98533218699404</v>
+        <v>86.93428163653998</v>
       </c>
       <c r="O29" t="n">
-        <v>0.1232359099800571</v>
+        <v>0.8277467809400223</v>
       </c>
       <c r="P29" t="n">
-        <v>48.9602704771003</v>
+        <v>48.8783046835624</v>
       </c>
       <c r="Q29" t="n">
-        <v>49.08350638708036</v>
+        <v>49.70605146450242</v>
       </c>
       <c r="R29" t="n">
-        <v>0.1232359099800571</v>
+        <v>0.8277467809400223</v>
       </c>
       <c r="S29" t="n">
-        <v>48.9602704771003</v>
+        <v>48.8783046835624</v>
       </c>
       <c r="T29" t="n">
-        <v>49.08350638708036</v>
+        <v>49.70605146450242</v>
       </c>
     </row>
     <row r="30">
@@ -2259,61 +2259,61 @@
         <v>0.056</v>
       </c>
       <c r="B30" t="n">
-        <v>0.176164966410073</v>
+        <v>0.1747895082798712</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.3600595231175447</v>
+        <v>-0.3571226507692072</v>
       </c>
       <c r="D30" t="n">
-        <v>-2.421473607354704</v>
+        <v>-2.427347352051379</v>
       </c>
       <c r="E30" t="n">
-        <v>0.6945875713515964</v>
+        <v>0.6565972762312424</v>
       </c>
       <c r="F30" t="n">
-        <v>-1.413286063371219</v>
+        <v>-1.405884477141734</v>
       </c>
       <c r="G30" t="n">
-        <v>2.826572126741141</v>
+        <v>2.811768954283021</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.2148036143880325</v>
+        <v>-0.7398362442402246</v>
       </c>
       <c r="I30" t="n">
-        <v>17.99996372375397</v>
+        <v>17.96031131282974</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.2148036143880325</v>
+        <v>-1.425907869085391</v>
       </c>
       <c r="K30" t="n">
-        <v>17.99996372375397</v>
+        <v>17.99995725508513</v>
       </c>
       <c r="L30" t="n">
-        <v>30.56021754113331</v>
+        <v>30.55504607312645</v>
       </c>
       <c r="M30" t="n">
-        <v>101.8690446933705</v>
+        <v>102.0437067569055</v>
       </c>
       <c r="N30" t="n">
-        <v>86.58868798936491</v>
+        <v>86.73715074336963</v>
       </c>
       <c r="O30" t="n">
-        <v>0.303619566756143</v>
+        <v>1.043918993562879</v>
       </c>
       <c r="P30" t="n">
-        <v>50.87819574084698</v>
+        <v>50.50017263996438</v>
       </c>
       <c r="Q30" t="n">
-        <v>51.18181530760312</v>
+        <v>51.54409163352725</v>
       </c>
       <c r="R30" t="n">
-        <v>0.303619566756143</v>
+        <v>1.043918993562879</v>
       </c>
       <c r="S30" t="n">
-        <v>50.87819574084698</v>
+        <v>50.50017263996438</v>
       </c>
       <c r="T30" t="n">
-        <v>51.18181530760312</v>
+        <v>51.54409163352725</v>
       </c>
     </row>
     <row r="31">
@@ -2321,61 +2321,61 @@
         <v>0.058</v>
       </c>
       <c r="B31" t="n">
-        <v>0.1775422562455385</v>
+        <v>0.1761301153087713</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.3630055330156614</v>
+        <v>-0.3599859269744105</v>
       </c>
       <c r="D31" t="n">
-        <v>-2.41558158755847</v>
+        <v>-2.421620799640972</v>
       </c>
       <c r="E31" t="n">
-        <v>0.7312330871705142</v>
+        <v>0.6919991194632432</v>
       </c>
       <c r="F31" t="n">
-        <v>-1.486065934113986</v>
+        <v>-1.457497002148071</v>
       </c>
       <c r="G31" t="n">
-        <v>2.972131868228179</v>
+        <v>2.914994004295527</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.3317350456004391</v>
+        <v>-0.8741735180197523</v>
       </c>
       <c r="I31" t="n">
-        <v>17.99995930747975</v>
+        <v>17.95885622703466</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.3317350456004391</v>
+        <v>-1.585432055068011</v>
       </c>
       <c r="K31" t="n">
-        <v>17.99995930747975</v>
+        <v>17.99995764249523</v>
       </c>
       <c r="L31" t="n">
-        <v>30.43186298577388</v>
+        <v>30.53307247852565</v>
       </c>
       <c r="M31" t="n">
-        <v>101.4411342260141</v>
+        <v>101.7806459346925</v>
       </c>
       <c r="N31" t="n">
-        <v>86.22496409211196</v>
+        <v>86.51354904448863</v>
       </c>
       <c r="O31" t="n">
-        <v>0.4984765376964994</v>
+        <v>1.278525744221311</v>
       </c>
       <c r="P31" t="n">
-        <v>53.49825226939513</v>
+        <v>52.34984882398223</v>
       </c>
       <c r="Q31" t="n">
-        <v>53.99672880709163</v>
+        <v>53.62837456820354</v>
       </c>
       <c r="R31" t="n">
-        <v>0.4984765376964994</v>
+        <v>1.278525744221311</v>
       </c>
       <c r="S31" t="n">
-        <v>53.49825226939513</v>
+        <v>52.34984882398223</v>
       </c>
       <c r="T31" t="n">
-        <v>53.99672880709163</v>
+        <v>53.62837456820354</v>
       </c>
     </row>
     <row r="32">
@@ -2383,61 +2383,61 @@
         <v>0.06</v>
       </c>
       <c r="B32" t="n">
-        <v>0.1789632407445543</v>
+        <v>0.1775167502233924</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.3660472221889143</v>
+        <v>-0.3629505024269315</v>
       </c>
       <c r="D32" t="n">
-        <v>-2.409498209211964</v>
+        <v>-2.41569164873593</v>
       </c>
       <c r="E32" t="n">
-        <v>0.7681922016712944</v>
+        <v>0.7278440666277967</v>
       </c>
       <c r="F32" t="n">
-        <v>-1.565121405659333</v>
+        <v>-1.517614152639035</v>
       </c>
       <c r="G32" t="n">
-        <v>3.130242811319377</v>
+        <v>3.035228305279187</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.449378276277326</v>
+        <v>-1.011321494033297</v>
       </c>
       <c r="I32" t="n">
-        <v>17.99995094878328</v>
+        <v>17.95715909240724</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.449378276277326</v>
+        <v>-1.751917200521146</v>
       </c>
       <c r="K32" t="n">
-        <v>17.99995094878328</v>
+        <v>17.99995581151168</v>
       </c>
       <c r="L32" t="n">
-        <v>30.31895268651041</v>
+        <v>30.44212978037058</v>
       </c>
       <c r="M32" t="n">
-        <v>101.0649468828232</v>
+        <v>101.4759618567797</v>
       </c>
       <c r="N32" t="n">
-        <v>85.90520485039968</v>
+        <v>86.25456757826275</v>
       </c>
       <c r="O32" t="n">
-        <v>0.708272948610582</v>
+        <v>1.537771324310838</v>
       </c>
       <c r="P32" t="n">
-        <v>56.34421577435644</v>
+        <v>54.50400391885729</v>
       </c>
       <c r="Q32" t="n">
-        <v>57.05248872296701</v>
+        <v>56.04177524316813</v>
       </c>
       <c r="R32" t="n">
-        <v>0.708272948610582</v>
+        <v>1.537771324310838</v>
       </c>
       <c r="S32" t="n">
-        <v>56.34421577435644</v>
+        <v>54.50400391885729</v>
       </c>
       <c r="T32" t="n">
-        <v>57.05248872296701</v>
+        <v>56.04177524316813</v>
       </c>
     </row>
     <row r="33">
@@ -2445,61 +2445,61 @@
         <v>0.062</v>
       </c>
       <c r="B33" t="n">
-        <v>0.1804632633240781</v>
+        <v>0.1789808070524687</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.3692619829832007</v>
+        <v>-0.3660852983991668</v>
       </c>
       <c r="D33" t="n">
-        <v>-2.403068687623392</v>
+        <v>-2.40942205679146</v>
       </c>
       <c r="E33" t="n">
-        <v>0.8057185762411611</v>
+        <v>0.7642696790853035</v>
       </c>
       <c r="F33" t="n">
-        <v>-1.655528639666447</v>
+        <v>-1.589162581041375</v>
       </c>
       <c r="G33" t="n">
-        <v>3.311057279332302</v>
+        <v>3.178325162082944</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.5683090615159814</v>
+        <v>-1.15235679782443</v>
       </c>
       <c r="I33" t="n">
-        <v>17.99993545874716</v>
+        <v>17.95513699964857</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.5683090615159814</v>
+        <v>-1.927868137372621</v>
       </c>
       <c r="K33" t="n">
-        <v>17.99993545874716</v>
+        <v>17.99995138443394</v>
       </c>
       <c r="L33" t="n">
-        <v>30.23397907922516</v>
+        <v>30.3581218242867</v>
       </c>
       <c r="M33" t="n">
-        <v>100.7823200827225</v>
+        <v>101.1955630177573</v>
       </c>
       <c r="N33" t="n">
-        <v>85.66497207031414</v>
+        <v>86.01622856509373</v>
       </c>
       <c r="O33" t="n">
-        <v>0.9450929034415854</v>
+        <v>1.838770462951836</v>
       </c>
       <c r="P33" t="n">
-        <v>59.59881622347199</v>
+        <v>57.06703941245202</v>
       </c>
       <c r="Q33" t="n">
-        <v>60.54390912691358</v>
+        <v>58.90580987540385</v>
       </c>
       <c r="R33" t="n">
-        <v>0.9450929034415854</v>
+        <v>1.838770462951836</v>
       </c>
       <c r="S33" t="n">
-        <v>59.59881622347199</v>
+        <v>57.06703941245202</v>
       </c>
       <c r="T33" t="n">
-        <v>60.54390912691358</v>
+        <v>58.90580987540385</v>
       </c>
     </row>
     <row r="34">
@@ -2507,61 +2507,61 @@
         <v>0.064</v>
       </c>
       <c r="B34" t="n">
-        <v>0.1820666162953124</v>
+        <v>0.1804794107539863</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.3727035987175684</v>
+        <v>-0.3692960771954614</v>
       </c>
       <c r="D34" t="n">
-        <v>-2.396185456154656</v>
+        <v>-2.40300049919887</v>
       </c>
       <c r="E34" t="n">
-        <v>0.8437609880642465</v>
+        <v>0.8009397978801563</v>
       </c>
       <c r="F34" t="n">
-        <v>-1.755463152768203</v>
+        <v>-1.665493331743682</v>
       </c>
       <c r="G34" t="n">
-        <v>3.51092630553614</v>
+        <v>3.330986663485973</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.6678571864458062</v>
+        <v>-1.29500906637296</v>
       </c>
       <c r="I34" t="n">
-        <v>17.99991743039732</v>
+        <v>17.95297869059135</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.6678571864458062</v>
+        <v>-2.107769812263877</v>
       </c>
       <c r="K34" t="n">
-        <v>17.99991743039732</v>
+        <v>17.99994560254651</v>
       </c>
       <c r="L34" t="n">
-        <v>30.19362528216136</v>
+        <v>30.27875322830055</v>
       </c>
       <c r="M34" t="n">
-        <v>100.6479697527613</v>
+        <v>100.931046851151</v>
       </c>
       <c r="N34" t="n">
-        <v>85.55077428984713</v>
+        <v>85.79138982347835</v>
       </c>
       <c r="O34" t="n">
-        <v>1.178723899331071</v>
+        <v>2.158236477955629</v>
       </c>
       <c r="P34" t="n">
-        <v>63.19638097019192</v>
+        <v>59.80108415437118</v>
       </c>
       <c r="Q34" t="n">
-        <v>64.375104869523</v>
+        <v>61.95932063232681</v>
       </c>
       <c r="R34" t="n">
-        <v>1.178723899331071</v>
+        <v>2.158236477955629</v>
       </c>
       <c r="S34" t="n">
-        <v>63.19638097019192</v>
+        <v>59.80108415437118</v>
       </c>
       <c r="T34" t="n">
-        <v>64.375104869523</v>
+        <v>61.95932063232681</v>
       </c>
     </row>
     <row r="35">
@@ -2569,61 +2569,61 @@
         <v>0.066</v>
       </c>
       <c r="B35" t="n">
-        <v>0.1837223848321474</v>
+        <v>0.1820952842608633</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.3762603952736687</v>
+        <v>-0.3727650756948901</v>
       </c>
       <c r="D35" t="n">
-        <v>-2.389071863042456</v>
+        <v>-2.396062502200013</v>
       </c>
       <c r="E35" t="n">
-        <v>0.8820486148978314</v>
+        <v>0.8382847712793073</v>
       </c>
       <c r="F35" t="n">
-        <v>-1.859816004958798</v>
+        <v>-1.754672725494091</v>
       </c>
       <c r="G35" t="n">
-        <v>3.719632009918213</v>
+        <v>3.509345450988576</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.7591567809239465</v>
+        <v>-1.441900033060433</v>
       </c>
       <c r="I35" t="n">
-        <v>17.9998957365087</v>
+        <v>17.95045136358845</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.7591567809239465</v>
+        <v>-2.298180323101549</v>
       </c>
       <c r="K35" t="n">
-        <v>17.9998957365087</v>
+        <v>17.99993313444739</v>
       </c>
       <c r="L35" t="n">
-        <v>30.17582038564337</v>
+        <v>30.23155325699364</v>
       </c>
       <c r="M35" t="n">
-        <v>100.5887073181772</v>
+        <v>100.774076876822</v>
       </c>
       <c r="N35" t="n">
-        <v>85.5004012204506</v>
+        <v>85.65796534529868</v>
       </c>
       <c r="O35" t="n">
-        <v>1.41285120299756</v>
+        <v>2.538643218755034</v>
       </c>
       <c r="P35" t="n">
-        <v>66.95298700335255</v>
+        <v>62.99403957106987</v>
       </c>
       <c r="Q35" t="n">
-        <v>68.36583820635011</v>
+        <v>65.5326827898249</v>
       </c>
       <c r="R35" t="n">
-        <v>1.41285120299756</v>
+        <v>2.538643218755034</v>
       </c>
       <c r="S35" t="n">
-        <v>66.95298700335255</v>
+        <v>62.99403957106987</v>
       </c>
       <c r="T35" t="n">
-        <v>68.36583820635011</v>
+        <v>65.5326827898249</v>
       </c>
     </row>
     <row r="36">
@@ -2631,61 +2631,61 @@
         <v>0.068</v>
       </c>
       <c r="B36" t="n">
-        <v>0.1855292918172551</v>
+        <v>0.1837665744759077</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.3801506027499856</v>
+        <v>-0.3763565471099967</v>
       </c>
       <c r="D36" t="n">
-        <v>-2.381291448089822</v>
+        <v>-2.3888795593698</v>
       </c>
       <c r="E36" t="n">
-        <v>0.92084165753487</v>
+        <v>0.8758632900680468</v>
       </c>
       <c r="F36" t="n">
-        <v>-1.971858991997608</v>
+        <v>-1.847900692200934</v>
       </c>
       <c r="G36" t="n">
-        <v>3.943717983995006</v>
+        <v>3.695801384402716</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.8459656329216528</v>
+        <v>-1.585095242974032</v>
       </c>
       <c r="I36" t="n">
-        <v>17.99983450085395</v>
+        <v>17.94780991145114</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.8459656329216528</v>
+        <v>-2.486870780768088</v>
       </c>
       <c r="K36" t="n">
-        <v>17.99983450085395</v>
+        <v>17.99992071097122</v>
       </c>
       <c r="L36" t="n">
-        <v>30.22199850863259</v>
+        <v>30.20338750805328</v>
       </c>
       <c r="M36" t="n">
-        <v>100.7444096343145</v>
+        <v>100.6804547094128</v>
       </c>
       <c r="N36" t="n">
-        <v>85.6327481891673</v>
+        <v>85.57838650300089</v>
       </c>
       <c r="O36" t="n">
-        <v>1.67416534909738</v>
+        <v>2.935936625860736</v>
       </c>
       <c r="P36" t="n">
-        <v>70.98626250804651</v>
+        <v>66.33125954378858</v>
       </c>
       <c r="Q36" t="n">
-        <v>72.66042785714389</v>
+        <v>69.26719616964931</v>
       </c>
       <c r="R36" t="n">
-        <v>1.67416534909738</v>
+        <v>2.935936625860736</v>
       </c>
       <c r="S36" t="n">
-        <v>70.98626250804651</v>
+        <v>66.33125954378858</v>
       </c>
       <c r="T36" t="n">
-        <v>72.66042785714389</v>
+        <v>69.26719616964931</v>
       </c>
     </row>
     <row r="37">
@@ -2693,61 +2693,61 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B37" t="n">
-        <v>0.1874061443002209</v>
+        <v>0.1855260671298466</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.3841961804153858</v>
+        <v>-0.3801429490833866</v>
       </c>
       <c r="D37" t="n">
-        <v>-2.373200292759022</v>
+        <v>-2.38130675542302</v>
       </c>
       <c r="E37" t="n">
-        <v>0.9597842256116929</v>
+        <v>0.9138135247820994</v>
       </c>
       <c r="F37" t="n">
-        <v>-2.085169437104732</v>
+        <v>-1.947572455744663</v>
       </c>
       <c r="G37" t="n">
-        <v>4.170338874209136</v>
+        <v>3.895144911488511</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.9222640452744805</v>
+        <v>-1.722408205966147</v>
       </c>
       <c r="I37" t="n">
-        <v>17.9998100780056</v>
+        <v>17.94498681526591</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.9222640452744805</v>
+        <v>-2.672823564369542</v>
       </c>
       <c r="K37" t="n">
-        <v>17.9998100780056</v>
+        <v>17.9999083585179</v>
       </c>
       <c r="L37" t="n">
-        <v>30.29500689609452</v>
+        <v>30.20551704172188</v>
       </c>
       <c r="M37" t="n">
-        <v>100.9882542629391</v>
+        <v>100.6876582902973</v>
       </c>
       <c r="N37" t="n">
-        <v>85.84001612349826</v>
+        <v>85.58450954675267</v>
       </c>
       <c r="O37" t="n">
-        <v>1.926697724698083</v>
+        <v>3.360107218607154</v>
       </c>
       <c r="P37" t="n">
-        <v>75.06531092235194</v>
+        <v>69.89809412386646</v>
       </c>
       <c r="Q37" t="n">
-        <v>76.99200864705003</v>
+        <v>73.25820134247363</v>
       </c>
       <c r="R37" t="n">
-        <v>1.926697724698083</v>
+        <v>3.360107218607154</v>
       </c>
       <c r="S37" t="n">
-        <v>75.06531092235194</v>
+        <v>69.89809412386646</v>
       </c>
       <c r="T37" t="n">
-        <v>76.99200864705003</v>
+        <v>73.25820134247363</v>
       </c>
     </row>
     <row r="38">
@@ -2755,61 +2755,61 @@
         <v>0.07200000000000001</v>
       </c>
       <c r="B38" t="n">
-        <v>0.1893814524228548</v>
+        <v>0.187395295929479</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.388460457951685</v>
+        <v>-0.3841732686773262</v>
       </c>
       <c r="D38" t="n">
-        <v>-2.364671737686423</v>
+        <v>-2.373246116235141</v>
       </c>
       <c r="E38" t="n">
-        <v>0.9989372664604798</v>
+        <v>0.9520909844335156</v>
       </c>
       <c r="F38" t="n">
-        <v>-2.200263962655766</v>
+        <v>-2.051804769287028</v>
       </c>
       <c r="G38" t="n">
-        <v>4.400527925312089</v>
+        <v>4.103609538573943</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.9837679091557471</v>
+        <v>-1.857192339426585</v>
       </c>
       <c r="I38" t="n">
-        <v>17.99983747305138</v>
+        <v>17.94203616338844</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.9837679091557471</v>
+        <v>-2.858473066838654</v>
       </c>
       <c r="K38" t="n">
-        <v>17.99983747305138</v>
+        <v>17.99989705788233</v>
       </c>
       <c r="L38" t="n">
-        <v>30.40578170072432</v>
+        <v>30.24544291216908</v>
       </c>
       <c r="M38" t="n">
-        <v>101.3561684603496</v>
+        <v>100.8210728681583</v>
       </c>
       <c r="N38" t="n">
-        <v>86.15274319129718</v>
+        <v>85.69791193793459</v>
       </c>
       <c r="O38" t="n">
-        <v>2.16686883533699</v>
+        <v>3.820360120556794</v>
       </c>
       <c r="P38" t="n">
-        <v>79.20878951777368</v>
+        <v>73.62667207091661</v>
       </c>
       <c r="Q38" t="n">
-        <v>81.37565835311068</v>
+        <v>77.44703219147341</v>
       </c>
       <c r="R38" t="n">
-        <v>2.16686883533699</v>
+        <v>3.820360120556794</v>
       </c>
       <c r="S38" t="n">
-        <v>79.20878951777368</v>
+        <v>73.62667207091661</v>
       </c>
       <c r="T38" t="n">
-        <v>81.37565835311068</v>
+        <v>77.44703219147341</v>
       </c>
     </row>
     <row r="39">
@@ -2817,61 +2817,61 @@
         <v>0.074</v>
       </c>
       <c r="B39" t="n">
-        <v>0.1914860670471376</v>
+        <v>0.1893143494520337</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.3930146062189734</v>
+        <v>-0.388314405985534</v>
       </c>
       <c r="D39" t="n">
-        <v>-2.355563441151846</v>
+        <v>-2.364963841618725</v>
       </c>
       <c r="E39" t="n">
-        <v>1.03826240509162</v>
+        <v>0.9905134513933541</v>
       </c>
       <c r="F39" t="n">
-        <v>-2.31447804036051</v>
+        <v>-2.158007086954329</v>
       </c>
       <c r="G39" t="n">
-        <v>4.628956080721174</v>
+        <v>4.316014173910144</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.048456450323583</v>
+        <v>-1.990645703839577</v>
       </c>
       <c r="I39" t="n">
-        <v>17.99986351919399</v>
+        <v>17.93903100903768</v>
       </c>
       <c r="J39" t="n">
-        <v>-1.048456450323583</v>
+        <v>-3.04375316227329</v>
       </c>
       <c r="K39" t="n">
-        <v>17.99986351919399</v>
+        <v>17.99988680888982</v>
       </c>
       <c r="L39" t="n">
-        <v>30.55518985538351</v>
+        <v>30.30239068286672</v>
       </c>
       <c r="M39" t="n">
-        <v>101.8542292676741</v>
+        <v>101.0112994778846</v>
       </c>
       <c r="N39" t="n">
-        <v>86.57609487752296</v>
+        <v>85.85960455620189</v>
       </c>
       <c r="O39" t="n">
-        <v>2.431679059300735</v>
+        <v>4.296366936308985</v>
       </c>
       <c r="P39" t="n">
-        <v>83.32058163372149</v>
+        <v>77.42508523555536</v>
       </c>
       <c r="Q39" t="n">
-        <v>85.75226069302222</v>
+        <v>81.72145217186433</v>
       </c>
       <c r="R39" t="n">
-        <v>2.431679059300735</v>
+        <v>4.296366936308985</v>
       </c>
       <c r="S39" t="n">
-        <v>83.32058163372149</v>
+        <v>77.42508523555536</v>
       </c>
       <c r="T39" t="n">
-        <v>85.75226069302222</v>
+        <v>81.72145217186433</v>
       </c>
     </row>
     <row r="40">
@@ -2879,61 +2879,61 @@
         <v>0.076</v>
       </c>
       <c r="B40" t="n">
-        <v>0.1936494178740843</v>
+        <v>0.1913906534106625</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.3977009418991275</v>
+        <v>-0.3928078310406494</v>
       </c>
       <c r="D40" t="n">
-        <v>-2.346190769791538</v>
+        <v>-2.355976991508494</v>
       </c>
       <c r="E40" t="n">
-        <v>1.077657472326255</v>
+        <v>1.029262501985379</v>
       </c>
       <c r="F40" t="n">
-        <v>-2.42795316486685</v>
+        <v>-2.266726874358669</v>
       </c>
       <c r="G40" t="n">
-        <v>4.855906329733234</v>
+        <v>4.533453748716777</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.112504671537382</v>
+        <v>-2.11318889287136</v>
       </c>
       <c r="I40" t="n">
-        <v>17.99989037619999</v>
+        <v>17.93597927987424</v>
       </c>
       <c r="J40" t="n">
-        <v>-1.112504671537382</v>
+        <v>-3.21935160755839</v>
       </c>
       <c r="K40" t="n">
-        <v>17.99989037619999</v>
+        <v>17.99990097773115</v>
       </c>
       <c r="L40" t="n">
-        <v>30.72044530238431</v>
+        <v>30.40794516409451</v>
       </c>
       <c r="M40" t="n">
-        <v>102.4053054964298</v>
+        <v>101.3627117097551</v>
       </c>
       <c r="N40" t="n">
-        <v>87.04450967196536</v>
+        <v>86.15830495329187</v>
       </c>
       <c r="O40" t="n">
-        <v>2.702180427272738</v>
+        <v>4.798979079361134</v>
       </c>
       <c r="P40" t="n">
-        <v>87.40578306748684</v>
+        <v>81.31148638436933</v>
       </c>
       <c r="Q40" t="n">
-        <v>90.10796349475957</v>
+        <v>86.11046546373046</v>
       </c>
       <c r="R40" t="n">
-        <v>2.702180427272738</v>
+        <v>4.798979079361134</v>
       </c>
       <c r="S40" t="n">
-        <v>87.40578306748684</v>
+        <v>81.31148638436933</v>
       </c>
       <c r="T40" t="n">
-        <v>90.10796349475957</v>
+        <v>86.11046546373046</v>
       </c>
     </row>
     <row r="41">
@@ -2941,61 +2941,61 @@
         <v>0.078</v>
       </c>
       <c r="B41" t="n">
-        <v>0.1959556598872416</v>
+        <v>0.1935223388659998</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.4027113334330478</v>
+        <v>-0.3974265865529459</v>
       </c>
       <c r="D41" t="n">
-        <v>-2.336169986723698</v>
+        <v>-2.346739480483901</v>
       </c>
       <c r="E41" t="n">
-        <v>1.117183143181343</v>
+        <v>1.068095007337892</v>
       </c>
       <c r="F41" t="n">
-        <v>-2.538005793321477</v>
+        <v>-2.375274584369042</v>
       </c>
       <c r="G41" t="n">
-        <v>5.076011586643117</v>
+        <v>4.750549168736943</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.164993216860414</v>
+        <v>-2.235877077799618</v>
       </c>
       <c r="I41" t="n">
-        <v>17.99992602861812</v>
+        <v>17.93293263106323</v>
       </c>
       <c r="J41" t="n">
-        <v>-1.164993216860414</v>
+        <v>-3.39501107497171</v>
       </c>
       <c r="K41" t="n">
-        <v>17.99992602861812</v>
+        <v>17.99991537434242</v>
       </c>
       <c r="L41" t="n">
-        <v>30.91609860723858</v>
+        <v>30.52710342823348</v>
       </c>
       <c r="M41" t="n">
-        <v>103.0561089443205</v>
+        <v>101.7595483696636</v>
       </c>
       <c r="N41" t="n">
-        <v>87.59769260267245</v>
+        <v>86.49561611421407</v>
       </c>
       <c r="O41" t="n">
-        <v>2.960162923921343</v>
+        <v>5.316937529640884</v>
       </c>
       <c r="P41" t="n">
-        <v>91.3678377034351</v>
+        <v>85.1909761246656</v>
       </c>
       <c r="Q41" t="n">
-        <v>94.32800062735645</v>
+        <v>90.50791365430648</v>
       </c>
       <c r="R41" t="n">
-        <v>2.960162923921343</v>
+        <v>5.316937529640884</v>
       </c>
       <c r="S41" t="n">
-        <v>91.3678377034351</v>
+        <v>85.1909761246656</v>
       </c>
       <c r="T41" t="n">
-        <v>94.32800062735645</v>
+        <v>90.50791365430648</v>
       </c>
     </row>
     <row r="42">
@@ -3003,61 +3003,61 @@
         <v>0.08</v>
       </c>
       <c r="B42" t="n">
-        <v>0.1983350109966719</v>
+        <v>0.1957597584491582</v>
       </c>
       <c r="C42" t="n">
-        <v>-0.4078898802573222</v>
+        <v>-0.4022846224633359</v>
       </c>
       <c r="D42" t="n">
-        <v>-2.325812893075149</v>
+        <v>-2.337023408663121</v>
       </c>
       <c r="E42" t="n">
-        <v>1.156775299370524</v>
+        <v>1.107086844179029</v>
       </c>
       <c r="F42" t="n">
-        <v>-2.645682341891634</v>
+        <v>-2.483493764920116</v>
       </c>
       <c r="G42" t="n">
-        <v>5.2913646837835</v>
+        <v>4.966987529841311</v>
       </c>
       <c r="H42" t="n">
-        <v>-1.226050614399612</v>
+        <v>-2.358842088302529</v>
       </c>
       <c r="I42" t="n">
-        <v>17.99995009283126</v>
+        <v>17.92989568164037</v>
       </c>
       <c r="J42" t="n">
-        <v>-1.226050614399612</v>
+        <v>-3.570787045583546</v>
       </c>
       <c r="K42" t="n">
-        <v>17.99995009283126</v>
+        <v>17.99993020581113</v>
       </c>
       <c r="L42" t="n">
-        <v>31.11973445740557</v>
+        <v>30.67223397926725</v>
       </c>
       <c r="M42" t="n">
-        <v>103.7340891173938</v>
+        <v>102.2431091624648</v>
       </c>
       <c r="N42" t="n">
-        <v>88.17397574978473</v>
+        <v>86.90664278809506</v>
       </c>
       <c r="O42" t="n">
-        <v>3.247863612742625</v>
+        <v>5.864195087139072</v>
       </c>
       <c r="P42" t="n">
-        <v>95.24430154506297</v>
+        <v>89.05727063198574</v>
       </c>
       <c r="Q42" t="n">
-        <v>98.49216515780559</v>
+        <v>94.92146571912481</v>
       </c>
       <c r="R42" t="n">
-        <v>3.247863612742625</v>
+        <v>5.864195087139072</v>
       </c>
       <c r="S42" t="n">
-        <v>95.24430154506297</v>
+        <v>89.05727063198574</v>
       </c>
       <c r="T42" t="n">
-        <v>98.49216515780559</v>
+        <v>94.92146571912481</v>
       </c>
     </row>
     <row r="43">
@@ -3065,61 +3065,61 @@
         <v>0.082</v>
       </c>
       <c r="B43" t="n">
-        <v>0.2007952686138895</v>
+        <v>0.1981012672403487</v>
       </c>
       <c r="C43" t="n">
-        <v>-0.4132545168843985</v>
+        <v>-0.4073811684017338</v>
       </c>
       <c r="D43" t="n">
-        <v>-2.315083619820996</v>
+        <v>-2.326830316786325</v>
       </c>
       <c r="E43" t="n">
-        <v>1.196441031851503</v>
+        <v>1.146212017724795</v>
       </c>
       <c r="F43" t="n">
-        <v>-2.750729391049601</v>
+        <v>-2.590118233120919</v>
       </c>
       <c r="G43" t="n">
-        <v>5.501458782098885</v>
+        <v>5.180236466242275</v>
       </c>
       <c r="H43" t="n">
-        <v>-1.296590770499588</v>
+        <v>-2.479348317205173</v>
       </c>
       <c r="I43" t="n">
-        <v>17.9999613329056</v>
+        <v>17.92690264432181</v>
       </c>
       <c r="J43" t="n">
-        <v>-1.296590770499588</v>
+        <v>-3.743326014968182</v>
       </c>
       <c r="K43" t="n">
-        <v>17.9999613329056</v>
+        <v>17.99994397849583</v>
       </c>
       <c r="L43" t="n">
-        <v>31.33220422698105</v>
+        <v>30.83534070401096</v>
       </c>
       <c r="M43" t="n">
-        <v>104.4421445347212</v>
+        <v>102.7864137005223</v>
       </c>
       <c r="N43" t="n">
-        <v>88.77582285451305</v>
+        <v>87.36845164544395</v>
       </c>
       <c r="O43" t="n">
-        <v>3.568452071609074</v>
+        <v>6.430319972983306</v>
       </c>
       <c r="P43" t="n">
-        <v>99.02604595203488</v>
+        <v>92.86517059761525</v>
       </c>
       <c r="Q43" t="n">
-        <v>102.594498023644</v>
+        <v>99.29549057059855</v>
       </c>
       <c r="R43" t="n">
-        <v>3.568452071609074</v>
+        <v>6.430319972983306</v>
       </c>
       <c r="S43" t="n">
-        <v>99.02604595203488</v>
+        <v>92.86517059761525</v>
       </c>
       <c r="T43" t="n">
-        <v>102.594498023644</v>
+        <v>99.29549057059855</v>
       </c>
     </row>
     <row r="44">
@@ -3127,61 +3127,61 @@
         <v>0.08400000000000001</v>
       </c>
       <c r="B44" t="n">
-        <v>0.203375327416971</v>
+        <v>0.2004956768915385</v>
       </c>
       <c r="C44" t="n">
-        <v>-0.4188992676756086</v>
+        <v>-0.4125989313792339</v>
       </c>
       <c r="D44" t="n">
-        <v>-2.303794118238576</v>
+        <v>-2.316394790831326</v>
       </c>
       <c r="E44" t="n">
-        <v>1.236264297061276</v>
+        <v>1.185404956473869</v>
       </c>
       <c r="F44" t="n">
-        <v>-2.851947866071295</v>
+        <v>-2.695932226764598</v>
       </c>
       <c r="G44" t="n">
-        <v>5.703895732142609</v>
+        <v>5.391864453527538</v>
       </c>
       <c r="H44" t="n">
-        <v>-1.36611720435664</v>
+        <v>-2.598604928941312</v>
       </c>
       <c r="I44" t="n">
-        <v>17.9999695394444</v>
+        <v>17.92393192428404</v>
       </c>
       <c r="J44" t="n">
-        <v>-1.36611720435664</v>
+        <v>-3.914219855602437</v>
       </c>
       <c r="K44" t="n">
-        <v>17.9999695394444</v>
+        <v>17.99995721307878</v>
       </c>
       <c r="L44" t="n">
-        <v>31.54721904065255</v>
+        <v>31.00758339075047</v>
       </c>
       <c r="M44" t="n">
-        <v>105.1585334621732</v>
+        <v>103.3600815736786</v>
       </c>
       <c r="N44" t="n">
-        <v>89.3847534428472</v>
+        <v>87.85606933762685</v>
       </c>
       <c r="O44" t="n">
-        <v>3.900814760843227</v>
+        <v>7.0060337289349</v>
       </c>
       <c r="P44" t="n">
-        <v>102.6699504663684</v>
+        <v>96.64339292871267</v>
       </c>
       <c r="Q44" t="n">
-        <v>106.5707652272116</v>
+        <v>103.6494266576476</v>
       </c>
       <c r="R44" t="n">
-        <v>3.900814760843227</v>
+        <v>7.0060337289349</v>
       </c>
       <c r="S44" t="n">
-        <v>102.6699504663684</v>
+        <v>96.64339292871267</v>
       </c>
       <c r="T44" t="n">
-        <v>106.5707652272116</v>
+        <v>103.6494266576476</v>
       </c>
     </row>
     <row r="45">
@@ -3189,61 +3189,61 @@
         <v>0.08600000000000001</v>
       </c>
       <c r="B45" t="n">
-        <v>0.2060050570792263</v>
+        <v>0.2030381823736871</v>
       </c>
       <c r="C45" t="n">
-        <v>-0.424661214342874</v>
+        <v>-0.418161092684795</v>
       </c>
       <c r="D45" t="n">
-        <v>-2.292270224904045</v>
+        <v>-2.305270468220203</v>
       </c>
       <c r="E45" t="n">
-        <v>1.276172018409811</v>
+        <v>1.224806124418556</v>
       </c>
       <c r="F45" t="n">
-        <v>-2.951815047381908</v>
+        <v>-2.798771845117729</v>
       </c>
       <c r="G45" t="n">
-        <v>5.903630094764151</v>
+        <v>5.597543690235572</v>
       </c>
       <c r="H45" t="n">
-        <v>-1.440510255053872</v>
+        <v>-2.727593688732799</v>
       </c>
       <c r="I45" t="n">
-        <v>17.99997627120436</v>
+        <v>17.92103870158994</v>
       </c>
       <c r="J45" t="n">
-        <v>-1.440510255053872</v>
+        <v>-4.09339434915025</v>
       </c>
       <c r="K45" t="n">
-        <v>17.99997627120436</v>
+        <v>17.99996406762226</v>
       </c>
       <c r="L45" t="n">
-        <v>31.76157040804844</v>
+        <v>31.19410497253195</v>
       </c>
       <c r="M45" t="n">
-        <v>105.8727328891118</v>
+        <v>103.9816289372153</v>
       </c>
       <c r="N45" t="n">
-        <v>89.99182295574505</v>
+        <v>88.38438459663304</v>
       </c>
       <c r="O45" t="n">
-        <v>4.254634204567088</v>
+        <v>7.643020441874082</v>
       </c>
       <c r="P45" t="n">
-        <v>106.2652017700791</v>
+        <v>100.3133892707058</v>
       </c>
       <c r="Q45" t="n">
-        <v>110.5198359746462</v>
+        <v>107.9564097125799</v>
       </c>
       <c r="R45" t="n">
-        <v>4.254634204567088</v>
+        <v>7.643020441874082</v>
       </c>
       <c r="S45" t="n">
-        <v>106.2652017700791</v>
+        <v>100.3133892707058</v>
       </c>
       <c r="T45" t="n">
-        <v>110.5198359746462</v>
+        <v>107.9564097125799</v>
       </c>
     </row>
     <row r="46">
@@ -3251,61 +3251,61 @@
         <v>0.08799999999999999</v>
       </c>
       <c r="B46" t="n">
-        <v>0.208746842062816</v>
+        <v>0.2056268802799503</v>
       </c>
       <c r="C46" t="n">
-        <v>-0.4306899522084807</v>
+        <v>-0.423832388612513</v>
       </c>
       <c r="D46" t="n">
-        <v>-2.280212749172832</v>
+        <v>-2.293927876364767</v>
       </c>
       <c r="E46" t="n">
-        <v>1.316313751658672</v>
+        <v>1.264291889316661</v>
       </c>
       <c r="F46" t="n">
-        <v>-3.049170046053859</v>
+        <v>-2.900800424928789</v>
       </c>
       <c r="G46" t="n">
-        <v>6.098340092107438</v>
+        <v>5.80160084985854</v>
       </c>
       <c r="H46" t="n">
-        <v>-1.537892202601551</v>
+        <v>-2.858431010673899</v>
       </c>
       <c r="I46" t="n">
-        <v>17.99997918288261</v>
+        <v>17.9181675314771</v>
       </c>
       <c r="J46" t="n">
-        <v>-1.537892202601551</v>
+        <v>-4.274021618039149</v>
       </c>
       <c r="K46" t="n">
-        <v>17.99997918288261</v>
+        <v>17.99997010346011</v>
       </c>
       <c r="L46" t="n">
-        <v>31.97052090244761</v>
+        <v>31.3822657498724</v>
       </c>
       <c r="M46" t="n">
-        <v>106.5691702042861</v>
+        <v>104.6086454350029</v>
       </c>
       <c r="N46" t="n">
-        <v>90.5837946736432</v>
+        <v>88.91734861975247</v>
       </c>
       <c r="O46" t="n">
-        <v>4.694511815027239</v>
+        <v>8.297356712113293</v>
       </c>
       <c r="P46" t="n">
-        <v>109.769995020043</v>
+        <v>103.9538204566073</v>
       </c>
       <c r="Q46" t="n">
-        <v>114.4645068350702</v>
+        <v>112.2511771687206</v>
       </c>
       <c r="R46" t="n">
-        <v>4.694511815027239</v>
+        <v>8.297356712113293</v>
       </c>
       <c r="S46" t="n">
-        <v>109.769995020043</v>
+        <v>103.9538204566073</v>
       </c>
       <c r="T46" t="n">
-        <v>114.4645068350702</v>
+        <v>112.2511771687206</v>
       </c>
     </row>
     <row r="47">
@@ -3313,61 +3313,61 @@
         <v>0.09</v>
       </c>
       <c r="B47" t="n">
-        <v>0.2115589259987036</v>
+        <v>0.2083163647776209</v>
       </c>
       <c r="C47" t="n">
-        <v>-0.4368892273114995</v>
+        <v>-0.4297420327357727</v>
       </c>
       <c r="D47" t="n">
-        <v>-2.267814198966794</v>
+        <v>-2.282108588118247</v>
       </c>
       <c r="E47" t="n">
-        <v>1.356672909995655</v>
+        <v>1.303964859806927</v>
       </c>
       <c r="F47" t="n">
-        <v>-3.146096807694038</v>
+        <v>-3.00107499999024</v>
       </c>
       <c r="G47" t="n">
-        <v>6.292193615387908</v>
+        <v>6.002149999979984</v>
       </c>
       <c r="H47" t="n">
-        <v>-1.637703797646186</v>
+        <v>-2.99314312241711</v>
       </c>
       <c r="I47" t="n">
-        <v>17.99998166316428</v>
+        <v>17.91534419444089</v>
       </c>
       <c r="J47" t="n">
-        <v>-1.637703797646186</v>
+        <v>-4.457667722412347</v>
       </c>
       <c r="K47" t="n">
-        <v>17.99998166316428</v>
+        <v>17.99997450944061</v>
       </c>
       <c r="L47" t="n">
-        <v>32.173729949372</v>
+        <v>31.57362709039741</v>
       </c>
       <c r="M47" t="n">
-        <v>107.2464429316414</v>
+        <v>105.2463306005133</v>
       </c>
       <c r="N47" t="n">
-        <v>91.15947649189518</v>
+        <v>89.45938101043632</v>
       </c>
       <c r="O47" t="n">
-        <v>5.158223632370292</v>
+        <v>8.989312355390307</v>
       </c>
       <c r="P47" t="n">
-        <v>113.2593699395042</v>
+        <v>107.5303037670864</v>
       </c>
       <c r="Q47" t="n">
-        <v>118.4175935718745</v>
+        <v>116.5196161224767</v>
       </c>
       <c r="R47" t="n">
-        <v>5.158223632370292</v>
+        <v>8.989312355390307</v>
       </c>
       <c r="S47" t="n">
-        <v>113.2593699395042</v>
+        <v>107.5303037670864</v>
       </c>
       <c r="T47" t="n">
-        <v>118.4175935718745</v>
+        <v>116.5196161224767</v>
       </c>
     </row>
     <row r="48">
@@ -3375,61 +3375,61 @@
         <v>0.092</v>
       </c>
       <c r="B48" t="n">
-        <v>0.2144323515171459</v>
+        <v>0.2110922619914161</v>
       </c>
       <c r="C48" t="n">
-        <v>-0.4432373100949372</v>
+        <v>-0.4358597771808657</v>
       </c>
       <c r="D48" t="n">
-        <v>-2.255118033399919</v>
+        <v>-2.269873099228062</v>
       </c>
       <c r="E48" t="n">
-        <v>1.397221789495707</v>
+        <v>1.343859486049605</v>
       </c>
       <c r="F48" t="n">
-        <v>-3.242649897517233</v>
+        <v>-3.100643861681366</v>
       </c>
       <c r="G48" t="n">
-        <v>6.485299795035038</v>
+        <v>6.201287723362423</v>
       </c>
       <c r="H48" t="n">
-        <v>-1.739635458746448</v>
+        <v>-3.139138931670561</v>
       </c>
       <c r="I48" t="n">
-        <v>17.99998376701718</v>
+        <v>17.91253931165872</v>
       </c>
       <c r="J48" t="n">
-        <v>-1.739635458746448</v>
+        <v>-4.652253136171067</v>
       </c>
       <c r="K48" t="n">
-        <v>17.99998376701718</v>
+        <v>17.99997746855813</v>
       </c>
       <c r="L48" t="n">
-        <v>32.37192911403291</v>
+        <v>31.76386682719687</v>
       </c>
       <c r="M48" t="n">
-        <v>107.9069929894917</v>
+        <v>105.8803517687575</v>
       </c>
       <c r="N48" t="n">
-        <v>91.72094404106792</v>
+        <v>89.9982990034439</v>
       </c>
       <c r="O48" t="n">
-        <v>5.642732743575336</v>
+        <v>9.743325554794733</v>
       </c>
       <c r="P48" t="n">
-        <v>116.7352911052112</v>
+        <v>111.0804456356662</v>
       </c>
       <c r="Q48" t="n">
-        <v>122.3780238487865</v>
+        <v>120.8237711904609</v>
       </c>
       <c r="R48" t="n">
-        <v>5.642732743575336</v>
+        <v>9.743325554794733</v>
       </c>
       <c r="S48" t="n">
-        <v>116.7352911052112</v>
+        <v>111.0804456356662</v>
       </c>
       <c r="T48" t="n">
-        <v>122.3780238487865</v>
+        <v>120.8237711904609</v>
       </c>
     </row>
     <row r="49">
@@ -3437,61 +3437,61 @@
         <v>0.094</v>
       </c>
       <c r="B49" t="n">
-        <v>0.2174210094810733</v>
+        <v>0.2139209177169417</v>
       </c>
       <c r="C49" t="n">
-        <v>-0.4498700670976333</v>
+        <v>-0.442104575418073</v>
       </c>
       <c r="D49" t="n">
-        <v>-2.241852519394527</v>
+        <v>-2.257383502753647</v>
       </c>
       <c r="E49" t="n">
-        <v>1.438247751400885</v>
+        <v>1.383889442231419</v>
       </c>
       <c r="F49" t="n">
-        <v>-3.340747766946896</v>
+        <v>-3.199781856379805</v>
       </c>
       <c r="G49" t="n">
-        <v>6.681495533893854</v>
+        <v>6.399563712760489</v>
       </c>
       <c r="H49" t="n">
-        <v>-1.869319056511533</v>
+        <v>-3.292023901618807</v>
       </c>
       <c r="I49" t="n">
-        <v>17.99998436976467</v>
+        <v>17.90974569595646</v>
       </c>
       <c r="J49" t="n">
-        <v>-1.869319056511533</v>
+        <v>-4.853517447532152</v>
       </c>
       <c r="K49" t="n">
-        <v>17.99998436976467</v>
+        <v>17.99997954430638</v>
       </c>
       <c r="L49" t="n">
-        <v>32.56123479077083</v>
+        <v>31.95342177886324</v>
       </c>
       <c r="M49" t="n">
-        <v>108.5379997392976</v>
+        <v>106.5121359162088</v>
       </c>
       <c r="N49" t="n">
-        <v>92.257299778403</v>
+        <v>90.53531552877746</v>
       </c>
       <c r="O49" t="n">
-        <v>6.253749019526738</v>
+        <v>10.53522744060714</v>
       </c>
       <c r="P49" t="n">
-        <v>120.2668152313018</v>
+        <v>114.6145049722556</v>
       </c>
       <c r="Q49" t="n">
-        <v>126.5205642508286</v>
+        <v>125.1497324128628</v>
       </c>
       <c r="R49" t="n">
-        <v>6.253749019526738</v>
+        <v>10.53522744060714</v>
       </c>
       <c r="S49" t="n">
-        <v>120.2668152313018</v>
+        <v>114.6145049722556</v>
       </c>
       <c r="T49" t="n">
-        <v>126.5205642508286</v>
+        <v>125.1497324128628</v>
       </c>
     </row>
     <row r="50">
@@ -3499,61 +3499,61 @@
         <v>0.096</v>
       </c>
       <c r="B50" t="n">
-        <v>0.2204559367421149</v>
+        <v>0.2168777406202689</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.4566184674238627</v>
+        <v>-0.4486638474385078</v>
       </c>
       <c r="D50" t="n">
-        <v>-2.228355718742068</v>
+        <v>-2.244264958712778</v>
       </c>
       <c r="E50" t="n">
-        <v>1.479493641257034</v>
+        <v>1.424355624830096</v>
       </c>
       <c r="F50" t="n">
-        <v>-3.440040150740437</v>
+        <v>-3.299608340433111</v>
       </c>
       <c r="G50" t="n">
-        <v>6.880080301480573</v>
+        <v>6.59921668086605</v>
       </c>
       <c r="H50" t="n">
-        <v>-2.003551477834664</v>
+        <v>-3.455775957537492</v>
       </c>
       <c r="I50" t="n">
-        <v>17.99998469475554</v>
+        <v>17.90693182804028</v>
       </c>
       <c r="J50" t="n">
-        <v>-2.003551477834664</v>
+        <v>-5.065984827668849</v>
       </c>
       <c r="K50" t="n">
-        <v>17.99998469475554</v>
+        <v>17.9999807832405</v>
       </c>
       <c r="L50" t="n">
-        <v>32.74815234160041</v>
+        <v>32.13915787714219</v>
       </c>
       <c r="M50" t="n">
-        <v>109.1610506379782</v>
+        <v>107.1311924751372</v>
       </c>
       <c r="N50" t="n">
-        <v>92.78689304228143</v>
+        <v>91.06151360386662</v>
       </c>
       <c r="O50" t="n">
-        <v>6.89705630983463</v>
+        <v>11.41414125551137</v>
       </c>
       <c r="P50" t="n">
-        <v>123.8413401288406</v>
+        <v>118.1713317352709</v>
       </c>
       <c r="Q50" t="n">
-        <v>130.7383964386752</v>
+        <v>129.5854729907823</v>
       </c>
       <c r="R50" t="n">
-        <v>6.89705630983463</v>
+        <v>11.41414125551137</v>
       </c>
       <c r="S50" t="n">
-        <v>123.8413401288406</v>
+        <v>118.1713317352709</v>
       </c>
       <c r="T50" t="n">
-        <v>130.7383964386752</v>
+        <v>129.5854729907823</v>
       </c>
     </row>
     <row r="51">
@@ -3561,61 +3561,61 @@
         <v>0.098</v>
       </c>
       <c r="B51" t="n">
-        <v>0.2235908237178494</v>
+        <v>0.2198780515685296</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.46361804314259</v>
+        <v>-0.4553314375463748</v>
       </c>
       <c r="D51" t="n">
-        <v>-2.214356567304613</v>
+        <v>-2.230929778497044</v>
       </c>
       <c r="E51" t="n">
-        <v>1.521243083256776</v>
+        <v>1.464999029341219</v>
       </c>
       <c r="F51" t="n">
-        <v>-3.542488545041317</v>
+        <v>-3.400194583782785</v>
       </c>
       <c r="G51" t="n">
-        <v>7.084977090082955</v>
+        <v>6.80038916756486</v>
       </c>
       <c r="H51" t="n">
-        <v>-2.141003451216692</v>
+        <v>-3.626024747989738</v>
       </c>
       <c r="I51" t="n">
-        <v>17.99998474531996</v>
+        <v>17.9040961462631</v>
       </c>
       <c r="J51" t="n">
-        <v>-2.141003451216692</v>
+        <v>-5.285319704875737</v>
       </c>
       <c r="K51" t="n">
-        <v>17.99998474531996</v>
+        <v>17.99998163352577</v>
       </c>
       <c r="L51" t="n">
-        <v>32.93109586644709</v>
+        <v>32.32396842510191</v>
       </c>
       <c r="M51" t="n">
-        <v>109.770828332709</v>
+        <v>107.7471810809076</v>
       </c>
       <c r="N51" t="n">
-        <v>93.30520408280262</v>
+        <v>91.58510391877142</v>
       </c>
       <c r="O51" t="n">
-        <v>7.591582129781068</v>
+        <v>12.33626058781387</v>
       </c>
       <c r="P51" t="n">
-        <v>127.5294795476597</v>
+        <v>121.7546023960491</v>
       </c>
       <c r="Q51" t="n">
-        <v>135.1210616774408</v>
+        <v>134.0908629838629</v>
       </c>
       <c r="R51" t="n">
-        <v>7.591582129781068</v>
+        <v>12.33626058781387</v>
       </c>
       <c r="S51" t="n">
-        <v>127.5294795476597</v>
+        <v>121.7546023960491</v>
       </c>
       <c r="T51" t="n">
-        <v>135.1210616774408</v>
+        <v>134.0908629838629</v>
       </c>
     </row>
     <row r="52">
@@ -3623,61 +3623,61 @@
         <v>0.1</v>
       </c>
       <c r="B52" t="n">
-        <v>0.2268065115188507</v>
+        <v>0.2229791999970495</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.4708238988654899</v>
+        <v>-0.4622510529507552</v>
       </c>
       <c r="D52" t="n">
-        <v>-2.199944855858813</v>
+        <v>-2.217090547688283</v>
       </c>
       <c r="E52" t="n">
-        <v>1.56345184315888</v>
+        <v>1.506068988200693</v>
       </c>
       <c r="F52" t="n">
-        <v>-3.648614234231137</v>
+        <v>-3.502823946666269</v>
       </c>
       <c r="G52" t="n">
-        <v>7.297228468462405</v>
+        <v>7.00564789333316</v>
       </c>
       <c r="H52" t="n">
-        <v>-2.296375978462442</v>
+        <v>-3.81284054189982</v>
       </c>
       <c r="I52" t="n">
-        <v>17.99998372103837</v>
+        <v>17.90120189132951</v>
       </c>
       <c r="J52" t="n">
-        <v>-2.296375978462442</v>
+        <v>-5.522218627872959</v>
       </c>
       <c r="K52" t="n">
-        <v>17.99998372103837</v>
+        <v>17.99998152662551</v>
       </c>
       <c r="L52" t="n">
-        <v>33.11531269645431</v>
+        <v>32.50683088803019</v>
       </c>
       <c r="M52" t="n">
-        <v>110.3849119040972</v>
+        <v>108.3567248450514</v>
       </c>
       <c r="N52" t="n">
-        <v>93.82717511848259</v>
+        <v>92.10321611829366</v>
       </c>
       <c r="O52" t="n">
-        <v>8.389976586512791</v>
+        <v>13.36588059203018</v>
       </c>
       <c r="P52" t="n">
-        <v>131.3499934018321</v>
+        <v>125.4092021549227</v>
       </c>
       <c r="Q52" t="n">
-        <v>139.7399699883449</v>
+        <v>138.7750827469529</v>
       </c>
       <c r="R52" t="n">
-        <v>8.389976586512791</v>
+        <v>13.36588059203018</v>
       </c>
       <c r="S52" t="n">
-        <v>131.3499934018321</v>
+        <v>125.4092021549227</v>
       </c>
       <c r="T52" t="n">
-        <v>139.7399699883449</v>
+        <v>138.7750827469529</v>
       </c>
     </row>
     <row r="53">
@@ -3685,61 +3685,61 @@
         <v>0.102</v>
       </c>
       <c r="B53" t="n">
-        <v>0.2300775740300131</v>
+        <v>0.2261606009956719</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.4781711231376014</v>
+        <v>-0.4693748687848112</v>
       </c>
       <c r="D53" t="n">
-        <v>-2.18525040731459</v>
+        <v>-2.202842916020171</v>
       </c>
       <c r="E53" t="n">
-        <v>1.605975384446334</v>
+        <v>1.547534267850456</v>
       </c>
       <c r="F53" t="n">
-        <v>-3.757260060288111</v>
+        <v>-3.608148729296419</v>
       </c>
       <c r="G53" t="n">
-        <v>7.514520120575611</v>
+        <v>7.216297458593216</v>
       </c>
       <c r="H53" t="n">
-        <v>-2.464029883687322</v>
+        <v>-4.007557722891522</v>
       </c>
       <c r="I53" t="n">
-        <v>17.99998196013948</v>
+        <v>17.89823113321548</v>
       </c>
       <c r="J53" t="n">
-        <v>-2.464029883687322</v>
+        <v>-5.768334302788174</v>
       </c>
       <c r="K53" t="n">
-        <v>17.99998196013948</v>
+        <v>17.99998092738165</v>
       </c>
       <c r="L53" t="n">
-        <v>33.3004021525019</v>
+        <v>32.69068220063158</v>
       </c>
       <c r="M53" t="n">
-        <v>111.0019463942551</v>
+        <v>108.9695655280785</v>
       </c>
       <c r="N53" t="n">
-        <v>94.35165443511687</v>
+        <v>92.62413069886671</v>
       </c>
       <c r="O53" t="n">
-        <v>9.259554668384562</v>
+        <v>14.47358125593955</v>
       </c>
       <c r="P53" t="n">
-        <v>135.2612265768307</v>
+        <v>129.1585456735047</v>
       </c>
       <c r="Q53" t="n">
-        <v>144.5207812452152</v>
+        <v>143.6321269294443</v>
       </c>
       <c r="R53" t="n">
-        <v>9.259554668384562</v>
+        <v>14.47358125593955</v>
       </c>
       <c r="S53" t="n">
-        <v>135.2612265768307</v>
+        <v>129.1585456735047</v>
       </c>
       <c r="T53" t="n">
-        <v>144.5207812452152</v>
+        <v>143.6321269294443</v>
       </c>
     </row>
     <row r="54">
@@ -3747,61 +3747,61 @@
         <v>0.104</v>
       </c>
       <c r="B54" t="n">
-        <v>0.233483908246525</v>
+        <v>0.2294004056291379</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.4858690669580941</v>
+        <v>-0.4766472910412465</v>
       </c>
       <c r="D54" t="n">
-        <v>-2.169854519673605</v>
+        <v>-2.1882980715073</v>
       </c>
       <c r="E54" t="n">
-        <v>1.649320087448185</v>
+        <v>1.589287241352922</v>
       </c>
       <c r="F54" t="n">
-        <v>-3.873204847025161</v>
+        <v>-3.715435097835077</v>
       </c>
       <c r="G54" t="n">
-        <v>7.746409694050416</v>
+        <v>7.430870195669137</v>
       </c>
       <c r="H54" t="n">
-        <v>-2.633222442896436</v>
+        <v>-4.208025121294122</v>
       </c>
       <c r="I54" t="n">
-        <v>17.99997733313819</v>
+        <v>17.89520470007685</v>
       </c>
       <c r="J54" t="n">
-        <v>-2.633222442896436</v>
+        <v>-6.02115744903764</v>
       </c>
       <c r="K54" t="n">
-        <v>17.99997733313819</v>
+        <v>17.99997996983578</v>
       </c>
       <c r="L54" t="n">
-        <v>33.49566324344375</v>
+        <v>32.87525314645032</v>
       </c>
       <c r="M54" t="n">
-        <v>111.6528961437463</v>
+        <v>109.5848055367138</v>
       </c>
       <c r="N54" t="n">
-        <v>94.90496172218438</v>
+        <v>93.14708470620671</v>
       </c>
       <c r="O54" t="n">
-        <v>10.21206753510173</v>
+        <v>15.63810495157532</v>
       </c>
       <c r="P54" t="n">
-        <v>139.435198167282</v>
+        <v>132.9768387589187</v>
       </c>
       <c r="Q54" t="n">
-        <v>149.6472657023837</v>
+        <v>148.6149437104941</v>
       </c>
       <c r="R54" t="n">
-        <v>10.21206753510173</v>
+        <v>15.63810495157532</v>
       </c>
       <c r="S54" t="n">
-        <v>139.435198167282</v>
+        <v>132.9768387589187</v>
       </c>
       <c r="T54" t="n">
-        <v>149.6472657023837</v>
+        <v>148.6149437104941</v>
       </c>
     </row>
     <row r="55">
@@ -3809,61 +3809,61 @@
         <v>0.106</v>
       </c>
       <c r="B55" t="n">
-        <v>0.2369431028495447</v>
+        <v>0.2327689298560856</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.4937059581068882</v>
+        <v>-0.4842530403885267</v>
       </c>
       <c r="D55" t="n">
-        <v>-2.154180737376016</v>
+        <v>-2.17308657281274</v>
       </c>
       <c r="E55" t="n">
-        <v>1.692994175073878</v>
+        <v>1.631740510417514</v>
       </c>
       <c r="F55" t="n">
-        <v>-3.992170371131576</v>
+        <v>-3.82834325973811</v>
       </c>
       <c r="G55" t="n">
-        <v>7.984340742263524</v>
+        <v>7.656686519476402</v>
       </c>
       <c r="H55" t="n">
-        <v>-2.811064871905925</v>
+        <v>-4.42972744448677</v>
       </c>
       <c r="I55" t="n">
-        <v>17.99993920830535</v>
+        <v>17.89201762733983</v>
       </c>
       <c r="J55" t="n">
-        <v>-2.811064871905925</v>
+        <v>-6.297958955238967</v>
       </c>
       <c r="K55" t="n">
-        <v>17.99993920830535</v>
+        <v>17.99997690726444</v>
       </c>
       <c r="L55" t="n">
-        <v>33.69678186059303</v>
+        <v>33.06684694613374</v>
       </c>
       <c r="M55" t="n">
-        <v>112.3249788712242</v>
+        <v>110.2235337094479</v>
       </c>
       <c r="N55" t="n">
-        <v>95.47623204054061</v>
+        <v>93.69000365303071</v>
       </c>
       <c r="O55" t="n">
-        <v>11.23223776208273</v>
+        <v>16.97640297590919</v>
       </c>
       <c r="P55" t="n">
-        <v>143.7176362616385</v>
+        <v>136.9930585607978</v>
       </c>
       <c r="Q55" t="n">
-        <v>154.9498740237212</v>
+        <v>153.969461536707</v>
       </c>
       <c r="R55" t="n">
-        <v>11.23223776208273</v>
+        <v>16.97640297590919</v>
       </c>
       <c r="S55" t="n">
-        <v>143.7176362616385</v>
+        <v>136.9930585607978</v>
       </c>
       <c r="T55" t="n">
-        <v>154.9498740237212</v>
+        <v>153.969461536707</v>
       </c>
     </row>
     <row r="56">
@@ -3871,61 +3871,61 @@
         <v>0.108</v>
       </c>
       <c r="B56" t="n">
-        <v>0.2405079972116752</v>
+        <v>0.2361845718627489</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.5018213302434503</v>
+        <v>-0.4919823192437271</v>
       </c>
       <c r="D56" t="n">
-        <v>-2.137949993102892</v>
+        <v>-2.157628015102339</v>
       </c>
       <c r="E56" t="n">
-        <v>1.73732977648753</v>
+        <v>1.674461267667308</v>
       </c>
       <c r="F56" t="n">
-        <v>-4.117233189801159</v>
+        <v>-3.94351696860979</v>
       </c>
       <c r="G56" t="n">
-        <v>8.234466379601775</v>
+        <v>7.887033937220572</v>
       </c>
       <c r="H56" t="n">
-        <v>-3.008927128618161</v>
+        <v>-4.6569151580524</v>
       </c>
       <c r="I56" t="n">
-        <v>17.99982314495545</v>
+        <v>17.88876518442562</v>
       </c>
       <c r="J56" t="n">
-        <v>-3.008927128618161</v>
+        <v>-6.581351438733978</v>
       </c>
       <c r="K56" t="n">
-        <v>17.99982314495545</v>
+        <v>17.99997236294043</v>
       </c>
       <c r="L56" t="n">
-        <v>33.91025029117844</v>
+        <v>33.26242858473774</v>
       </c>
       <c r="M56" t="n">
-        <v>113.0419855742466</v>
+        <v>110.8755792216802</v>
       </c>
       <c r="N56" t="n">
-        <v>96.08568773810957</v>
+        <v>94.24424233842818</v>
       </c>
       <c r="O56" t="n">
-        <v>12.3996234646143</v>
+        <v>18.37379689740602</v>
       </c>
       <c r="P56" t="n">
-        <v>148.2189254229473</v>
+        <v>141.089034600491</v>
       </c>
       <c r="Q56" t="n">
-        <v>160.6185488875616</v>
+        <v>159.462831497897</v>
       </c>
       <c r="R56" t="n">
-        <v>12.3996234646143</v>
+        <v>18.37379689740602</v>
       </c>
       <c r="S56" t="n">
-        <v>148.2189254229473</v>
+        <v>141.089034600491</v>
       </c>
       <c r="T56" t="n">
-        <v>160.6185488875616</v>
+        <v>159.462831497897</v>
       </c>
     </row>
     <row r="57">
@@ -3933,61 +3933,61 @@
         <v>0.11</v>
       </c>
       <c r="B57" t="n">
-        <v>0.2441747802824308</v>
+        <v>0.2397172617934967</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.5102107001873869</v>
+        <v>-0.5000201559678142</v>
       </c>
       <c r="D57" t="n">
-        <v>-2.121171253215019</v>
+        <v>-2.141552341654164</v>
       </c>
       <c r="E57" t="n">
-        <v>1.782126678055807</v>
+        <v>1.717858947659727</v>
       </c>
       <c r="F57" t="n">
-        <v>-4.245413651998962</v>
+        <v>-4.064550476273083</v>
       </c>
       <c r="G57" t="n">
-        <v>8.490827303997776</v>
+        <v>8.129100952545512</v>
       </c>
       <c r="H57" t="n">
-        <v>-3.179661419530711</v>
+        <v>-4.895175942965484</v>
       </c>
       <c r="I57" t="n">
-        <v>17.96410298582564</v>
+        <v>17.885343020423</v>
       </c>
       <c r="J57" t="n">
-        <v>-3.179661419530711</v>
+        <v>-6.878676575386748</v>
       </c>
       <c r="K57" t="n">
-        <v>17.96410298582564</v>
+        <v>17.99996334385389</v>
       </c>
       <c r="L57" t="n">
-        <v>34.13361650651926</v>
+        <v>33.46949844570322</v>
       </c>
       <c r="M57" t="n">
-        <v>113.7868624553939</v>
+        <v>111.5659750366111</v>
       </c>
       <c r="N57" t="n">
-        <v>96.71883308708478</v>
+        <v>94.83107878111944</v>
       </c>
       <c r="O57" t="n">
-        <v>13.51214672836795</v>
+        <v>19.91295551226121</v>
       </c>
       <c r="P57" t="n">
-        <v>152.520884613906</v>
+        <v>145.3912917291756</v>
       </c>
       <c r="Q57" t="n">
-        <v>166.0330313422739</v>
+        <v>165.3042472414368</v>
       </c>
       <c r="R57" t="n">
-        <v>13.51214672836795</v>
+        <v>19.91295551226121</v>
       </c>
       <c r="S57" t="n">
-        <v>152.520884613906</v>
+        <v>145.3912917291756</v>
       </c>
       <c r="T57" t="n">
-        <v>166.0330313422739</v>
+        <v>165.3042472414368</v>
       </c>
     </row>
     <row r="58">
@@ -3995,61 +3995,61 @@
         <v>0.112</v>
       </c>
       <c r="B58" t="n">
-        <v>0.2478966779127062</v>
+        <v>0.2433340367042864</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.5187483548010344</v>
+        <v>-0.508283881805809</v>
       </c>
       <c r="D58" t="n">
-        <v>-2.104095943987724</v>
+        <v>-2.125024889978175</v>
       </c>
       <c r="E58" t="n">
-        <v>1.827171464636626</v>
+        <v>1.761761534212566</v>
       </c>
       <c r="F58" t="n">
-        <v>-4.375255618780047</v>
+        <v>-4.190075850682071</v>
       </c>
       <c r="G58" t="n">
-        <v>8.750511237561019</v>
+        <v>8.380151701363639</v>
       </c>
       <c r="H58" t="n">
-        <v>-3.336101462992194</v>
+        <v>-5.146692900547372</v>
       </c>
       <c r="I58" t="n">
-        <v>17.90934137862484</v>
+        <v>17.8817388773114</v>
       </c>
       <c r="J58" t="n">
-        <v>-3.336101462992194</v>
+        <v>-7.191449915680222</v>
       </c>
       <c r="K58" t="n">
-        <v>17.90934137862484</v>
+        <v>17.99989901630063</v>
       </c>
       <c r="L58" t="n">
-        <v>34.36222760918744</v>
+        <v>33.68778886866106</v>
       </c>
       <c r="M58" t="n">
-        <v>114.5465186735821</v>
+        <v>112.2946358223887</v>
       </c>
       <c r="N58" t="n">
-        <v>97.36454087254481</v>
+        <v>95.4504404490304</v>
       </c>
       <c r="O58" t="n">
-        <v>14.59652079745455</v>
+        <v>21.58592584717566</v>
       </c>
       <c r="P58" t="n">
-        <v>156.7157162037434</v>
+        <v>149.8510868152732</v>
       </c>
       <c r="Q58" t="n">
-        <v>171.3122370011979</v>
+        <v>171.4370126624489</v>
       </c>
       <c r="R58" t="n">
-        <v>14.59652079745455</v>
+        <v>21.58592584717566</v>
       </c>
       <c r="S58" t="n">
-        <v>156.7157162037434</v>
+        <v>149.8510868152732</v>
       </c>
       <c r="T58" t="n">
-        <v>171.3122370011979</v>
+        <v>171.4370126624489</v>
       </c>
     </row>
     <row r="59">
@@ -4057,61 +4057,61 @@
         <v>0.114</v>
       </c>
       <c r="B59" t="n">
-        <v>0.2517724111399489</v>
+        <v>0.2470234066309037</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.5277119127446741</v>
+        <v>-0.5167426296773612</v>
       </c>
       <c r="D59" t="n">
-        <v>-2.086168828100444</v>
+        <v>-2.108107394235071</v>
       </c>
       <c r="E59" t="n">
-        <v>1.872630929747328</v>
+        <v>1.806100033335368</v>
       </c>
       <c r="F59" t="n">
-        <v>-4.505537349891359</v>
+        <v>-4.319479291510735</v>
       </c>
       <c r="G59" t="n">
-        <v>9.011074699782498</v>
+        <v>8.638958583022671</v>
       </c>
       <c r="H59" t="n">
-        <v>-3.516666555937553</v>
+        <v>-5.409654613949226</v>
       </c>
       <c r="I59" t="n">
-        <v>17.83812807432184</v>
+        <v>17.87797762199869</v>
       </c>
       <c r="J59" t="n">
-        <v>-3.516666555937553</v>
+        <v>-7.517560508206465</v>
       </c>
       <c r="K59" t="n">
-        <v>17.83812807432184</v>
+        <v>17.99978693801931</v>
       </c>
       <c r="L59" t="n">
-        <v>34.58709761820736</v>
+        <v>33.91576659695008</v>
       </c>
       <c r="M59" t="n">
-        <v>115.2974877212964</v>
+        <v>113.0563327837458</v>
       </c>
       <c r="N59" t="n">
-        <v>98.00286456310194</v>
+        <v>96.09788286618392</v>
       </c>
       <c r="O59" t="n">
-        <v>15.85964110696697</v>
+        <v>23.37442292575814</v>
       </c>
       <c r="P59" t="n">
-        <v>160.7287398600747</v>
+        <v>154.4468927621233</v>
       </c>
       <c r="Q59" t="n">
-        <v>176.5883809670416</v>
+        <v>177.8213156878815</v>
       </c>
       <c r="R59" t="n">
-        <v>15.85964110696697</v>
+        <v>23.37442292575814</v>
       </c>
       <c r="S59" t="n">
-        <v>160.7287398600747</v>
+        <v>154.4468927621233</v>
       </c>
       <c r="T59" t="n">
-        <v>176.5883809670416</v>
+        <v>177.8213156878815</v>
       </c>
     </row>
     <row r="60">
@@ -4119,61 +4119,61 @@
         <v>0.116</v>
       </c>
       <c r="B60" t="n">
-        <v>0.2557028714529068</v>
+        <v>0.2508522104294301</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.5368320502543428</v>
+        <v>-0.5255842275278543</v>
       </c>
       <c r="D60" t="n">
-        <v>-2.067928553081107</v>
+        <v>-2.090424198534085</v>
       </c>
       <c r="E60" t="n">
-        <v>1.918317487577177</v>
+        <v>1.851208412428035</v>
       </c>
       <c r="F60" t="n">
-        <v>-4.637374313218743</v>
+        <v>-4.455145437437088</v>
       </c>
       <c r="G60" t="n">
-        <v>9.274748626436905</v>
+        <v>8.910290874874073</v>
       </c>
       <c r="H60" t="n">
-        <v>-3.709293163408691</v>
+        <v>-5.671984162024066</v>
       </c>
       <c r="I60" t="n">
-        <v>17.77584261012634</v>
+        <v>17.85690880930294</v>
       </c>
       <c r="J60" t="n">
-        <v>-3.709293163408691</v>
+        <v>-7.846095135493365</v>
       </c>
       <c r="K60" t="n">
-        <v>17.77584261012634</v>
+        <v>17.98254391063866</v>
       </c>
       <c r="L60" t="n">
-        <v>34.81215492809418</v>
+        <v>34.16308441828707</v>
       </c>
       <c r="M60" t="n">
-        <v>116.0474193068466</v>
+        <v>113.881084783838</v>
       </c>
       <c r="N60" t="n">
-        <v>98.64030641081963</v>
+        <v>96.79892206626232</v>
       </c>
       <c r="O60" t="n">
-        <v>17.21470846528355</v>
+        <v>25.29482350402153</v>
       </c>
       <c r="P60" t="n">
-        <v>164.8607045688169</v>
+        <v>159.1056223811503</v>
       </c>
       <c r="Q60" t="n">
-        <v>182.0754130341004</v>
+        <v>184.4004458851718</v>
       </c>
       <c r="R60" t="n">
-        <v>17.21470846528355</v>
+        <v>25.29482350402153</v>
       </c>
       <c r="S60" t="n">
-        <v>164.8607045688169</v>
+        <v>159.1056223811503</v>
       </c>
       <c r="T60" t="n">
-        <v>182.0754130341004</v>
+        <v>184.4004458851718</v>
       </c>
     </row>
     <row r="61">
@@ -4181,61 +4181,61 @@
         <v>0.118</v>
       </c>
       <c r="B61" t="n">
-        <v>0.2597310828511091</v>
+        <v>0.2547337601672821</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.5462318632173341</v>
+        <v>-0.5345727826187363</v>
       </c>
       <c r="D61" t="n">
-        <v>-2.049128927155125</v>
+        <v>-2.072447088352321</v>
       </c>
       <c r="E61" t="n">
-        <v>1.964409668316736</v>
+        <v>1.896601519576645</v>
       </c>
       <c r="F61" t="n">
-        <v>-4.771989163125342</v>
+        <v>-4.593049616102648</v>
       </c>
       <c r="G61" t="n">
-        <v>9.543978326251148</v>
+        <v>9.18609923220404</v>
       </c>
       <c r="H61" t="n">
-        <v>-3.923463511409355</v>
+        <v>-5.939621911114085</v>
       </c>
       <c r="I61" t="n">
-        <v>17.72950365665749</v>
+        <v>17.83307688905618</v>
       </c>
       <c r="J61" t="n">
-        <v>-3.923463511409355</v>
+        <v>-8.181030123772176</v>
       </c>
       <c r="K61" t="n">
-        <v>17.72950365665749</v>
+        <v>17.96260088823026</v>
       </c>
       <c r="L61" t="n">
-        <v>35.0375467864549</v>
+        <v>34.41734934581687</v>
       </c>
       <c r="M61" t="n">
-        <v>116.7954978236447</v>
+        <v>114.7286791681242</v>
       </c>
       <c r="N61" t="n">
-        <v>99.27617315009802</v>
+        <v>97.51937729290556</v>
       </c>
       <c r="O61" t="n">
-        <v>18.73400755069035</v>
+        <v>27.29207393349943</v>
       </c>
       <c r="P61" t="n">
-        <v>169.2051164927057</v>
+        <v>163.8146628663055</v>
       </c>
       <c r="Q61" t="n">
-        <v>187.9391240433961</v>
+        <v>191.1067367998049</v>
       </c>
       <c r="R61" t="n">
-        <v>18.73400755069035</v>
+        <v>27.29207393349943</v>
       </c>
       <c r="S61" t="n">
-        <v>169.2051164927057</v>
+        <v>163.8146628663055</v>
       </c>
       <c r="T61" t="n">
-        <v>187.9391240433961</v>
+        <v>191.1067367998049</v>
       </c>
     </row>
     <row r="62">
@@ -4243,61 +4243,61 @@
         <v>0.12</v>
       </c>
       <c r="B62" t="n">
-        <v>0.2638717215950075</v>
+        <v>0.2587531128886048</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.5559618726202832</v>
+        <v>-0.5439497349388978</v>
       </c>
       <c r="D62" t="n">
-        <v>-2.029668908349227</v>
+        <v>-2.053693183711998</v>
       </c>
       <c r="E62" t="n">
-        <v>2.011298959972312</v>
+        <v>1.942724879222931</v>
       </c>
       <c r="F62" t="n">
-        <v>-4.915401736211898</v>
+        <v>-4.736526457860356</v>
       </c>
       <c r="G62" t="n">
-        <v>9.830803472423897</v>
+        <v>9.473052915721405</v>
       </c>
       <c r="H62" t="n">
-        <v>-4.186716202142805</v>
+        <v>-6.232740901660236</v>
       </c>
       <c r="I62" t="n">
-        <v>17.70549142568473</v>
+        <v>17.80994800882984</v>
       </c>
       <c r="J62" t="n">
-        <v>-4.186716202142805</v>
+        <v>-8.54416581309609</v>
       </c>
       <c r="K62" t="n">
-        <v>17.70549142568473</v>
+        <v>17.94351805494151</v>
       </c>
       <c r="L62" t="n">
-        <v>35.27565267151317</v>
+        <v>34.68899168114062</v>
       </c>
       <c r="M62" t="n">
-        <v>117.5883810601845</v>
+        <v>115.6338357061778</v>
       </c>
       <c r="N62" t="n">
-        <v>99.95012390115683</v>
+        <v>98.28876035025115</v>
       </c>
       <c r="O62" t="n">
-        <v>20.60708825633008</v>
+        <v>29.54652485814561</v>
       </c>
       <c r="P62" t="n">
-        <v>174.0562750964732</v>
+        <v>168.7106373427363</v>
       </c>
       <c r="Q62" t="n">
-        <v>194.6633633528033</v>
+        <v>198.2571622008819</v>
       </c>
       <c r="R62" t="n">
-        <v>20.60708825633008</v>
+        <v>29.54652485814561</v>
       </c>
       <c r="S62" t="n">
-        <v>174.0562750964732</v>
+        <v>168.7106373427363</v>
       </c>
       <c r="T62" t="n">
-        <v>194.6633633528033</v>
+        <v>198.2571622008819</v>
       </c>
     </row>
     <row r="63">
@@ -4305,61 +4305,61 @@
         <v>0.122</v>
       </c>
       <c r="B63" t="n">
-        <v>0.2680691806467594</v>
+        <v>0.2628577247941897</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.5658592888539006</v>
+        <v>-0.5535736934458847</v>
       </c>
       <c r="D63" t="n">
-        <v>-2.009874075881992</v>
+        <v>-2.034445266698024</v>
       </c>
       <c r="E63" t="n">
-        <v>2.058623468311039</v>
+        <v>1.989405910654561</v>
       </c>
       <c r="F63" t="n">
-        <v>-5.063786737442703</v>
+        <v>-4.885057200770921</v>
       </c>
       <c r="G63" t="n">
-        <v>10.12757347488471</v>
+        <v>9.770114401542502</v>
       </c>
       <c r="H63" t="n">
-        <v>-4.473568791145917</v>
+        <v>-6.546189833133295</v>
       </c>
       <c r="I63" t="n">
-        <v>17.69405767597764</v>
+        <v>17.79668242806558</v>
       </c>
       <c r="J63" t="n">
-        <v>-4.473568791145917</v>
+        <v>-8.930097747109505</v>
       </c>
       <c r="K63" t="n">
-        <v>17.69405767597764</v>
+        <v>17.93444104112733</v>
       </c>
       <c r="L63" t="n">
-        <v>35.52240909962443</v>
+        <v>34.97522096727659</v>
       </c>
       <c r="M63" t="n">
-        <v>118.4110191189068</v>
+        <v>116.587413274714</v>
       </c>
       <c r="N63" t="n">
-        <v>100.6493662510707</v>
+        <v>99.09930128350692</v>
       </c>
       <c r="O63" t="n">
-        <v>22.65911913467492</v>
+        <v>32.00864566338954</v>
       </c>
       <c r="P63" t="n">
-        <v>179.1992420724999</v>
+        <v>173.8750490219919</v>
       </c>
       <c r="Q63" t="n">
-        <v>201.8583612071749</v>
+        <v>205.8836946853814</v>
       </c>
       <c r="R63" t="n">
-        <v>22.65911913467492</v>
+        <v>32.00864566338954</v>
       </c>
       <c r="S63" t="n">
-        <v>179.1992420724999</v>
+        <v>173.8750490219919</v>
       </c>
       <c r="T63" t="n">
-        <v>201.8583612071749</v>
+        <v>205.8836946853814</v>
       </c>
     </row>
     <row r="64">
@@ -4367,61 +4367,61 @@
         <v>0.124</v>
       </c>
       <c r="B64" t="n">
-        <v>0.2724295348454476</v>
+        <v>0.2670494764825861</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.5762426864680328</v>
+        <v>-0.5634501064615477</v>
       </c>
       <c r="D64" t="n">
-        <v>-1.989107280653728</v>
+        <v>-2.014692440666698</v>
       </c>
       <c r="E64" t="n">
-        <v>2.107567313016659</v>
+        <v>2.036656914678298</v>
       </c>
       <c r="F64" t="n">
-        <v>-5.23246881566921</v>
+        <v>-5.038753320908832</v>
       </c>
       <c r="G64" t="n">
-        <v>10.46493763133881</v>
+        <v>10.07750664181626</v>
       </c>
       <c r="H64" t="n">
-        <v>-4.814227242964034</v>
+        <v>-6.880417131796579</v>
       </c>
       <c r="I64" t="n">
-        <v>17.73355275981946</v>
+        <v>17.79349770580784</v>
       </c>
       <c r="J64" t="n">
-        <v>-4.814227242964034</v>
+        <v>-9.339328752400089</v>
       </c>
       <c r="K64" t="n">
-        <v>17.73355275981946</v>
+        <v>17.93559054945745</v>
       </c>
       <c r="L64" t="n">
-        <v>35.81951722669086</v>
+        <v>35.27635895488158</v>
       </c>
       <c r="M64" t="n">
-        <v>119.4006217532613</v>
+        <v>117.5904799172575</v>
       </c>
       <c r="N64" t="n">
-        <v>101.4905284902721</v>
+        <v>99.95190792966888</v>
       </c>
       <c r="O64" t="n">
-        <v>25.2259004209834</v>
+        <v>34.68301701323287</v>
       </c>
       <c r="P64" t="n">
-        <v>185.5887798697682</v>
+        <v>179.3138189390733</v>
       </c>
       <c r="Q64" t="n">
-        <v>210.8146802907516</v>
+        <v>213.9968359523062</v>
       </c>
       <c r="R64" t="n">
-        <v>25.2259004209834</v>
+        <v>34.68301701323287</v>
       </c>
       <c r="S64" t="n">
-        <v>185.5887798697682</v>
+        <v>179.3138189390733</v>
       </c>
       <c r="T64" t="n">
-        <v>210.8146802907516</v>
+        <v>213.9968359523062</v>
       </c>
     </row>
     <row r="65">
@@ -4429,61 +4429,61 @@
         <v>0.126</v>
       </c>
       <c r="B65" t="n">
-        <v>0.2768735148807814</v>
+        <v>0.2713895868705221</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.5868781926015767</v>
+        <v>-0.5737673663219566</v>
       </c>
       <c r="D65" t="n">
-        <v>-1.96783626838664</v>
+        <v>-1.99405792094588</v>
       </c>
       <c r="E65" t="n">
-        <v>2.157455155080798</v>
+        <v>2.085097367730609</v>
       </c>
       <c r="F65" t="n">
-        <v>-5.413128979619969</v>
+        <v>-5.204580171881753</v>
       </c>
       <c r="G65" t="n">
-        <v>10.82625795924047</v>
+        <v>10.40916034376355</v>
       </c>
       <c r="H65" t="n">
-        <v>-5.181287364668253</v>
+        <v>-7.258367758691692</v>
       </c>
       <c r="I65" t="n">
-        <v>17.78411658302051</v>
+        <v>17.80423073978761</v>
       </c>
       <c r="J65" t="n">
-        <v>-5.181287364668253</v>
+        <v>-9.798202882569989</v>
       </c>
       <c r="K65" t="n">
-        <v>17.78411658302051</v>
+        <v>17.95099990063468</v>
       </c>
       <c r="L65" t="n">
-        <v>36.15507459412301</v>
+        <v>35.61390872738502</v>
       </c>
       <c r="M65" t="n">
-        <v>120.5188438036918</v>
+        <v>118.7156627388453</v>
       </c>
       <c r="N65" t="n">
-        <v>102.441017233138</v>
+        <v>100.9083133280185</v>
       </c>
       <c r="O65" t="n">
-        <v>28.08791993851895</v>
+        <v>37.8229026480638</v>
       </c>
       <c r="P65" t="n">
-        <v>192.5488101333324</v>
+        <v>185.3304032539194</v>
       </c>
       <c r="Q65" t="n">
-        <v>220.6367300718514</v>
+        <v>223.1533059019832</v>
       </c>
       <c r="R65" t="n">
-        <v>28.08791993851895</v>
+        <v>37.8229026480638</v>
       </c>
       <c r="S65" t="n">
-        <v>192.5488101333324</v>
+        <v>185.3304032539194</v>
       </c>
       <c r="T65" t="n">
-        <v>220.6367300718514</v>
+        <v>223.1533059019832</v>
       </c>
     </row>
     <row r="66">
@@ -4491,61 +4491,61 @@
         <v>0.128</v>
       </c>
       <c r="B66" t="n">
-        <v>0.2814338097301561</v>
+        <v>0.2757896598847113</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.5978643553829909</v>
+        <v>-0.5842647741602748</v>
       </c>
       <c r="D66" t="n">
-        <v>-1.945863942823811</v>
+        <v>-1.973063105269244</v>
       </c>
       <c r="E66" t="n">
-        <v>2.208655998982831</v>
+        <v>2.134032084769191</v>
       </c>
       <c r="F66" t="n">
-        <v>-5.610449411132377</v>
+        <v>-5.375475871833284</v>
       </c>
       <c r="G66" t="n">
-        <v>11.22089882226411</v>
+        <v>10.75095174366823</v>
       </c>
       <c r="H66" t="n">
-        <v>-5.585069454682166</v>
+        <v>-7.650504628311842</v>
       </c>
       <c r="I66" t="n">
-        <v>17.85007586786207</v>
+        <v>17.81819086438668</v>
       </c>
       <c r="J66" t="n">
-        <v>-5.585069454682166</v>
+        <v>-10.27373685376648</v>
       </c>
       <c r="K66" t="n">
-        <v>17.85007586786207</v>
+        <v>17.9697792839724</v>
       </c>
       <c r="L66" t="n">
-        <v>36.54411084347186</v>
+        <v>35.96757748564654</v>
       </c>
       <c r="M66" t="n">
-        <v>121.8159620429439</v>
+        <v>119.8945826090823</v>
       </c>
       <c r="N66" t="n">
-        <v>103.5435677365023</v>
+        <v>101.91039521772</v>
       </c>
       <c r="O66" t="n">
-        <v>31.36058503331165</v>
+        <v>41.1411602032975</v>
       </c>
       <c r="P66" t="n">
-        <v>200.3023358976969</v>
+        <v>191.5636008140847</v>
       </c>
       <c r="Q66" t="n">
-        <v>231.6629209310086</v>
+        <v>232.7047610173822</v>
       </c>
       <c r="R66" t="n">
-        <v>31.36058503331165</v>
+        <v>41.1411602032975</v>
       </c>
       <c r="S66" t="n">
-        <v>200.3023358976969</v>
+        <v>191.5636008140847</v>
       </c>
       <c r="T66" t="n">
-        <v>231.6629209310086</v>
+        <v>232.7047610173822</v>
       </c>
     </row>
     <row r="67">
@@ -4553,61 +4553,61 @@
         <v>0.13</v>
       </c>
       <c r="B67" t="n">
-        <v>0.2861706166115277</v>
+        <v>0.2803591999507932</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.6093903341066917</v>
+        <v>-0.595278575969189</v>
       </c>
       <c r="D67" t="n">
-        <v>-1.92281198537641</v>
+        <v>-1.951035501651415</v>
       </c>
       <c r="E67" t="n">
-        <v>2.261799011072138</v>
+        <v>2.184413521105603</v>
       </c>
       <c r="F67" t="n">
-        <v>-5.831136978395296</v>
+        <v>-5.561308691944728</v>
       </c>
       <c r="G67" t="n">
-        <v>11.66227395679042</v>
+        <v>11.12261738388865</v>
       </c>
       <c r="H67" t="n">
-        <v>-6.007429389259598</v>
+        <v>-8.069890010481176</v>
       </c>
       <c r="I67" t="n">
-        <v>17.9282478279006</v>
+        <v>17.83243409105551</v>
       </c>
       <c r="J67" t="n">
-        <v>-6.007429389259598</v>
+        <v>-10.7838086521502</v>
       </c>
       <c r="K67" t="n">
-        <v>17.9282478279006</v>
+        <v>17.98926299616834</v>
       </c>
       <c r="L67" t="n">
-        <v>37.02648866459535</v>
+        <v>36.37196964090396</v>
       </c>
       <c r="M67" t="n">
-        <v>123.423602667166</v>
+        <v>121.2415191834251</v>
       </c>
       <c r="N67" t="n">
-        <v>104.9100622670911</v>
+        <v>103.0552913059113</v>
       </c>
       <c r="O67" t="n">
-        <v>35.09591460243755</v>
+        <v>44.92750653129957</v>
       </c>
       <c r="P67" t="n">
-        <v>209.109283552153</v>
+        <v>198.3466260379575</v>
       </c>
       <c r="Q67" t="n">
-        <v>244.2051981545906</v>
+        <v>243.2741325692571</v>
       </c>
       <c r="R67" t="n">
-        <v>35.09591460243755</v>
+        <v>44.92750653129957</v>
       </c>
       <c r="S67" t="n">
-        <v>209.109283552153</v>
+        <v>198.3466260379575</v>
       </c>
       <c r="T67" t="n">
-        <v>244.2051981545906</v>
+        <v>243.2741325692571</v>
       </c>
     </row>
     <row r="68">
@@ -4615,61 +4615,61 @@
         <v>0.132</v>
       </c>
       <c r="B68" t="n">
-        <v>0.2909908094973953</v>
+        <v>0.2850225955978436</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.6211740141049246</v>
+        <v>-0.6065872058690966</v>
       </c>
       <c r="D68" t="n">
-        <v>-1.899244625379944</v>
+        <v>-1.9284182418516</v>
       </c>
       <c r="E68" t="n">
-        <v>2.315786657096758</v>
+        <v>2.235550308043351</v>
       </c>
       <c r="F68" t="n">
-        <v>-6.061408232110679</v>
+        <v>-5.754409911684292</v>
       </c>
       <c r="G68" t="n">
-        <v>12.12281646422195</v>
+        <v>11.50881982336761</v>
       </c>
       <c r="H68" t="n">
-        <v>-6.431555304160784</v>
+        <v>-8.502480549622028</v>
       </c>
       <c r="I68" t="n">
-        <v>17.99986815231951</v>
+        <v>17.83767070821566</v>
       </c>
       <c r="J68" t="n">
-        <v>-6.431555304160784</v>
+        <v>-11.31063258652396</v>
       </c>
       <c r="K68" t="n">
-        <v>17.99986815231951</v>
+        <v>17.99994506772514</v>
       </c>
       <c r="L68" t="n">
-        <v>37.55079185189283</v>
+        <v>36.80377873042038</v>
       </c>
       <c r="M68" t="n">
-        <v>125.1707744506095</v>
+        <v>122.6801427368905</v>
       </c>
       <c r="N68" t="n">
-        <v>106.3951582830181</v>
+        <v>104.2781213263569</v>
       </c>
       <c r="O68" t="n">
-        <v>39.00305123479696</v>
+        <v>48.97708639655795</v>
       </c>
       <c r="P68" t="n">
-        <v>218.2091053501953</v>
+        <v>205.289267249356</v>
       </c>
       <c r="Q68" t="n">
-        <v>257.2121565849923</v>
+        <v>254.266353645914</v>
       </c>
       <c r="R68" t="n">
-        <v>39.00305123479696</v>
+        <v>48.97708639655795</v>
       </c>
       <c r="S68" t="n">
-        <v>218.2091053501953</v>
+        <v>205.289267249356</v>
       </c>
       <c r="T68" t="n">
-        <v>257.2121565849923</v>
+        <v>254.266353645914</v>
       </c>
     </row>
     <row r="69">
@@ -4677,61 +4677,61 @@
         <v>0.134</v>
       </c>
       <c r="B69" t="n">
-        <v>0.2960295177983928</v>
+        <v>0.2897995858746146</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.6336448654397457</v>
+        <v>-0.6182526700401471</v>
       </c>
       <c r="D69" t="n">
-        <v>-1.874302922710302</v>
+        <v>-1.905087313509499</v>
       </c>
       <c r="E69" t="n">
-        <v>2.371666130838372</v>
+        <v>2.287601305633062</v>
       </c>
       <c r="F69" t="n">
-        <v>-6.310372010591236</v>
+        <v>-5.956308169979229</v>
       </c>
       <c r="G69" t="n">
-        <v>12.62074402118244</v>
+        <v>11.9126163399601</v>
       </c>
       <c r="H69" t="n">
-        <v>-6.829371720333145</v>
+        <v>-8.951053461905758</v>
       </c>
       <c r="I69" t="n">
-        <v>17.9999461454927</v>
+        <v>17.83200650880616</v>
       </c>
       <c r="J69" t="n">
-        <v>-6.829371720333145</v>
+        <v>-11.85773184885562</v>
       </c>
       <c r="K69" t="n">
-        <v>17.9999461454927</v>
+        <v>17.99997439919959</v>
       </c>
       <c r="L69" t="n">
-        <v>38.17538484176271</v>
+        <v>37.2687708918765</v>
       </c>
       <c r="M69" t="n">
-        <v>127.2519823668959</v>
+        <v>124.2297362330715</v>
       </c>
       <c r="N69" t="n">
-        <v>108.1641850118615</v>
+        <v>105.5952757981108</v>
       </c>
       <c r="O69" t="n">
-        <v>43.15405722960605</v>
+        <v>53.34526123385822</v>
       </c>
       <c r="P69" t="n">
-        <v>227.1727355105025</v>
+        <v>212.4250937653827</v>
       </c>
       <c r="Q69" t="n">
-        <v>270.3267927401086</v>
+        <v>265.7703549992409</v>
       </c>
       <c r="R69" t="n">
-        <v>43.15405722960605</v>
+        <v>53.34526123385822</v>
       </c>
       <c r="S69" t="n">
-        <v>227.1727355105025</v>
+        <v>212.4250937653827</v>
       </c>
       <c r="T69" t="n">
-        <v>270.3267927401086</v>
+        <v>265.7703549992409</v>
       </c>
     </row>
     <row r="70">
@@ -4739,61 +4739,61 @@
         <v>0.136</v>
       </c>
       <c r="B70" t="n">
-        <v>0.3011903626498733</v>
+        <v>0.2947433251238878</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.6465178482192488</v>
+        <v>-0.6304623880850567</v>
       </c>
       <c r="D70" t="n">
-        <v>-1.848556957151295</v>
+        <v>-1.88066787741968</v>
       </c>
       <c r="E70" t="n">
-        <v>2.428417619438381</v>
+        <v>2.340976355362255</v>
       </c>
       <c r="F70" t="n">
-        <v>-6.565707570984753</v>
+        <v>-6.170413920704739</v>
       </c>
       <c r="G70" t="n">
-        <v>13.13141514196935</v>
+        <v>12.34082784140967</v>
       </c>
       <c r="H70" t="n">
-        <v>-7.244592133065285</v>
+        <v>-9.435278582713964</v>
       </c>
       <c r="I70" t="n">
-        <v>17.99998880298596</v>
+        <v>17.82597957378983</v>
       </c>
       <c r="J70" t="n">
-        <v>-7.244592133065285</v>
+        <v>-12.44644057601788</v>
       </c>
       <c r="K70" t="n">
-        <v>17.99998880298596</v>
+        <v>17.99998524635371</v>
       </c>
       <c r="L70" t="n">
-        <v>38.84319917631493</v>
+        <v>37.77990365736019</v>
       </c>
       <c r="M70" t="n">
-        <v>129.477585234741</v>
+        <v>125.9333382095497</v>
       </c>
       <c r="N70" t="n">
-        <v>110.0559474495299</v>
+        <v>107.0433374781172</v>
       </c>
       <c r="O70" t="n">
-        <v>47.62948477895475</v>
+        <v>58.29513813624651</v>
       </c>
       <c r="P70" t="n">
-        <v>236.365326696299</v>
+        <v>219.9854713257431</v>
       </c>
       <c r="Q70" t="n">
-        <v>283.9948114752538</v>
+        <v>278.2806094619896</v>
       </c>
       <c r="R70" t="n">
-        <v>47.62948477895475</v>
+        <v>58.29513813624651</v>
       </c>
       <c r="S70" t="n">
-        <v>236.365326696299</v>
+        <v>219.9854713257431</v>
       </c>
       <c r="T70" t="n">
-        <v>283.9948114752538</v>
+        <v>278.2806094619896</v>
       </c>
     </row>
     <row r="71">
@@ -4801,61 +4801,61 @@
         <v>0.138</v>
       </c>
       <c r="B71" t="n">
-        <v>0.306484806591138</v>
+        <v>0.2997567678188246</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.6598307025586638</v>
+        <v>-0.642902596213925</v>
       </c>
       <c r="D71" t="n">
-        <v>-1.821931248472465</v>
+        <v>-1.855787461161943</v>
       </c>
       <c r="E71" t="n">
-        <v>2.486122961662872</v>
+        <v>2.394919731865988</v>
       </c>
       <c r="F71" t="n">
-        <v>-6.828012906277844</v>
+        <v>-6.389849738535599</v>
       </c>
       <c r="G71" t="n">
-        <v>13.65602581255595</v>
+        <v>12.77969947706922</v>
       </c>
       <c r="H71" t="n">
-        <v>-7.678849910859745</v>
+        <v>-9.936604885617225</v>
       </c>
       <c r="I71" t="n">
-        <v>17.99999280853878</v>
+        <v>17.81979655084161</v>
       </c>
       <c r="J71" t="n">
-        <v>-7.678849910859745</v>
+        <v>-13.0548515580226</v>
       </c>
       <c r="K71" t="n">
-        <v>17.99999280853878</v>
+        <v>17.99999031346828</v>
       </c>
       <c r="L71" t="n">
-        <v>39.55829118725462</v>
+        <v>38.31043114349969</v>
       </c>
       <c r="M71" t="n">
-        <v>131.8611345487681</v>
+        <v>127.7016567792166</v>
       </c>
       <c r="N71" t="n">
-        <v>112.0819643664529</v>
+        <v>108.5464082623341</v>
       </c>
       <c r="O71" t="n">
-        <v>52.4597809095884</v>
+        <v>63.51281447157047</v>
       </c>
       <c r="P71" t="n">
-        <v>245.8083669448903</v>
+        <v>227.7311879914317</v>
       </c>
       <c r="Q71" t="n">
-        <v>298.2681478544787</v>
+        <v>291.2440024630022</v>
       </c>
       <c r="R71" t="n">
-        <v>52.4597809095884</v>
+        <v>63.51281447157047</v>
       </c>
       <c r="S71" t="n">
-        <v>245.8083669448903</v>
+        <v>227.7311879914317</v>
       </c>
       <c r="T71" t="n">
-        <v>298.2681478544787</v>
+        <v>291.2440024630022</v>
       </c>
     </row>
     <row r="72">
@@ -4863,61 +4863,61 @@
         <v>0.14</v>
       </c>
       <c r="B72" t="n">
-        <v>0.3119916740907785</v>
+        <v>0.3049737336290836</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.6738844738284002</v>
+        <v>-0.6560368913117827</v>
       </c>
       <c r="D72" t="n">
-        <v>-1.793823705932993</v>
+        <v>-1.829518870966228</v>
       </c>
       <c r="E72" t="n">
-        <v>2.545591761304871</v>
+        <v>2.450627520764653</v>
       </c>
       <c r="F72" t="n">
-        <v>-7.104412687999108</v>
+        <v>-6.626454069613255</v>
       </c>
       <c r="G72" t="n">
-        <v>14.20882537599828</v>
+        <v>13.25290813922713</v>
       </c>
       <c r="H72" t="n">
-        <v>-8.190975642050285</v>
+        <v>-10.50339956351187</v>
       </c>
       <c r="I72" t="n">
-        <v>17.9999944799633</v>
+        <v>17.81312625788139</v>
       </c>
       <c r="J72" t="n">
-        <v>-8.190975642050285</v>
+        <v>-13.73710914948314</v>
       </c>
       <c r="K72" t="n">
-        <v>17.9999944799633</v>
+        <v>17.99999226264449</v>
       </c>
       <c r="L72" t="n">
-        <v>40.34113063604675</v>
+        <v>38.89834649013427</v>
       </c>
       <c r="M72" t="n">
-        <v>134.4705631618231</v>
+        <v>129.6613326300466</v>
       </c>
       <c r="N72" t="n">
-        <v>114.2999786875496</v>
+        <v>110.2121327355396</v>
       </c>
       <c r="O72" t="n">
-        <v>58.29204650736403</v>
+        <v>69.68657395728356</v>
       </c>
       <c r="P72" t="n">
-        <v>255.7587787875487</v>
+        <v>236.0736952244141</v>
       </c>
       <c r="Q72" t="n">
-        <v>314.0508252949127</v>
+        <v>305.7602691816977</v>
       </c>
       <c r="R72" t="n">
-        <v>58.29204650736403</v>
+        <v>69.68657395728356</v>
       </c>
       <c r="S72" t="n">
-        <v>255.7587787875487</v>
+        <v>236.0736952244141</v>
       </c>
       <c r="T72" t="n">
-        <v>314.0508252949127</v>
+        <v>305.7602691816977</v>
       </c>
     </row>
     <row r="73">
@@ -4925,61 +4925,61 @@
         <v>0.142</v>
       </c>
       <c r="B73" t="n">
-        <v>0.3175893347037473</v>
+        <v>0.3102864763108083</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.6882654517071023</v>
+        <v>-0.6695136129864432</v>
       </c>
       <c r="D73" t="n">
-        <v>-1.765061750175589</v>
+        <v>-1.802565427616907</v>
       </c>
       <c r="E73" t="n">
-        <v>2.605884223267829</v>
+        <v>2.507247582518535</v>
       </c>
       <c r="F73" t="n">
-        <v>-7.388010454026085</v>
+        <v>-6.872638860031232</v>
       </c>
       <c r="G73" t="n">
-        <v>14.77602090805201</v>
+        <v>13.74527772006357</v>
       </c>
       <c r="H73" t="n">
-        <v>-8.733503201907633</v>
+        <v>-11.10132964040744</v>
       </c>
       <c r="I73" t="n">
-        <v>17.99999558094444</v>
+        <v>17.80618529328926</v>
       </c>
       <c r="J73" t="n">
-        <v>-8.733503201907633</v>
+        <v>-14.45517740410268</v>
       </c>
       <c r="K73" t="n">
-        <v>17.99999558094444</v>
+        <v>17.99999370914215</v>
       </c>
       <c r="L73" t="n">
-        <v>41.15231403582511</v>
+        <v>39.5146312902674</v>
       </c>
       <c r="M73" t="n">
-        <v>137.1744840376584</v>
+        <v>131.7155829255576</v>
       </c>
       <c r="N73" t="n">
-        <v>116.5983114320096</v>
+        <v>111.958245486724</v>
       </c>
       <c r="O73" t="n">
-        <v>64.57264774961223</v>
+        <v>76.38251325035063</v>
       </c>
       <c r="P73" t="n">
-        <v>265.9683111596771</v>
+        <v>244.748975547881</v>
       </c>
       <c r="Q73" t="n">
-        <v>330.5409589092893</v>
+        <v>321.1314887982317</v>
       </c>
       <c r="R73" t="n">
-        <v>64.57264774961223</v>
+        <v>76.38251325035063</v>
       </c>
       <c r="S73" t="n">
-        <v>265.9683111596771</v>
+        <v>244.748975547881</v>
       </c>
       <c r="T73" t="n">
-        <v>330.5409589092893</v>
+        <v>321.1314887982317</v>
       </c>
     </row>
     <row r="74">
@@ -4987,61 +4987,61 @@
         <v>0.144</v>
       </c>
       <c r="B74" t="n">
-        <v>0.3233979130859818</v>
+        <v>0.3157368714930716</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.7034288387593461</v>
+        <v>-0.6834824772193905</v>
       </c>
       <c r="D74" t="n">
-        <v>-1.734734976071101</v>
+        <v>-1.774627699151012</v>
       </c>
       <c r="E74" t="n">
-        <v>2.668238168178816</v>
+        <v>2.565178781687666</v>
       </c>
       <c r="F74" t="n">
-        <v>-7.690814796007821</v>
+        <v>-7.132592884757275</v>
       </c>
       <c r="G74" t="n">
-        <v>15.38162959201575</v>
+        <v>14.2651857695131</v>
       </c>
       <c r="H74" t="n">
-        <v>-9.340558021341767</v>
+        <v>-11.74400815669304</v>
       </c>
       <c r="I74" t="n">
-        <v>17.99999626124104</v>
+        <v>17.79885531382967</v>
       </c>
       <c r="J74" t="n">
-        <v>-9.340558021341767</v>
+        <v>-15.22471348445459</v>
       </c>
       <c r="K74" t="n">
-        <v>17.99999626124104</v>
+        <v>17.99999443317981</v>
       </c>
       <c r="L74" t="n">
-        <v>42.02804560553113</v>
+        <v>40.1716892557089</v>
       </c>
       <c r="M74" t="n">
-        <v>140.0935713307409</v>
+        <v>133.9057575689637</v>
       </c>
       <c r="N74" t="n">
-        <v>119.0795356311298</v>
+        <v>113.8198939336191</v>
       </c>
       <c r="O74" t="n">
-        <v>71.93727027671989</v>
+        <v>83.82894016232953</v>
       </c>
       <c r="P74" t="n">
-        <v>276.8692753739306</v>
+        <v>253.9025242394437</v>
       </c>
       <c r="Q74" t="n">
-        <v>348.8065456506505</v>
+        <v>337.7314644017732</v>
       </c>
       <c r="R74" t="n">
-        <v>71.93727027671989</v>
+        <v>83.82894016232953</v>
       </c>
       <c r="S74" t="n">
-        <v>276.8692753739306</v>
+        <v>253.9025242394437</v>
       </c>
       <c r="T74" t="n">
-        <v>348.8065456506505</v>
+        <v>337.7314644017732</v>
       </c>
     </row>
     <row r="75">
@@ -5049,61 +5049,61 @@
         <v>0.146</v>
       </c>
       <c r="B75" t="n">
-        <v>0.3293495043775924</v>
+        <v>0.3213663764289975</v>
       </c>
       <c r="C75" t="n">
-        <v>-0.7191571863363891</v>
+        <v>-0.6981247379889154</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.703278280917015</v>
+        <v>-1.745343177611962</v>
       </c>
       <c r="E75" t="n">
-        <v>2.732221153564494</v>
+        <v>2.624973862139448</v>
       </c>
       <c r="F75" t="n">
-        <v>-8.011500084231011</v>
+        <v>-7.413886530796536</v>
       </c>
       <c r="G75" t="n">
-        <v>16.02300016846212</v>
+        <v>14.82777306159275</v>
       </c>
       <c r="H75" t="n">
-        <v>-10.02736735726269</v>
+        <v>-12.46201546510147</v>
       </c>
       <c r="I75" t="n">
-        <v>17.9999966387056</v>
+        <v>17.790922145611</v>
       </c>
       <c r="J75" t="n">
-        <v>-10.02736735726269</v>
+        <v>-16.07999209213018</v>
       </c>
       <c r="K75" t="n">
-        <v>17.9999966387056</v>
+        <v>17.99999374577945</v>
       </c>
       <c r="L75" t="n">
-        <v>42.94981436194838</v>
+        <v>40.87259027458617</v>
       </c>
       <c r="M75" t="n">
-        <v>143.1661236659026</v>
+        <v>136.2862701238077</v>
       </c>
       <c r="N75" t="n">
-        <v>121.6912051160172</v>
+        <v>115.8433296052366</v>
       </c>
       <c r="O75" t="n">
-        <v>80.48560641032314</v>
+        <v>92.54166503248888</v>
       </c>
       <c r="P75" t="n">
-        <v>288.413949220883</v>
+        <v>263.7964822607657</v>
       </c>
       <c r="Q75" t="n">
-        <v>368.8995556312061</v>
+        <v>356.3381472932546</v>
       </c>
       <c r="R75" t="n">
-        <v>80.48560641032314</v>
+        <v>92.54166503248888</v>
       </c>
       <c r="S75" t="n">
-        <v>288.413949220883</v>
+        <v>263.7964822607657</v>
       </c>
       <c r="T75" t="n">
-        <v>368.8995556312061</v>
+        <v>356.3381472932546</v>
       </c>
     </row>
     <row r="76">
@@ -5111,61 +5111,61 @@
         <v>0.148</v>
       </c>
       <c r="B76" t="n">
-        <v>0.3354244382908534</v>
+        <v>0.3270745231870421</v>
       </c>
       <c r="C76" t="n">
-        <v>-0.7353727886134571</v>
+        <v>-0.7130658213930433</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.670847076362879</v>
+        <v>-1.715461010803707</v>
       </c>
       <c r="E76" t="n">
-        <v>2.797609117869904</v>
+        <v>2.685559196555364</v>
       </c>
       <c r="F76" t="n">
-        <v>-8.347606936819492</v>
+        <v>-7.704113114238487</v>
       </c>
       <c r="G76" t="n">
-        <v>16.69521387363882</v>
+        <v>15.4082262284789</v>
       </c>
       <c r="H76" t="n">
-        <v>-10.78296161053725</v>
+        <v>-13.19004395190698</v>
       </c>
       <c r="I76" t="n">
-        <v>17.99999675499025</v>
+        <v>17.78273662940292</v>
       </c>
       <c r="J76" t="n">
-        <v>-10.78296161053725</v>
+        <v>-16.94965115165536</v>
       </c>
       <c r="K76" t="n">
-        <v>17.99999675499025</v>
+        <v>17.99999261922447</v>
       </c>
       <c r="L76" t="n">
-        <v>43.91128825636432</v>
+        <v>41.54134912615572</v>
       </c>
       <c r="M76" t="n">
-        <v>146.3710331477324</v>
+        <v>138.7452746283815</v>
       </c>
       <c r="N76" t="n">
-        <v>124.4153781755726</v>
+        <v>117.9334834341243</v>
       </c>
       <c r="O76" t="n">
-        <v>90.05484576270112</v>
+        <v>101.6269892469588</v>
       </c>
       <c r="P76" t="n">
-        <v>300.5137955625778</v>
+        <v>273.9999961559246</v>
       </c>
       <c r="Q76" t="n">
-        <v>390.5686413252789</v>
+        <v>375.6269854028833</v>
       </c>
       <c r="R76" t="n">
-        <v>90.05484576270112</v>
+        <v>101.6269892469588</v>
       </c>
       <c r="S76" t="n">
-        <v>300.5137955625778</v>
+        <v>273.9999961559246</v>
       </c>
       <c r="T76" t="n">
-        <v>390.5686413252789</v>
+        <v>375.6269854028833</v>
       </c>
     </row>
     <row r="77">
@@ -5173,61 +5173,61 @@
         <v>0.15</v>
       </c>
       <c r="B77" t="n">
-        <v>0.3417498690762725</v>
+        <v>0.3330211807508452</v>
       </c>
       <c r="C77" t="n">
-        <v>-0.7526418330291491</v>
+        <v>-0.7289649903741631</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.636308987531495</v>
+        <v>-1.683662672841467</v>
       </c>
       <c r="E77" t="n">
-        <v>2.866239626282573</v>
+        <v>2.748079475934381</v>
       </c>
       <c r="F77" t="n">
-        <v>-8.725075037548031</v>
+        <v>-8.01426152982758</v>
       </c>
       <c r="G77" t="n">
-        <v>17.45015007509604</v>
+        <v>16.02852305965467</v>
       </c>
       <c r="H77" t="n">
-        <v>-11.66509250350942</v>
+        <v>-13.56989282114349</v>
       </c>
       <c r="I77" t="n">
-        <v>17.99999561759741</v>
+        <v>17.77399095079563</v>
       </c>
       <c r="J77" t="n">
-        <v>-11.66509250350942</v>
+        <v>-17.48085244769934</v>
       </c>
       <c r="K77" t="n">
-        <v>17.99999561759741</v>
+        <v>17.99999312593676</v>
       </c>
       <c r="L77" t="n">
-        <v>44.95722919864489</v>
+        <v>41.26868532091316</v>
       </c>
       <c r="M77" t="n">
-        <v>149.8800573181579</v>
+        <v>141.3589170492828</v>
       </c>
       <c r="N77" t="n">
-        <v>127.3980487204342</v>
+        <v>120.1550794918903</v>
       </c>
       <c r="O77" t="n">
-        <v>102.0101742687919</v>
+        <v>108.8307431839328</v>
       </c>
       <c r="P77" t="n">
-        <v>314.1026242120655</v>
+        <v>284.8872286872443</v>
       </c>
       <c r="Q77" t="n">
-        <v>416.1127984808574</v>
+        <v>393.7179718711771</v>
       </c>
       <c r="R77" t="n">
-        <v>102.0101742687919</v>
+        <v>108.8307431839328</v>
       </c>
       <c r="S77" t="n">
-        <v>314.1026242120655</v>
+        <v>284.8872286872443</v>
       </c>
       <c r="T77" t="n">
-        <v>416.1127984808574</v>
+        <v>393.7179718711771</v>
       </c>
     </row>
     <row r="78">
@@ -5235,61 +5235,61 @@
         <v>0.152</v>
       </c>
       <c r="B78" t="n">
-        <v>0.3481767459574294</v>
+        <v>0.3390530388565615</v>
       </c>
       <c r="C78" t="n">
-        <v>-0.7703625275589185</v>
+        <v>-0.7452470097957196</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.600867598471956</v>
+        <v>-1.651098633998354</v>
       </c>
       <c r="E78" t="n">
-        <v>2.935991778622859</v>
+        <v>2.810827309355576</v>
       </c>
       <c r="F78" t="n">
-        <v>-9.116822112776298</v>
+        <v>-8.323818962768243</v>
       </c>
       <c r="G78" t="n">
-        <v>18.23364422555268</v>
+        <v>16.64763792553535</v>
       </c>
       <c r="H78" t="n">
-        <v>-12.43423396705476</v>
+        <v>-13.79465115327994</v>
       </c>
       <c r="I78" t="n">
-        <v>17.99999445633618</v>
+        <v>17.76526187975375</v>
       </c>
       <c r="J78" t="n">
-        <v>-12.43423396705476</v>
+        <v>-17.85667480711084</v>
       </c>
       <c r="K78" t="n">
-        <v>17.99999445633618</v>
+        <v>17.9999935745038</v>
       </c>
       <c r="L78" t="n">
-        <v>45.67055974036791</v>
+        <v>40.58105600776774</v>
       </c>
       <c r="M78" t="n">
-        <v>153.4794872665986</v>
+        <v>143.927184131296</v>
       </c>
       <c r="N78" t="n">
-        <v>130.4575641766088</v>
+        <v>122.3381065116016</v>
       </c>
       <c r="O78" t="n">
-        <v>113.4136005387572</v>
+        <v>114.8180083448541</v>
       </c>
       <c r="P78" t="n">
-        <v>328.2054947625944</v>
+        <v>295.7470528633343</v>
       </c>
       <c r="Q78" t="n">
-        <v>441.6190953013515</v>
+        <v>410.5650612081884</v>
       </c>
       <c r="R78" t="n">
-        <v>113.4136005387572</v>
+        <v>114.8180083448541</v>
       </c>
       <c r="S78" t="n">
-        <v>328.2054947625944</v>
+        <v>295.7470528633343</v>
       </c>
       <c r="T78" t="n">
-        <v>441.6190953013515</v>
+        <v>410.5650612081884</v>
       </c>
     </row>
     <row r="79">
@@ -5297,61 +5297,61 @@
         <v>0.154</v>
       </c>
       <c r="B79" t="n">
-        <v>0.3548230608813375</v>
+        <v>0.3452311050320049</v>
       </c>
       <c r="C79" t="n">
-        <v>-0.7890839529091556</v>
+        <v>-0.7621860182766583</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.563424747771482</v>
+        <v>-1.617220617036477</v>
       </c>
       <c r="E79" t="n">
-        <v>3.007988289775849</v>
+        <v>2.873965636035599</v>
       </c>
       <c r="F79" t="n">
-        <v>-9.537109094058069</v>
+        <v>-8.632362242156248</v>
       </c>
       <c r="G79" t="n">
-        <v>19.07421818811608</v>
+        <v>17.26472448431377</v>
       </c>
       <c r="H79" t="n">
-        <v>-12.80300972227034</v>
+        <v>-13.7532669521278</v>
       </c>
       <c r="I79" t="n">
-        <v>17.99999370290919</v>
+        <v>17.75656130806206</v>
       </c>
       <c r="J79" t="n">
-        <v>-12.80300972227034</v>
+        <v>-17.96585972630005</v>
       </c>
       <c r="K79" t="n">
-        <v>17.99999370290919</v>
+        <v>17.99999392329088</v>
       </c>
       <c r="L79" t="n">
-        <v>45.31608716988821</v>
+        <v>39.18132669441793</v>
       </c>
       <c r="M79" t="n">
-        <v>157.2433700358147</v>
+        <v>146.4175850335518</v>
       </c>
       <c r="N79" t="n">
-        <v>133.6568645304424</v>
+        <v>124.454947278519</v>
       </c>
       <c r="O79" t="n">
-        <v>122.1814920097614</v>
+        <v>118.7177225137576</v>
       </c>
       <c r="P79" t="n">
-        <v>343.3358069561415</v>
+        <v>306.5598430344454</v>
       </c>
       <c r="Q79" t="n">
-        <v>465.5172989659029</v>
+        <v>425.277565548203</v>
       </c>
       <c r="R79" t="n">
-        <v>122.1814920097614</v>
+        <v>118.7177225137576</v>
       </c>
       <c r="S79" t="n">
-        <v>343.3358069561415</v>
+        <v>306.5598430344454</v>
       </c>
       <c r="T79" t="n">
-        <v>465.5172989659029</v>
+        <v>425.277565548203</v>
       </c>
     </row>
     <row r="80">
@@ -5359,61 +5359,61 @@
         <v>0.156</v>
       </c>
       <c r="B80" t="n">
-        <v>0.361629589976217</v>
+        <v>0.3515397020904036</v>
       </c>
       <c r="C80" t="n">
-        <v>-0.8086435359588727</v>
+        <v>-0.7798278047060888</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.524305581672048</v>
+        <v>-1.581937044177616</v>
       </c>
       <c r="E80" t="n">
-        <v>3.080754383277951</v>
+        <v>2.937019819532513</v>
       </c>
       <c r="F80" t="n">
-        <v>-9.965129112984025</v>
+        <v>-8.93481805005055</v>
       </c>
       <c r="G80" t="n">
-        <v>19.93025822596792</v>
+        <v>17.86963610010143</v>
       </c>
       <c r="H80" t="n">
-        <v>-12.90688446854577</v>
+        <v>-13.63979347940319</v>
       </c>
       <c r="I80" t="n">
-        <v>17.99999047694334</v>
+        <v>17.74803239852128</v>
       </c>
       <c r="J80" t="n">
-        <v>-12.90688446854577</v>
+        <v>-17.99998468782786</v>
       </c>
       <c r="K80" t="n">
-        <v>17.99999047694334</v>
+        <v>17.99999426753271</v>
       </c>
       <c r="L80" t="n">
-        <v>44.27001050234939</v>
+        <v>37.45910095133461</v>
       </c>
       <c r="M80" t="n">
-        <v>160.9337423077991</v>
+        <v>148.6398419091147</v>
       </c>
       <c r="N80" t="n">
-        <v>136.7936809616292</v>
+        <v>126.3438656227475</v>
       </c>
       <c r="O80" t="n">
-        <v>128.5982799715348</v>
+        <v>121.8391462643559</v>
       </c>
       <c r="P80" t="n">
-        <v>358.7444556105113</v>
+        <v>317.1474217836222</v>
       </c>
       <c r="Q80" t="n">
-        <v>487.342735582046</v>
+        <v>438.9865680479781</v>
       </c>
       <c r="R80" t="n">
-        <v>128.5982799715348</v>
+        <v>121.8391462643559</v>
       </c>
       <c r="S80" t="n">
-        <v>358.7444556105113</v>
+        <v>317.1474217836222</v>
       </c>
       <c r="T80" t="n">
-        <v>487.342735582046</v>
+        <v>438.9865680479781</v>
       </c>
     </row>
     <row r="81">
@@ -5421,61 +5421,61 @@
         <v>0.158</v>
       </c>
       <c r="B81" t="n">
-        <v>0.3685446031089627</v>
+        <v>0.3579086411099318</v>
       </c>
       <c r="C81" t="n">
-        <v>-0.8287706514001181</v>
+        <v>-0.7977959265154392</v>
       </c>
       <c r="D81" t="n">
-        <v>-1.484051350789557</v>
+        <v>-1.546000800558915</v>
       </c>
       <c r="E81" t="n">
-        <v>3.154041575508061</v>
+        <v>3.000035509497093</v>
       </c>
       <c r="F81" t="n">
-        <v>-10.39838531759521</v>
+        <v>-9.234527869766815</v>
       </c>
       <c r="G81" t="n">
-        <v>20.79677063519025</v>
+        <v>18.46905573953153</v>
       </c>
       <c r="H81" t="n">
-        <v>-12.83138974387881</v>
+        <v>-13.49353791480907</v>
       </c>
       <c r="I81" t="n">
-        <v>17.99998557677479</v>
+        <v>17.73958091769081</v>
       </c>
       <c r="J81" t="n">
-        <v>-12.83138974387881</v>
+        <v>-17.99998751525527</v>
       </c>
       <c r="K81" t="n">
-        <v>17.99998557677479</v>
+        <v>17.9999946036182</v>
       </c>
       <c r="L81" t="n">
-        <v>42.755635652454</v>
+        <v>35.58788253423769</v>
       </c>
       <c r="M81" t="n">
-        <v>164.5743392352127</v>
+        <v>150.7365936179974</v>
       </c>
       <c r="N81" t="n">
-        <v>139.8881883499307</v>
+        <v>128.1261045752978</v>
       </c>
       <c r="O81" t="n">
-        <v>133.4230913898105</v>
+        <v>124.6059448599063</v>
       </c>
       <c r="P81" t="n">
-        <v>374.3415711337749</v>
+        <v>327.6332501568734</v>
       </c>
       <c r="Q81" t="n">
-        <v>507.7646625235854</v>
+        <v>452.2391950167797</v>
       </c>
       <c r="R81" t="n">
-        <v>133.4230913898105</v>
+        <v>124.6059448599063</v>
       </c>
       <c r="S81" t="n">
-        <v>374.3415711337749</v>
+        <v>327.6332501568734</v>
       </c>
       <c r="T81" t="n">
-        <v>507.7646625235854</v>
+        <v>452.2391950167797</v>
       </c>
     </row>
     <row r="82">
@@ -5483,61 +5483,61 @@
         <v>0.16</v>
       </c>
       <c r="B82" t="n">
-        <v>0.3756570757401033</v>
+        <v>0.3644247553901814</v>
       </c>
       <c r="C82" t="n">
-        <v>-0.8502255540239015</v>
+        <v>-0.8167698766227397</v>
       </c>
       <c r="D82" t="n">
-        <v>-1.44114154554199</v>
+        <v>-1.508052900344314</v>
       </c>
       <c r="E82" t="n">
-        <v>3.226561059529679</v>
+        <v>3.063015654381504</v>
       </c>
       <c r="F82" t="n">
-        <v>-10.8152384816382</v>
+        <v>-9.537372882171189</v>
       </c>
       <c r="G82" t="n">
-        <v>21.63047696327658</v>
+        <v>19.07474576434285</v>
       </c>
       <c r="H82" t="n">
-        <v>-12.41250104741436</v>
+        <v>-13.34574793068564</v>
       </c>
       <c r="I82" t="n">
-        <v>17.7607611841712</v>
+        <v>17.7310401306996</v>
       </c>
       <c r="J82" t="n">
-        <v>-12.41250104741436</v>
+        <v>-17.99998589718518</v>
       </c>
       <c r="K82" t="n">
-        <v>17.7607611841712</v>
+        <v>17.99999404597683</v>
       </c>
       <c r="L82" t="n">
-        <v>40.82024978890213</v>
+        <v>33.36644842215731</v>
       </c>
       <c r="M82" t="n">
-        <v>167.6135683852596</v>
+        <v>152.3039483676611</v>
       </c>
       <c r="N82" t="n">
-        <v>142.4715331274707</v>
+        <v>129.458356112512</v>
       </c>
       <c r="O82" t="n">
-        <v>134.123726828288</v>
+        <v>127.2530064593334</v>
       </c>
       <c r="P82" t="n">
-        <v>384.034913203845</v>
+        <v>338.2115727015666</v>
       </c>
       <c r="Q82" t="n">
-        <v>518.1586400321331</v>
+        <v>465.4645791609</v>
       </c>
       <c r="R82" t="n">
-        <v>134.123726828288</v>
+        <v>127.2530064593334</v>
       </c>
       <c r="S82" t="n">
-        <v>384.034913203845</v>
+        <v>338.2115727015666</v>
       </c>
       <c r="T82" t="n">
-        <v>518.1586400321331</v>
+        <v>465.4645791609</v>
       </c>
     </row>
     <row r="83">
@@ -5545,61 +5545,61 @@
         <v>0.162</v>
       </c>
       <c r="B83" t="n">
-        <v>0.3828110550289994</v>
+        <v>0.3709797314289706</v>
       </c>
       <c r="C83" t="n">
-        <v>-0.8721344159618722</v>
+        <v>-0.8360869184457437</v>
       </c>
       <c r="D83" t="n">
-        <v>-1.397323821666049</v>
+        <v>-1.469418816698306</v>
       </c>
       <c r="E83" t="n">
-        <v>3.297887895186614</v>
+        <v>3.126028284318726</v>
       </c>
       <c r="F83" t="n">
-        <v>-11.21221502448452</v>
+        <v>-9.846861307848503</v>
       </c>
       <c r="G83" t="n">
-        <v>22.42443004896929</v>
+        <v>19.69372261569836</v>
       </c>
       <c r="H83" t="n">
-        <v>-11.89771796089602</v>
+        <v>-13.19471582187476</v>
       </c>
       <c r="I83" t="n">
-        <v>17.3863462364367</v>
+        <v>17.72230111397336</v>
       </c>
       <c r="J83" t="n">
-        <v>-11.89771796089602</v>
+        <v>-17.99998414010483</v>
       </c>
       <c r="K83" t="n">
-        <v>17.3863462364367</v>
+        <v>17.99998260285471</v>
       </c>
       <c r="L83" t="n">
-        <v>38.91535056786522</v>
+        <v>31.02292817011894</v>
       </c>
       <c r="M83" t="n">
-        <v>170.2094124919924</v>
+        <v>153.6766027110554</v>
       </c>
       <c r="N83" t="n">
-        <v>144.6780006181935</v>
+        <v>130.6251123043971</v>
       </c>
       <c r="O83" t="n">
-        <v>133.300147891681</v>
+        <v>129.9040178539308</v>
       </c>
       <c r="P83" t="n">
-        <v>389.6902677242841</v>
+        <v>349.0154700052937</v>
       </c>
       <c r="Q83" t="n">
-        <v>522.990415615965</v>
+        <v>478.9194878592244</v>
       </c>
       <c r="R83" t="n">
-        <v>133.300147891681</v>
+        <v>129.9040178539308</v>
       </c>
       <c r="S83" t="n">
-        <v>389.6902677242841</v>
+        <v>349.0154700052937</v>
       </c>
       <c r="T83" t="n">
-        <v>522.990415615965</v>
+        <v>478.9194878592244</v>
       </c>
     </row>
     <row r="84">
@@ -5607,61 +5607,61 @@
         <v>0.164</v>
       </c>
       <c r="B84" t="n">
-        <v>0.3900364651488606</v>
+        <v>0.3776150312338843</v>
       </c>
       <c r="C84" t="n">
-        <v>-0.8949268091449026</v>
+        <v>-0.8561131000443788</v>
       </c>
       <c r="D84" t="n">
-        <v>-1.351739035299988</v>
+        <v>-1.429366453501036</v>
       </c>
       <c r="E84" t="n">
-        <v>3.366558943373754</v>
+        <v>3.189108057943793</v>
       </c>
       <c r="F84" t="n">
-        <v>-11.56537407097752</v>
+        <v>-10.17008107235496</v>
       </c>
       <c r="G84" t="n">
-        <v>23.13074814195469</v>
+        <v>20.34016214470863</v>
       </c>
       <c r="H84" t="n">
-        <v>-11.20403400199143</v>
+        <v>-13.03698253239351</v>
       </c>
       <c r="I84" t="n">
-        <v>16.72960490122185</v>
+        <v>17.7131523741807</v>
       </c>
       <c r="J84" t="n">
-        <v>-11.20403400199143</v>
+        <v>-17.99998209570273</v>
       </c>
       <c r="K84" t="n">
-        <v>16.72960490122185</v>
+        <v>17.99994866042109</v>
       </c>
       <c r="L84" t="n">
-        <v>37.13252394529977</v>
+        <v>28.42706682695294</v>
       </c>
       <c r="M84" t="n">
-        <v>171.8567812270518</v>
+        <v>154.646828793732</v>
       </c>
       <c r="N84" t="n">
-        <v>146.078264042994</v>
+        <v>131.4498044746722</v>
       </c>
       <c r="O84" t="n">
-        <v>129.468950792352</v>
+        <v>132.5631931205559</v>
       </c>
       <c r="P84" t="n">
-        <v>386.7601953102478</v>
+        <v>360.285610085187</v>
       </c>
       <c r="Q84" t="n">
-        <v>516.2291461025997</v>
+        <v>492.8488032057429</v>
       </c>
       <c r="R84" t="n">
-        <v>129.468950792352</v>
+        <v>132.5631931205559</v>
       </c>
       <c r="S84" t="n">
-        <v>386.7601953102478</v>
+        <v>360.285610085187</v>
       </c>
       <c r="T84" t="n">
-        <v>516.2291461025997</v>
+        <v>492.8488032057429</v>
       </c>
     </row>
     <row r="85">
@@ -5669,61 +5669,61 @@
         <v>0.166</v>
       </c>
       <c r="B85" t="n">
-        <v>0.3972352221706624</v>
+        <v>0.3843051002153176</v>
       </c>
       <c r="C85" t="n">
-        <v>-0.9183763470045636</v>
+        <v>-0.8768452834095309</v>
       </c>
       <c r="D85" t="n">
-        <v>-1.304839959580666</v>
+        <v>-1.387902086770731</v>
       </c>
       <c r="E85" t="n">
-        <v>3.431019575769832</v>
+        <v>3.251190369255098</v>
       </c>
       <c r="F85" t="n">
-        <v>-11.85449555002054</v>
+        <v>-10.49618085688373</v>
       </c>
       <c r="G85" t="n">
-        <v>23.70899110004093</v>
+        <v>20.9923617137669</v>
       </c>
       <c r="H85" t="n">
-        <v>-10.4181345009429</v>
+        <v>-12.87781879768975</v>
       </c>
       <c r="I85" t="n">
-        <v>15.8688653261757</v>
+        <v>17.40614908024608</v>
       </c>
       <c r="J85" t="n">
-        <v>-10.4181345009429</v>
+        <v>-17.99995505584901</v>
       </c>
       <c r="K85" t="n">
-        <v>15.8688653261757</v>
+        <v>17.70214138041019</v>
       </c>
       <c r="L85" t="n">
-        <v>35.31705352680832</v>
+        <v>26.39123664161304</v>
       </c>
       <c r="M85" t="n">
-        <v>172.1294723613276</v>
+        <v>155.0574276387297</v>
       </c>
       <c r="N85" t="n">
-        <v>146.3100515071285</v>
+        <v>131.7988134929203</v>
       </c>
       <c r="O85" t="n">
-        <v>123.3632000629285</v>
+        <v>135.1328945553871</v>
       </c>
       <c r="P85" t="n">
-        <v>375.9133769345344</v>
+        <v>365.1900668852797</v>
       </c>
       <c r="Q85" t="n">
-        <v>499.2765769974629</v>
+        <v>500.3229614406667</v>
       </c>
       <c r="R85" t="n">
-        <v>123.3632000629285</v>
+        <v>135.1328945553871</v>
       </c>
       <c r="S85" t="n">
-        <v>375.9133769345344</v>
+        <v>365.1900668852797</v>
       </c>
       <c r="T85" t="n">
-        <v>499.2765769974629</v>
+        <v>500.3229614406667</v>
       </c>
     </row>
     <row r="86">
@@ -5731,61 +5731,61 @@
         <v>0.168</v>
       </c>
       <c r="B86" t="n">
-        <v>0.4044182918464533</v>
+        <v>0.3910252668942307</v>
       </c>
       <c r="C86" t="n">
-        <v>-0.9421768514509978</v>
+        <v>-0.8979654409773151</v>
       </c>
       <c r="D86" t="n">
-        <v>-1.257238950687798</v>
+        <v>-1.345661771635163</v>
       </c>
       <c r="E86" t="n">
-        <v>3.493197349875389</v>
+        <v>3.312724537963663</v>
       </c>
       <c r="F86" t="n">
-        <v>-12.10901787327401</v>
+        <v>-10.82386331942369</v>
       </c>
       <c r="G86" t="n">
-        <v>24.21803574654846</v>
+        <v>21.64772663884938</v>
       </c>
       <c r="H86" t="n">
-        <v>-9.582985312258895</v>
+        <v>-12.71786898018714</v>
       </c>
       <c r="I86" t="n">
-        <v>14.89890527771501</v>
+        <v>16.93546364184089</v>
       </c>
       <c r="J86" t="n">
-        <v>-9.582985312258895</v>
+        <v>-17.9999142800659</v>
       </c>
       <c r="K86" t="n">
-        <v>14.89890527771501</v>
+        <v>17.24069658744867</v>
       </c>
       <c r="L86" t="n">
-        <v>33.4836749754689</v>
+        <v>24.66316438580148</v>
       </c>
       <c r="M86" t="n">
-        <v>171.6567472111905</v>
+        <v>155.160490523328</v>
       </c>
       <c r="N86" t="n">
-        <v>145.9082351295119</v>
+        <v>131.8864169448288</v>
       </c>
       <c r="O86" t="n">
-        <v>116.0386173915722</v>
+        <v>137.6534267951919</v>
       </c>
       <c r="P86" t="n">
-        <v>360.8172256416406</v>
+        <v>366.5963442022358</v>
       </c>
       <c r="Q86" t="n">
-        <v>476.8558430332127</v>
+        <v>504.2497709974277</v>
       </c>
       <c r="R86" t="n">
-        <v>116.0386173915722</v>
+        <v>137.6534267951919</v>
       </c>
       <c r="S86" t="n">
-        <v>360.8172256416406</v>
+        <v>366.5963442022358</v>
       </c>
       <c r="T86" t="n">
-        <v>476.8558430332127</v>
+        <v>504.2497709974277</v>
       </c>
     </row>
     <row r="87">
@@ -5793,61 +5793,61 @@
         <v>0.17</v>
       </c>
       <c r="B87" t="n">
-        <v>0.4114094735995338</v>
+        <v>0.3977599256976097</v>
       </c>
       <c r="C87" t="n">
-        <v>-0.9666318559497221</v>
+        <v>-0.9200874342281777</v>
       </c>
       <c r="D87" t="n">
-        <v>-1.208328941690349</v>
+        <v>-1.301417785133438</v>
       </c>
       <c r="E87" t="n">
-        <v>3.547292311210378</v>
+        <v>3.369897146701912</v>
       </c>
       <c r="F87" t="n">
-        <v>-12.25444464384227</v>
+        <v>-11.11542990564873</v>
       </c>
       <c r="G87" t="n">
-        <v>24.5088892876846</v>
+        <v>22.2308598112972</v>
       </c>
       <c r="H87" t="n">
-        <v>-8.656061680158002</v>
+        <v>-12.42972099666061</v>
       </c>
       <c r="I87" t="n">
-        <v>13.6950926219253</v>
+        <v>16.13890221431551</v>
       </c>
       <c r="J87" t="n">
-        <v>-8.656061680158002</v>
+        <v>-17.85405079061719</v>
       </c>
       <c r="K87" t="n">
-        <v>13.6950926219253</v>
+        <v>16.4523573376548</v>
       </c>
       <c r="L87" t="n">
-        <v>31.56385085334496</v>
+        <v>23.22273598974051</v>
       </c>
       <c r="M87" t="n">
-        <v>168.5364216425728</v>
+        <v>153.9319257775651</v>
       </c>
       <c r="N87" t="n">
-        <v>143.2559583961869</v>
+        <v>130.8421369109303</v>
       </c>
       <c r="O87" t="n">
-        <v>105.988453233203</v>
+        <v>138.1029815058021</v>
       </c>
       <c r="P87" t="n">
-        <v>335.426115104854</v>
+        <v>358.4574883372817</v>
       </c>
       <c r="Q87" t="n">
-        <v>441.414568338057</v>
+        <v>496.5604698430839</v>
       </c>
       <c r="R87" t="n">
-        <v>105.988453233203</v>
+        <v>138.1029815058021</v>
       </c>
       <c r="S87" t="n">
-        <v>335.426115104854</v>
+        <v>358.4574883372817</v>
       </c>
       <c r="T87" t="n">
-        <v>441.414568338057</v>
+        <v>496.5604698430839</v>
       </c>
     </row>
     <row r="88">
@@ -5855,61 +5855,61 @@
         <v>0.172</v>
       </c>
       <c r="B88" t="n">
-        <v>0.4182809460144329</v>
+        <v>0.4044699171194528</v>
       </c>
       <c r="C88" t="n">
-        <v>-0.9911961544948641</v>
+        <v>-0.9424921087336045</v>
       </c>
       <c r="D88" t="n">
-        <v>-1.159200344600065</v>
+        <v>-1.256608436122584</v>
       </c>
       <c r="E88" t="n">
-        <v>3.597974734702703</v>
+        <v>3.424959798925205</v>
       </c>
       <c r="F88" t="n">
-        <v>-12.36099867762228</v>
+        <v>-11.38719608431691</v>
       </c>
       <c r="G88" t="n">
-        <v>24.7219973552444</v>
+        <v>22.77439216863244</v>
       </c>
       <c r="H88" t="n">
-        <v>-7.720629774995865</v>
+        <v>-12.09591708846536</v>
       </c>
       <c r="I88" t="n">
-        <v>12.43312869463512</v>
+        <v>15.25598985669296</v>
       </c>
       <c r="J88" t="n">
-        <v>-7.720629774995865</v>
+        <v>-17.65286877761201</v>
       </c>
       <c r="K88" t="n">
-        <v>12.43312869463512</v>
+        <v>15.57710878627067</v>
       </c>
       <c r="L88" t="n">
-        <v>29.57132432421405</v>
+        <v>21.80573427480795</v>
       </c>
       <c r="M88" t="n">
-        <v>164.3177031213625</v>
+        <v>152.1189666884547</v>
       </c>
       <c r="N88" t="n">
-        <v>139.6700476531581</v>
+        <v>129.3011216851865</v>
       </c>
       <c r="O88" t="n">
-        <v>95.41790583547092</v>
+        <v>137.6995463709591</v>
       </c>
       <c r="P88" t="n">
-        <v>307.3235683939112</v>
+        <v>347.2546897330127</v>
       </c>
       <c r="Q88" t="n">
-        <v>402.7414742293821</v>
+        <v>484.9542361039718</v>
       </c>
       <c r="R88" t="n">
-        <v>95.41790583547092</v>
+        <v>137.6995463709591</v>
       </c>
       <c r="S88" t="n">
-        <v>307.3235683939112</v>
+        <v>347.2546897330127</v>
       </c>
       <c r="T88" t="n">
-        <v>402.7414742293821</v>
+        <v>484.9542361039718</v>
       </c>
     </row>
     <row r="89">
@@ -5917,61 +5917,61 @@
         <v>0.174</v>
       </c>
       <c r="B89" t="n">
-        <v>0.4249412747525282</v>
+        <v>0.4111163611430509</v>
       </c>
       <c r="C89" t="n">
-        <v>-1.015953226195083</v>
+        <v>-0.9655170762597286</v>
       </c>
       <c r="D89" t="n">
-        <v>-1.109686201199626</v>
+        <v>-1.210558501070336</v>
       </c>
       <c r="E89" t="n">
-        <v>3.642638114081352</v>
+        <v>3.475104520177518</v>
       </c>
       <c r="F89" t="n">
-        <v>-12.39898886586111</v>
+        <v>-11.61236611325969</v>
       </c>
       <c r="G89" t="n">
-        <v>24.79797773172217</v>
+        <v>23.22473222652025</v>
       </c>
       <c r="H89" t="n">
-        <v>-6.770190953208052</v>
+        <v>-11.65882327136966</v>
       </c>
       <c r="I89" t="n">
-        <v>11.06859738653768</v>
+        <v>14.18543002960734</v>
       </c>
       <c r="J89" t="n">
-        <v>-6.770190953208052</v>
+        <v>-17.32565793464039</v>
       </c>
       <c r="K89" t="n">
-        <v>11.06859738653768</v>
+        <v>14.51289875400127</v>
       </c>
       <c r="L89" t="n">
-        <v>27.45056507939736</v>
+        <v>20.42122664757652</v>
       </c>
       <c r="M89" t="n">
-        <v>158.161635934549</v>
+        <v>148.9553131621154</v>
       </c>
       <c r="N89" t="n">
-        <v>134.4373905443667</v>
+        <v>126.6120161877981</v>
       </c>
       <c r="O89" t="n">
-        <v>83.92950497554924</v>
+        <v>135.336386430001</v>
       </c>
       <c r="P89" t="n">
-        <v>274.4385827193254</v>
+        <v>329.2072119240389</v>
       </c>
       <c r="Q89" t="n">
-        <v>358.3680876948746</v>
+        <v>464.5435983540399</v>
       </c>
       <c r="R89" t="n">
-        <v>83.92950497554924</v>
+        <v>135.336386430001</v>
       </c>
       <c r="S89" t="n">
-        <v>274.4385827193254</v>
+        <v>329.2072119240389</v>
       </c>
       <c r="T89" t="n">
-        <v>358.3680876948746</v>
+        <v>464.5435983540399</v>
       </c>
     </row>
     <row r="90">
@@ -5979,61 +5979,61 @@
         <v>0.176</v>
       </c>
       <c r="B90" t="n">
-        <v>0.4312889885075148</v>
+        <v>0.417640567112089</v>
       </c>
       <c r="C90" t="n">
-        <v>-1.040691236503673</v>
+        <v>-0.9889208942937515</v>
       </c>
       <c r="D90" t="n">
-        <v>-1.060210180582446</v>
+        <v>-1.163750865002291</v>
       </c>
       <c r="E90" t="n">
-        <v>3.679863405269769</v>
+        <v>3.520063517401596</v>
       </c>
       <c r="F90" t="n">
-        <v>-12.37108404626812</v>
+        <v>-11.79128762717997</v>
       </c>
       <c r="G90" t="n">
-        <v>24.74216809253622</v>
+        <v>23.58257525436048</v>
       </c>
       <c r="H90" t="n">
-        <v>-5.834284544039778</v>
+        <v>-11.17277495949809</v>
       </c>
       <c r="I90" t="n">
-        <v>9.659512324992791</v>
+        <v>13.00848976922245</v>
       </c>
       <c r="J90" t="n">
-        <v>-5.834284544039778</v>
+        <v>-16.92692332156192</v>
       </c>
       <c r="K90" t="n">
-        <v>9.659512324992791</v>
+        <v>13.34100408030893</v>
       </c>
       <c r="L90" t="n">
-        <v>25.19625937879187</v>
+        <v>19.02184978389315</v>
       </c>
       <c r="M90" t="n">
-        <v>149.7431831960913</v>
+        <v>144.4139855640585</v>
       </c>
       <c r="N90" t="n">
-        <v>127.2817057166776</v>
+        <v>122.7518877294497</v>
       </c>
       <c r="O90" t="n">
-        <v>72.21000049069124</v>
+        <v>131.6913810280296</v>
       </c>
       <c r="P90" t="n">
-        <v>239.1002931777358</v>
+        <v>306.5329811372173</v>
       </c>
       <c r="Q90" t="n">
-        <v>311.3102936684271</v>
+        <v>438.224362165247</v>
       </c>
       <c r="R90" t="n">
-        <v>72.21000049069124</v>
+        <v>131.6913810280296</v>
       </c>
       <c r="S90" t="n">
-        <v>239.1002931777358</v>
+        <v>306.5329811372173</v>
       </c>
       <c r="T90" t="n">
-        <v>311.3102936684271</v>
+        <v>438.224362165247</v>
       </c>
     </row>
     <row r="91">
@@ -6041,61 +6041,61 @@
         <v>0.178</v>
       </c>
       <c r="B91" t="n">
-        <v>0.4374776472551569</v>
+        <v>0.424084372864918</v>
       </c>
       <c r="C91" t="n">
-        <v>-1.065401848840297</v>
+        <v>-1.012573895471729</v>
       </c>
       <c r="D91" t="n">
-        <v>-1.010788955909199</v>
+        <v>-1.116444862646336</v>
       </c>
       <c r="E91" t="n">
-        <v>3.713357270374646</v>
+        <v>3.561611683730394</v>
       </c>
       <c r="F91" t="n">
-        <v>-12.31225664599322</v>
+        <v>-11.93978988565191</v>
       </c>
       <c r="G91" t="n">
-        <v>24.6245132919864</v>
+        <v>23.87957977130234</v>
       </c>
       <c r="H91" t="n">
-        <v>-4.90887500991905</v>
+        <v>-10.6545275752626</v>
       </c>
       <c r="I91" t="n">
-        <v>8.233481747710442</v>
+        <v>11.76157940117758</v>
       </c>
       <c r="J91" t="n">
-        <v>-4.90887500991905</v>
+        <v>-16.48114503946073</v>
       </c>
       <c r="K91" t="n">
-        <v>8.233481747710442</v>
+        <v>12.09828147595295</v>
       </c>
       <c r="L91" t="n">
-        <v>22.87275666100973</v>
+        <v>17.61269290669507</v>
       </c>
       <c r="M91" t="n">
-        <v>140.213610854261</v>
+        <v>138.9665138553905</v>
       </c>
       <c r="N91" t="n">
-        <v>119.1815692261218</v>
+        <v>118.1215367770819</v>
       </c>
       <c r="O91" t="n">
-        <v>60.45065895174929</v>
+        <v>127.2032613227143</v>
       </c>
       <c r="P91" t="n">
-        <v>202.7827156487155</v>
+        <v>280.8155741389837</v>
       </c>
       <c r="Q91" t="n">
-        <v>263.2333746004647</v>
+        <v>408.0188354616981</v>
       </c>
       <c r="R91" t="n">
-        <v>60.45065895174929</v>
+        <v>127.2032613227143</v>
       </c>
       <c r="S91" t="n">
-        <v>202.7827156487155</v>
+        <v>280.8155741389837</v>
       </c>
       <c r="T91" t="n">
-        <v>263.2333746004647</v>
+        <v>408.0188354616981</v>
       </c>
     </row>
     <row r="92">
@@ -6103,61 +6103,61 @@
         <v>0.18</v>
       </c>
       <c r="B92" t="n">
-        <v>0.4431950863134844</v>
+        <v>0.4302453973850813</v>
       </c>
       <c r="C92" t="n">
-        <v>-1.089841307270238</v>
+        <v>-1.036573167274632</v>
       </c>
       <c r="D92" t="n">
-        <v>-0.9619100390493183</v>
+        <v>-1.06844631904053</v>
       </c>
       <c r="E92" t="n">
-        <v>3.736365114306672</v>
+        <v>3.594079251038476</v>
       </c>
       <c r="F92" t="n">
-        <v>-12.18976863118761</v>
+        <v>-12.02032458505594</v>
       </c>
       <c r="G92" t="n">
-        <v>24.37953726237508</v>
+        <v>24.04064917011209</v>
       </c>
       <c r="H92" t="n">
-        <v>-4.047869882565365</v>
+        <v>-10.11094063587185</v>
       </c>
       <c r="I92" t="n">
-        <v>6.818676405690518</v>
+        <v>10.4178611799482</v>
       </c>
       <c r="J92" t="n">
-        <v>-4.047869882565365</v>
+        <v>-15.97685903337915</v>
       </c>
       <c r="K92" t="n">
-        <v>6.818676405690518</v>
+        <v>10.75683433324678</v>
       </c>
       <c r="L92" t="n">
-        <v>20.33083147335405</v>
+        <v>16.12032024061394</v>
       </c>
       <c r="M92" t="n">
-        <v>127.8210980364264</v>
+        <v>131.1995419847644</v>
       </c>
       <c r="N92" t="n">
-        <v>108.6479333309624</v>
+        <v>111.5196106870498</v>
       </c>
       <c r="O92" t="n">
-        <v>49.40779768042171</v>
+        <v>121.5082272454817</v>
       </c>
       <c r="P92" t="n">
-        <v>166.4504502449122</v>
+        <v>250.3106425025418</v>
       </c>
       <c r="Q92" t="n">
-        <v>215.858247925334</v>
+        <v>371.8188697480235</v>
       </c>
       <c r="R92" t="n">
-        <v>49.40779768042171</v>
+        <v>121.5082272454817</v>
       </c>
       <c r="S92" t="n">
-        <v>166.4504502449122</v>
+        <v>250.3106425025418</v>
       </c>
       <c r="T92" t="n">
-        <v>215.858247925334</v>
+        <v>371.8188697480235</v>
       </c>
     </row>
     <row r="93">
@@ -6165,61 +6165,61 @@
         <v>0.182</v>
       </c>
       <c r="B93" t="n">
-        <v>0.4486865782848803</v>
+        <v>0.4362889532226863</v>
       </c>
       <c r="C93" t="n">
-        <v>-1.114082763524896</v>
+        <v>-1.060637854216534</v>
       </c>
       <c r="D93" t="n">
-        <v>-0.9134271265400024</v>
+        <v>-1.020316945156725</v>
       </c>
       <c r="E93" t="n">
-        <v>3.7542679702328</v>
+        <v>3.623165010560625</v>
       </c>
       <c r="F93" t="n">
-        <v>-12.05022569252548</v>
+        <v>-12.08058127438222</v>
       </c>
       <c r="G93" t="n">
-        <v>24.10045138505086</v>
+        <v>24.16116254876568</v>
       </c>
       <c r="H93" t="n">
-        <v>-3.221826942768383</v>
+        <v>-9.569879990713178</v>
       </c>
       <c r="I93" t="n">
-        <v>5.441731316947004</v>
+        <v>9.061061738194612</v>
       </c>
       <c r="J93" t="n">
-        <v>-3.221826942768383</v>
+        <v>-15.4652036526117</v>
       </c>
       <c r="K93" t="n">
-        <v>5.441731316947004</v>
+        <v>9.401734130132208</v>
       </c>
       <c r="L93" t="n">
-        <v>17.7280619386896</v>
+        <v>14.59460631374302</v>
       </c>
       <c r="M93" t="n">
-        <v>114.2486811147937</v>
+        <v>122.6173982562628</v>
       </c>
       <c r="N93" t="n">
-        <v>97.11137894757466</v>
+        <v>104.2247885178234</v>
       </c>
       <c r="O93" t="n">
-        <v>38.88919885799101</v>
+        <v>115.6070431426617</v>
       </c>
       <c r="P93" t="n">
-        <v>131.3711264049482</v>
+        <v>218.9118666212237</v>
       </c>
       <c r="Q93" t="n">
-        <v>170.2603252629392</v>
+        <v>334.5189097638855</v>
       </c>
       <c r="R93" t="n">
-        <v>38.88919885799101</v>
+        <v>115.6070431426617</v>
       </c>
       <c r="S93" t="n">
-        <v>131.3711264049482</v>
+        <v>218.9118666212237</v>
       </c>
       <c r="T93" t="n">
-        <v>170.2603252629392</v>
+        <v>334.5189097638855</v>
       </c>
     </row>
     <row r="94">
@@ -6227,61 +6227,61 @@
         <v>0.184</v>
       </c>
       <c r="B94" t="n">
-        <v>0.4538675248351715</v>
+        <v>0.4420386642412129</v>
       </c>
       <c r="C94" t="n">
-        <v>-1.138052082308175</v>
+        <v>-1.084816463772982</v>
       </c>
       <c r="D94" t="n">
-        <v>-0.8654884889734423</v>
+        <v>-0.9719597260438301</v>
       </c>
       <c r="E94" t="n">
-        <v>3.765154446034018</v>
+        <v>3.6440386714052</v>
       </c>
       <c r="F94" t="n">
-        <v>-11.88724218384822</v>
+        <v>-12.09515603829194</v>
       </c>
       <c r="G94" t="n">
-        <v>23.77448436769656</v>
+        <v>24.19031207658301</v>
       </c>
       <c r="H94" t="n">
-        <v>-2.443836613009419</v>
+        <v>-9.043412187646899</v>
       </c>
       <c r="I94" t="n">
-        <v>4.116821987798947</v>
+        <v>7.688738523727777</v>
       </c>
       <c r="J94" t="n">
-        <v>-2.443836613009419</v>
+        <v>-14.94584833433337</v>
       </c>
       <c r="K94" t="n">
-        <v>4.116821987798947</v>
+        <v>8.029821924007598</v>
       </c>
       <c r="L94" t="n">
-        <v>15.0416669250677</v>
+        <v>12.9862678272077</v>
       </c>
       <c r="M94" t="n">
-        <v>99.05458443727875</v>
+        <v>112.0901622140164</v>
       </c>
       <c r="N94" t="n">
-        <v>84.19639677168693</v>
+        <v>95.27663788191393</v>
       </c>
       <c r="O94" t="n">
-        <v>29.09115503440185</v>
+        <v>109.3772995129606</v>
       </c>
       <c r="P94" t="n">
-        <v>98.01386621646313</v>
+        <v>185.971182170296</v>
       </c>
       <c r="Q94" t="n">
-        <v>127.105021250865</v>
+        <v>295.3484816832566</v>
       </c>
       <c r="R94" t="n">
-        <v>29.09115503440185</v>
+        <v>109.3772995129606</v>
       </c>
       <c r="S94" t="n">
-        <v>98.01386621646313</v>
+        <v>185.971182170296</v>
       </c>
       <c r="T94" t="n">
-        <v>127.105021250865</v>
+        <v>295.3484816832566</v>
       </c>
     </row>
     <row r="95">
@@ -6289,61 +6289,61 @@
         <v>0.186</v>
       </c>
       <c r="B95" t="n">
-        <v>0.4586341639119573</v>
+        <v>0.4475409935012684</v>
       </c>
       <c r="C95" t="n">
-        <v>-1.161593589791231</v>
+        <v>-1.108984059668873</v>
       </c>
       <c r="D95" t="n">
-        <v>-0.8184054740073321</v>
+        <v>-0.923624534252047</v>
       </c>
       <c r="E95" t="n">
-        <v>3.765980174919285</v>
+        <v>3.658326346986347</v>
       </c>
       <c r="F95" t="n">
-        <v>-11.71687500615299</v>
+        <v>-12.08682167074918</v>
       </c>
       <c r="G95" t="n">
-        <v>23.43375001230604</v>
+        <v>24.1736433414978</v>
       </c>
       <c r="H95" t="n">
-        <v>-1.76549831397359</v>
+        <v>-8.544951262975355</v>
       </c>
       <c r="I95" t="n">
-        <v>2.917081743596448</v>
+        <v>6.339098187769338</v>
       </c>
       <c r="J95" t="n">
-        <v>-1.76549831397359</v>
+        <v>-14.44332023830095</v>
       </c>
       <c r="K95" t="n">
-        <v>2.917081743596448</v>
+        <v>6.679946558884457</v>
       </c>
       <c r="L95" t="n">
-        <v>12.21190601471191</v>
+        <v>11.31496190404837</v>
       </c>
       <c r="M95" t="n">
-        <v>82.00673544642817</v>
+        <v>100.184510888167</v>
       </c>
       <c r="N95" t="n">
-        <v>69.70572512946394</v>
+        <v>85.15683425494198</v>
       </c>
       <c r="O95" t="n">
-        <v>20.76180483118897</v>
+        <v>103.2891618346383</v>
       </c>
       <c r="P95" t="n">
-        <v>68.62934449495803</v>
+        <v>153.2830322418687</v>
       </c>
       <c r="Q95" t="n">
-        <v>89.391149326147</v>
+        <v>256.5721940765069</v>
       </c>
       <c r="R95" t="n">
-        <v>20.76180483118897</v>
+        <v>103.2891618346383</v>
       </c>
       <c r="S95" t="n">
-        <v>68.62934449495803</v>
+        <v>153.2830322418687</v>
       </c>
       <c r="T95" t="n">
-        <v>89.391149326147</v>
+        <v>256.5721940765069</v>
       </c>
     </row>
     <row r="96">
@@ -6351,61 +6351,61 @@
         <v>0.188</v>
       </c>
       <c r="B96" t="n">
-        <v>0.4632147538463412</v>
+        <v>0.4528498265472807</v>
       </c>
       <c r="C96" t="n">
-        <v>-1.184940253143663</v>
+        <v>-1.133143040937585</v>
       </c>
       <c r="D96" t="n">
-        <v>-0.7717121473024665</v>
+        <v>-0.8753065717146237</v>
       </c>
       <c r="E96" t="n">
-        <v>3.762069204284109</v>
+        <v>3.667462619238105</v>
       </c>
       <c r="F96" t="n">
-        <v>-11.54572965552547</v>
+        <v>-12.0605683174636</v>
       </c>
       <c r="G96" t="n">
-        <v>23.09145931105093</v>
+        <v>24.12113663492888</v>
       </c>
       <c r="H96" t="n">
-        <v>-1.120102088074524</v>
+        <v>-8.06839666223831</v>
       </c>
       <c r="I96" t="n">
-        <v>1.770196125382459</v>
+        <v>5.007199867803127</v>
       </c>
       <c r="J96" t="n">
-        <v>-1.120102088074524</v>
+        <v>-13.95395400116054</v>
       </c>
       <c r="K96" t="n">
-        <v>1.770196125382459</v>
+        <v>5.347307894355623</v>
       </c>
       <c r="L96" t="n">
-        <v>9.357228539872295</v>
+        <v>9.594404327614125</v>
       </c>
       <c r="M96" t="n">
-        <v>64.17027317516741</v>
+        <v>87.2006954308755</v>
       </c>
       <c r="N96" t="n">
-        <v>54.5447321988923</v>
+        <v>74.12059111624417</v>
       </c>
       <c r="O96" t="n">
-        <v>12.95176502986091</v>
+        <v>97.31178501292531</v>
       </c>
       <c r="P96" t="n">
-        <v>40.941197167751</v>
+        <v>120.7924088987525</v>
       </c>
       <c r="Q96" t="n">
-        <v>53.8929621976119</v>
+        <v>218.1041939116777</v>
       </c>
       <c r="R96" t="n">
-        <v>12.95176502986091</v>
+        <v>97.31178501292531</v>
       </c>
       <c r="S96" t="n">
-        <v>40.941197167751</v>
+        <v>120.7924088987525</v>
       </c>
       <c r="T96" t="n">
-        <v>53.8929621976119</v>
+        <v>218.1041939116777</v>
       </c>
     </row>
     <row r="97">
@@ -6413,61 +6413,61 @@
         <v>0.19</v>
       </c>
       <c r="B97" t="n">
-        <v>0.4673482718462806</v>
+        <v>0.4577472573317933</v>
       </c>
       <c r="C97" t="n">
-        <v>-1.207806564350027</v>
+        <v>-1.157198880413259</v>
       </c>
       <c r="D97" t="n">
-        <v>-0.7259795248897394</v>
+        <v>-0.8271948927632755</v>
       </c>
       <c r="E97" t="n">
-        <v>3.745802859642702</v>
+        <v>3.66549049606814</v>
       </c>
       <c r="F97" t="n">
-        <v>-11.38400021953434</v>
+        <v>-12.01917401220364</v>
       </c>
       <c r="G97" t="n">
-        <v>22.76800043906871</v>
+        <v>24.0383480244072</v>
       </c>
       <c r="H97" t="n">
-        <v>-0.5013494729742607</v>
+        <v>-7.670684253133736</v>
       </c>
       <c r="I97" t="n">
-        <v>0.7354024732483113</v>
+        <v>3.7839585214458</v>
       </c>
       <c r="J97" t="n">
-        <v>-0.5013494729742607</v>
+        <v>-13.53604117108911</v>
       </c>
       <c r="K97" t="n">
-        <v>0.7354024732483113</v>
+        <v>4.12289922858994</v>
       </c>
       <c r="L97" t="n">
-        <v>6.61819264080191</v>
+        <v>7.779366393645399</v>
       </c>
       <c r="M97" t="n">
-        <v>44.63374368712613</v>
+        <v>72.26662825471944</v>
       </c>
       <c r="N97" t="n">
-        <v>37.9386821340572</v>
+        <v>61.42663401651152</v>
       </c>
       <c r="O97" t="n">
-        <v>5.765972111866482</v>
+        <v>92.20713698261544</v>
       </c>
       <c r="P97" t="n">
-        <v>16.93967967129643</v>
+        <v>91.03410761554633</v>
       </c>
       <c r="Q97" t="n">
-        <v>22.70565178316291</v>
+        <v>183.2412445981618</v>
       </c>
       <c r="R97" t="n">
-        <v>5.765972111866482</v>
+        <v>92.20713698261544</v>
       </c>
       <c r="S97" t="n">
-        <v>16.93967967129643</v>
+        <v>91.03410761554633</v>
       </c>
       <c r="T97" t="n">
-        <v>22.70565178316291</v>
+        <v>183.2412445981618</v>
       </c>
     </row>
     <row r="98">
@@ -6475,61 +6475,61 @@
         <v>0.192</v>
       </c>
       <c r="B98" t="n">
-        <v>0.471254049791263</v>
+        <v>0.462494215239381</v>
       </c>
       <c r="C98" t="n">
-        <v>-1.230455788370755</v>
+        <v>-1.181211605650564</v>
       </c>
       <c r="D98" t="n">
-        <v>-0.6806810768482841</v>
+        <v>-0.7791694422886647</v>
       </c>
       <c r="E98" t="n">
-        <v>3.722401123264455</v>
+        <v>3.659270848484322</v>
       </c>
       <c r="F98" t="n">
-        <v>-11.24587354423202</v>
+        <v>-11.97576097081602</v>
       </c>
       <c r="G98" t="n">
-        <v>22.49174708846409</v>
+        <v>23.95152194163056</v>
       </c>
       <c r="H98" t="n">
-        <v>-0.02805384662161023</v>
+        <v>-7.29141210529387</v>
       </c>
       <c r="I98" t="n">
-        <v>-0.1085460289266454</v>
+        <v>2.597307011684241</v>
       </c>
       <c r="J98" t="n">
-        <v>-0.02805384662161023</v>
+        <v>-13.13558345905209</v>
       </c>
       <c r="K98" t="n">
-        <v>-0.1085460289266454</v>
+        <v>2.935023471061232</v>
       </c>
       <c r="L98" t="n">
-        <v>3.679490864796678</v>
+        <v>5.96399240261559</v>
       </c>
       <c r="M98" t="n">
-        <v>24.42328932227404</v>
+        <v>56.68509131849391</v>
       </c>
       <c r="N98" t="n">
-        <v>20.75979592393293</v>
+        <v>48.18232762071982</v>
       </c>
       <c r="O98" t="n">
-        <v>0.3354345362946103</v>
+        <v>87.32466474326435</v>
       </c>
       <c r="P98" t="n">
-        <v>-2.360910990561768</v>
+        <v>62.23758246891219</v>
       </c>
       <c r="Q98" t="n">
-        <v>-2.02547645426716</v>
+        <v>149.5622472121765</v>
       </c>
       <c r="R98" t="n">
-        <v>2.544129943878109</v>
+        <v>87.32466474326435</v>
       </c>
       <c r="S98" t="n">
-        <v>8.693585699992205</v>
+        <v>62.23758246891219</v>
       </c>
       <c r="T98" t="n">
-        <v>11.23771564387031</v>
+        <v>149.5622472121765</v>
       </c>
     </row>
     <row r="99">
@@ -6537,61 +6537,185 @@
         <v>0.194</v>
       </c>
       <c r="B99" t="n">
-        <v>0.475522529447167</v>
+        <v>0.4668621071719831</v>
       </c>
       <c r="C99" t="n">
-        <v>-1.256599986623214</v>
+        <v>-1.205107697234987</v>
       </c>
       <c r="D99" t="n">
-        <v>-0.6283926803433659</v>
+        <v>-0.7313772591198202</v>
       </c>
       <c r="E99" t="n">
-        <v>3.686106925198386</v>
+        <v>3.64207628423438</v>
       </c>
       <c r="F99" t="n">
-        <v>-11.11452875342903</v>
+        <v>-11.93250034819335</v>
       </c>
       <c r="G99" t="n">
-        <v>22.2290575068581</v>
+        <v>23.86500069638746</v>
       </c>
       <c r="H99" t="n">
-        <v>0.3405593536656045</v>
+        <v>-6.943119399932409</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.8522479458026609</v>
+        <v>1.498139699094362</v>
       </c>
       <c r="J99" t="n">
-        <v>0.287973590732752</v>
+        <v>-12.76617956985076</v>
       </c>
       <c r="K99" t="n">
-        <v>-0.7461526332553131</v>
+        <v>1.834636208913425</v>
       </c>
       <c r="L99" t="n">
-        <v>1.402982012857584e-12</v>
+        <v>4.19870623546511</v>
       </c>
       <c r="M99" t="n">
-        <v>3.48418695082237</v>
+        <v>39.57047810441688</v>
       </c>
       <c r="N99" t="n">
-        <v>2.961558908199013</v>
+        <v>33.63490638875435</v>
       </c>
       <c r="O99" t="n">
-        <v>-3.785156728565565</v>
+        <v>82.85746951741811</v>
       </c>
       <c r="P99" t="n">
-        <v>-18.94466859734904</v>
+        <v>35.80798469951063</v>
       </c>
       <c r="Q99" t="n">
-        <v>-22.7298253259146</v>
+        <v>118.6654542169287</v>
       </c>
       <c r="R99" t="n">
-        <v>3.785156728565565</v>
+        <v>82.85746951741811</v>
       </c>
       <c r="S99" t="n">
-        <v>18.94466859734904</v>
+        <v>35.80798469951063</v>
       </c>
       <c r="T99" t="n">
-        <v>22.7298253259146</v>
+        <v>118.6654542169287</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>0.196</v>
+      </c>
+      <c r="B100" t="n">
+        <v>0.4709886085482775</v>
+      </c>
+      <c r="C100" t="n">
+        <v>-1.228953056004141</v>
+      </c>
+      <c r="D100" t="n">
+        <v>-0.6836865415815115</v>
+      </c>
+      <c r="E100" t="n">
+        <v>3.617321197366421</v>
+      </c>
+      <c r="F100" t="n">
+        <v>-11.90395802519363</v>
+      </c>
+      <c r="G100" t="n">
+        <v>23.80791605038793</v>
+      </c>
+      <c r="H100" t="n">
+        <v>-6.704902850818103</v>
+      </c>
+      <c r="I100" t="n">
+        <v>0.5598346931242471</v>
+      </c>
+      <c r="J100" t="n">
+        <v>-12.51403436711259</v>
+      </c>
+      <c r="K100" t="n">
+        <v>0.8955263094347169</v>
+      </c>
+      <c r="L100" t="n">
+        <v>2.315258047217489</v>
+      </c>
+      <c r="M100" t="n">
+        <v>21.66117568195241</v>
+      </c>
+      <c r="N100" t="n">
+        <v>18.41199932965955</v>
+      </c>
+      <c r="O100" t="n">
+        <v>79.81610571054078</v>
+      </c>
+      <c r="P100" t="n">
+        <v>13.34267829649874</v>
+      </c>
+      <c r="Q100" t="n">
+        <v>93.15878400703951</v>
+      </c>
+      <c r="R100" t="n">
+        <v>79.81610571054078</v>
+      </c>
+      <c r="S100" t="n">
+        <v>18.58430885797517</v>
+      </c>
+      <c r="T100" t="n">
+        <v>93.15878400703951</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>0.198</v>
+      </c>
+      <c r="B101" t="n">
+        <v>0.4755225286461454</v>
+      </c>
+      <c r="C101" t="n">
+        <v>-1.256599981439484</v>
+      </c>
+      <c r="D101" t="n">
+        <v>-0.628392690710825</v>
+      </c>
+      <c r="E101" t="n">
+        <v>3.580422390291515</v>
+      </c>
+      <c r="F101" t="n">
+        <v>-11.88664712114061</v>
+      </c>
+      <c r="G101" t="n">
+        <v>23.77329424227928</v>
+      </c>
+      <c r="H101" t="n">
+        <v>-6.546681677367581</v>
+      </c>
+      <c r="I101" t="n">
+        <v>-0.3570094456500732</v>
+      </c>
+      <c r="J101" t="n">
+        <v>-12.37056659476471</v>
+      </c>
+      <c r="K101" t="n">
+        <v>0.1058911301977961</v>
+      </c>
+      <c r="L101" t="n">
+        <v>4.320258442858203e-13</v>
+      </c>
+      <c r="M101" t="n">
+        <v>3.015341206030449</v>
+      </c>
+      <c r="N101" t="n">
+        <v>2.563040025125879</v>
+      </c>
+      <c r="O101" t="n">
+        <v>77.81809491330536</v>
+      </c>
+      <c r="P101" t="n">
+        <v>-8.487290598712203</v>
+      </c>
+      <c r="Q101" t="n">
+        <v>69.33080431459315</v>
+      </c>
+      <c r="R101" t="n">
+        <v>77.81809491330536</v>
+      </c>
+      <c r="S101" t="n">
+        <v>8.487290598712203</v>
+      </c>
+      <c r="T101" t="n">
+        <v>69.33080431459315</v>
       </c>
     </row>
   </sheetData>

--- a/code/goal19/nlp_demo/task0_vertjump_no_cvt_results.xlsx
+++ b/code/goal19/nlp_demo/task0_vertjump_no_cvt_results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T101"/>
+  <dimension ref="A1:T99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -523,61 +523,61 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.1461830126705125</v>
+        <v>0.1461830283436809</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.2967000339617897</v>
+        <v>-0.2967000667403363</v>
       </c>
       <c r="D2" t="n">
-        <v>-2.548192585666214</v>
+        <v>-2.54819252010912</v>
       </c>
       <c r="E2" t="n">
-        <v>1.405343351662499e-25</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>1.032175778623011e-23</v>
+        <v>-4.599527505201061e-24</v>
       </c>
       <c r="G2" t="n">
-        <v>-3.19644665953929e-23</v>
+        <v>-1.404616657079581e-24</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.048276159022536</v>
+        <v>0.3457072863789525</v>
       </c>
       <c r="I2" t="n">
-        <v>8.11487625433203</v>
+        <v>6.919556354232888</v>
       </c>
       <c r="J2" t="n">
-        <v>-1.048276159022536</v>
+        <v>0.3457072863789525</v>
       </c>
       <c r="K2" t="n">
-        <v>8.11487625433203</v>
+        <v>6.919556354232888</v>
       </c>
       <c r="L2" t="n">
-        <v>9.88632007705316</v>
+        <v>9.885990242817744</v>
       </c>
       <c r="M2" t="n">
-        <v>32.95512540000004</v>
+        <v>32.9551254</v>
       </c>
       <c r="N2" t="n">
-        <v>28.01185659000003</v>
+        <v>32.9551254</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.082005260651026e-23</v>
+        <v>-1.590090172448412e-24</v>
       </c>
       <c r="P2" t="n">
-        <v>-2.593876909573432e-22</v>
+        <v>-9.719324114756371e-24</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.702077435638535e-22</v>
+        <v>-1.130941428720478e-23</v>
       </c>
       <c r="R2" t="n">
-        <v>1.082005260651026e-23</v>
+        <v>1.590090172448412e-24</v>
       </c>
       <c r="S2" t="n">
-        <v>2.593876909573432e-22</v>
+        <v>9.719324114756371e-24</v>
       </c>
       <c r="T2" t="n">
-        <v>2.702077435638535e-22</v>
+        <v>1.130941428720478e-23</v>
       </c>
     </row>
     <row r="3">
@@ -585,61 +585,61 @@
         <v>0.002</v>
       </c>
       <c r="B3" t="n">
-        <v>0.1463450074372451</v>
+        <v>0.1461855631117916</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.2970388560434017</v>
+        <v>-0.2967053679101204</v>
       </c>
       <c r="D3" t="n">
-        <v>-2.54751494150299</v>
+        <v>-2.548181917769553</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01225214608800845</v>
+        <v>0.001529308617205707</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.2015949650031156</v>
+        <v>-0.003198369348973506</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4031899300062489</v>
+        <v>0.006396738697726413</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.9913382892612282</v>
+        <v>0.4445539428888974</v>
       </c>
       <c r="I3" t="n">
-        <v>8.340509704685473</v>
+        <v>7.527807713656079</v>
       </c>
       <c r="J3" t="n">
-        <v>-1.089716632182749</v>
+        <v>0.4429931386465984</v>
       </c>
       <c r="K3" t="n">
-        <v>8.346194682698561</v>
+        <v>7.527897907671718</v>
       </c>
       <c r="L3" t="n">
-        <v>10.60181120998474</v>
+        <v>10.67840558977601</v>
       </c>
       <c r="M3" t="n">
-        <v>35.34462475805658</v>
+        <v>35.59867644853519</v>
       </c>
       <c r="N3" t="n">
-        <v>30.04293104434809</v>
+        <v>35.59867644853519</v>
       </c>
       <c r="O3" t="n">
-        <v>0.192035388060578</v>
+        <v>-0.001629702496527709</v>
       </c>
       <c r="P3" t="n">
-        <v>3.424735579464122</v>
+        <v>0.05071148134888846</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.6167709675247</v>
+        <v>0.04908177885236075</v>
       </c>
       <c r="R3" t="n">
-        <v>0.192035388060578</v>
+        <v>0.001629702496527709</v>
       </c>
       <c r="S3" t="n">
-        <v>3.424735579464122</v>
+        <v>0.05071148134888846</v>
       </c>
       <c r="T3" t="n">
-        <v>3.6167709675247</v>
+        <v>0.04908177885236075</v>
       </c>
     </row>
     <row r="4">
@@ -647,61 +647,61 @@
         <v>0.004</v>
       </c>
       <c r="B4" t="n">
-        <v>0.146602243174131</v>
+        <v>0.146191561961751</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.2975769836724323</v>
+        <v>-0.2967179138731168</v>
       </c>
       <c r="D4" t="n">
-        <v>-2.546438686244928</v>
+        <v>-2.54815682584356</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0245674416530214</v>
+        <v>0.004100913012282513</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3930385780820428</v>
+        <v>-0.0085766218764697</v>
       </c>
       <c r="G4" t="n">
-        <v>0.786077156164123</v>
+        <v>0.01715324375271592</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.9296868422867096</v>
+        <v>0.4882552171470146</v>
       </c>
       <c r="I4" t="n">
-        <v>8.630127094616366</v>
+        <v>8.129402397727782</v>
       </c>
       <c r="J4" t="n">
-        <v>-1.121489668390746</v>
+        <v>0.4840698256712975</v>
       </c>
       <c r="K4" t="n">
-        <v>8.64121078251828</v>
+        <v>8.129644258464696</v>
       </c>
       <c r="L4" t="n">
-        <v>11.37701615412466</v>
+        <v>11.40927040326835</v>
       </c>
       <c r="M4" t="n">
-        <v>38.0451608286163</v>
+        <v>38.23289514462546</v>
       </c>
       <c r="N4" t="n">
-        <v>32.33838670432386</v>
+        <v>38.23289514462546</v>
       </c>
       <c r="O4" t="n">
-        <v>0.360110507551188</v>
+        <v>-0.003919932910838871</v>
       </c>
       <c r="P4" t="n">
-        <v>6.846836669354487</v>
+        <v>0.1445176509240315</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.206947176905675</v>
+        <v>0.1405977180131927</v>
       </c>
       <c r="R4" t="n">
-        <v>0.360110507551188</v>
+        <v>0.003919932910838871</v>
       </c>
       <c r="S4" t="n">
-        <v>6.846836669354487</v>
+        <v>0.1445176509240315</v>
       </c>
       <c r="T4" t="n">
-        <v>7.206947176905675</v>
+        <v>0.1405977180131927</v>
       </c>
     </row>
     <row r="5">
@@ -709,61 +709,61 @@
         <v>0.006</v>
       </c>
       <c r="B5" t="n">
-        <v>0.1470625250577804</v>
+        <v>0.1462042096611401</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.298540014821102</v>
+        <v>-0.2967443652636758</v>
       </c>
       <c r="D5" t="n">
-        <v>-2.544512623947589</v>
+        <v>-2.548103923062442</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03701736686276877</v>
+        <v>0.008673067045261457</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.5628403190829061</v>
+        <v>-0.01813887341465924</v>
       </c>
       <c r="G5" t="n">
-        <v>1.125680638165873</v>
+        <v>0.03627774682951001</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.8579864249050759</v>
+        <v>0.4261121842150932</v>
       </c>
       <c r="I5" t="n">
-        <v>9.056153136885099</v>
+        <v>8.718220469107786</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.132652500617534</v>
+        <v>0.4172604139887395</v>
       </c>
       <c r="K5" t="n">
-        <v>9.072025233883238</v>
+        <v>8.718731985338081</v>
       </c>
       <c r="L5" t="n">
-        <v>12.27952617773733</v>
+        <v>12.02199706437417</v>
       </c>
       <c r="M5" t="n">
-        <v>41.40880234501677</v>
+        <v>40.84920161781235</v>
       </c>
       <c r="N5" t="n">
-        <v>35.19748199326425</v>
+        <v>40.84920161781235</v>
       </c>
       <c r="O5" t="n">
-        <v>0.4771042468256589</v>
+        <v>-0.00747795977487274</v>
       </c>
       <c r="P5" t="n">
-        <v>10.26332123774387</v>
+        <v>0.3210384057032233</v>
       </c>
       <c r="Q5" t="n">
-        <v>10.74042548456953</v>
+        <v>0.3135604459283505</v>
       </c>
       <c r="R5" t="n">
-        <v>0.4771042468256589</v>
+        <v>0.00747795977487274</v>
       </c>
       <c r="S5" t="n">
-        <v>10.26332123774387</v>
+        <v>0.3210384057032233</v>
       </c>
       <c r="T5" t="n">
-        <v>10.74042548456953</v>
+        <v>0.3135604459283505</v>
       </c>
     </row>
     <row r="6">
@@ -771,61 +771,61 @@
         <v>0.008</v>
       </c>
       <c r="B6" t="n">
-        <v>0.1476797978872671</v>
+        <v>0.1462305835119929</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.2998321096263668</v>
+        <v>-0.2967995246439457</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.54192843433706</v>
+        <v>-2.547993604301902</v>
       </c>
       <c r="E6" t="n">
-        <v>0.04998400824735147</v>
+        <v>0.01526207818565205</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.7115648948736895</v>
+        <v>-0.03191978697126585</v>
       </c>
       <c r="G6" t="n">
-        <v>1.42312978974726</v>
+        <v>0.06383957394263562</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.7496664755668619</v>
+        <v>0.462788107655081</v>
       </c>
       <c r="I6" t="n">
-        <v>9.533818588262791</v>
+        <v>9.290659351821814</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.096910144265222</v>
+        <v>0.4472112516131033</v>
       </c>
       <c r="K6" t="n">
-        <v>9.553884718298228</v>
+        <v>9.291559489814405</v>
       </c>
       <c r="L6" t="n">
-        <v>13.26055863694993</v>
+        <v>12.76749346581387</v>
       </c>
       <c r="M6" t="n">
-        <v>45.20590108600094</v>
+        <v>43.36708103762538</v>
       </c>
       <c r="N6" t="n">
-        <v>38.4250159231008</v>
+        <v>43.36708103762538</v>
       </c>
       <c r="O6" t="n">
-        <v>0.5216886758916832</v>
+        <v>-0.01563187360417112</v>
       </c>
       <c r="P6" t="n">
-        <v>13.66015130572234</v>
+        <v>0.6049433329859176</v>
       </c>
       <c r="Q6" t="n">
-        <v>14.18183998161402</v>
+        <v>0.5893114593817466</v>
       </c>
       <c r="R6" t="n">
-        <v>0.5216886758916832</v>
+        <v>0.01563187360417112</v>
       </c>
       <c r="S6" t="n">
-        <v>13.66015130572234</v>
+        <v>0.6049433329859176</v>
       </c>
       <c r="T6" t="n">
-        <v>14.18183998161402</v>
+        <v>0.5893114593817466</v>
       </c>
     </row>
     <row r="7">
@@ -833,61 +833,61 @@
         <v>0.01</v>
       </c>
       <c r="B7" t="n">
-        <v>0.1483859213270266</v>
+        <v>0.1462640853394215</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.3013104413292513</v>
+        <v>-0.2968695922096074</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.538971770931291</v>
+        <v>-2.547853469170578</v>
       </c>
       <c r="E7" t="n">
-        <v>0.06324309036618904</v>
+        <v>0.02285671893225538</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.8483606362864669</v>
+        <v>-0.04780423560627289</v>
       </c>
       <c r="G7" t="n">
-        <v>1.69672127257252</v>
+        <v>0.09560847121234703</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.620621332524647</v>
+        <v>0.5406569983616321</v>
       </c>
       <c r="I7" t="n">
-        <v>10.04070988441131</v>
+        <v>9.855105866605516</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.034621323032443</v>
+        <v>0.5173285313857708</v>
       </c>
       <c r="K7" t="n">
-        <v>10.06463365435458</v>
+        <v>9.85645394604961</v>
       </c>
       <c r="L7" t="n">
-        <v>14.2860316611006</v>
+        <v>13.56750994744641</v>
       </c>
       <c r="M7" t="n">
-        <v>49.24831931803015</v>
+        <v>45.83884679865808</v>
       </c>
       <c r="N7" t="n">
-        <v>41.86107142032563</v>
+        <v>45.83884679865808</v>
       </c>
       <c r="O7" t="n">
-        <v>0.5252923250334167</v>
+        <v>-0.02577630094885529</v>
       </c>
       <c r="P7" t="n">
-        <v>17.04585771082453</v>
+        <v>0.9433009257200409</v>
       </c>
       <c r="Q7" t="n">
-        <v>17.57115003585795</v>
+        <v>0.9175246247711856</v>
       </c>
       <c r="R7" t="n">
-        <v>0.5252923250334167</v>
+        <v>0.02577630094885529</v>
       </c>
       <c r="S7" t="n">
-        <v>17.04585771082453</v>
+        <v>0.9433009257200409</v>
       </c>
       <c r="T7" t="n">
-        <v>17.57115003585795</v>
+        <v>0.9175246247711856</v>
       </c>
     </row>
     <row r="8">
@@ -895,61 +895,61 @@
         <v>0.012</v>
       </c>
       <c r="B8" t="n">
-        <v>0.1492744130248635</v>
+        <v>0.1463263958071951</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.303172155489029</v>
+        <v>-0.2969999179788634</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.535248342611735</v>
+        <v>-2.547592817632066</v>
       </c>
       <c r="E8" t="n">
-        <v>0.07753433851120492</v>
+        <v>0.03321548250141316</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.9511967314871428</v>
+        <v>-0.06947246685973824</v>
       </c>
       <c r="G8" t="n">
-        <v>1.90239346297455</v>
+        <v>0.1389449337195375</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.4804509755794532</v>
+        <v>0.4695135943391527</v>
       </c>
       <c r="I8" t="n">
-        <v>10.61563453019374</v>
+        <v>10.4032478861019</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.9446349805451788</v>
+        <v>0.4356110305116005</v>
       </c>
       <c r="K8" t="n">
-        <v>10.64245827802168</v>
+        <v>10.40520700966735</v>
       </c>
       <c r="L8" t="n">
-        <v>15.36866048189103</v>
+        <v>14.13826046327149</v>
       </c>
       <c r="M8" t="n">
-        <v>53.63262463974404</v>
+        <v>48.28004313002036</v>
       </c>
       <c r="N8" t="n">
-        <v>45.58773094378243</v>
+        <v>48.28004313002036</v>
       </c>
       <c r="O8" t="n">
-        <v>0.4471336110964794</v>
+        <v>-0.03162051901606956</v>
       </c>
       <c r="P8" t="n">
-        <v>20.27621608104271</v>
+        <v>1.460853391719668</v>
       </c>
       <c r="Q8" t="n">
-        <v>20.72334969213919</v>
+        <v>1.429232872703599</v>
       </c>
       <c r="R8" t="n">
-        <v>0.4471336110964794</v>
+        <v>0.03162051901606956</v>
       </c>
       <c r="S8" t="n">
-        <v>20.27621608104271</v>
+        <v>1.460853391719668</v>
       </c>
       <c r="T8" t="n">
-        <v>20.72334969213919</v>
+        <v>1.429232872703599</v>
       </c>
     </row>
     <row r="9">
@@ -957,61 +957,61 @@
         <v>0.014</v>
       </c>
       <c r="B9" t="n">
-        <v>0.1502084332773912</v>
+        <v>0.1464030937600296</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.3051299667039215</v>
+        <v>-0.2971603427617172</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.53133272018195</v>
+        <v>-2.547271968066358</v>
       </c>
       <c r="E9" t="n">
-        <v>0.09227826466974175</v>
+        <v>0.04458590054001688</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.043506684501408</v>
+        <v>-0.09325902180184482</v>
       </c>
       <c r="G9" t="n">
-        <v>2.087013369003324</v>
+        <v>0.1865180436038421</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.3397234960015003</v>
+        <v>0.4515857620985777</v>
       </c>
       <c r="I9" t="n">
-        <v>11.20277452564193</v>
+        <v>10.94114241926202</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.8489547580381873</v>
+        <v>0.4060753594592774</v>
       </c>
       <c r="K9" t="n">
-        <v>11.23220141414488</v>
+        <v>10.94377232367684</v>
       </c>
       <c r="L9" t="n">
-        <v>16.45979931219317</v>
+        <v>14.77949138300558</v>
       </c>
       <c r="M9" t="n">
-        <v>58.05424721679858</v>
+        <v>50.6627092153263</v>
       </c>
       <c r="N9" t="n">
-        <v>49.34611013427879</v>
+        <v>50.6627092153263</v>
       </c>
       <c r="O9" t="n">
-        <v>0.3507350322142301</v>
+        <v>-0.04306228775371796</v>
       </c>
       <c r="P9" t="n">
-        <v>23.41303483738055</v>
+        <v>2.054306485614064</v>
       </c>
       <c r="Q9" t="n">
-        <v>23.76376986959478</v>
+        <v>2.011244197860345</v>
       </c>
       <c r="R9" t="n">
-        <v>0.3507350322142301</v>
+        <v>0.04306228775371796</v>
       </c>
       <c r="S9" t="n">
-        <v>23.41303483738055</v>
+        <v>2.054306485614064</v>
       </c>
       <c r="T9" t="n">
-        <v>23.76376986959478</v>
+        <v>2.011244197860345</v>
       </c>
     </row>
     <row r="10">
@@ -1019,61 +1019,61 @@
         <v>0.016</v>
       </c>
       <c r="B10" t="n">
-        <v>0.1512402727017285</v>
+        <v>0.1465042725824083</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.3072944215322459</v>
+        <v>-0.2973719821955112</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.527003810525302</v>
+        <v>-2.54684868919877</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1080843511410948</v>
+        <v>0.05767768829581212</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.112260202893645</v>
+        <v>-0.1206499874977867</v>
       </c>
       <c r="G10" t="n">
-        <v>2.224520405786797</v>
+        <v>0.2412999749955307</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.1988189179612083</v>
+        <v>0.5242063102734722</v>
       </c>
       <c r="I10" t="n">
-        <v>11.81396872283974</v>
+        <v>11.4616004529163</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.7416018969733071</v>
+        <v>0.4653291163745523</v>
       </c>
       <c r="K10" t="n">
-        <v>11.84533446056133</v>
+        <v>11.46500278256373</v>
       </c>
       <c r="L10" t="n">
-        <v>17.56657669889296</v>
+        <v>15.5406474714693</v>
       </c>
       <c r="M10" t="n">
-        <v>62.53398182093753</v>
+        <v>52.94578379370564</v>
       </c>
       <c r="N10" t="n">
-        <v>53.15388454779689</v>
+        <v>52.94578379370564</v>
       </c>
       <c r="O10" t="n">
-        <v>0.2161454929426774</v>
+        <v>-0.06402850827361119</v>
       </c>
       <c r="P10" t="n">
-        <v>26.32372916520886</v>
+        <v>2.776907471718563</v>
       </c>
       <c r="Q10" t="n">
-        <v>26.53987465815154</v>
+        <v>2.712878963444952</v>
       </c>
       <c r="R10" t="n">
-        <v>0.2161454929426774</v>
+        <v>0.06402850827361119</v>
       </c>
       <c r="S10" t="n">
-        <v>26.32372916520886</v>
+        <v>2.776907471718563</v>
       </c>
       <c r="T10" t="n">
-        <v>26.53987465815154</v>
+        <v>2.712878963444952</v>
       </c>
     </row>
     <row r="11">
@@ -1081,61 +1081,61 @@
         <v>0.018</v>
       </c>
       <c r="B11" t="n">
-        <v>0.1523237427491662</v>
+        <v>0.146639470607072</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.3095688711649115</v>
+        <v>-0.297654810346023</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.52245491125997</v>
+        <v>-2.546283032897747</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1249545214687733</v>
+        <v>0.0726333618168406</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.164441182494852</v>
+        <v>-0.1519483991987851</v>
       </c>
       <c r="G11" t="n">
-        <v>2.328882364989454</v>
+        <v>0.3038967983974715</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.07000746216955059</v>
+        <v>0.4872685700792649</v>
       </c>
       <c r="I11" t="n">
-        <v>12.42537302794652</v>
+        <v>11.96749515590879</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.6382547592270383</v>
+        <v>0.4131177512702578</v>
       </c>
       <c r="K11" t="n">
-        <v>12.45821026929288</v>
+        <v>11.9717801007662</v>
       </c>
       <c r="L11" t="n">
-        <v>18.65794902576715</v>
+        <v>16.13084028120297</v>
       </c>
       <c r="M11" t="n">
-        <v>66.92409413742709</v>
+        <v>55.19657362420181</v>
       </c>
       <c r="N11" t="n">
-        <v>56.88548001681302</v>
+        <v>55.19657362420181</v>
       </c>
       <c r="O11" t="n">
-        <v>0.07832347083319938</v>
+        <v>-0.07224449399979578</v>
       </c>
       <c r="P11" t="n">
-        <v>28.96963808805511</v>
+        <v>3.659019296286166</v>
       </c>
       <c r="Q11" t="n">
-        <v>29.04796155888831</v>
+        <v>3.58677480228637</v>
       </c>
       <c r="R11" t="n">
-        <v>0.1304780909803657</v>
+        <v>0.07224449399979578</v>
       </c>
       <c r="S11" t="n">
-        <v>28.96963808805511</v>
+        <v>3.659019296286166</v>
       </c>
       <c r="T11" t="n">
-        <v>29.04796155888831</v>
+        <v>3.58677480228637</v>
       </c>
     </row>
     <row r="12">
@@ -1143,61 +1143,61 @@
         <v>0.02</v>
       </c>
       <c r="B12" t="n">
-        <v>0.1534421432451628</v>
+        <v>0.1467914864186649</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.311917737250916</v>
+        <v>-0.2979728341035074</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.517757179087961</v>
+        <v>-2.545646985382778</v>
       </c>
       <c r="E12" t="n">
-        <v>0.142544592587377</v>
+        <v>0.08847791163207935</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.205410091062012</v>
+        <v>-0.1851107720949886</v>
       </c>
       <c r="G12" t="n">
-        <v>2.41082018212486</v>
+        <v>0.3702215441898863</v>
       </c>
       <c r="H12" t="n">
-        <v>0.05062245020351591</v>
+        <v>0.4140763891200559</v>
       </c>
       <c r="I12" t="n">
-        <v>13.03691948054381</v>
+        <v>12.46577761665373</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.5376176742347459</v>
+        <v>0.3237423323377015</v>
       </c>
       <c r="K12" t="n">
-        <v>13.07091204511177</v>
+        <v>12.47099774042681</v>
       </c>
       <c r="L12" t="n">
-        <v>19.73889913385963</v>
+        <v>16.66245818934534</v>
       </c>
       <c r="M12" t="n">
-        <v>71.2535729282976</v>
+        <v>57.42482423060746</v>
       </c>
       <c r="N12" t="n">
-        <v>60.56553698905296</v>
+        <v>57.42482423060746</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.06168547191964846</v>
+        <v>-0.07685941102981791</v>
       </c>
       <c r="P12" t="n">
-        <v>31.43640772470796</v>
+        <v>4.618259178616568</v>
       </c>
       <c r="Q12" t="n">
-        <v>31.37472225278831</v>
+        <v>4.54139976758675</v>
       </c>
       <c r="R12" t="n">
-        <v>0.07790872460361446</v>
+        <v>0.07685941102981791</v>
       </c>
       <c r="S12" t="n">
-        <v>31.43640772470796</v>
+        <v>4.618259178616568</v>
       </c>
       <c r="T12" t="n">
-        <v>31.37472225278831</v>
+        <v>4.54139976758675</v>
       </c>
     </row>
     <row r="13">
@@ -1205,61 +1205,61 @@
         <v>0.022</v>
       </c>
       <c r="B13" t="n">
-        <v>0.1546033738544638</v>
+        <v>0.146996591835576</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.314359473764</v>
+        <v>-0.2984019985269621</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.512873706061793</v>
+        <v>-2.544788656535869</v>
       </c>
       <c r="E13" t="n">
-        <v>0.1619867671088955</v>
+        <v>0.1066743688287661</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.226600578546658</v>
+        <v>-0.2232126215581611</v>
       </c>
       <c r="G13" t="n">
-        <v>2.453201157093115</v>
+        <v>0.4464252431163757</v>
       </c>
       <c r="H13" t="n">
-        <v>0.1479688630632462</v>
+        <v>0.4761754140216274</v>
       </c>
       <c r="I13" t="n">
-        <v>13.62595702025168</v>
+        <v>12.93427455811989</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.4506122192675227</v>
+        <v>0.3672476547012448</v>
       </c>
       <c r="K13" t="n">
-        <v>13.66054715656669</v>
+        <v>12.94056915404783</v>
       </c>
       <c r="L13" t="n">
-        <v>20.77483203038565</v>
+        <v>17.37097760672128</v>
       </c>
       <c r="M13" t="n">
-        <v>75.28451064525514</v>
+        <v>59.49017238657576</v>
       </c>
       <c r="N13" t="n">
-        <v>63.99183404846686</v>
+        <v>59.49017238657576</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.1827905771822487</v>
+        <v>-0.1077919810300174</v>
       </c>
       <c r="P13" t="n">
-        <v>33.44314330273032</v>
+        <v>5.796874321169286</v>
       </c>
       <c r="Q13" t="n">
-        <v>33.26035272554807</v>
+        <v>5.689082340139269</v>
       </c>
       <c r="R13" t="n">
-        <v>0.1827905771822487</v>
+        <v>0.1077919810300174</v>
       </c>
       <c r="S13" t="n">
-        <v>33.44314330273032</v>
+        <v>5.796874321169286</v>
       </c>
       <c r="T13" t="n">
-        <v>33.26035272554807</v>
+        <v>5.689082340139269</v>
       </c>
     </row>
     <row r="14">
@@ -1267,61 +1267,61 @@
         <v>0.024</v>
       </c>
       <c r="B14" t="n">
-        <v>0.1557726187310537</v>
+        <v>0.147227244014674</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.3168191161272472</v>
+        <v>-0.2988846740330924</v>
       </c>
       <c r="D14" t="n">
-        <v>-2.507954421335299</v>
+        <v>-2.543823305523608</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1821066726952599</v>
+        <v>0.1258076919500549</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.242435846810195</v>
+        <v>-0.2632872384476654</v>
       </c>
       <c r="G14" t="n">
-        <v>2.484871693619615</v>
+        <v>0.5265744768953836</v>
       </c>
       <c r="H14" t="n">
-        <v>0.2348064866048855</v>
+        <v>0.4769182603822887</v>
       </c>
       <c r="I14" t="n">
-        <v>14.20142885177641</v>
+        <v>13.39315801506353</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.3715022066384895</v>
+        <v>0.348434088019828</v>
       </c>
       <c r="K14" t="n">
-        <v>14.23646554265645</v>
+        <v>13.40058271518776</v>
       </c>
       <c r="L14" t="n">
-        <v>21.78798086059916</v>
+        <v>17.98226174518442</v>
       </c>
       <c r="M14" t="n">
-        <v>79.18272572939492</v>
+        <v>61.53197522236678</v>
       </c>
       <c r="N14" t="n">
-        <v>67.30531686998567</v>
+        <v>61.53197522236678</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.2918196694477683</v>
+        <v>-0.1235782226143609</v>
       </c>
       <c r="P14" t="n">
-        <v>35.29031135242914</v>
+        <v>7.071669686068279</v>
       </c>
       <c r="Q14" t="n">
-        <v>34.99849168298137</v>
+        <v>6.948091463453918</v>
       </c>
       <c r="R14" t="n">
-        <v>0.2918196694477683</v>
+        <v>0.1235782226143609</v>
       </c>
       <c r="S14" t="n">
-        <v>35.29031135242914</v>
+        <v>7.071669686068279</v>
       </c>
       <c r="T14" t="n">
-        <v>34.99849168298137</v>
+        <v>6.948091463453918</v>
       </c>
     </row>
     <row r="15">
@@ -1329,61 +1329,61 @@
         <v>0.026</v>
       </c>
       <c r="B15" t="n">
-        <v>0.1569551228287347</v>
+        <v>0.1474965729589295</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.3193092278922173</v>
+        <v>-0.2994483631550714</v>
       </c>
       <c r="D15" t="n">
-        <v>-2.502974197805358</v>
+        <v>-2.542695927279651</v>
       </c>
       <c r="E15" t="n">
-        <v>0.2038777077206989</v>
+        <v>0.1463593922059876</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.246764315526081</v>
+        <v>-0.3063485454664623</v>
       </c>
       <c r="G15" t="n">
-        <v>2.49352863105295</v>
+        <v>0.6126970909327573</v>
       </c>
       <c r="H15" t="n">
-        <v>0.2944148605579441</v>
+        <v>0.3847703329126044</v>
       </c>
       <c r="I15" t="n">
-        <v>14.73949109088955</v>
+        <v>13.8374870450898</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.3140061254187834</v>
+        <v>0.2352722427249707</v>
       </c>
       <c r="K15" t="n">
-        <v>14.7746498445874</v>
+        <v>13.84612607407195</v>
       </c>
       <c r="L15" t="n">
-        <v>22.74045835383424</v>
+        <v>18.44633560235868</v>
       </c>
       <c r="M15" t="n">
-        <v>82.73838474562538</v>
+        <v>63.53813139528927</v>
       </c>
       <c r="N15" t="n">
-        <v>70.32762703378157</v>
+        <v>63.53813139528927</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.3672079545916056</v>
+        <v>-0.1164335353062001</v>
       </c>
       <c r="P15" t="n">
-        <v>36.75590682827092</v>
+        <v>8.492078019267812</v>
       </c>
       <c r="Q15" t="n">
-        <v>36.38869887367932</v>
+        <v>8.375644483961612</v>
       </c>
       <c r="R15" t="n">
-        <v>0.3672079545916056</v>
+        <v>0.1164335353062001</v>
       </c>
       <c r="S15" t="n">
-        <v>36.75590682827092</v>
+        <v>8.492078019267812</v>
       </c>
       <c r="T15" t="n">
-        <v>36.38869887367932</v>
+        <v>8.375644483961612</v>
       </c>
     </row>
     <row r="16">
@@ -1391,61 +1391,61 @@
         <v>0.028</v>
       </c>
       <c r="B16" t="n">
-        <v>0.1581366926208119</v>
+        <v>0.1478190535297194</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.3217992879160035</v>
+        <v>-0.3001234683821153</v>
       </c>
       <c r="D16" t="n">
-        <v>-2.497994077757786</v>
+        <v>-2.541345716825563</v>
       </c>
       <c r="E16" t="n">
-        <v>0.2268649260098548</v>
+        <v>0.1685495931121893</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.246263081926188</v>
+        <v>-0.3528726552105581</v>
       </c>
       <c r="G16" t="n">
-        <v>2.492526163852864</v>
+        <v>0.7057453104212078</v>
       </c>
       <c r="H16" t="n">
-        <v>0.335610784217529</v>
+        <v>0.3982054713251305</v>
       </c>
       <c r="I16" t="n">
-        <v>15.24355272988936</v>
+        <v>14.25560436500383</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.2725655997624507</v>
+        <v>0.2260036155823781</v>
       </c>
       <c r="K16" t="n">
-        <v>15.27869734879969</v>
+        <v>14.26555537388077</v>
       </c>
       <c r="L16" t="n">
-        <v>23.64555825980998</v>
+        <v>19.0469980176106</v>
       </c>
       <c r="M16" t="n">
-        <v>86.00608364960686</v>
+        <v>65.40608075314296</v>
       </c>
       <c r="N16" t="n">
-        <v>73.10517110216584</v>
+        <v>65.40608075314296</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.4181870823382526</v>
+        <v>-0.1421517472786023</v>
       </c>
       <c r="P16" t="n">
-        <v>37.99234408155354</v>
+        <v>10.08733519536386</v>
       </c>
       <c r="Q16" t="n">
-        <v>37.57415699921529</v>
+        <v>9.945183448085258</v>
       </c>
       <c r="R16" t="n">
-        <v>0.4181870823382526</v>
+        <v>0.1421517472786023</v>
       </c>
       <c r="S16" t="n">
-        <v>37.99234408155354</v>
+        <v>10.08733519536386</v>
       </c>
       <c r="T16" t="n">
-        <v>37.57415699921529</v>
+        <v>9.945183448085258</v>
       </c>
     </row>
     <row r="17">
@@ -1453,61 +1453,61 @@
         <v>0.03</v>
       </c>
       <c r="B17" t="n">
-        <v>0.15931751129134</v>
+        <v>0.1481667141696819</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.3242893063432091</v>
+        <v>-0.3008513689859416</v>
       </c>
       <c r="D17" t="n">
-        <v>-2.493014040903375</v>
+        <v>-2.53988991561791</v>
       </c>
       <c r="E17" t="n">
-        <v>0.250829877337519</v>
+        <v>0.1914854310646693</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.241879078630989</v>
+        <v>-0.4009743853612133</v>
       </c>
       <c r="G17" t="n">
-        <v>2.483758157260669</v>
+        <v>0.8019487707228585</v>
       </c>
       <c r="H17" t="n">
-        <v>0.362004283350398</v>
+        <v>0.4358549273165953</v>
       </c>
       <c r="I17" t="n">
-        <v>15.72028007557031</v>
+        <v>14.66221318262137</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.2440327070215247</v>
+        <v>0.2401794272603232</v>
       </c>
       <c r="K17" t="n">
-        <v>15.75530106558769</v>
+        <v>14.67352066028856</v>
       </c>
       <c r="L17" t="n">
-        <v>24.51256963609596</v>
+        <v>19.67488434687004</v>
       </c>
       <c r="M17" t="n">
-        <v>89.0422811640215</v>
+        <v>67.21948233612662</v>
       </c>
       <c r="N17" t="n">
-        <v>75.68593898941828</v>
+        <v>67.21948233612662</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.4495428191524768</v>
+        <v>-0.1740576738115228</v>
       </c>
       <c r="P17" t="n">
-        <v>39.04455287854479</v>
+        <v>11.76352532761931</v>
       </c>
       <c r="Q17" t="n">
-        <v>38.59501005939232</v>
+        <v>11.58946765380779</v>
       </c>
       <c r="R17" t="n">
-        <v>0.4495428191524768</v>
+        <v>0.1740576738115228</v>
       </c>
       <c r="S17" t="n">
-        <v>39.04455287854479</v>
+        <v>11.76352532761931</v>
       </c>
       <c r="T17" t="n">
-        <v>38.59501005939232</v>
+        <v>11.58946765380779</v>
       </c>
     </row>
     <row r="18">
@@ -1515,61 +1515,61 @@
         <v>0.032</v>
       </c>
       <c r="B18" t="n">
-        <v>0.160488670106283</v>
+        <v>0.1485867212808347</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.3267619795783088</v>
+        <v>-0.301731066523018</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.488068694433176</v>
+        <v>-2.538130520543757</v>
       </c>
       <c r="E18" t="n">
-        <v>0.2766625931279135</v>
+        <v>0.2163129295867934</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.234834950028424</v>
+        <v>-0.4530937935797019</v>
       </c>
       <c r="G18" t="n">
-        <v>2.469669900056827</v>
+        <v>0.9061875871592129</v>
       </c>
       <c r="H18" t="n">
-        <v>0.3559652860011956</v>
+        <v>0.3315916769364962</v>
       </c>
       <c r="I18" t="n">
-        <v>16.13282358146893</v>
+        <v>15.04320632554056</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.2466341696126751</v>
+        <v>0.1104819056696016</v>
       </c>
       <c r="K18" t="n">
-        <v>16.16764592705974</v>
+        <v>15.05598357051951</v>
       </c>
       <c r="L18" t="n">
-        <v>25.29215879705997</v>
+        <v>20.07378902320652</v>
       </c>
       <c r="M18" t="n">
-        <v>91.60013206954135</v>
+        <v>68.96570731130252</v>
       </c>
       <c r="N18" t="n">
-        <v>77.86011225911014</v>
+        <v>68.96570731130252</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.4396145803215375</v>
+        <v>-0.1468609429244618</v>
       </c>
       <c r="P18" t="n">
-        <v>39.8385242436111</v>
+        <v>13.65667755197943</v>
       </c>
       <c r="Q18" t="n">
-        <v>39.39890966328956</v>
+        <v>13.50981660905497</v>
       </c>
       <c r="R18" t="n">
-        <v>0.4396145803215375</v>
+        <v>0.1468609429244618</v>
       </c>
       <c r="S18" t="n">
-        <v>39.8385242436111</v>
+        <v>13.65667755197943</v>
       </c>
       <c r="T18" t="n">
-        <v>39.39890966328956</v>
+        <v>13.50981660905497</v>
       </c>
     </row>
     <row r="19">
@@ -1577,61 +1577,61 @@
         <v>0.034</v>
       </c>
       <c r="B19" t="n">
-        <v>0.1616560952107498</v>
+        <v>0.1490430818472378</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.3292278754535332</v>
+        <v>-0.3026871314980999</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.483136902682727</v>
+        <v>-2.536218390593593</v>
       </c>
       <c r="E19" t="n">
-        <v>0.3031524608703647</v>
+        <v>0.2419505026398209</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.227732835270322</v>
+        <v>-0.5069451539142372</v>
       </c>
       <c r="G19" t="n">
-        <v>2.455465670541697</v>
+        <v>1.013890307828138</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3394332849245827</v>
+        <v>0.2877680509842657</v>
       </c>
       <c r="I19" t="n">
-        <v>16.5216834162065</v>
+        <v>15.40748494909548</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.2597003386873346</v>
+        <v>0.04037881587411797</v>
       </c>
       <c r="K19" t="n">
-        <v>16.55630548216114</v>
+        <v>15.42178080243585</v>
       </c>
       <c r="L19" t="n">
-        <v>26.04127047511572</v>
+        <v>20.55027338212694</v>
       </c>
       <c r="M19" t="n">
-        <v>93.98460009874481</v>
+        <v>70.62642135807621</v>
       </c>
       <c r="N19" t="n">
-        <v>79.88691008393309</v>
+        <v>70.62642135807621</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.4168005585863472</v>
+        <v>-0.1469962750368024</v>
       </c>
       <c r="P19" t="n">
-        <v>40.567344504327</v>
+        <v>15.64162625982735</v>
       </c>
       <c r="Q19" t="n">
-        <v>40.15054394574065</v>
+        <v>15.49462998479055</v>
       </c>
       <c r="R19" t="n">
-        <v>0.4168005585863472</v>
+        <v>0.1469962750368024</v>
       </c>
       <c r="S19" t="n">
-        <v>40.567344504327</v>
+        <v>15.64162625982735</v>
       </c>
       <c r="T19" t="n">
-        <v>40.15054394574065</v>
+        <v>15.49462998479055</v>
       </c>
     </row>
     <row r="20">
@@ -1639,61 +1639,61 @@
         <v>0.036</v>
       </c>
       <c r="B20" t="n">
-        <v>0.1628137461650647</v>
+        <v>0.1495485463939887</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.3316759150035779</v>
+        <v>-0.3037463488461609</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.478240823582638</v>
+        <v>-2.534099955897472</v>
       </c>
       <c r="E20" t="n">
-        <v>0.3312612306518148</v>
+        <v>0.2686822738528858</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.221997707151859</v>
+        <v>-0.563135927162468</v>
       </c>
       <c r="G20" t="n">
-        <v>2.443995414303071</v>
+        <v>1.126271854325098</v>
       </c>
       <c r="H20" t="n">
-        <v>0.2986303614960819</v>
+        <v>0.3255825006898004</v>
       </c>
       <c r="I20" t="n">
-        <v>16.85030427796023</v>
+        <v>15.74918664221176</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.2977045195940252</v>
+        <v>0.05077216823451607</v>
       </c>
       <c r="K20" t="n">
-        <v>16.8847646133019</v>
+        <v>15.76506707535774</v>
       </c>
       <c r="L20" t="n">
-        <v>26.7157838098677</v>
+        <v>21.13154753840705</v>
       </c>
       <c r="M20" t="n">
-        <v>95.93319758515322</v>
+        <v>72.17163257523194</v>
       </c>
       <c r="N20" t="n">
-        <v>81.54321794738024</v>
+        <v>72.17163257523194</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.3650617837804264</v>
+        <v>-0.1840500534192869</v>
       </c>
       <c r="P20" t="n">
-        <v>41.17987305026563</v>
+        <v>17.75056793313519</v>
       </c>
       <c r="Q20" t="n">
-        <v>40.8148112664852</v>
+        <v>17.5665178797159</v>
       </c>
       <c r="R20" t="n">
-        <v>0.3650617837804264</v>
+        <v>0.1840500534192869</v>
       </c>
       <c r="S20" t="n">
-        <v>41.17987305026563</v>
+        <v>17.75056793313519</v>
       </c>
       <c r="T20" t="n">
-        <v>40.8148112664852</v>
+        <v>17.5665178797159</v>
       </c>
     </row>
     <row r="21">
@@ -1701,61 +1701,61 @@
         <v>0.038</v>
       </c>
       <c r="B21" t="n">
-        <v>0.1639680698973427</v>
+        <v>0.1501242714922729</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.3341186898370312</v>
+        <v>-0.3049533770027137</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.473355273915731</v>
+        <v>-2.531685899584366</v>
       </c>
       <c r="E21" t="n">
-        <v>0.3602994296153517</v>
+        <v>0.2967478390227744</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.219005458933033</v>
+        <v>-0.6222037167570618</v>
       </c>
       <c r="G21" t="n">
-        <v>2.438010917865533</v>
+        <v>1.244407433514205</v>
       </c>
       <c r="H21" t="n">
-        <v>0.2421413012655994</v>
+        <v>0.2442827504939239</v>
       </c>
       <c r="I21" t="n">
-        <v>17.13929564886921</v>
+        <v>16.06655355782987</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.3527333626937205</v>
+        <v>-0.05935266328352228</v>
       </c>
       <c r="K21" t="n">
-        <v>17.17367160281112</v>
+        <v>16.08409970264243</v>
       </c>
       <c r="L21" t="n">
-        <v>27.34101914194695</v>
+        <v>21.51650739723206</v>
       </c>
       <c r="M21" t="n">
-        <v>97.62269954749092</v>
+        <v>73.649564302915</v>
       </c>
       <c r="N21" t="n">
-        <v>82.97929461536729</v>
+        <v>73.649564302915</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.2951878246550604</v>
+        <v>-0.147191244541638</v>
       </c>
       <c r="P21" t="n">
-        <v>41.78567554688167</v>
+        <v>20.01872440243642</v>
       </c>
       <c r="Q21" t="n">
-        <v>41.49048772222661</v>
+        <v>19.87153315789478</v>
       </c>
       <c r="R21" t="n">
-        <v>0.2951878246550604</v>
+        <v>0.147191244541638</v>
       </c>
       <c r="S21" t="n">
-        <v>41.78567554688167</v>
+        <v>20.01872440243642</v>
       </c>
       <c r="T21" t="n">
-        <v>41.49048772222661</v>
+        <v>19.87153315789478</v>
       </c>
     </row>
     <row r="22">
@@ -1763,61 +1763,61 @@
         <v>0.04</v>
       </c>
       <c r="B22" t="n">
-        <v>0.1651192251917341</v>
+        <v>0.1507319404649332</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.3365564512005915</v>
+        <v>-0.3062276466732657</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.46847975118861</v>
+        <v>-2.529137360243261</v>
       </c>
       <c r="E22" t="n">
-        <v>0.3902227028542811</v>
+        <v>0.325389028825371</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.21862519287105</v>
+        <v>-0.6825175635218678</v>
       </c>
       <c r="G22" t="n">
-        <v>2.437250385743409</v>
+        <v>1.365035127043598</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1707146896527194</v>
+        <v>0.1426368606922963</v>
       </c>
       <c r="I22" t="n">
-        <v>17.3905487567996</v>
+        <v>16.37179924657119</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.423974404468353</v>
+        <v>-0.1904317103063752</v>
       </c>
       <c r="K22" t="n">
-        <v>17.42491398723858</v>
+        <v>16.3910462418625</v>
       </c>
       <c r="L22" t="n">
-        <v>27.91932815263566</v>
+        <v>21.86214512777263</v>
       </c>
       <c r="M22" t="n">
-        <v>99.0654707339459</v>
+        <v>75.08335234172543</v>
       </c>
       <c r="N22" t="n">
-        <v>84.20565012385401</v>
+        <v>75.08335234172543</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.2080441418864108</v>
+        <v>-0.09761579782010779</v>
       </c>
       <c r="P22" t="n">
-        <v>42.38507297967448</v>
+        <v>22.35385931991017</v>
       </c>
       <c r="Q22" t="n">
-        <v>42.17702883778806</v>
+        <v>22.25624352209007</v>
       </c>
       <c r="R22" t="n">
-        <v>0.2080441418864108</v>
+        <v>0.09761579782010779</v>
       </c>
       <c r="S22" t="n">
-        <v>42.38507297967448</v>
+        <v>22.35385931991017</v>
       </c>
       <c r="T22" t="n">
-        <v>42.17702883778806</v>
+        <v>22.25624352209007</v>
       </c>
     </row>
     <row r="23">
@@ -1825,61 +1825,61 @@
         <v>0.042</v>
       </c>
       <c r="B23" t="n">
-        <v>0.1662736198712599</v>
+        <v>0.1514258576488921</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.3390040010724412</v>
+        <v>-0.3076836793447527</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.46358465144491</v>
+        <v>-2.526225294900288</v>
       </c>
       <c r="E23" t="n">
-        <v>0.4214520729936305</v>
+        <v>0.3554196620970418</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.224701362855879</v>
+        <v>-0.7458640918270539</v>
       </c>
       <c r="G23" t="n">
-        <v>2.449402725711856</v>
+        <v>1.491728183654041</v>
       </c>
       <c r="H23" t="n">
-        <v>0.08227638989779323</v>
+        <v>0.1669879963649815</v>
       </c>
       <c r="I23" t="n">
-        <v>17.58104091757924</v>
+        <v>16.63865869157774</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.515377875175876</v>
+        <v>-0.1969936804466208</v>
       </c>
       <c r="K23" t="n">
-        <v>17.61557749601177</v>
+        <v>16.65969205896726</v>
       </c>
       <c r="L23" t="n">
-        <v>28.43108115727134</v>
+        <v>22.36882805041581</v>
       </c>
       <c r="M23" t="n">
-        <v>100.12987143683</v>
+        <v>76.32541131312928</v>
       </c>
       <c r="N23" t="n">
-        <v>85.11039072130548</v>
+        <v>76.32541131312928</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.1002848949250411</v>
+        <v>-0.1254873190662198</v>
       </c>
       <c r="P23" t="n">
-        <v>43.06490769688701</v>
+        <v>24.8408922329319</v>
       </c>
       <c r="Q23" t="n">
-        <v>42.96462280196197</v>
+        <v>24.71540491386568</v>
       </c>
       <c r="R23" t="n">
-        <v>0.1002848949250411</v>
+        <v>0.1254873190662198</v>
       </c>
       <c r="S23" t="n">
-        <v>43.06490769688701</v>
+        <v>24.8408922329319</v>
       </c>
       <c r="T23" t="n">
-        <v>42.96462280196197</v>
+        <v>24.71540491386568</v>
       </c>
     </row>
     <row r="24">
@@ -1887,61 +1887,61 @@
         <v>0.044</v>
       </c>
       <c r="B24" t="n">
-        <v>0.1674312584276098</v>
+        <v>0.1521659066372446</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.3414595744548679</v>
+        <v>-0.3092371346161183</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.458673504680057</v>
+        <v>-2.523118384357557</v>
       </c>
       <c r="E24" t="n">
-        <v>0.4531414634116908</v>
+        <v>0.3860742948129997</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.233452305533906</v>
+        <v>-0.8105946425205065</v>
       </c>
       <c r="G24" t="n">
-        <v>2.466904611066617</v>
+        <v>1.621189285041089</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.01273239272786142</v>
+        <v>0.1209857811892221</v>
       </c>
       <c r="I24" t="n">
-        <v>17.74867905927334</v>
+        <v>16.88947574254042</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.6146571178284074</v>
+        <v>-0.2745844043607851</v>
       </c>
       <c r="K24" t="n">
-        <v>17.78346241428938</v>
+        <v>16.91233451145949</v>
       </c>
       <c r="L24" t="n">
-        <v>28.91742005070443</v>
+        <v>22.75664103215388</v>
       </c>
       <c r="M24" t="n">
-        <v>101.0579526134805</v>
+        <v>77.52106030538</v>
       </c>
       <c r="N24" t="n">
-        <v>85.89925972145841</v>
+        <v>77.52106030538</v>
       </c>
       <c r="O24" t="n">
-        <v>0.01613203911631498</v>
+        <v>-0.09332604557642502</v>
       </c>
       <c r="P24" t="n">
-        <v>43.78511988809567</v>
+        <v>27.39780822346564</v>
       </c>
       <c r="Q24" t="n">
-        <v>43.80125192721199</v>
+        <v>27.30448217788922</v>
       </c>
       <c r="R24" t="n">
-        <v>0.02565234500971721</v>
+        <v>0.1112088505456648</v>
       </c>
       <c r="S24" t="n">
-        <v>43.78511988809567</v>
+        <v>27.39780822346564</v>
       </c>
       <c r="T24" t="n">
-        <v>43.80125192721199</v>
+        <v>27.30448217788922</v>
       </c>
     </row>
     <row r="25">
@@ -1949,61 +1949,61 @@
         <v>0.046</v>
       </c>
       <c r="B25" t="n">
-        <v>0.1686034670413478</v>
+        <v>0.1529616560094989</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.3439491594205626</v>
+        <v>-0.3109082197154363</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.453694334748667</v>
+        <v>-2.519776214158921</v>
       </c>
       <c r="E25" t="n">
-        <v>0.4859309931123427</v>
+        <v>0.4174823558645315</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.249898182326363</v>
+        <v>-0.8769962871451082</v>
       </c>
       <c r="G25" t="n">
-        <v>2.499796364653278</v>
+        <v>1.753992574290521</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.1253294749937992</v>
+        <v>-0.009962355841224263</v>
       </c>
       <c r="I25" t="n">
-        <v>17.85695354137159</v>
+        <v>17.1209229136839</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.7352797879690642</v>
+        <v>-0.4379365439680371</v>
       </c>
       <c r="K25" t="n">
-        <v>17.8922006701132</v>
+        <v>17.14565420898139</v>
       </c>
       <c r="L25" t="n">
-        <v>29.3365915036102</v>
+        <v>23.00092827433268</v>
       </c>
       <c r="M25" t="n">
-        <v>101.6501331721379</v>
+        <v>78.66067304043932</v>
       </c>
       <c r="N25" t="n">
-        <v>86.40261319631723</v>
+        <v>78.66067304043932</v>
       </c>
       <c r="O25" t="n">
-        <v>0.1577783069906202</v>
+        <v>0.01131992166079682</v>
       </c>
       <c r="P25" t="n">
-        <v>44.6409192927287</v>
+        <v>30.0391023192312</v>
       </c>
       <c r="Q25" t="n">
-        <v>44.79869759971932</v>
+        <v>30.050422240892</v>
       </c>
       <c r="R25" t="n">
-        <v>0.1610757793632293</v>
+        <v>0.04603771389039353</v>
       </c>
       <c r="S25" t="n">
-        <v>44.6409192927287</v>
+        <v>30.0391023192312</v>
       </c>
       <c r="T25" t="n">
-        <v>44.79869759971932</v>
+        <v>30.050422240892</v>
       </c>
     </row>
     <row r="26">
@@ -2011,61 +2011,61 @@
         <v>0.048</v>
       </c>
       <c r="B26" t="n">
-        <v>0.1697900945529388</v>
+        <v>0.1538417983883552</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.3464712019652739</v>
+        <v>-0.3127579653429182</v>
       </c>
       <c r="D26" t="n">
-        <v>-2.448650249659245</v>
+        <v>-2.516076722903956</v>
       </c>
       <c r="E26" t="n">
-        <v>0.5191507791003723</v>
+        <v>0.4498336295291155</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.270193467936519</v>
+        <v>-0.9455369948708091</v>
       </c>
       <c r="G26" t="n">
-        <v>2.54038693587372</v>
+        <v>1.891073989741656</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.2385900163220737</v>
+        <v>-0.02842663000741689</v>
       </c>
       <c r="I26" t="n">
-        <v>17.92801530231662</v>
+        <v>17.31500954167881</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.8584444286750952</v>
+        <v>-0.4898486835043717</v>
       </c>
       <c r="K26" t="n">
-        <v>17.96383475811244</v>
+        <v>17.34167368493417</v>
       </c>
       <c r="L26" t="n">
-        <v>29.72802051113145</v>
+        <v>23.38898533793781</v>
       </c>
       <c r="M26" t="n">
-        <v>102.0788626409346</v>
+        <v>79.61698559988005</v>
       </c>
       <c r="N26" t="n">
-        <v>86.76703324479438</v>
+        <v>79.61698559988005</v>
       </c>
       <c r="O26" t="n">
-        <v>0.304653830544622</v>
+        <v>0.02638375172694456</v>
       </c>
       <c r="P26" t="n">
-        <v>45.54491223497331</v>
+        <v>32.76144413083021</v>
       </c>
       <c r="Q26" t="n">
-        <v>45.84956606551793</v>
+        <v>32.78782788255715</v>
       </c>
       <c r="R26" t="n">
-        <v>0.304653830544622</v>
+        <v>0.02638375172694456</v>
       </c>
       <c r="S26" t="n">
-        <v>45.54491223497331</v>
+        <v>32.76144413083021</v>
       </c>
       <c r="T26" t="n">
-        <v>45.84956606551793</v>
+        <v>32.78782788255715</v>
       </c>
     </row>
     <row r="27">
@@ -2073,61 +2073,61 @@
         <v>0.05</v>
       </c>
       <c r="B27" t="n">
-        <v>0.170992975072246</v>
+        <v>0.1547587739321581</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.3490298307517063</v>
+        <v>-0.3146857786548042</v>
       </c>
       <c r="D27" t="n">
-        <v>-2.44353299208638</v>
+        <v>-2.512221096280185</v>
       </c>
       <c r="E27" t="n">
-        <v>0.552855550753044</v>
+        <v>0.4825630768437127</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.294827814122195</v>
+        <v>-1.014945453879386</v>
       </c>
       <c r="G27" t="n">
-        <v>2.589655628243376</v>
+        <v>2.029890907758505</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.3525984099043412</v>
+        <v>-0.03942219204684674</v>
       </c>
       <c r="I27" t="n">
-        <v>17.95713081673121</v>
+        <v>17.49409998934578</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.9844743831959726</v>
+        <v>-0.5347155735399871</v>
       </c>
       <c r="K27" t="n">
-        <v>17.99364496108944</v>
+        <v>17.52272145114518</v>
       </c>
       <c r="L27" t="n">
-        <v>30.08817818408229</v>
+        <v>23.77671066208134</v>
       </c>
       <c r="M27" t="n">
-        <v>102.3233497458701</v>
+        <v>80.50991021175621</v>
       </c>
       <c r="N27" t="n">
-        <v>86.97484728398958</v>
+        <v>80.50991021175621</v>
       </c>
       <c r="O27" t="n">
-        <v>0.4574237805504869</v>
+        <v>0.042180326309015</v>
       </c>
       <c r="P27" t="n">
-        <v>46.50322901990351</v>
+        <v>35.51547115033173</v>
       </c>
       <c r="Q27" t="n">
-        <v>46.960652800454</v>
+        <v>35.55765147664075</v>
       </c>
       <c r="R27" t="n">
-        <v>0.4574237805504869</v>
+        <v>0.042180326309015</v>
       </c>
       <c r="S27" t="n">
-        <v>46.50322901990351</v>
+        <v>35.51547115033173</v>
       </c>
       <c r="T27" t="n">
-        <v>46.960652800454</v>
+        <v>35.55765147664075</v>
       </c>
     </row>
     <row r="28">
@@ -2135,61 +2135,61 @@
         <v>0.052</v>
       </c>
       <c r="B28" t="n">
-        <v>0.1722303190978648</v>
+        <v>0.1557702787238894</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.3516651129960671</v>
+        <v>-0.316814282939907</v>
       </c>
       <c r="D28" t="n">
-        <v>-2.438262427597659</v>
+        <v>-2.507964087709979</v>
       </c>
       <c r="E28" t="n">
-        <v>0.5870832864035619</v>
+        <v>0.516140006117625</v>
       </c>
       <c r="F28" t="n">
-        <v>-1.326177609486279</v>
+        <v>-1.086338977621626</v>
       </c>
       <c r="G28" t="n">
-        <v>2.652355218972449</v>
+        <v>2.172677955243238</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.4783515173048836</v>
+        <v>-0.1842138594540767</v>
       </c>
       <c r="I28" t="n">
-        <v>17.96253990248105</v>
+        <v>17.6395171360479</v>
       </c>
       <c r="J28" t="n">
-        <v>-1.125526190734188</v>
+        <v>-0.71434728053343</v>
       </c>
       <c r="K28" t="n">
-        <v>17.99993811106856</v>
+        <v>17.67015189521683</v>
       </c>
       <c r="L28" t="n">
-        <v>30.33225372958709</v>
+        <v>23.93177643991894</v>
       </c>
       <c r="M28" t="n">
-        <v>102.3400800378955</v>
+        <v>81.30120527598719</v>
       </c>
       <c r="N28" t="n">
-        <v>86.98906803221118</v>
+        <v>81.30120527598719</v>
       </c>
       <c r="O28" t="n">
-        <v>0.6373844766935622</v>
+        <v>0.2062288551921539</v>
       </c>
       <c r="P28" t="n">
-        <v>47.64299375337482</v>
+        <v>38.33726313155465</v>
       </c>
       <c r="Q28" t="n">
-        <v>48.28037823006838</v>
+        <v>38.54349198674681</v>
       </c>
       <c r="R28" t="n">
-        <v>0.6373844766935622</v>
+        <v>0.2062288551921539</v>
       </c>
       <c r="S28" t="n">
-        <v>47.64299375337482</v>
+        <v>38.33726313155465</v>
       </c>
       <c r="T28" t="n">
-        <v>48.28037823006838</v>
+        <v>38.54349198674681</v>
       </c>
     </row>
     <row r="29">
@@ -2197,61 +2197,61 @@
         <v>0.054</v>
       </c>
       <c r="B29" t="n">
-        <v>0.1734833388776607</v>
+        <v>0.1568358972682814</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.3543351656981921</v>
+        <v>-0.3190580542593901</v>
       </c>
       <c r="D29" t="n">
-        <v>-2.432922322193409</v>
+        <v>-2.503476545071013</v>
       </c>
       <c r="E29" t="n">
-        <v>0.6215269591507254</v>
+        <v>0.5500888774072863</v>
       </c>
       <c r="F29" t="n">
-        <v>-1.360635032102857</v>
+        <v>-1.158648080352863</v>
       </c>
       <c r="G29" t="n">
-        <v>2.721270064206858</v>
+        <v>2.317296160705709</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.60760191116186</v>
+        <v>-0.2610547597314152</v>
       </c>
       <c r="I29" t="n">
-        <v>17.96158529998867</v>
+        <v>17.76057781132135</v>
       </c>
       <c r="J29" t="n">
-        <v>-1.271591806828054</v>
+        <v>-0.8264750229436122</v>
       </c>
       <c r="K29" t="n">
-        <v>17.99995520789398</v>
+        <v>17.7932516871873</v>
       </c>
       <c r="L29" t="n">
-        <v>30.52541763986686</v>
+        <v>24.1741016290527</v>
       </c>
       <c r="M29" t="n">
-        <v>102.2756254547529</v>
+        <v>81.97439886028698</v>
       </c>
       <c r="N29" t="n">
-        <v>86.93428163653998</v>
+        <v>81.97439886028698</v>
       </c>
       <c r="O29" t="n">
-        <v>0.8277467809400223</v>
+        <v>0.3026121931021309</v>
       </c>
       <c r="P29" t="n">
-        <v>48.8783046835624</v>
+        <v>41.16437465728276</v>
       </c>
       <c r="Q29" t="n">
-        <v>49.70605146450242</v>
+        <v>41.46698685038489</v>
       </c>
       <c r="R29" t="n">
-        <v>0.8277467809400223</v>
+        <v>0.3026121931021309</v>
       </c>
       <c r="S29" t="n">
-        <v>48.8783046835624</v>
+        <v>41.16437465728276</v>
       </c>
       <c r="T29" t="n">
-        <v>49.70605146450242</v>
+        <v>41.46698685038489</v>
       </c>
     </row>
     <row r="30">
@@ -2259,61 +2259,61 @@
         <v>0.056</v>
       </c>
       <c r="B30" t="n">
-        <v>0.1747895082798712</v>
+        <v>0.1579599895334822</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.3571226507692072</v>
+        <v>-0.3214263797274102</v>
       </c>
       <c r="D30" t="n">
-        <v>-2.427347352051379</v>
+        <v>-2.498739894134973</v>
       </c>
       <c r="E30" t="n">
-        <v>0.6565972762312424</v>
+        <v>0.5844396582396528</v>
       </c>
       <c r="F30" t="n">
-        <v>-1.405884477141734</v>
+        <v>-1.231946530663016</v>
       </c>
       <c r="G30" t="n">
-        <v>2.811768954283021</v>
+        <v>2.463893061325736</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.7398362442402246</v>
+        <v>-0.2644700705694382</v>
       </c>
       <c r="I30" t="n">
-        <v>17.96031131282974</v>
+        <v>17.85531960386767</v>
       </c>
       <c r="J30" t="n">
-        <v>-1.425907869085391</v>
+        <v>-0.86565997753299</v>
       </c>
       <c r="K30" t="n">
-        <v>17.99995725508513</v>
+        <v>17.89006049603236</v>
       </c>
       <c r="L30" t="n">
-        <v>30.55504607312645</v>
+        <v>24.51071675749356</v>
       </c>
       <c r="M30" t="n">
-        <v>102.0437067569055</v>
+        <v>82.51997547801119</v>
       </c>
       <c r="N30" t="n">
-        <v>86.73715074336963</v>
+        <v>82.51997547801119</v>
       </c>
       <c r="O30" t="n">
-        <v>1.043918993562879</v>
+        <v>0.3258785267223554</v>
       </c>
       <c r="P30" t="n">
-        <v>50.50017263996438</v>
+        <v>43.99723432548728</v>
       </c>
       <c r="Q30" t="n">
-        <v>51.54409163352725</v>
+        <v>44.32311285220964</v>
       </c>
       <c r="R30" t="n">
-        <v>1.043918993562879</v>
+        <v>0.3258785267223554</v>
       </c>
       <c r="S30" t="n">
-        <v>50.50017263996438</v>
+        <v>43.99723432548728</v>
       </c>
       <c r="T30" t="n">
-        <v>51.54409163352725</v>
+        <v>44.32311285220964</v>
       </c>
     </row>
     <row r="31">
@@ -2321,61 +2321,61 @@
         <v>0.058</v>
       </c>
       <c r="B31" t="n">
-        <v>0.1761301153087713</v>
+        <v>0.1591785716899572</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.3599859269744105</v>
+        <v>-0.3239967452592443</v>
       </c>
       <c r="D31" t="n">
-        <v>-2.421620799640972</v>
+        <v>-2.493599163071305</v>
       </c>
       <c r="E31" t="n">
-        <v>0.6919991194632432</v>
+        <v>0.6192457219904247</v>
       </c>
       <c r="F31" t="n">
-        <v>-1.457497002148071</v>
+        <v>-1.306467133850382</v>
       </c>
       <c r="G31" t="n">
-        <v>2.914994004295527</v>
+        <v>2.612934267700758</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.8741735180197523</v>
+        <v>-0.3953536116528379</v>
       </c>
       <c r="I31" t="n">
-        <v>17.95885622703466</v>
+        <v>17.91498952345574</v>
       </c>
       <c r="J31" t="n">
-        <v>-1.585432055068011</v>
+        <v>-1.032909572971824</v>
       </c>
       <c r="K31" t="n">
-        <v>17.99995764249523</v>
+        <v>17.95183189663032</v>
       </c>
       <c r="L31" t="n">
-        <v>30.53307247852565</v>
+        <v>24.61834315891178</v>
       </c>
       <c r="M31" t="n">
-        <v>101.7806459346925</v>
+        <v>82.955174781319</v>
       </c>
       <c r="N31" t="n">
-        <v>86.51354904448863</v>
+        <v>82.955174781319</v>
       </c>
       <c r="O31" t="n">
-        <v>1.278525744221311</v>
+        <v>0.5246446835394629</v>
       </c>
       <c r="P31" t="n">
-        <v>52.34984882398223</v>
+        <v>46.81604529098314</v>
       </c>
       <c r="Q31" t="n">
-        <v>53.62837456820354</v>
+        <v>47.3406899745226</v>
       </c>
       <c r="R31" t="n">
-        <v>1.278525744221311</v>
+        <v>0.5246446835394629</v>
       </c>
       <c r="S31" t="n">
-        <v>52.34984882398223</v>
+        <v>46.81604529098314</v>
       </c>
       <c r="T31" t="n">
-        <v>53.62837456820354</v>
+        <v>47.3406899745226</v>
       </c>
     </row>
     <row r="32">
@@ -2383,61 +2383,61 @@
         <v>0.06</v>
       </c>
       <c r="B32" t="n">
-        <v>0.1775167502233924</v>
+        <v>0.1604367152051878</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.3629505024269315</v>
+        <v>-0.3266518821503147</v>
       </c>
       <c r="D32" t="n">
-        <v>-2.41569164873593</v>
+        <v>-2.488288889289164</v>
       </c>
       <c r="E32" t="n">
-        <v>0.7278440666277967</v>
+        <v>0.6542041176679407</v>
       </c>
       <c r="F32" t="n">
-        <v>-1.517614152639035</v>
+        <v>-1.381425722791013</v>
       </c>
       <c r="G32" t="n">
-        <v>3.035228305279187</v>
+        <v>2.762851445582323</v>
       </c>
       <c r="H32" t="n">
-        <v>-1.011321494033297</v>
+        <v>-0.5300550005825861</v>
       </c>
       <c r="I32" t="n">
-        <v>17.95715909240724</v>
+        <v>17.95841447528031</v>
       </c>
       <c r="J32" t="n">
-        <v>-1.751917200521146</v>
+        <v>-1.2041907533046</v>
       </c>
       <c r="K32" t="n">
-        <v>17.99995581151168</v>
+        <v>17.99737068066302</v>
       </c>
       <c r="L32" t="n">
-        <v>30.44212978037058</v>
+        <v>24.70699135645055</v>
       </c>
       <c r="M32" t="n">
-        <v>101.4759618567797</v>
+        <v>83.324379242398</v>
       </c>
       <c r="N32" t="n">
-        <v>86.25456757826275</v>
+        <v>83.324379242398</v>
       </c>
       <c r="O32" t="n">
-        <v>1.537771324310838</v>
+        <v>0.7325330224477017</v>
       </c>
       <c r="P32" t="n">
-        <v>54.50400391885729</v>
+        <v>49.61641522130546</v>
       </c>
       <c r="Q32" t="n">
-        <v>56.04177524316813</v>
+        <v>50.34894824375316</v>
       </c>
       <c r="R32" t="n">
-        <v>1.537771324310838</v>
+        <v>0.7325330224477017</v>
       </c>
       <c r="S32" t="n">
-        <v>54.50400391885729</v>
+        <v>49.61641522130546</v>
       </c>
       <c r="T32" t="n">
-        <v>56.04177524316813</v>
+        <v>50.34894824375316</v>
       </c>
     </row>
     <row r="33">
@@ -2445,61 +2445,61 @@
         <v>0.062</v>
       </c>
       <c r="B33" t="n">
-        <v>0.1789808070524687</v>
+        <v>0.1617918432411418</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.3660852983991668</v>
+        <v>-0.3295153019621189</v>
       </c>
       <c r="D33" t="n">
-        <v>-2.40942205679146</v>
+        <v>-2.482562049665555</v>
       </c>
       <c r="E33" t="n">
-        <v>0.7642696790853035</v>
+        <v>0.6894370622525022</v>
       </c>
       <c r="F33" t="n">
-        <v>-1.589162581041375</v>
+        <v>-1.457267649050029</v>
       </c>
       <c r="G33" t="n">
-        <v>3.178325162082944</v>
+        <v>2.914535298100112</v>
       </c>
       <c r="H33" t="n">
-        <v>-1.15235679782443</v>
+        <v>-0.5461313402671381</v>
       </c>
       <c r="I33" t="n">
-        <v>17.95513699964857</v>
+        <v>17.9579831892049</v>
       </c>
       <c r="J33" t="n">
-        <v>-1.927868137372621</v>
+        <v>-1.257277953003552</v>
       </c>
       <c r="K33" t="n">
-        <v>17.99995138443394</v>
+        <v>17.99907813690811</v>
       </c>
       <c r="L33" t="n">
-        <v>30.3581218242867</v>
+        <v>24.94772698679971</v>
       </c>
       <c r="M33" t="n">
-        <v>101.1955630177573</v>
+        <v>83.4807038056998</v>
       </c>
       <c r="N33" t="n">
-        <v>86.01622856509373</v>
+        <v>83.4807038056998</v>
       </c>
       <c r="O33" t="n">
-        <v>1.838770462951836</v>
+        <v>0.7965584550604252</v>
       </c>
       <c r="P33" t="n">
-        <v>57.06703941245202</v>
+        <v>52.3391383872005</v>
       </c>
       <c r="Q33" t="n">
-        <v>58.90580987540385</v>
+        <v>53.13569684226092</v>
       </c>
       <c r="R33" t="n">
-        <v>1.838770462951836</v>
+        <v>0.7965584550604252</v>
       </c>
       <c r="S33" t="n">
-        <v>57.06703941245202</v>
+        <v>52.3391383872005</v>
       </c>
       <c r="T33" t="n">
-        <v>58.90580987540385</v>
+        <v>53.13569684226092</v>
       </c>
     </row>
     <row r="34">
@@ -2507,61 +2507,61 @@
         <v>0.064</v>
       </c>
       <c r="B34" t="n">
-        <v>0.1804794107539863</v>
+        <v>0.1632065038610029</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.3692960771954614</v>
+        <v>-0.3325072110236712</v>
       </c>
       <c r="D34" t="n">
-        <v>-2.40300049919887</v>
+        <v>-2.47657823154245</v>
       </c>
       <c r="E34" t="n">
-        <v>0.8009397978801563</v>
+        <v>0.724773187642365</v>
       </c>
       <c r="F34" t="n">
-        <v>-1.665493331743682</v>
+        <v>-1.533536977930622</v>
       </c>
       <c r="G34" t="n">
-        <v>3.330986663485973</v>
+        <v>3.067073955861193</v>
       </c>
       <c r="H34" t="n">
-        <v>-1.29500906637296</v>
+        <v>-0.6384089591233365</v>
       </c>
       <c r="I34" t="n">
-        <v>17.95297869059135</v>
+        <v>17.95667493906252</v>
       </c>
       <c r="J34" t="n">
-        <v>-2.107769812263877</v>
+        <v>-1.38677500435348</v>
       </c>
       <c r="K34" t="n">
-        <v>17.99994560254651</v>
+        <v>17.99992068184016</v>
       </c>
       <c r="L34" t="n">
-        <v>30.27875322830055</v>
+        <v>25.05647777811547</v>
       </c>
       <c r="M34" t="n">
-        <v>100.931046851151</v>
+        <v>83.65712749506473</v>
       </c>
       <c r="N34" t="n">
-        <v>85.79138982347835</v>
+        <v>83.65712749506473</v>
       </c>
       <c r="O34" t="n">
-        <v>2.158236477955629</v>
+        <v>0.9864589753113882</v>
       </c>
       <c r="P34" t="n">
-        <v>59.80108415437118</v>
+        <v>55.07425684163188</v>
       </c>
       <c r="Q34" t="n">
-        <v>61.95932063232681</v>
+        <v>56.06071581694327</v>
       </c>
       <c r="R34" t="n">
-        <v>2.158236477955629</v>
+        <v>0.9864589753113882</v>
       </c>
       <c r="S34" t="n">
-        <v>59.80108415437118</v>
+        <v>55.07425684163188</v>
       </c>
       <c r="T34" t="n">
-        <v>61.95932063232681</v>
+        <v>56.06071581694327</v>
       </c>
     </row>
     <row r="35">
@@ -2569,61 +2569,61 @@
         <v>0.066</v>
       </c>
       <c r="B35" t="n">
-        <v>0.1820952842608633</v>
+        <v>0.1646787627805698</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.3727650756948901</v>
+        <v>-0.3356234345669789</v>
       </c>
       <c r="D35" t="n">
-        <v>-2.396062502200013</v>
+        <v>-2.470345784455836</v>
       </c>
       <c r="E35" t="n">
-        <v>0.8382847712793073</v>
+        <v>0.7602091413708882</v>
       </c>
       <c r="F35" t="n">
-        <v>-1.754672725494091</v>
+        <v>-1.610219822615114</v>
       </c>
       <c r="G35" t="n">
-        <v>3.509345450988576</v>
+        <v>3.22043964523021</v>
       </c>
       <c r="H35" t="n">
-        <v>-1.441900033060433</v>
+        <v>-0.8044119872872363</v>
       </c>
       <c r="I35" t="n">
-        <v>17.95045136358845</v>
+        <v>17.95451821845495</v>
       </c>
       <c r="J35" t="n">
-        <v>-2.298180323101549</v>
+        <v>-1.590199260723412</v>
       </c>
       <c r="K35" t="n">
-        <v>17.99993313444739</v>
+        <v>17.99992641745269</v>
       </c>
       <c r="L35" t="n">
-        <v>30.23155325699364</v>
+        <v>25.03753207422897</v>
       </c>
       <c r="M35" t="n">
-        <v>100.774076876822</v>
+        <v>83.85299726606817</v>
       </c>
       <c r="N35" t="n">
-        <v>85.65796534529868</v>
+        <v>83.85299726606817</v>
       </c>
       <c r="O35" t="n">
-        <v>2.538643218755034</v>
+        <v>1.29814475243275</v>
       </c>
       <c r="P35" t="n">
-        <v>62.99403957106987</v>
+        <v>57.82136784698581</v>
       </c>
       <c r="Q35" t="n">
-        <v>65.5326827898249</v>
+        <v>59.11951259941856</v>
       </c>
       <c r="R35" t="n">
-        <v>2.538643218755034</v>
+        <v>1.29814475243275</v>
       </c>
       <c r="S35" t="n">
-        <v>62.99403957106987</v>
+        <v>57.82136784698581</v>
       </c>
       <c r="T35" t="n">
-        <v>65.5326827898249</v>
+        <v>59.11951259941856</v>
       </c>
     </row>
     <row r="36">
@@ -2631,61 +2631,61 @@
         <v>0.068</v>
       </c>
       <c r="B36" t="n">
-        <v>0.1837665744759077</v>
+        <v>0.1662512364863071</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.3763565471099967</v>
+        <v>-0.3389571614208728</v>
       </c>
       <c r="D36" t="n">
-        <v>-2.3888795593698</v>
+        <v>-2.463678330748048</v>
       </c>
       <c r="E36" t="n">
-        <v>0.8758632900680468</v>
+        <v>0.7958103676021192</v>
       </c>
       <c r="F36" t="n">
-        <v>-1.847900692200934</v>
+        <v>-1.687646504484327</v>
       </c>
       <c r="G36" t="n">
-        <v>3.695801384402716</v>
+        <v>3.375293008968464</v>
       </c>
       <c r="H36" t="n">
-        <v>-1.585095242974032</v>
+        <v>-0.8343064736808632</v>
       </c>
       <c r="I36" t="n">
-        <v>17.94780991145114</v>
+        <v>17.95234375174523</v>
       </c>
       <c r="J36" t="n">
-        <v>-2.486870780768088</v>
+        <v>-1.657877967869215</v>
       </c>
       <c r="K36" t="n">
-        <v>17.99992071097122</v>
+        <v>17.99993538317168</v>
       </c>
       <c r="L36" t="n">
-        <v>30.20338750805328</v>
+        <v>25.13664322389383</v>
       </c>
       <c r="M36" t="n">
-        <v>100.6804547094128</v>
+        <v>84.00023719326546</v>
       </c>
       <c r="N36" t="n">
-        <v>85.57838650300089</v>
+        <v>84.00023719326546</v>
       </c>
       <c r="O36" t="n">
-        <v>2.935936625860736</v>
+        <v>1.408335118035227</v>
       </c>
       <c r="P36" t="n">
-        <v>66.33125954378858</v>
+        <v>60.59418854366722</v>
       </c>
       <c r="Q36" t="n">
-        <v>69.26719616964931</v>
+        <v>62.00252366170245</v>
       </c>
       <c r="R36" t="n">
-        <v>2.935936625860736</v>
+        <v>1.408335118035227</v>
       </c>
       <c r="S36" t="n">
-        <v>66.33125954378858</v>
+        <v>60.59418854366722</v>
       </c>
       <c r="T36" t="n">
-        <v>69.26719616964931</v>
+        <v>62.00252366170245</v>
       </c>
     </row>
     <row r="37">
@@ -2693,61 +2693,61 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B37" t="n">
-        <v>0.1855260671298466</v>
+        <v>0.1678641885426003</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.3801429490833866</v>
+        <v>-0.3423790493108133</v>
       </c>
       <c r="D37" t="n">
-        <v>-2.38130675542302</v>
+        <v>-2.456834554968167</v>
       </c>
       <c r="E37" t="n">
-        <v>0.9138135247820994</v>
+        <v>0.8314819430664161</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.947572455744663</v>
+        <v>-1.765391706497334</v>
       </c>
       <c r="G37" t="n">
-        <v>3.895144911488511</v>
+        <v>3.53078341299446</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.722408205966147</v>
+        <v>-0.8732969043186132</v>
       </c>
       <c r="I37" t="n">
-        <v>17.94498681526591</v>
+        <v>17.950157737078</v>
       </c>
       <c r="J37" t="n">
-        <v>-2.672823564369542</v>
+        <v>-1.734808057089313</v>
       </c>
       <c r="K37" t="n">
-        <v>17.9999083585179</v>
+        <v>17.99994178320123</v>
       </c>
       <c r="L37" t="n">
-        <v>30.20551704172188</v>
+        <v>25.23185856204685</v>
       </c>
       <c r="M37" t="n">
-        <v>100.6876582902973</v>
+        <v>84.15711880030666</v>
       </c>
       <c r="N37" t="n">
-        <v>85.58450954675267</v>
+        <v>84.15711880030666</v>
       </c>
       <c r="O37" t="n">
-        <v>3.360107218607154</v>
+        <v>1.545635299446565</v>
       </c>
       <c r="P37" t="n">
-        <v>69.89809412386646</v>
+        <v>63.37802044648489</v>
       </c>
       <c r="Q37" t="n">
-        <v>73.25820134247363</v>
+        <v>64.92365574593146</v>
       </c>
       <c r="R37" t="n">
-        <v>3.360107218607154</v>
+        <v>1.545635299446565</v>
       </c>
       <c r="S37" t="n">
-        <v>69.89809412386646</v>
+        <v>63.37802044648489</v>
       </c>
       <c r="T37" t="n">
-        <v>73.25820134247363</v>
+        <v>64.92365574593146</v>
       </c>
     </row>
     <row r="38">
@@ -2755,61 +2755,61 @@
         <v>0.07200000000000001</v>
       </c>
       <c r="B38" t="n">
-        <v>0.187395295929479</v>
+        <v>0.1695727027279887</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.3841732686773262</v>
+        <v>-0.3460096275091304</v>
       </c>
       <c r="D38" t="n">
-        <v>-2.373246116235141</v>
+        <v>-2.449573398571532</v>
       </c>
       <c r="E38" t="n">
-        <v>0.9520909844335156</v>
+        <v>0.8673261092571445</v>
       </c>
       <c r="F38" t="n">
-        <v>-2.051804769287028</v>
+        <v>-1.84392161579142</v>
       </c>
       <c r="G38" t="n">
-        <v>4.103609538573943</v>
+        <v>3.687843231583407</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.857192339426585</v>
+        <v>-1.049828642001179</v>
       </c>
       <c r="I38" t="n">
-        <v>17.94203616338844</v>
+        <v>17.94793652531688</v>
       </c>
       <c r="J38" t="n">
-        <v>-2.858473066838654</v>
+        <v>-1.949662390507392</v>
       </c>
       <c r="K38" t="n">
-        <v>17.99989705788233</v>
+        <v>17.99993511488221</v>
       </c>
       <c r="L38" t="n">
-        <v>30.24544291216908</v>
+        <v>25.22443758873218</v>
       </c>
       <c r="M38" t="n">
-        <v>100.8210728681583</v>
+        <v>84.38981089674192</v>
       </c>
       <c r="N38" t="n">
-        <v>85.69791193793459</v>
+        <v>84.38981089674192</v>
       </c>
       <c r="O38" t="n">
-        <v>3.820360120556794</v>
+        <v>1.943479838195915</v>
       </c>
       <c r="P38" t="n">
-        <v>73.62667207091661</v>
+        <v>66.18898301597969</v>
       </c>
       <c r="Q38" t="n">
-        <v>77.44703219147341</v>
+        <v>68.1324628541756</v>
       </c>
       <c r="R38" t="n">
-        <v>3.820360120556794</v>
+        <v>1.943479838195915</v>
       </c>
       <c r="S38" t="n">
-        <v>73.62667207091661</v>
+        <v>66.18898301597969</v>
       </c>
       <c r="T38" t="n">
-        <v>77.44703219147341</v>
+        <v>68.1324628541756</v>
       </c>
     </row>
     <row r="39">
@@ -2817,61 +2817,61 @@
         <v>0.074</v>
       </c>
       <c r="B39" t="n">
-        <v>0.1893143494520337</v>
+        <v>0.1713450994863427</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.388314405985534</v>
+        <v>-0.3497806659038762</v>
       </c>
       <c r="D39" t="n">
-        <v>-2.364963841618725</v>
+        <v>-2.442031321782041</v>
       </c>
       <c r="E39" t="n">
-        <v>0.9905134513933541</v>
+        <v>0.9032966348467867</v>
       </c>
       <c r="F39" t="n">
-        <v>-2.158007086954329</v>
+        <v>-1.923031103716295</v>
       </c>
       <c r="G39" t="n">
-        <v>4.316014173910144</v>
+        <v>3.846062207432854</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.990645703839577</v>
+        <v>-1.139870044055133</v>
       </c>
       <c r="I39" t="n">
-        <v>17.93903100903768</v>
+        <v>17.9457077703966</v>
       </c>
       <c r="J39" t="n">
-        <v>-3.04375316227329</v>
+        <v>-2.078309222668685</v>
       </c>
       <c r="K39" t="n">
-        <v>17.99988680888982</v>
+        <v>17.9999372475214</v>
       </c>
       <c r="L39" t="n">
-        <v>30.30239068286672</v>
+        <v>25.29027848598</v>
       </c>
       <c r="M39" t="n">
-        <v>101.0112994778846</v>
+        <v>84.59076775903212</v>
       </c>
       <c r="N39" t="n">
-        <v>85.85960455620189</v>
+        <v>84.59076775903212</v>
       </c>
       <c r="O39" t="n">
-        <v>4.296366936308985</v>
+        <v>2.192729596962083</v>
       </c>
       <c r="P39" t="n">
-        <v>77.42508523555536</v>
+        <v>69.02009452920301</v>
       </c>
       <c r="Q39" t="n">
-        <v>81.72145217186433</v>
+        <v>71.21282412616509</v>
       </c>
       <c r="R39" t="n">
-        <v>4.296366936308985</v>
+        <v>2.192729596962083</v>
       </c>
       <c r="S39" t="n">
-        <v>77.42508523555536</v>
+        <v>69.02009452920301</v>
       </c>
       <c r="T39" t="n">
-        <v>81.72145217186433</v>
+        <v>71.21282412616509</v>
       </c>
     </row>
     <row r="40">
@@ -2879,61 +2879,61 @@
         <v>0.076</v>
       </c>
       <c r="B40" t="n">
-        <v>0.1913906534106625</v>
+        <v>0.1731728250549343</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.3928078310406494</v>
+        <v>-0.3536733571249462</v>
       </c>
       <c r="D40" t="n">
-        <v>-2.355976991508494</v>
+        <v>-2.434245939339901</v>
       </c>
       <c r="E40" t="n">
-        <v>1.029262501985379</v>
+        <v>0.9393766005369087</v>
       </c>
       <c r="F40" t="n">
-        <v>-2.266726874358669</v>
+        <v>-2.002642565725683</v>
       </c>
       <c r="G40" t="n">
-        <v>4.533453748716777</v>
+        <v>4.005285131450394</v>
       </c>
       <c r="H40" t="n">
-        <v>-2.11318889287136</v>
+        <v>-1.15500201235856</v>
       </c>
       <c r="I40" t="n">
-        <v>17.93597927987424</v>
+        <v>17.94347248233273</v>
       </c>
       <c r="J40" t="n">
-        <v>-3.21935160755839</v>
+        <v>-2.132291584432693</v>
       </c>
       <c r="K40" t="n">
-        <v>17.99990097773115</v>
+        <v>17.99994700268618</v>
       </c>
       <c r="L40" t="n">
-        <v>30.40794516409451</v>
+        <v>25.41957161982109</v>
       </c>
       <c r="M40" t="n">
-        <v>101.3627117097551</v>
+        <v>84.76423867850029</v>
       </c>
       <c r="N40" t="n">
-        <v>86.15830495329187</v>
+        <v>84.76423867850029</v>
       </c>
       <c r="O40" t="n">
-        <v>4.798979079361134</v>
+        <v>2.313281152097487</v>
       </c>
       <c r="P40" t="n">
-        <v>81.31148638436933</v>
+        <v>71.86865707848034</v>
       </c>
       <c r="Q40" t="n">
-        <v>86.11046546373046</v>
+        <v>74.18193823057781</v>
       </c>
       <c r="R40" t="n">
-        <v>4.798979079361134</v>
+        <v>2.313281152097487</v>
       </c>
       <c r="S40" t="n">
-        <v>81.31148638436933</v>
+        <v>71.86865707848034</v>
       </c>
       <c r="T40" t="n">
-        <v>86.11046546373046</v>
+        <v>74.18193823057781</v>
       </c>
     </row>
     <row r="41">
@@ -2941,61 +2941,61 @@
         <v>0.078</v>
       </c>
       <c r="B41" t="n">
-        <v>0.1935223388659998</v>
+        <v>0.1751059863280901</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.3974265865529459</v>
+        <v>-0.3577996100939366</v>
       </c>
       <c r="D41" t="n">
-        <v>-2.346739480483901</v>
+        <v>-2.42599343340192</v>
       </c>
       <c r="E41" t="n">
-        <v>1.068095007337892</v>
+        <v>0.9756829208085245</v>
       </c>
       <c r="F41" t="n">
-        <v>-2.375274584369042</v>
+        <v>-2.083305469654087</v>
       </c>
       <c r="G41" t="n">
-        <v>4.750549168736943</v>
+        <v>4.166610939308234</v>
       </c>
       <c r="H41" t="n">
-        <v>-2.235877077799618</v>
+        <v>-1.322215504752047</v>
       </c>
       <c r="I41" t="n">
-        <v>17.93293263106323</v>
+        <v>17.94119269021671</v>
       </c>
       <c r="J41" t="n">
-        <v>-3.39501107497171</v>
+        <v>-2.338868573943242</v>
       </c>
       <c r="K41" t="n">
-        <v>17.99991537434242</v>
+        <v>17.99994190446096</v>
       </c>
       <c r="L41" t="n">
-        <v>30.52710342823348</v>
+        <v>25.44012477487976</v>
       </c>
       <c r="M41" t="n">
-        <v>101.7595483696636</v>
+        <v>85.02586502391969</v>
       </c>
       <c r="N41" t="n">
-        <v>86.49561611421407</v>
+        <v>85.02586502391969</v>
       </c>
       <c r="O41" t="n">
-        <v>5.316937529640884</v>
+        <v>2.764989615579162</v>
       </c>
       <c r="P41" t="n">
-        <v>85.1909761246656</v>
+        <v>74.75371690456848</v>
       </c>
       <c r="Q41" t="n">
-        <v>90.50791365430648</v>
+        <v>77.51870652014765</v>
       </c>
       <c r="R41" t="n">
-        <v>5.316937529640884</v>
+        <v>2.764989615579162</v>
       </c>
       <c r="S41" t="n">
-        <v>85.1909761246656</v>
+        <v>74.75371690456848</v>
       </c>
       <c r="T41" t="n">
-        <v>90.50791365430648</v>
+        <v>77.51870652014765</v>
       </c>
     </row>
     <row r="42">
@@ -3003,61 +3003,61 @@
         <v>0.08</v>
       </c>
       <c r="B42" t="n">
-        <v>0.1957597584491582</v>
+        <v>0.177080460133252</v>
       </c>
       <c r="C42" t="n">
-        <v>-0.4022846224633359</v>
+        <v>-0.3620178645843435</v>
       </c>
       <c r="D42" t="n">
-        <v>-2.337023408663121</v>
+        <v>-2.417556924421106</v>
       </c>
       <c r="E42" t="n">
-        <v>1.107086844179029</v>
+        <v>1.012082919347145</v>
       </c>
       <c r="F42" t="n">
-        <v>-2.483493764920116</v>
+        <v>-2.164406752247467</v>
       </c>
       <c r="G42" t="n">
-        <v>4.966987529841311</v>
+        <v>4.328813504495732</v>
       </c>
       <c r="H42" t="n">
-        <v>-2.358842088302529</v>
+        <v>-1.474457458607505</v>
       </c>
       <c r="I42" t="n">
-        <v>17.92989568164037</v>
+        <v>17.93890226541279</v>
       </c>
       <c r="J42" t="n">
-        <v>-3.570787045583546</v>
+        <v>-2.530687953704268</v>
       </c>
       <c r="K42" t="n">
-        <v>17.99993020581113</v>
+        <v>17.99993853582618</v>
       </c>
       <c r="L42" t="n">
-        <v>30.67223397926725</v>
+        <v>25.47542053194223</v>
       </c>
       <c r="M42" t="n">
-        <v>102.2431091624648</v>
+        <v>85.28608640311217</v>
       </c>
       <c r="N42" t="n">
-        <v>86.90664278809506</v>
+        <v>85.28608640311217</v>
       </c>
       <c r="O42" t="n">
-        <v>5.864195087139072</v>
+        <v>3.191983620625801</v>
       </c>
       <c r="P42" t="n">
-        <v>89.05727063198574</v>
+        <v>77.65404213907631</v>
       </c>
       <c r="Q42" t="n">
-        <v>94.92146571912481</v>
+        <v>80.84602575970212</v>
       </c>
       <c r="R42" t="n">
-        <v>5.864195087139072</v>
+        <v>3.191983620625801</v>
       </c>
       <c r="S42" t="n">
-        <v>89.05727063198574</v>
+        <v>77.65404213907631</v>
       </c>
       <c r="T42" t="n">
-        <v>94.92146571912481</v>
+        <v>80.84602575970212</v>
       </c>
     </row>
     <row r="43">
@@ -3065,61 +3065,61 @@
         <v>0.082</v>
       </c>
       <c r="B43" t="n">
-        <v>0.1981012672403487</v>
+        <v>0.1791491391234832</v>
       </c>
       <c r="C43" t="n">
-        <v>-0.4073811684017338</v>
+        <v>-0.3664465156535064</v>
       </c>
       <c r="D43" t="n">
-        <v>-2.326830316786325</v>
+        <v>-2.40869962228278</v>
       </c>
       <c r="E43" t="n">
-        <v>1.146212017724795</v>
+        <v>1.048702743496206</v>
       </c>
       <c r="F43" t="n">
-        <v>-2.590118233120919</v>
+        <v>-2.246540547181997</v>
       </c>
       <c r="G43" t="n">
-        <v>5.180236466242275</v>
+        <v>4.49308109436339</v>
       </c>
       <c r="H43" t="n">
-        <v>-2.479348317205173</v>
+        <v>-1.499695309313993</v>
       </c>
       <c r="I43" t="n">
-        <v>17.92690264432181</v>
+        <v>17.93659607056423</v>
       </c>
       <c r="J43" t="n">
-        <v>-3.743326014968182</v>
+        <v>-2.596007096338808</v>
       </c>
       <c r="K43" t="n">
-        <v>17.99994397849583</v>
+        <v>17.99994851399475</v>
       </c>
       <c r="L43" t="n">
-        <v>30.83534070401096</v>
+        <v>25.61576199869195</v>
       </c>
       <c r="M43" t="n">
-        <v>102.7864137005223</v>
+        <v>85.49833323030856</v>
       </c>
       <c r="N43" t="n">
-        <v>87.36845164544395</v>
+        <v>85.49833323030856</v>
       </c>
       <c r="O43" t="n">
-        <v>6.430319972983306</v>
+        <v>3.370231067144434</v>
       </c>
       <c r="P43" t="n">
-        <v>92.86517059761525</v>
+        <v>80.59037880193894</v>
       </c>
       <c r="Q43" t="n">
-        <v>99.29549057059855</v>
+        <v>83.96060986908338</v>
       </c>
       <c r="R43" t="n">
-        <v>6.430319972983306</v>
+        <v>3.370231067144434</v>
       </c>
       <c r="S43" t="n">
-        <v>92.86517059761525</v>
+        <v>80.59037880193894</v>
       </c>
       <c r="T43" t="n">
-        <v>99.29549057059855</v>
+        <v>83.96060986908338</v>
       </c>
     </row>
     <row r="44">
@@ -3127,61 +3127,61 @@
         <v>0.08400000000000001</v>
       </c>
       <c r="B44" t="n">
-        <v>0.2004956768915385</v>
+        <v>0.181286508391177</v>
       </c>
       <c r="C44" t="n">
-        <v>-0.4125989313792339</v>
+        <v>-0.3710299539402925</v>
       </c>
       <c r="D44" t="n">
-        <v>-2.316394790831326</v>
+        <v>-2.399532745709208</v>
       </c>
       <c r="E44" t="n">
-        <v>1.185404956473869</v>
+        <v>1.085495415316881</v>
       </c>
       <c r="F44" t="n">
-        <v>-2.695932226764598</v>
+        <v>-2.329498415636278</v>
       </c>
       <c r="G44" t="n">
-        <v>5.391864453527538</v>
+        <v>4.658996831272174</v>
       </c>
       <c r="H44" t="n">
-        <v>-2.598604928941312</v>
+        <v>-1.624226631208478</v>
       </c>
       <c r="I44" t="n">
-        <v>17.92393192428404</v>
+        <v>17.93425673987975</v>
       </c>
       <c r="J44" t="n">
-        <v>-3.914219855602437</v>
+        <v>-2.761021858038982</v>
       </c>
       <c r="K44" t="n">
-        <v>17.99995721307878</v>
+        <v>17.99994859520069</v>
       </c>
       <c r="L44" t="n">
-        <v>31.00758339075047</v>
+        <v>25.68824661122432</v>
       </c>
       <c r="M44" t="n">
-        <v>103.3600815736786</v>
+        <v>85.77141017487824</v>
       </c>
       <c r="N44" t="n">
-        <v>87.85606933762685</v>
+        <v>85.77141017487824</v>
       </c>
       <c r="O44" t="n">
-        <v>7.0060337289349</v>
+        <v>3.794014446447593</v>
       </c>
       <c r="P44" t="n">
-        <v>96.64339292871267</v>
+        <v>83.55540157406246</v>
       </c>
       <c r="Q44" t="n">
-        <v>103.6494266576476</v>
+        <v>87.34941602051005</v>
       </c>
       <c r="R44" t="n">
-        <v>7.0060337289349</v>
+        <v>3.794014446447593</v>
       </c>
       <c r="S44" t="n">
-        <v>96.64339292871267</v>
+        <v>83.55540157406246</v>
       </c>
       <c r="T44" t="n">
-        <v>103.6494266576476</v>
+        <v>87.34941602051005</v>
       </c>
     </row>
     <row r="45">
@@ -3189,61 +3189,61 @@
         <v>0.08600000000000001</v>
       </c>
       <c r="B45" t="n">
-        <v>0.2030381823736871</v>
+        <v>0.1834770875926986</v>
       </c>
       <c r="C45" t="n">
-        <v>-0.418161092684795</v>
+        <v>-0.3757332959152188</v>
       </c>
       <c r="D45" t="n">
-        <v>-2.305270468220203</v>
+        <v>-2.390126061759356</v>
       </c>
       <c r="E45" t="n">
-        <v>1.224806124418556</v>
+        <v>1.122421981096186</v>
       </c>
       <c r="F45" t="n">
-        <v>-2.798771845117729</v>
+        <v>-2.413094640770352</v>
       </c>
       <c r="G45" t="n">
-        <v>5.597543690235572</v>
+        <v>4.826189281541804</v>
       </c>
       <c r="H45" t="n">
-        <v>-2.727593688732799</v>
+        <v>-1.825674210055424</v>
       </c>
       <c r="I45" t="n">
-        <v>17.92103870158994</v>
+        <v>17.93189174099737</v>
       </c>
       <c r="J45" t="n">
-        <v>-4.09339434915025</v>
+        <v>-3.003264394751355</v>
       </c>
       <c r="K45" t="n">
-        <v>17.99996406762226</v>
+        <v>17.99994100986711</v>
       </c>
       <c r="L45" t="n">
-        <v>31.19410497253195</v>
+        <v>25.70816688923881</v>
       </c>
       <c r="M45" t="n">
-        <v>103.9816289372153</v>
+        <v>86.0916082935025</v>
       </c>
       <c r="N45" t="n">
-        <v>88.38438459663304</v>
+        <v>86.0916082935025</v>
       </c>
       <c r="O45" t="n">
-        <v>7.643020441874082</v>
+        <v>4.407998698689914</v>
       </c>
       <c r="P45" t="n">
-        <v>100.3133892707058</v>
+        <v>86.54264562744925</v>
       </c>
       <c r="Q45" t="n">
-        <v>107.9564097125799</v>
+        <v>90.95064432613917</v>
       </c>
       <c r="R45" t="n">
-        <v>7.643020441874082</v>
+        <v>4.407998698689914</v>
       </c>
       <c r="S45" t="n">
-        <v>100.3133892707058</v>
+        <v>86.54264562744925</v>
       </c>
       <c r="T45" t="n">
-        <v>107.9564097125799</v>
+        <v>90.95064432613917</v>
       </c>
     </row>
     <row r="46">
@@ -3251,61 +3251,61 @@
         <v>0.08799999999999999</v>
       </c>
       <c r="B46" t="n">
-        <v>0.2056268802799503</v>
+        <v>0.1857790756189425</v>
       </c>
       <c r="C46" t="n">
-        <v>-0.423832388612513</v>
+        <v>-0.3806901403764877</v>
       </c>
       <c r="D46" t="n">
-        <v>-2.293927876364767</v>
+        <v>-2.380212372836818</v>
       </c>
       <c r="E46" t="n">
-        <v>1.264291889316661</v>
+        <v>1.159651558105925</v>
       </c>
       <c r="F46" t="n">
-        <v>-2.900800424928789</v>
+        <v>-2.498154872160081</v>
       </c>
       <c r="G46" t="n">
-        <v>5.80160084985854</v>
+        <v>4.996309744320117</v>
       </c>
       <c r="H46" t="n">
-        <v>-2.858431010673899</v>
+        <v>-1.877721380468068</v>
       </c>
       <c r="I46" t="n">
-        <v>17.9181675314771</v>
+        <v>17.92950157215829</v>
       </c>
       <c r="J46" t="n">
-        <v>-4.274021618039149</v>
+        <v>-3.096820958082188</v>
       </c>
       <c r="K46" t="n">
-        <v>17.99997010346011</v>
+        <v>17.99994953955321</v>
       </c>
       <c r="L46" t="n">
-        <v>31.3822657498724</v>
+        <v>25.84860995133353</v>
       </c>
       <c r="M46" t="n">
-        <v>104.6086454350029</v>
+        <v>86.35359161640231</v>
       </c>
       <c r="N46" t="n">
-        <v>88.91734861975247</v>
+        <v>86.35359161640231</v>
       </c>
       <c r="O46" t="n">
-        <v>8.297356712113293</v>
+        <v>4.692959394503596</v>
       </c>
       <c r="P46" t="n">
-        <v>103.9538204566073</v>
+        <v>89.5810657871003</v>
       </c>
       <c r="Q46" t="n">
-        <v>112.2511771687206</v>
+        <v>94.27402518160389</v>
       </c>
       <c r="R46" t="n">
-        <v>8.297356712113293</v>
+        <v>4.692959394503596</v>
       </c>
       <c r="S46" t="n">
-        <v>103.9538204566073</v>
+        <v>89.5810657871003</v>
       </c>
       <c r="T46" t="n">
-        <v>112.2511771687206</v>
+        <v>94.27402518160389</v>
       </c>
     </row>
     <row r="47">
@@ -3313,61 +3313,61 @@
         <v>0.09</v>
       </c>
       <c r="B47" t="n">
-        <v>0.2083163647776209</v>
+        <v>0.1881234704523109</v>
       </c>
       <c r="C47" t="n">
-        <v>-0.4297420327357727</v>
+        <v>-0.3857442245868294</v>
       </c>
       <c r="D47" t="n">
-        <v>-2.282108588118247</v>
+        <v>-2.370104204416134</v>
       </c>
       <c r="E47" t="n">
-        <v>1.303964859806927</v>
+        <v>1.197002645564076</v>
       </c>
       <c r="F47" t="n">
-        <v>-3.00107499999024</v>
+        <v>-2.583809638506757</v>
       </c>
       <c r="G47" t="n">
-        <v>6.002149999979984</v>
+        <v>5.167619277012728</v>
       </c>
       <c r="H47" t="n">
-        <v>-2.99314312241711</v>
+        <v>-1.958991092482435</v>
       </c>
       <c r="I47" t="n">
-        <v>17.91534419444089</v>
+        <v>17.92709178821987</v>
       </c>
       <c r="J47" t="n">
-        <v>-4.457667722412347</v>
+        <v>-3.219890196073733</v>
       </c>
       <c r="K47" t="n">
-        <v>17.99997450944061</v>
+        <v>17.99995522002575</v>
       </c>
       <c r="L47" t="n">
-        <v>31.57362709039741</v>
+        <v>25.97255075497577</v>
       </c>
       <c r="M47" t="n">
-        <v>105.2463306005133</v>
+        <v>86.63866355715638</v>
       </c>
       <c r="N47" t="n">
-        <v>89.45938101043632</v>
+        <v>86.63866355715638</v>
       </c>
       <c r="O47" t="n">
-        <v>8.989312355390307</v>
+        <v>5.068254319469885</v>
       </c>
       <c r="P47" t="n">
-        <v>107.5303037670864</v>
+        <v>92.64023513945372</v>
       </c>
       <c r="Q47" t="n">
-        <v>116.5196161224767</v>
+        <v>97.70848945892359</v>
       </c>
       <c r="R47" t="n">
-        <v>8.989312355390307</v>
+        <v>5.068254319469885</v>
       </c>
       <c r="S47" t="n">
-        <v>107.5303037670864</v>
+        <v>92.64023513945372</v>
       </c>
       <c r="T47" t="n">
-        <v>116.5196161224767</v>
+        <v>97.70848945892359</v>
       </c>
     </row>
     <row r="48">
@@ -3375,61 +3375,61 @@
         <v>0.092</v>
       </c>
       <c r="B48" t="n">
-        <v>0.2110922619914161</v>
+        <v>0.1905611305190694</v>
       </c>
       <c r="C48" t="n">
-        <v>-0.4358597771808657</v>
+        <v>-0.3910127826455627</v>
       </c>
       <c r="D48" t="n">
-        <v>-2.269873099228062</v>
+        <v>-2.359567088298668</v>
       </c>
       <c r="E48" t="n">
-        <v>1.343859486049605</v>
+        <v>1.234626054047546</v>
       </c>
       <c r="F48" t="n">
-        <v>-3.100643861681366</v>
+        <v>-2.670802664135263</v>
       </c>
       <c r="G48" t="n">
-        <v>6.201287723362423</v>
+        <v>5.341605328271057</v>
       </c>
       <c r="H48" t="n">
-        <v>-3.139138931670561</v>
+        <v>-2.175435912524906</v>
       </c>
       <c r="I48" t="n">
-        <v>17.91253931165872</v>
+        <v>17.9246306002937</v>
       </c>
       <c r="J48" t="n">
-        <v>-4.652253136171067</v>
+        <v>-3.478787612622915</v>
       </c>
       <c r="K48" t="n">
-        <v>17.99997746855813</v>
+        <v>17.99994723542232</v>
       </c>
       <c r="L48" t="n">
-        <v>31.76386682719687</v>
+        <v>26.00882211647424</v>
       </c>
       <c r="M48" t="n">
-        <v>105.8803517687575</v>
+        <v>87.01178114708516</v>
       </c>
       <c r="N48" t="n">
-        <v>89.9982990034439</v>
+        <v>87.01178114708516</v>
       </c>
       <c r="O48" t="n">
-        <v>9.743325554794733</v>
+        <v>5.819772769968922</v>
       </c>
       <c r="P48" t="n">
-        <v>111.0804456356662</v>
+        <v>95.74608370944952</v>
       </c>
       <c r="Q48" t="n">
-        <v>120.8237711904609</v>
+        <v>101.5658564794184</v>
       </c>
       <c r="R48" t="n">
-        <v>9.743325554794733</v>
+        <v>5.819772769968922</v>
       </c>
       <c r="S48" t="n">
-        <v>111.0804456356662</v>
+        <v>95.74608370944952</v>
       </c>
       <c r="T48" t="n">
-        <v>120.8237711904609</v>
+        <v>101.5658564794184</v>
       </c>
     </row>
     <row r="49">
@@ -3437,61 +3437,61 @@
         <v>0.094</v>
       </c>
       <c r="B49" t="n">
-        <v>0.2139209177169417</v>
+        <v>0.1930728997830606</v>
       </c>
       <c r="C49" t="n">
-        <v>-0.442104575418073</v>
+        <v>-0.396453730482542</v>
       </c>
       <c r="D49" t="n">
-        <v>-2.257383502753647</v>
+        <v>-2.348685192624709</v>
       </c>
       <c r="E49" t="n">
-        <v>1.383889442231419</v>
+        <v>1.272482409858371</v>
       </c>
       <c r="F49" t="n">
-        <v>-3.199781856379805</v>
+        <v>-2.758958240283518</v>
       </c>
       <c r="G49" t="n">
-        <v>6.399563712760489</v>
+        <v>5.517916480567364</v>
       </c>
       <c r="H49" t="n">
-        <v>-3.292023901618807</v>
+        <v>-2.293140395092862</v>
       </c>
       <c r="I49" t="n">
-        <v>17.90974569595646</v>
+        <v>17.92214751012715</v>
       </c>
       <c r="J49" t="n">
-        <v>-4.853517447532152</v>
+        <v>-3.639512016351219</v>
       </c>
       <c r="K49" t="n">
-        <v>17.99997954430638</v>
+        <v>17.99995013250315</v>
       </c>
       <c r="L49" t="n">
-        <v>31.95342177886324</v>
+        <v>26.12262432627346</v>
       </c>
       <c r="M49" t="n">
-        <v>106.5121359162088</v>
+        <v>87.34512570828254</v>
       </c>
       <c r="N49" t="n">
-        <v>90.53531552877746</v>
+        <v>87.34512570828254</v>
       </c>
       <c r="O49" t="n">
-        <v>10.53522744060714</v>
+        <v>6.32944888834623</v>
       </c>
       <c r="P49" t="n">
-        <v>114.6145049722556</v>
+        <v>98.89263293942948</v>
       </c>
       <c r="Q49" t="n">
-        <v>125.1497324128628</v>
+        <v>105.2220818277757</v>
       </c>
       <c r="R49" t="n">
-        <v>10.53522744060714</v>
+        <v>6.32944888834623</v>
       </c>
       <c r="S49" t="n">
-        <v>114.6145049722556</v>
+        <v>98.89263293942948</v>
       </c>
       <c r="T49" t="n">
-        <v>125.1497324128628</v>
+        <v>105.2220818277757</v>
       </c>
     </row>
     <row r="50">
@@ -3499,61 +3499,61 @@
         <v>0.096</v>
       </c>
       <c r="B50" t="n">
-        <v>0.2168777406202689</v>
+        <v>0.1956359316245929</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.4486638474385078</v>
+        <v>-0.4020139232270987</v>
       </c>
       <c r="D50" t="n">
-        <v>-2.244264958712778</v>
+        <v>-2.337564807135596</v>
       </c>
       <c r="E50" t="n">
-        <v>1.424355624830096</v>
+        <v>1.310499899251498</v>
       </c>
       <c r="F50" t="n">
-        <v>-3.299608340433111</v>
+        <v>-2.847917972169379</v>
       </c>
       <c r="G50" t="n">
-        <v>6.59921668086605</v>
+        <v>5.695835944337837</v>
       </c>
       <c r="H50" t="n">
-        <v>-3.455775957537492</v>
+        <v>-2.342544526351665</v>
       </c>
       <c r="I50" t="n">
-        <v>17.90693182804028</v>
+        <v>17.91964926981274</v>
       </c>
       <c r="J50" t="n">
-        <v>-5.065984827668849</v>
+        <v>-3.732328496770322</v>
       </c>
       <c r="K50" t="n">
-        <v>17.9999807832405</v>
+        <v>17.9999605566279</v>
       </c>
       <c r="L50" t="n">
-        <v>32.13915787714219</v>
+        <v>26.29005592717744</v>
       </c>
       <c r="M50" t="n">
-        <v>107.1311924751372</v>
+        <v>87.65095859690045</v>
       </c>
       <c r="N50" t="n">
-        <v>91.06151360386662</v>
+        <v>87.65095859690045</v>
       </c>
       <c r="O50" t="n">
-        <v>11.41414125551137</v>
+        <v>6.671838600095626</v>
       </c>
       <c r="P50" t="n">
-        <v>118.1713317352709</v>
+        <v>102.0673355001204</v>
       </c>
       <c r="Q50" t="n">
-        <v>129.5854729907823</v>
+        <v>108.739174100216</v>
       </c>
       <c r="R50" t="n">
-        <v>11.41414125551137</v>
+        <v>6.671838600095626</v>
       </c>
       <c r="S50" t="n">
-        <v>118.1713317352709</v>
+        <v>102.0673355001204</v>
       </c>
       <c r="T50" t="n">
-        <v>129.5854729907823</v>
+        <v>108.739174100216</v>
       </c>
     </row>
     <row r="51">
@@ -3561,61 +3561,61 @@
         <v>0.098</v>
       </c>
       <c r="B51" t="n">
-        <v>0.2198780515685296</v>
+        <v>0.1983172871436097</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.4553314375463748</v>
+        <v>-0.4078528014164143</v>
       </c>
       <c r="D51" t="n">
-        <v>-2.230929778497044</v>
+        <v>-2.325887050756965</v>
       </c>
       <c r="E51" t="n">
-        <v>1.464999029341219</v>
+        <v>1.34891547599</v>
       </c>
       <c r="F51" t="n">
-        <v>-3.400194583782785</v>
+        <v>-2.938902306094756</v>
       </c>
       <c r="G51" t="n">
-        <v>6.80038916756486</v>
+        <v>5.877804612189685</v>
       </c>
       <c r="H51" t="n">
-        <v>-3.626024747989738</v>
+        <v>-2.564038243223639</v>
       </c>
       <c r="I51" t="n">
-        <v>17.9040961462631</v>
+        <v>17.91707640075553</v>
       </c>
       <c r="J51" t="n">
-        <v>-5.285319704875737</v>
+        <v>-3.99822256859788</v>
       </c>
       <c r="K51" t="n">
-        <v>17.99998163352577</v>
+        <v>17.9999534457874</v>
       </c>
       <c r="L51" t="n">
-        <v>32.32396842510191</v>
+        <v>26.35262205024016</v>
       </c>
       <c r="M51" t="n">
-        <v>107.7471810809076</v>
+        <v>88.07670347841074</v>
       </c>
       <c r="N51" t="n">
-        <v>91.58510391877142</v>
+        <v>88.07670347841074</v>
       </c>
       <c r="O51" t="n">
-        <v>12.33626058781387</v>
+        <v>7.549851223163643</v>
       </c>
       <c r="P51" t="n">
-        <v>121.7546023960491</v>
+        <v>105.312756762162</v>
       </c>
       <c r="Q51" t="n">
-        <v>134.0908629838629</v>
+        <v>112.8626079853256</v>
       </c>
       <c r="R51" t="n">
-        <v>12.33626058781387</v>
+        <v>7.549851223163643</v>
       </c>
       <c r="S51" t="n">
-        <v>121.7546023960491</v>
+        <v>105.312756762162</v>
       </c>
       <c r="T51" t="n">
-        <v>134.0908629838629</v>
+        <v>112.8626079853256</v>
       </c>
     </row>
     <row r="52">
@@ -3623,61 +3623,61 @@
         <v>0.1</v>
       </c>
       <c r="B52" t="n">
-        <v>0.2229791999970495</v>
+        <v>0.2010424604509816</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.4622510529507552</v>
+        <v>-0.413796013566191</v>
       </c>
       <c r="D52" t="n">
-        <v>-2.217090547688283</v>
+        <v>-2.314000626457411</v>
       </c>
       <c r="E52" t="n">
-        <v>1.506068988200693</v>
+        <v>1.387487224730425</v>
       </c>
       <c r="F52" t="n">
-        <v>-3.502823946666269</v>
+        <v>-3.030692390126656</v>
       </c>
       <c r="G52" t="n">
-        <v>7.00564789333316</v>
+        <v>6.061384780253988</v>
       </c>
       <c r="H52" t="n">
-        <v>-3.81284054189982</v>
+        <v>-2.750945543189495</v>
       </c>
       <c r="I52" t="n">
-        <v>17.90120189132951</v>
+        <v>17.91448481231057</v>
       </c>
       <c r="J52" t="n">
-        <v>-5.522218627872959</v>
+        <v>-4.229923429571303</v>
       </c>
       <c r="K52" t="n">
-        <v>17.99998152662551</v>
+        <v>17.99995033771215</v>
       </c>
       <c r="L52" t="n">
-        <v>32.50683088803019</v>
+        <v>26.44340111376487</v>
       </c>
       <c r="M52" t="n">
-        <v>108.3567248450514</v>
+        <v>88.49143430919106</v>
       </c>
       <c r="N52" t="n">
-        <v>92.10321611829366</v>
+        <v>88.49143430919106</v>
       </c>
       <c r="O52" t="n">
-        <v>13.36588059203018</v>
+        <v>8.339561160382944</v>
       </c>
       <c r="P52" t="n">
-        <v>125.4092021549227</v>
+        <v>108.5863981451976</v>
       </c>
       <c r="Q52" t="n">
-        <v>138.7750827469529</v>
+        <v>116.9259593055806</v>
       </c>
       <c r="R52" t="n">
-        <v>13.36588059203018</v>
+        <v>8.339561160382944</v>
       </c>
       <c r="S52" t="n">
-        <v>125.4092021549227</v>
+        <v>108.5863981451976</v>
       </c>
       <c r="T52" t="n">
-        <v>138.7750827469529</v>
+        <v>116.9259593055806</v>
       </c>
     </row>
     <row r="53">
@@ -3685,61 +3685,61 @@
         <v>0.102</v>
       </c>
       <c r="B53" t="n">
-        <v>0.2261606009956719</v>
+        <v>0.2038604297275334</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.4693748687848112</v>
+        <v>-0.4199607496024361</v>
       </c>
       <c r="D53" t="n">
-        <v>-2.202842916020171</v>
+        <v>-2.301671154384921</v>
       </c>
       <c r="E53" t="n">
-        <v>1.547534267850456</v>
+        <v>1.426394110642261</v>
       </c>
       <c r="F53" t="n">
-        <v>-3.608148729296419</v>
+        <v>-3.124217025462469</v>
       </c>
       <c r="G53" t="n">
-        <v>7.216297458593216</v>
+        <v>6.248434050924131</v>
       </c>
       <c r="H53" t="n">
-        <v>-4.007557722891522</v>
+        <v>-2.815168282076192</v>
       </c>
       <c r="I53" t="n">
-        <v>17.89823113321548</v>
+        <v>17.91185806462927</v>
       </c>
       <c r="J53" t="n">
-        <v>-5.768334302788174</v>
+        <v>-4.339786190501877</v>
       </c>
       <c r="K53" t="n">
-        <v>17.99998092738165</v>
+        <v>17.9999609847473</v>
       </c>
       <c r="L53" t="n">
-        <v>32.69068220063158</v>
+        <v>26.62764379271374</v>
       </c>
       <c r="M53" t="n">
-        <v>108.9695655280785</v>
+        <v>88.85497146771841</v>
       </c>
       <c r="N53" t="n">
-        <v>92.62413069886671</v>
+        <v>88.85497146771841</v>
       </c>
       <c r="O53" t="n">
-        <v>14.47358125593955</v>
+        <v>8.798119205742497</v>
       </c>
       <c r="P53" t="n">
-        <v>129.1585456735047</v>
+        <v>111.9208247800221</v>
       </c>
       <c r="Q53" t="n">
-        <v>143.6321269294443</v>
+        <v>120.7189439857646</v>
       </c>
       <c r="R53" t="n">
-        <v>14.47358125593955</v>
+        <v>8.798119205742497</v>
       </c>
       <c r="S53" t="n">
-        <v>129.1585456735047</v>
+        <v>111.9208247800221</v>
       </c>
       <c r="T53" t="n">
-        <v>143.6321269294443</v>
+        <v>120.7189439857646</v>
       </c>
     </row>
     <row r="54">
@@ -3747,61 +3747,61 @@
         <v>0.104</v>
       </c>
       <c r="B54" t="n">
-        <v>0.2294004056291379</v>
+        <v>0.2067587128854623</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.4766472910412465</v>
+        <v>-0.4263200241686995</v>
       </c>
       <c r="D54" t="n">
-        <v>-2.1882980715073</v>
+        <v>-2.288952605252395</v>
       </c>
       <c r="E54" t="n">
-        <v>1.589287241352922</v>
+        <v>1.465610887558237</v>
       </c>
       <c r="F54" t="n">
-        <v>-3.715435097835077</v>
+        <v>-3.219379197077927</v>
       </c>
       <c r="G54" t="n">
-        <v>7.430870195669137</v>
+        <v>6.438758394155546</v>
       </c>
       <c r="H54" t="n">
-        <v>-4.208025121294122</v>
+        <v>-2.996748961543883</v>
       </c>
       <c r="I54" t="n">
-        <v>17.89520470007685</v>
+        <v>17.90917316480046</v>
       </c>
       <c r="J54" t="n">
-        <v>-6.02115744903764</v>
+        <v>-4.567806009717911</v>
       </c>
       <c r="K54" t="n">
-        <v>17.99997996983578</v>
+        <v>17.99995965815805</v>
       </c>
       <c r="L54" t="n">
-        <v>32.87525314645032</v>
+        <v>26.74564354642349</v>
       </c>
       <c r="M54" t="n">
-        <v>109.5848055367138</v>
+        <v>89.30655045624236</v>
       </c>
       <c r="N54" t="n">
-        <v>93.14708470620671</v>
+        <v>89.30655045624236</v>
       </c>
       <c r="O54" t="n">
-        <v>15.63810495157532</v>
+        <v>9.663364324064919</v>
       </c>
       <c r="P54" t="n">
-        <v>132.9768387589187</v>
+        <v>115.3125027166075</v>
       </c>
       <c r="Q54" t="n">
-        <v>148.6149437104941</v>
+        <v>124.9758670406724</v>
       </c>
       <c r="R54" t="n">
-        <v>15.63810495157532</v>
+        <v>9.663364324064919</v>
       </c>
       <c r="S54" t="n">
-        <v>132.9768387589187</v>
+        <v>115.3125027166075</v>
       </c>
       <c r="T54" t="n">
-        <v>148.6149437104941</v>
+        <v>124.9758670406724</v>
       </c>
     </row>
     <row r="55">
@@ -3809,61 +3809,61 @@
         <v>0.106</v>
       </c>
       <c r="B55" t="n">
-        <v>0.2327689298560856</v>
+        <v>0.2097064855212306</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.4842530403885267</v>
+        <v>-0.4327991735325095</v>
       </c>
       <c r="D55" t="n">
-        <v>-2.17308657281274</v>
+        <v>-2.275994306524774</v>
       </c>
       <c r="E55" t="n">
-        <v>1.631740510417514</v>
+        <v>1.505018619558429</v>
       </c>
       <c r="F55" t="n">
-        <v>-3.82834325973811</v>
+        <v>-3.315550419856559</v>
       </c>
       <c r="G55" t="n">
-        <v>7.656686519476402</v>
+        <v>6.631100839714533</v>
       </c>
       <c r="H55" t="n">
-        <v>-4.42972744448677</v>
+        <v>-3.250645697714069</v>
       </c>
       <c r="I55" t="n">
-        <v>17.89201762733983</v>
+        <v>17.9064524315719</v>
       </c>
       <c r="J55" t="n">
-        <v>-6.297958955238967</v>
+        <v>-4.86863430260407</v>
       </c>
       <c r="K55" t="n">
-        <v>17.99997690726444</v>
+        <v>17.99995095341188</v>
       </c>
       <c r="L55" t="n">
-        <v>33.06684694613374</v>
+        <v>26.82282435670242</v>
       </c>
       <c r="M55" t="n">
-        <v>110.2235337094479</v>
+        <v>89.81238089071626</v>
       </c>
       <c r="N55" t="n">
-        <v>93.69000365303071</v>
+        <v>89.81238089071626</v>
       </c>
       <c r="O55" t="n">
-        <v>16.97640297590919</v>
+        <v>10.77921034150807</v>
       </c>
       <c r="P55" t="n">
-        <v>136.9930585607978</v>
+        <v>118.7394589510562</v>
       </c>
       <c r="Q55" t="n">
-        <v>153.969461536707</v>
+        <v>129.5186692925643</v>
       </c>
       <c r="R55" t="n">
-        <v>16.97640297590919</v>
+        <v>10.77921034150807</v>
       </c>
       <c r="S55" t="n">
-        <v>136.9930585607978</v>
+        <v>118.7394589510562</v>
       </c>
       <c r="T55" t="n">
-        <v>153.969461536707</v>
+        <v>129.5186692925643</v>
       </c>
     </row>
     <row r="56">
@@ -3871,61 +3871,61 @@
         <v>0.108</v>
       </c>
       <c r="B56" t="n">
-        <v>0.2361845718627489</v>
+        <v>0.2127806992059331</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.4919823192437271</v>
+        <v>-0.4395894462628536</v>
       </c>
       <c r="D56" t="n">
-        <v>-2.157628015102339</v>
+        <v>-2.262413761064086</v>
       </c>
       <c r="E56" t="n">
-        <v>1.674461267667308</v>
+        <v>1.544949055165115</v>
       </c>
       <c r="F56" t="n">
-        <v>-3.94351696860979</v>
+        <v>-3.414538606310624</v>
       </c>
       <c r="G56" t="n">
-        <v>7.887033937220572</v>
+        <v>6.829077212621051</v>
       </c>
       <c r="H56" t="n">
-        <v>-4.6569151580524</v>
+        <v>-3.338907341587689</v>
       </c>
       <c r="I56" t="n">
-        <v>17.88876518442562</v>
+        <v>17.90367107482087</v>
       </c>
       <c r="J56" t="n">
-        <v>-6.581351438733978</v>
+        <v>-5.005202181467274</v>
       </c>
       <c r="K56" t="n">
-        <v>17.99997236294043</v>
+        <v>17.99996106351883</v>
       </c>
       <c r="L56" t="n">
-        <v>33.26242858473774</v>
+        <v>27.02185865716892</v>
       </c>
       <c r="M56" t="n">
-        <v>110.8755792216802</v>
+        <v>90.24647094931468</v>
       </c>
       <c r="N56" t="n">
-        <v>94.24424233842818</v>
+        <v>90.24647094931468</v>
       </c>
       <c r="O56" t="n">
-        <v>18.37379689740602</v>
+        <v>11.40623911386878</v>
       </c>
       <c r="P56" t="n">
-        <v>141.089034600491</v>
+        <v>122.2651829086693</v>
       </c>
       <c r="Q56" t="n">
-        <v>159.462831497897</v>
+        <v>133.6714220225381</v>
       </c>
       <c r="R56" t="n">
-        <v>18.37379689740602</v>
+        <v>11.40623911386878</v>
       </c>
       <c r="S56" t="n">
-        <v>141.089034600491</v>
+        <v>122.2651829086693</v>
       </c>
       <c r="T56" t="n">
-        <v>159.462831497897</v>
+        <v>133.6714220225381</v>
       </c>
     </row>
     <row r="57">
@@ -3933,61 +3933,61 @@
         <v>0.11</v>
       </c>
       <c r="B57" t="n">
-        <v>0.2397172617934967</v>
+        <v>0.2159005390617524</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.5000201559678142</v>
+        <v>-0.4464936943672051</v>
       </c>
       <c r="D57" t="n">
-        <v>-2.141552341654164</v>
+        <v>-2.248605264855383</v>
       </c>
       <c r="E57" t="n">
-        <v>1.717858947659727</v>
+        <v>1.585079412778483</v>
       </c>
       <c r="F57" t="n">
-        <v>-4.064550476273083</v>
+        <v>-3.514626293723851</v>
       </c>
       <c r="G57" t="n">
-        <v>8.129100952545512</v>
+        <v>7.029252587446795</v>
       </c>
       <c r="H57" t="n">
-        <v>-4.895175942965484</v>
+        <v>-3.48010840122848</v>
       </c>
       <c r="I57" t="n">
-        <v>17.885343020423</v>
+        <v>17.9008534250698</v>
       </c>
       <c r="J57" t="n">
-        <v>-6.878676575386748</v>
+        <v>-5.195246032565719</v>
       </c>
       <c r="K57" t="n">
-        <v>17.99996334385389</v>
+        <v>17.9999658865528</v>
       </c>
       <c r="L57" t="n">
-        <v>33.46949844570322</v>
+        <v>27.19527082025824</v>
       </c>
       <c r="M57" t="n">
-        <v>111.5659750366111</v>
+        <v>90.72613695129439</v>
       </c>
       <c r="N57" t="n">
-        <v>94.83107878111944</v>
+        <v>90.72613695129439</v>
       </c>
       <c r="O57" t="n">
-        <v>19.91295551226121</v>
+        <v>12.24297341351812</v>
       </c>
       <c r="P57" t="n">
-        <v>145.3912917291756</v>
+        <v>125.8293765303613</v>
       </c>
       <c r="Q57" t="n">
-        <v>165.3042472414368</v>
+        <v>138.0723499438795</v>
       </c>
       <c r="R57" t="n">
-        <v>19.91295551226121</v>
+        <v>12.24297341351812</v>
       </c>
       <c r="S57" t="n">
-        <v>145.3912917291756</v>
+        <v>125.8293765303613</v>
       </c>
       <c r="T57" t="n">
-        <v>165.3042472414368</v>
+        <v>138.0723499438795</v>
       </c>
     </row>
     <row r="58">
@@ -3995,61 +3995,61 @@
         <v>0.112</v>
       </c>
       <c r="B58" t="n">
-        <v>0.2433340367042864</v>
+        <v>0.2191132582629193</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.508283881805809</v>
+        <v>-0.4536303941273538</v>
       </c>
       <c r="D58" t="n">
-        <v>-2.125024889978175</v>
+        <v>-2.234331865335086</v>
       </c>
       <c r="E58" t="n">
-        <v>1.761761534212566</v>
+        <v>1.625619635498717</v>
       </c>
       <c r="F58" t="n">
-        <v>-4.190075850682071</v>
+        <v>-3.616973424121486</v>
       </c>
       <c r="G58" t="n">
-        <v>8.380151701363639</v>
+        <v>7.233946848243728</v>
       </c>
       <c r="H58" t="n">
-        <v>-5.146692900547372</v>
+        <v>-3.757909319297936</v>
       </c>
       <c r="I58" t="n">
-        <v>17.8817388773114</v>
+        <v>17.89795820695216</v>
       </c>
       <c r="J58" t="n">
-        <v>-7.191449915680222</v>
+        <v>-5.52299235026922</v>
       </c>
       <c r="K58" t="n">
-        <v>17.99989901630063</v>
+        <v>17.99995685751239</v>
       </c>
       <c r="L58" t="n">
-        <v>33.68778886866106</v>
+        <v>27.29872172907009</v>
       </c>
       <c r="M58" t="n">
-        <v>112.2946358223887</v>
+        <v>91.31686187900944</v>
       </c>
       <c r="N58" t="n">
-        <v>95.4504404490304</v>
+        <v>91.31686187900944</v>
       </c>
       <c r="O58" t="n">
-        <v>21.58592584717566</v>
+        <v>13.60536785555876</v>
       </c>
       <c r="P58" t="n">
-        <v>149.8510868152732</v>
+        <v>129.4726051044056</v>
       </c>
       <c r="Q58" t="n">
-        <v>171.4370126624489</v>
+        <v>143.0779729599644</v>
       </c>
       <c r="R58" t="n">
-        <v>21.58592584717566</v>
+        <v>13.60536785555876</v>
       </c>
       <c r="S58" t="n">
-        <v>149.8510868152732</v>
+        <v>129.4726051044056</v>
       </c>
       <c r="T58" t="n">
-        <v>171.4370126624489</v>
+        <v>143.0779729599644</v>
       </c>
     </row>
     <row r="59">
@@ -4057,61 +4057,61 @@
         <v>0.114</v>
       </c>
       <c r="B59" t="n">
-        <v>0.2470234066309037</v>
+        <v>0.2224135247539797</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.5167426296773612</v>
+        <v>-0.4609902458324831</v>
       </c>
       <c r="D59" t="n">
-        <v>-2.108107394235071</v>
+        <v>-2.219612161924827</v>
       </c>
       <c r="E59" t="n">
-        <v>1.806100033335368</v>
+        <v>1.666573293523972</v>
       </c>
       <c r="F59" t="n">
-        <v>-4.319479291510735</v>
+        <v>-3.72165037180679</v>
       </c>
       <c r="G59" t="n">
-        <v>8.638958583022671</v>
+        <v>7.443300743613964</v>
       </c>
       <c r="H59" t="n">
-        <v>-5.409654613949226</v>
+        <v>-3.922273654727352</v>
       </c>
       <c r="I59" t="n">
-        <v>17.87797762199869</v>
+        <v>17.89501028857083</v>
       </c>
       <c r="J59" t="n">
-        <v>-7.517560508206465</v>
+        <v>-5.738439036169065</v>
       </c>
       <c r="K59" t="n">
-        <v>17.99978693801931</v>
+        <v>17.99996082905579</v>
       </c>
       <c r="L59" t="n">
-        <v>33.91576659695008</v>
+        <v>27.48221541754556</v>
       </c>
       <c r="M59" t="n">
-        <v>113.0563327837458</v>
+        <v>91.85650446840896</v>
       </c>
       <c r="N59" t="n">
-        <v>96.09788286618392</v>
+        <v>91.85650446840896</v>
       </c>
       <c r="O59" t="n">
-        <v>23.37442292575814</v>
+        <v>14.60441467019106</v>
       </c>
       <c r="P59" t="n">
-        <v>154.4468927621233</v>
+        <v>133.1975311499882</v>
       </c>
       <c r="Q59" t="n">
-        <v>177.8213156878815</v>
+        <v>147.8019458201792</v>
       </c>
       <c r="R59" t="n">
-        <v>23.37442292575814</v>
+        <v>14.60441467019106</v>
       </c>
       <c r="S59" t="n">
-        <v>154.4468927621233</v>
+        <v>133.1975311499882</v>
       </c>
       <c r="T59" t="n">
-        <v>177.8213156878815</v>
+        <v>147.8019458201792</v>
       </c>
     </row>
     <row r="60">
@@ -4119,61 +4119,61 @@
         <v>0.116</v>
       </c>
       <c r="B60" t="n">
-        <v>0.2508522104294301</v>
+        <v>0.2257616917439517</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.5255842275278543</v>
+        <v>-0.4684721925734574</v>
       </c>
       <c r="D60" t="n">
-        <v>-2.090424198534085</v>
+        <v>-2.204648268442878</v>
       </c>
       <c r="E60" t="n">
-        <v>1.851208412428035</v>
+        <v>1.707753157950386</v>
       </c>
       <c r="F60" t="n">
-        <v>-4.455145437437088</v>
+        <v>-3.827602052388887</v>
       </c>
       <c r="G60" t="n">
-        <v>8.910290874874073</v>
+        <v>7.655204104776674</v>
       </c>
       <c r="H60" t="n">
-        <v>-5.671984162024066</v>
+        <v>-4.024572460659477</v>
       </c>
       <c r="I60" t="n">
-        <v>17.85690880930294</v>
+        <v>17.89203353584266</v>
       </c>
       <c r="J60" t="n">
-        <v>-7.846095135493365</v>
+        <v>-5.892442262225254</v>
       </c>
       <c r="K60" t="n">
-        <v>17.98254391063866</v>
+        <v>17.99997191372001</v>
       </c>
       <c r="L60" t="n">
-        <v>34.16308441828707</v>
+        <v>27.70950359794452</v>
       </c>
       <c r="M60" t="n">
-        <v>113.881084783838</v>
+        <v>92.36819794032164</v>
       </c>
       <c r="N60" t="n">
-        <v>96.79892206626232</v>
+        <v>92.36819794032164</v>
       </c>
       <c r="O60" t="n">
-        <v>25.29482350402153</v>
+        <v>15.40465998391564</v>
       </c>
       <c r="P60" t="n">
-        <v>159.1056223811503</v>
+        <v>136.9671570332387</v>
       </c>
       <c r="Q60" t="n">
-        <v>184.4004458851718</v>
+        <v>152.3718170171543</v>
       </c>
       <c r="R60" t="n">
-        <v>25.29482350402153</v>
+        <v>15.40465998391564</v>
       </c>
       <c r="S60" t="n">
-        <v>159.1056223811503</v>
+        <v>136.9671570332387</v>
       </c>
       <c r="T60" t="n">
-        <v>184.4004458851718</v>
+        <v>152.3718170171543</v>
       </c>
     </row>
     <row r="61">
@@ -4181,61 +4181,61 @@
         <v>0.118</v>
       </c>
       <c r="B61" t="n">
-        <v>0.2547337601672821</v>
+        <v>0.2292459881389137</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.5345727826187363</v>
+        <v>-0.4763080296261935</v>
       </c>
       <c r="D61" t="n">
-        <v>-2.072447088352321</v>
+        <v>-2.188976594337406</v>
       </c>
       <c r="E61" t="n">
-        <v>1.896601519576645</v>
+        <v>1.749619280025643</v>
       </c>
       <c r="F61" t="n">
-        <v>-4.593049616102648</v>
+        <v>-3.937517311122787</v>
       </c>
       <c r="G61" t="n">
-        <v>9.18609923220404</v>
+        <v>7.875034622245757</v>
       </c>
       <c r="H61" t="n">
-        <v>-5.939621911114085</v>
+        <v>-4.328889430738734</v>
       </c>
       <c r="I61" t="n">
-        <v>17.83307688905618</v>
+        <v>17.88892482342521</v>
       </c>
       <c r="J61" t="n">
-        <v>-8.181030123772176</v>
+        <v>-6.250397878566653</v>
       </c>
       <c r="K61" t="n">
-        <v>17.96260088823026</v>
+        <v>17.99996281159887</v>
       </c>
       <c r="L61" t="n">
-        <v>34.41734934581687</v>
+        <v>27.84579941528192</v>
       </c>
       <c r="M61" t="n">
-        <v>114.7286791681242</v>
+        <v>93.05910420141112</v>
       </c>
       <c r="N61" t="n">
-        <v>97.51937729290556</v>
+        <v>93.05910420141112</v>
       </c>
       <c r="O61" t="n">
-        <v>27.29207393349943</v>
+        <v>17.06736551759598</v>
       </c>
       <c r="P61" t="n">
-        <v>163.8146628663055</v>
+        <v>140.8754501237571</v>
       </c>
       <c r="Q61" t="n">
-        <v>191.1067367998049</v>
+        <v>157.9428156413531</v>
       </c>
       <c r="R61" t="n">
-        <v>27.29207393349943</v>
+        <v>17.06736551759598</v>
       </c>
       <c r="S61" t="n">
-        <v>163.8146628663055</v>
+        <v>140.8754501237571</v>
       </c>
       <c r="T61" t="n">
-        <v>191.1067367998049</v>
+        <v>157.9428156413531</v>
       </c>
     </row>
     <row r="62">
@@ -4243,61 +4243,61 @@
         <v>0.12</v>
       </c>
       <c r="B62" t="n">
-        <v>0.2587531128886048</v>
+        <v>0.2327782340461729</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.5439497349388978</v>
+        <v>-0.4842711071782292</v>
       </c>
       <c r="D62" t="n">
-        <v>-2.053693183711998</v>
+        <v>-2.173050439233335</v>
       </c>
       <c r="E62" t="n">
-        <v>1.942724879222931</v>
+        <v>1.791743417890679</v>
       </c>
       <c r="F62" t="n">
-        <v>-4.736526457860356</v>
+        <v>-4.048958750747323</v>
       </c>
       <c r="G62" t="n">
-        <v>9.473052915721405</v>
+        <v>8.09791750149526</v>
       </c>
       <c r="H62" t="n">
-        <v>-6.232740901660236</v>
+        <v>-4.576109508409083</v>
       </c>
       <c r="I62" t="n">
-        <v>17.80994800882984</v>
+        <v>17.88577968085818</v>
       </c>
       <c r="J62" t="n">
-        <v>-8.54416581309609</v>
+        <v>-6.552001378773777</v>
       </c>
       <c r="K62" t="n">
-        <v>17.94351805494151</v>
+        <v>17.99996031762926</v>
       </c>
       <c r="L62" t="n">
-        <v>34.68899168114062</v>
+        <v>28.02085430512791</v>
       </c>
       <c r="M62" t="n">
-        <v>115.6338357061778</v>
+        <v>93.72419463208357</v>
       </c>
       <c r="N62" t="n">
-        <v>98.28876035025115</v>
+        <v>93.72419463208357</v>
       </c>
       <c r="O62" t="n">
-        <v>29.54652485814561</v>
+        <v>18.5348891457732</v>
       </c>
       <c r="P62" t="n">
-        <v>168.7106373427363</v>
+        <v>144.8372448701074</v>
       </c>
       <c r="Q62" t="n">
-        <v>198.2571622008819</v>
+        <v>163.3721340158806</v>
       </c>
       <c r="R62" t="n">
-        <v>29.54652485814561</v>
+        <v>18.5348891457732</v>
       </c>
       <c r="S62" t="n">
-        <v>168.7106373427363</v>
+        <v>144.8372448701074</v>
       </c>
       <c r="T62" t="n">
-        <v>198.2571622008819</v>
+        <v>163.3721340158806</v>
       </c>
     </row>
     <row r="63">
@@ -4305,61 +4305,61 @@
         <v>0.122</v>
       </c>
       <c r="B63" t="n">
-        <v>0.2628577247941897</v>
+        <v>0.2364041193936856</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.5535736934458847</v>
+        <v>-0.4924828360640586</v>
       </c>
       <c r="D63" t="n">
-        <v>-2.034445266698024</v>
+        <v>-2.156626981461676</v>
       </c>
       <c r="E63" t="n">
-        <v>1.989405910654561</v>
+        <v>1.834372476346292</v>
       </c>
       <c r="F63" t="n">
-        <v>-4.885057200770921</v>
+        <v>-4.163388997467816</v>
       </c>
       <c r="G63" t="n">
-        <v>9.770114401542502</v>
+        <v>8.326777994934897</v>
       </c>
       <c r="H63" t="n">
-        <v>-6.546189833133295</v>
+        <v>-4.703577817901772</v>
       </c>
       <c r="I63" t="n">
-        <v>17.79668242806558</v>
+        <v>17.88256404113671</v>
       </c>
       <c r="J63" t="n">
-        <v>-8.930097747109505</v>
+        <v>-6.735311648666066</v>
       </c>
       <c r="K63" t="n">
-        <v>17.93444104112733</v>
+        <v>17.99997161086529</v>
       </c>
       <c r="L63" t="n">
-        <v>34.97522096727659</v>
+        <v>28.27615493783026</v>
       </c>
       <c r="M63" t="n">
-        <v>116.587413274714</v>
+        <v>94.33314977449317</v>
       </c>
       <c r="N63" t="n">
-        <v>99.09930128350692</v>
+        <v>94.33314977449317</v>
       </c>
       <c r="O63" t="n">
-        <v>32.00864566338954</v>
+        <v>19.58915575750528</v>
       </c>
       <c r="P63" t="n">
-        <v>173.8750490219919</v>
+        <v>148.903821295439</v>
       </c>
       <c r="Q63" t="n">
-        <v>205.8836946853814</v>
+        <v>168.4929770529443</v>
       </c>
       <c r="R63" t="n">
-        <v>32.00864566338954</v>
+        <v>19.58915575750528</v>
       </c>
       <c r="S63" t="n">
-        <v>173.8750490219919</v>
+        <v>148.903821295439</v>
       </c>
       <c r="T63" t="n">
-        <v>205.8836946853814</v>
+        <v>168.4929770529443</v>
       </c>
     </row>
     <row r="64">
@@ -4367,61 +4367,61 @@
         <v>0.124</v>
       </c>
       <c r="B64" t="n">
-        <v>0.2670494764825861</v>
+        <v>0.2401261635662746</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.5634501064615477</v>
+        <v>-0.5009558041767358</v>
       </c>
       <c r="D64" t="n">
-        <v>-2.014692440666698</v>
+        <v>-2.139681045236322</v>
       </c>
       <c r="E64" t="n">
-        <v>2.036656914678298</v>
+        <v>1.877555546576614</v>
       </c>
       <c r="F64" t="n">
-        <v>-5.038753320908832</v>
+        <v>-4.281187396384329</v>
       </c>
       <c r="G64" t="n">
-        <v>10.07750664181626</v>
+        <v>8.5623747927685</v>
       </c>
       <c r="H64" t="n">
-        <v>-6.880417131796579</v>
+        <v>-4.975557435355064</v>
       </c>
       <c r="I64" t="n">
-        <v>17.79349770580784</v>
+        <v>17.87923933705325</v>
       </c>
       <c r="J64" t="n">
-        <v>-9.339328752400089</v>
+        <v>-7.064776884790617</v>
       </c>
       <c r="K64" t="n">
-        <v>17.93559054945745</v>
+        <v>17.99996882163128</v>
       </c>
       <c r="L64" t="n">
-        <v>35.27635895488158</v>
+        <v>28.47703661131223</v>
       </c>
       <c r="M64" t="n">
-        <v>117.5904799172575</v>
+        <v>95.08296943431422</v>
       </c>
       <c r="N64" t="n">
-        <v>99.95190792966888</v>
+        <v>95.08296943431422</v>
       </c>
       <c r="O64" t="n">
-        <v>34.68301701323287</v>
+        <v>21.32835806734216</v>
       </c>
       <c r="P64" t="n">
-        <v>179.3138189390733</v>
+        <v>153.0882134804474</v>
       </c>
       <c r="Q64" t="n">
-        <v>213.9968359523062</v>
+        <v>174.4165715477896</v>
       </c>
       <c r="R64" t="n">
-        <v>34.68301701323287</v>
+        <v>21.32835806734216</v>
       </c>
       <c r="S64" t="n">
-        <v>179.3138189390733</v>
+        <v>153.0882134804474</v>
       </c>
       <c r="T64" t="n">
-        <v>213.9968359523062</v>
+        <v>174.4165715477896</v>
       </c>
     </row>
     <row r="65">
@@ -4429,61 +4429,61 @@
         <v>0.126</v>
       </c>
       <c r="B65" t="n">
-        <v>0.2713895868705221</v>
+        <v>0.2438971264457182</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.5737673663219566</v>
+        <v>-0.5095618344354428</v>
       </c>
       <c r="D65" t="n">
-        <v>-1.99405792094588</v>
+        <v>-2.122468984718908</v>
       </c>
       <c r="E65" t="n">
-        <v>2.085097367730609</v>
+        <v>1.92102142416103</v>
       </c>
       <c r="F65" t="n">
-        <v>-5.204580171881753</v>
+        <v>-4.40070765500038</v>
       </c>
       <c r="G65" t="n">
-        <v>10.40916034376355</v>
+        <v>8.801415310002056</v>
       </c>
       <c r="H65" t="n">
-        <v>-7.258367758691692</v>
+        <v>-5.314417422622745</v>
       </c>
       <c r="I65" t="n">
-        <v>17.80423073978761</v>
+        <v>17.87585961259723</v>
       </c>
       <c r="J65" t="n">
-        <v>-9.798202882569989</v>
+        <v>-7.46196275826293</v>
       </c>
       <c r="K65" t="n">
-        <v>17.95099990063468</v>
+        <v>17.99995956846826</v>
       </c>
       <c r="L65" t="n">
-        <v>35.61390872738502</v>
+        <v>28.65349027932221</v>
       </c>
       <c r="M65" t="n">
-        <v>118.7156627388453</v>
+        <v>95.89945331547469</v>
       </c>
       <c r="N65" t="n">
-        <v>100.9083133280185</v>
+        <v>95.89945331547469</v>
       </c>
       <c r="O65" t="n">
-        <v>37.8229026480638</v>
+        <v>23.38773514693633</v>
       </c>
       <c r="P65" t="n">
-        <v>185.3304032539194</v>
+        <v>157.3328406586595</v>
       </c>
       <c r="Q65" t="n">
-        <v>223.1533059019832</v>
+        <v>180.7205758055958</v>
       </c>
       <c r="R65" t="n">
-        <v>37.8229026480638</v>
+        <v>23.38773514693633</v>
       </c>
       <c r="S65" t="n">
-        <v>185.3304032539194</v>
+        <v>157.3328406586595</v>
       </c>
       <c r="T65" t="n">
-        <v>223.1533059019832</v>
+        <v>180.7205758055958</v>
       </c>
     </row>
     <row r="66">
@@ -4491,61 +4491,61 @@
         <v>0.128</v>
       </c>
       <c r="B66" t="n">
-        <v>0.2757896598847113</v>
+        <v>0.2478112095923255</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.5842647741602748</v>
+        <v>-0.5185663569798002</v>
       </c>
       <c r="D66" t="n">
-        <v>-1.973063105269244</v>
+        <v>-2.104459939630193</v>
       </c>
       <c r="E66" t="n">
-        <v>2.134032084769191</v>
+        <v>1.965369404788651</v>
       </c>
       <c r="F66" t="n">
-        <v>-5.375475871833284</v>
+        <v>-4.525740392415602</v>
       </c>
       <c r="G66" t="n">
-        <v>10.75095174366823</v>
+        <v>9.051480784830961</v>
       </c>
       <c r="H66" t="n">
-        <v>-7.650504628311842</v>
+        <v>-5.473119946686923</v>
       </c>
       <c r="I66" t="n">
-        <v>17.81819086438668</v>
+        <v>17.87234517801681</v>
       </c>
       <c r="J66" t="n">
-        <v>-10.27373685376648</v>
+        <v>-7.681681258185737</v>
       </c>
       <c r="K66" t="n">
-        <v>17.9697792839724</v>
+        <v>17.99997105708292</v>
       </c>
       <c r="L66" t="n">
-        <v>35.96757748564654</v>
+        <v>28.9428868395614</v>
       </c>
       <c r="M66" t="n">
-        <v>119.8945826090823</v>
+        <v>96.6279674195077</v>
       </c>
       <c r="N66" t="n">
-        <v>101.91039521772</v>
+        <v>96.6279674195077</v>
       </c>
       <c r="O66" t="n">
-        <v>41.1411602032975</v>
+        <v>24.78284834800041</v>
       </c>
       <c r="P66" t="n">
-        <v>191.5636008140847</v>
+        <v>161.7706163681746</v>
       </c>
       <c r="Q66" t="n">
-        <v>232.7047610173822</v>
+        <v>186.553464716175</v>
       </c>
       <c r="R66" t="n">
-        <v>41.1411602032975</v>
+        <v>24.78284834800041</v>
       </c>
       <c r="S66" t="n">
-        <v>191.5636008140847</v>
+        <v>161.7706163681746</v>
       </c>
       <c r="T66" t="n">
-        <v>232.7047610173822</v>
+        <v>186.553464716175</v>
       </c>
     </row>
     <row r="67">
@@ -4553,61 +4553,61 @@
         <v>0.13</v>
       </c>
       <c r="B67" t="n">
-        <v>0.2803591999507932</v>
+        <v>0.2517786608169751</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.595278575969189</v>
+        <v>-0.527723452115786</v>
       </c>
       <c r="D67" t="n">
-        <v>-1.951035501651415</v>
+        <v>-2.086145749358221</v>
       </c>
       <c r="E67" t="n">
-        <v>2.184413521105603</v>
+        <v>2.01006948095291</v>
       </c>
       <c r="F67" t="n">
-        <v>-5.561308691944728</v>
+        <v>-4.653038235192041</v>
       </c>
       <c r="G67" t="n">
-        <v>11.12261738388865</v>
+        <v>9.306076470383392</v>
       </c>
       <c r="H67" t="n">
-        <v>-8.069890010481176</v>
+        <v>-5.713465514385737</v>
       </c>
       <c r="I67" t="n">
-        <v>17.83243409105551</v>
+        <v>17.86875920786461</v>
       </c>
       <c r="J67" t="n">
-        <v>-10.7838086521502</v>
+        <v>-7.984148173159452</v>
       </c>
       <c r="K67" t="n">
-        <v>17.98926299616834</v>
+        <v>17.99997488609702</v>
       </c>
       <c r="L67" t="n">
-        <v>36.37196964090396</v>
+        <v>29.20882531795879</v>
       </c>
       <c r="M67" t="n">
-        <v>121.2415191834251</v>
+        <v>97.44456072230498</v>
       </c>
       <c r="N67" t="n">
-        <v>103.0552913059113</v>
+        <v>97.44456072230498</v>
       </c>
       <c r="O67" t="n">
-        <v>44.92750653129957</v>
+        <v>26.60861395207813</v>
       </c>
       <c r="P67" t="n">
-        <v>198.3466260379575</v>
+        <v>166.287584836049</v>
       </c>
       <c r="Q67" t="n">
-        <v>243.2741325692571</v>
+        <v>192.8961987881271</v>
       </c>
       <c r="R67" t="n">
-        <v>44.92750653129957</v>
+        <v>26.60861395207813</v>
       </c>
       <c r="S67" t="n">
-        <v>198.3466260379575</v>
+        <v>166.287584836049</v>
       </c>
       <c r="T67" t="n">
-        <v>243.2741325692571</v>
+        <v>192.8961987881271</v>
       </c>
     </row>
     <row r="68">
@@ -4615,61 +4615,61 @@
         <v>0.132</v>
       </c>
       <c r="B68" t="n">
-        <v>0.2850225955978436</v>
+        <v>0.2558413793257311</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.6065872058690966</v>
+        <v>-0.5371529043792284</v>
       </c>
       <c r="D68" t="n">
-        <v>-1.9284182418516</v>
+        <v>-2.067286844831337</v>
       </c>
       <c r="E68" t="n">
-        <v>2.235550308043351</v>
+        <v>2.055398082384556</v>
       </c>
       <c r="F68" t="n">
-        <v>-5.754409911684292</v>
+        <v>-4.784379514492583</v>
       </c>
       <c r="G68" t="n">
-        <v>11.50881982336761</v>
+        <v>9.568759028985996</v>
       </c>
       <c r="H68" t="n">
-        <v>-8.502480549622028</v>
+        <v>-6.099551969119632</v>
       </c>
       <c r="I68" t="n">
-        <v>17.83767070821566</v>
+        <v>17.86504553965977</v>
       </c>
       <c r="J68" t="n">
-        <v>-11.31063258652396</v>
+        <v>-8.434329172192014</v>
       </c>
       <c r="K68" t="n">
-        <v>17.99994506772514</v>
+        <v>17.99996504196847</v>
       </c>
       <c r="L68" t="n">
-        <v>36.80377873042038</v>
+        <v>29.43288880611125</v>
       </c>
       <c r="M68" t="n">
-        <v>122.6801427368905</v>
+        <v>98.41838408397527</v>
       </c>
       <c r="N68" t="n">
-        <v>104.2781213263569</v>
+        <v>98.41838408397527</v>
       </c>
       <c r="O68" t="n">
-        <v>48.97708639655795</v>
+        <v>29.2031365797165</v>
       </c>
       <c r="P68" t="n">
-        <v>205.289267249356</v>
+        <v>170.9459201900197</v>
       </c>
       <c r="Q68" t="n">
-        <v>254.266353645914</v>
+        <v>200.1490567697362</v>
       </c>
       <c r="R68" t="n">
-        <v>48.97708639655795</v>
+        <v>29.2031365797165</v>
       </c>
       <c r="S68" t="n">
-        <v>205.289267249356</v>
+        <v>170.9459201900197</v>
       </c>
       <c r="T68" t="n">
-        <v>254.266353645914</v>
+        <v>200.1490567697362</v>
       </c>
     </row>
     <row r="69">
@@ -4677,61 +4677,61 @@
         <v>0.134</v>
       </c>
       <c r="B69" t="n">
-        <v>0.2897995858746146</v>
+        <v>0.2600107685586289</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.6182526700401471</v>
+        <v>-0.5468961070871764</v>
       </c>
       <c r="D69" t="n">
-        <v>-1.905087313509499</v>
+        <v>-2.047800439415441</v>
       </c>
       <c r="E69" t="n">
-        <v>2.287601305633062</v>
+        <v>2.101480116783733</v>
       </c>
       <c r="F69" t="n">
-        <v>-5.956308169979229</v>
+        <v>-4.920720324679545</v>
       </c>
       <c r="G69" t="n">
-        <v>11.9126163399601</v>
+        <v>9.841440649359345</v>
       </c>
       <c r="H69" t="n">
-        <v>-8.951053461905758</v>
+        <v>-6.353944193891852</v>
       </c>
       <c r="I69" t="n">
-        <v>17.83200650880616</v>
+        <v>17.86120551742054</v>
       </c>
       <c r="J69" t="n">
-        <v>-11.85773184885562</v>
+        <v>-8.755255712335471</v>
       </c>
       <c r="K69" t="n">
-        <v>17.99997439919959</v>
+        <v>17.99996983057651</v>
       </c>
       <c r="L69" t="n">
-        <v>37.2687708918765</v>
+        <v>29.73239409196513</v>
       </c>
       <c r="M69" t="n">
-        <v>124.2297362330715</v>
+        <v>99.32522222792917</v>
       </c>
       <c r="N69" t="n">
-        <v>105.5952757981108</v>
+        <v>99.32522222792917</v>
       </c>
       <c r="O69" t="n">
-        <v>53.34526123385822</v>
+        <v>31.28440387809092</v>
       </c>
       <c r="P69" t="n">
-        <v>212.4250937653827</v>
+        <v>175.7792708737789</v>
       </c>
       <c r="Q69" t="n">
-        <v>265.7703549992409</v>
+        <v>207.0636747518698</v>
       </c>
       <c r="R69" t="n">
-        <v>53.34526123385822</v>
+        <v>31.28440387809092</v>
       </c>
       <c r="S69" t="n">
-        <v>212.4250937653827</v>
+        <v>175.7792708737789</v>
       </c>
       <c r="T69" t="n">
-        <v>265.7703549992409</v>
+        <v>207.0636747518698</v>
       </c>
     </row>
     <row r="70">
@@ -4739,61 +4739,61 @@
         <v>0.136</v>
       </c>
       <c r="B70" t="n">
-        <v>0.2947433251238878</v>
+        <v>0.2642324012215275</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.6304623880850567</v>
+        <v>-0.5567936019810198</v>
       </c>
       <c r="D70" t="n">
-        <v>-1.88066787741968</v>
+        <v>-2.028005449627754</v>
       </c>
       <c r="E70" t="n">
-        <v>2.340976355362255</v>
+        <v>2.147933831286381</v>
       </c>
       <c r="F70" t="n">
-        <v>-6.170413920704739</v>
+        <v>-5.059542436798075</v>
       </c>
       <c r="G70" t="n">
-        <v>12.34082784140967</v>
+        <v>10.11908487359507</v>
       </c>
       <c r="H70" t="n">
-        <v>-9.435278582713964</v>
+        <v>-6.562484196337905</v>
       </c>
       <c r="I70" t="n">
-        <v>17.82597957378983</v>
+        <v>17.85730084241752</v>
       </c>
       <c r="J70" t="n">
-        <v>-12.44644057601788</v>
+        <v>-9.031540905495365</v>
       </c>
       <c r="K70" t="n">
-        <v>17.99998524635371</v>
+        <v>17.99997993913521</v>
       </c>
       <c r="L70" t="n">
-        <v>37.77990365736019</v>
+        <v>30.05954459202049</v>
       </c>
       <c r="M70" t="n">
-        <v>125.9333382095497</v>
+        <v>100.2149778072988</v>
       </c>
       <c r="N70" t="n">
-        <v>107.0433374781172</v>
+        <v>100.2149778072988</v>
       </c>
       <c r="O70" t="n">
-        <v>58.29513813624651</v>
+        <v>33.20763836721963</v>
       </c>
       <c r="P70" t="n">
-        <v>219.9854713257431</v>
+        <v>180.6994564433617</v>
       </c>
       <c r="Q70" t="n">
-        <v>278.2806094619896</v>
+        <v>213.9070948105813</v>
       </c>
       <c r="R70" t="n">
-        <v>58.29513813624651</v>
+        <v>33.20763836721963</v>
       </c>
       <c r="S70" t="n">
-        <v>219.9854713257431</v>
+        <v>180.6994564433617</v>
       </c>
       <c r="T70" t="n">
-        <v>278.2806094619896</v>
+        <v>213.9070948105813</v>
       </c>
     </row>
     <row r="71">
@@ -4801,61 +4801,61 @@
         <v>0.138</v>
       </c>
       <c r="B71" t="n">
-        <v>0.2997567678188246</v>
+        <v>0.2686029047039588</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.642902596213925</v>
+        <v>-0.5671425863227728</v>
       </c>
       <c r="D71" t="n">
-        <v>-1.855787461161943</v>
+        <v>-2.007307480944247</v>
       </c>
       <c r="E71" t="n">
-        <v>2.394919731865988</v>
+        <v>2.195497005902095</v>
       </c>
       <c r="F71" t="n">
-        <v>-6.389849738535599</v>
+        <v>-5.206050488528364</v>
       </c>
       <c r="G71" t="n">
-        <v>12.77969947706922</v>
+        <v>10.41210097705703</v>
       </c>
       <c r="H71" t="n">
-        <v>-9.936604885617225</v>
+        <v>-6.991093746946468</v>
       </c>
       <c r="I71" t="n">
-        <v>17.81979655084161</v>
+        <v>17.8531598501339</v>
       </c>
       <c r="J71" t="n">
-        <v>-13.0548515580226</v>
+        <v>-9.53164638534831</v>
       </c>
       <c r="K71" t="n">
-        <v>17.99999031346828</v>
+        <v>17.9999704739104</v>
       </c>
       <c r="L71" t="n">
-        <v>38.31043114349969</v>
+        <v>30.29048344335562</v>
       </c>
       <c r="M71" t="n">
-        <v>127.7016567792166</v>
+        <v>101.351815271988</v>
       </c>
       <c r="N71" t="n">
-        <v>108.5464082623341</v>
+        <v>101.351815271988</v>
       </c>
       <c r="O71" t="n">
-        <v>63.51281447157047</v>
+        <v>36.43620045834862</v>
       </c>
       <c r="P71" t="n">
-        <v>227.7311879914317</v>
+        <v>185.8881260783449</v>
       </c>
       <c r="Q71" t="n">
-        <v>291.2440024630022</v>
+        <v>222.3243265366935</v>
       </c>
       <c r="R71" t="n">
-        <v>63.51281447157047</v>
+        <v>36.43620045834862</v>
       </c>
       <c r="S71" t="n">
-        <v>227.7311879914317</v>
+        <v>185.8881260783449</v>
       </c>
       <c r="T71" t="n">
-        <v>291.2440024630022</v>
+        <v>222.3243265366935</v>
       </c>
     </row>
     <row r="72">
@@ -4863,61 +4863,61 @@
         <v>0.14</v>
       </c>
       <c r="B72" t="n">
-        <v>0.3049737336290836</v>
+        <v>0.27303518038335</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.6560368913117827</v>
+        <v>-0.5776852063905418</v>
       </c>
       <c r="D72" t="n">
-        <v>-1.829518870966228</v>
+        <v>-1.98622224080871</v>
       </c>
       <c r="E72" t="n">
-        <v>2.450627520764653</v>
+        <v>2.243546557863991</v>
       </c>
       <c r="F72" t="n">
-        <v>-6.626454069613255</v>
+        <v>-5.356083834001315</v>
       </c>
       <c r="G72" t="n">
-        <v>13.25290813922713</v>
+        <v>10.71216766800321</v>
       </c>
       <c r="H72" t="n">
-        <v>-10.50339956351187</v>
+        <v>-7.345048248090936</v>
       </c>
       <c r="I72" t="n">
-        <v>17.81312625788139</v>
+        <v>17.84892236379875</v>
       </c>
       <c r="J72" t="n">
-        <v>-13.73710914948314</v>
+        <v>-9.958817159083578</v>
       </c>
       <c r="K72" t="n">
-        <v>17.99999226264449</v>
+        <v>17.9999639279176</v>
       </c>
       <c r="L72" t="n">
-        <v>38.89834649013427</v>
+        <v>30.55965394073177</v>
       </c>
       <c r="M72" t="n">
-        <v>129.6613326300466</v>
+        <v>102.4486182552849</v>
       </c>
       <c r="N72" t="n">
-        <v>110.2121327355396</v>
+        <v>102.4486182552849</v>
       </c>
       <c r="O72" t="n">
-        <v>69.68657395728356</v>
+        <v>39.35870609749221</v>
       </c>
       <c r="P72" t="n">
-        <v>236.0736952244141</v>
+        <v>191.1999775566806</v>
       </c>
       <c r="Q72" t="n">
-        <v>305.7602691816977</v>
+        <v>230.5586836541728</v>
       </c>
       <c r="R72" t="n">
-        <v>69.68657395728356</v>
+        <v>39.35870609749221</v>
       </c>
       <c r="S72" t="n">
-        <v>236.0736952244141</v>
+        <v>191.1999775566806</v>
       </c>
       <c r="T72" t="n">
-        <v>305.7602691816977</v>
+        <v>230.5586836541728</v>
       </c>
     </row>
     <row r="73">
@@ -4925,61 +4925,61 @@
         <v>0.142</v>
       </c>
       <c r="B73" t="n">
-        <v>0.3102864763108083</v>
+        <v>0.2775654368380163</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.6695136129864432</v>
+        <v>-0.5885349642887536</v>
       </c>
       <c r="D73" t="n">
-        <v>-1.802565427616907</v>
+        <v>-1.964522725012286</v>
       </c>
       <c r="E73" t="n">
-        <v>2.507247582518535</v>
+        <v>2.29236758359241</v>
       </c>
       <c r="F73" t="n">
-        <v>-6.872638860031232</v>
+        <v>-5.511708870088769</v>
       </c>
       <c r="G73" t="n">
-        <v>13.74527772006357</v>
+        <v>11.02341774017664</v>
       </c>
       <c r="H73" t="n">
-        <v>-11.10132964040744</v>
+        <v>-7.580587669560865</v>
       </c>
       <c r="I73" t="n">
-        <v>17.80618529328926</v>
+        <v>17.8445318221662</v>
       </c>
       <c r="J73" t="n">
-        <v>-14.45517740410268</v>
+        <v>-10.27030159816418</v>
       </c>
       <c r="K73" t="n">
-        <v>17.99999370914215</v>
+        <v>17.99996201230269</v>
       </c>
       <c r="L73" t="n">
-        <v>39.5146312902674</v>
+        <v>30.88946606174268</v>
       </c>
       <c r="M73" t="n">
-        <v>131.7155829255576</v>
+        <v>103.4819200241584</v>
       </c>
       <c r="N73" t="n">
-        <v>111.958245486724</v>
+        <v>103.4819200241584</v>
       </c>
       <c r="O73" t="n">
-        <v>76.38251325035063</v>
+        <v>41.7957563065354</v>
       </c>
       <c r="P73" t="n">
-        <v>244.748975547881</v>
+        <v>196.7072155212587</v>
       </c>
       <c r="Q73" t="n">
-        <v>321.1314887982317</v>
+        <v>238.5029718277941</v>
       </c>
       <c r="R73" t="n">
-        <v>76.38251325035063</v>
+        <v>41.7957563065354</v>
       </c>
       <c r="S73" t="n">
-        <v>244.748975547881</v>
+        <v>196.7072155212587</v>
       </c>
       <c r="T73" t="n">
-        <v>321.1314887982317</v>
+        <v>238.5029718277941</v>
       </c>
     </row>
     <row r="74">
@@ -4987,61 +4987,61 @@
         <v>0.144</v>
       </c>
       <c r="B74" t="n">
-        <v>0.3157368714930716</v>
+        <v>0.2822150886314985</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.6834824772193905</v>
+        <v>-0.5997728127039509</v>
       </c>
       <c r="D74" t="n">
-        <v>-1.774627699151012</v>
+        <v>-1.942047028181892</v>
       </c>
       <c r="E74" t="n">
-        <v>2.565178781687666</v>
+        <v>2.342021868161566</v>
       </c>
       <c r="F74" t="n">
-        <v>-7.132592884757275</v>
+        <v>-5.67451400704358</v>
       </c>
       <c r="G74" t="n">
-        <v>14.2651857695131</v>
+        <v>11.34902801408699</v>
       </c>
       <c r="H74" t="n">
-        <v>-11.74400815669304</v>
+        <v>-7.885097058103835</v>
       </c>
       <c r="I74" t="n">
-        <v>17.79885531382967</v>
+        <v>17.83993729334982</v>
       </c>
       <c r="J74" t="n">
-        <v>-15.22471348445459</v>
+        <v>-10.6542598935411</v>
       </c>
       <c r="K74" t="n">
-        <v>17.99999443317981</v>
+        <v>17.99995858834845</v>
       </c>
       <c r="L74" t="n">
-        <v>40.1716892557089</v>
+        <v>30.73478400627228</v>
       </c>
       <c r="M74" t="n">
-        <v>133.9057575689637</v>
+        <v>104.4560039834401</v>
       </c>
       <c r="N74" t="n">
-        <v>113.8198939336191</v>
+        <v>104.4560039834401</v>
       </c>
       <c r="O74" t="n">
-        <v>83.82894016232953</v>
+        <v>44.78106918699799</v>
       </c>
       <c r="P74" t="n">
-        <v>253.9025242394437</v>
+        <v>202.4649019142433</v>
       </c>
       <c r="Q74" t="n">
-        <v>337.7314644017732</v>
+        <v>247.2459711012413</v>
       </c>
       <c r="R74" t="n">
-        <v>83.82894016232953</v>
+        <v>44.78106918699799</v>
       </c>
       <c r="S74" t="n">
-        <v>253.9025242394437</v>
+        <v>202.4649019142433</v>
       </c>
       <c r="T74" t="n">
-        <v>337.7314644017732</v>
+        <v>247.2459711012413</v>
       </c>
     </row>
     <row r="75">
@@ -5049,61 +5049,61 @@
         <v>0.146</v>
       </c>
       <c r="B75" t="n">
-        <v>0.3213663764289975</v>
+        <v>0.2869210756940344</v>
       </c>
       <c r="C75" t="n">
-        <v>-0.6981247379889154</v>
+        <v>-0.6111953926006399</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.745343177611962</v>
+        <v>-1.919201868388513</v>
       </c>
       <c r="E75" t="n">
-        <v>2.624973862139448</v>
+        <v>2.392054791537294</v>
       </c>
       <c r="F75" t="n">
-        <v>-7.413886530796536</v>
+        <v>-5.840745136447814</v>
       </c>
       <c r="G75" t="n">
-        <v>14.82777306159275</v>
+        <v>11.68149027289679</v>
       </c>
       <c r="H75" t="n">
-        <v>-12.46201546510147</v>
+        <v>-8.20170270742285</v>
       </c>
       <c r="I75" t="n">
-        <v>17.790922145611</v>
+        <v>17.83316866267809</v>
       </c>
       <c r="J75" t="n">
-        <v>-16.07999209213018</v>
+        <v>-11.05198633400938</v>
       </c>
       <c r="K75" t="n">
-        <v>17.99999374577945</v>
+        <v>17.99787767552594</v>
       </c>
       <c r="L75" t="n">
-        <v>40.87259027458617</v>
+        <v>30.41065187730083</v>
       </c>
       <c r="M75" t="n">
-        <v>136.2862701238077</v>
+        <v>105.3907929401546</v>
       </c>
       <c r="N75" t="n">
-        <v>115.8433296052366</v>
+        <v>105.3907929401546</v>
       </c>
       <c r="O75" t="n">
-        <v>92.54166503248888</v>
+        <v>47.90689500193633</v>
       </c>
       <c r="P75" t="n">
-        <v>263.7964822607657</v>
+        <v>208.3166275277965</v>
       </c>
       <c r="Q75" t="n">
-        <v>356.3381472932546</v>
+        <v>256.2235225297328</v>
       </c>
       <c r="R75" t="n">
-        <v>92.54166503248888</v>
+        <v>47.90689500193633</v>
       </c>
       <c r="S75" t="n">
-        <v>263.7964822607657</v>
+        <v>208.3166275277965</v>
       </c>
       <c r="T75" t="n">
-        <v>356.3381472932546</v>
+        <v>256.2235225297328</v>
       </c>
     </row>
     <row r="76">
@@ -5111,61 +5111,61 @@
         <v>0.148</v>
       </c>
       <c r="B76" t="n">
-        <v>0.3270745231870421</v>
+        <v>0.2917822884648186</v>
       </c>
       <c r="C76" t="n">
-        <v>-0.7130658213930433</v>
+        <v>-0.6231434288766046</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.715461010803707</v>
+        <v>-1.895305795836584</v>
       </c>
       <c r="E76" t="n">
-        <v>2.685559196555364</v>
+        <v>2.44298313473042</v>
       </c>
       <c r="F76" t="n">
-        <v>-7.704113114238487</v>
+        <v>-6.016804606114369</v>
       </c>
       <c r="G76" t="n">
-        <v>15.4082262284789</v>
+        <v>12.03360921222838</v>
       </c>
       <c r="H76" t="n">
-        <v>-13.19004395190698</v>
+        <v>-8.343466829461718</v>
       </c>
       <c r="I76" t="n">
-        <v>17.78273662940292</v>
+        <v>17.79925423011689</v>
       </c>
       <c r="J76" t="n">
-        <v>-16.94965115165536</v>
+        <v>-11.27966747724553</v>
       </c>
       <c r="K76" t="n">
-        <v>17.99999261922447</v>
+        <v>17.96892812000931</v>
       </c>
       <c r="L76" t="n">
-        <v>41.54134912615572</v>
+        <v>30.22187184852764</v>
       </c>
       <c r="M76" t="n">
-        <v>138.7452746283815</v>
+        <v>106.1017121980121</v>
       </c>
       <c r="N76" t="n">
-        <v>117.9334834341243</v>
+        <v>106.1017121980121</v>
       </c>
       <c r="O76" t="n">
-        <v>101.6269892469588</v>
+        <v>50.21667719712582</v>
       </c>
       <c r="P76" t="n">
-        <v>273.9999961559246</v>
+        <v>214.1817733353844</v>
       </c>
       <c r="Q76" t="n">
-        <v>375.6269854028833</v>
+        <v>264.3984505325103</v>
       </c>
       <c r="R76" t="n">
-        <v>101.6269892469588</v>
+        <v>50.21667719712582</v>
       </c>
       <c r="S76" t="n">
-        <v>273.9999961559246</v>
+        <v>214.1817733353844</v>
       </c>
       <c r="T76" t="n">
-        <v>375.6269854028833</v>
+        <v>264.3984505325103</v>
       </c>
     </row>
     <row r="77">
@@ -5173,61 +5173,61 @@
         <v>0.15</v>
       </c>
       <c r="B77" t="n">
-        <v>0.3330211807508452</v>
+        <v>0.2967137973622002</v>
       </c>
       <c r="C77" t="n">
-        <v>-0.7289649903741631</v>
+        <v>-0.6353407106303997</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.683662672841467</v>
+        <v>-1.870911232328994</v>
       </c>
       <c r="E77" t="n">
-        <v>2.748079475934381</v>
+        <v>2.494124947636833</v>
       </c>
       <c r="F77" t="n">
-        <v>-8.01426152982758</v>
+        <v>-6.197361715264774</v>
       </c>
       <c r="G77" t="n">
-        <v>16.02852305965467</v>
+        <v>12.39472343052894</v>
       </c>
       <c r="H77" t="n">
-        <v>-13.56989282114349</v>
+        <v>-8.54220595720564</v>
       </c>
       <c r="I77" t="n">
-        <v>17.77399095079563</v>
+        <v>17.72263033693865</v>
       </c>
       <c r="J77" t="n">
-        <v>-17.48085244769934</v>
+        <v>-11.56651847425485</v>
       </c>
       <c r="K77" t="n">
-        <v>17.99999312593676</v>
+        <v>17.89739593730911</v>
       </c>
       <c r="L77" t="n">
-        <v>41.26868532091316</v>
+        <v>29.80219395036853</v>
       </c>
       <c r="M77" t="n">
-        <v>141.3589170492828</v>
+        <v>106.5972957577541</v>
       </c>
       <c r="N77" t="n">
-        <v>120.1550794918903</v>
+        <v>106.5972957577541</v>
       </c>
       <c r="O77" t="n">
-        <v>108.8307431839328</v>
+        <v>52.96602666988287</v>
       </c>
       <c r="P77" t="n">
-        <v>284.8872286872443</v>
+        <v>219.6407231511955</v>
       </c>
       <c r="Q77" t="n">
-        <v>393.7179718711771</v>
+        <v>272.6067498210784</v>
       </c>
       <c r="R77" t="n">
-        <v>108.8307431839328</v>
+        <v>52.96602666988287</v>
       </c>
       <c r="S77" t="n">
-        <v>284.8872286872443</v>
+        <v>219.6407231511955</v>
       </c>
       <c r="T77" t="n">
-        <v>393.7179718711771</v>
+        <v>272.6067498210784</v>
       </c>
     </row>
     <row r="78">
@@ -5235,61 +5235,61 @@
         <v>0.152</v>
       </c>
       <c r="B78" t="n">
-        <v>0.3390530388565615</v>
+        <v>0.3017446875606784</v>
       </c>
       <c r="C78" t="n">
-        <v>-0.7452470097957196</v>
+        <v>-0.6478903637178401</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.651098633998354</v>
+        <v>-1.845811926154113</v>
       </c>
       <c r="E78" t="n">
-        <v>2.810827309355576</v>
+        <v>2.54556855381235</v>
       </c>
       <c r="F78" t="n">
-        <v>-8.323818962768243</v>
+        <v>-6.384277371968276</v>
       </c>
       <c r="G78" t="n">
-        <v>16.64763792553535</v>
+        <v>12.76855474393747</v>
       </c>
       <c r="H78" t="n">
-        <v>-13.79465115327994</v>
+        <v>-8.821493622557909</v>
       </c>
       <c r="I78" t="n">
-        <v>17.76526187975375</v>
+        <v>17.58562585139063</v>
       </c>
       <c r="J78" t="n">
-        <v>-17.85667480711084</v>
+        <v>-11.93702098007843</v>
       </c>
       <c r="K78" t="n">
-        <v>17.9999935745038</v>
+        <v>17.76566247328015</v>
       </c>
       <c r="L78" t="n">
-        <v>40.58105600776774</v>
+        <v>29.0560836897065</v>
       </c>
       <c r="M78" t="n">
-        <v>143.927184131296</v>
+        <v>106.788448008303</v>
       </c>
       <c r="N78" t="n">
-        <v>122.3381065116016</v>
+        <v>106.788448008303</v>
       </c>
       <c r="O78" t="n">
-        <v>114.8180083448541</v>
+        <v>56.3368153325163</v>
       </c>
       <c r="P78" t="n">
-        <v>295.7470528633343</v>
+        <v>224.5254125046316</v>
       </c>
       <c r="Q78" t="n">
-        <v>410.5650612081884</v>
+        <v>280.8622278371479</v>
       </c>
       <c r="R78" t="n">
-        <v>114.8180083448541</v>
+        <v>56.3368153325163</v>
       </c>
       <c r="S78" t="n">
-        <v>295.7470528633343</v>
+        <v>224.5254125046316</v>
       </c>
       <c r="T78" t="n">
-        <v>410.5650612081884</v>
+        <v>280.8622278371479</v>
       </c>
     </row>
     <row r="79">
@@ -5297,61 +5297,61 @@
         <v>0.154</v>
       </c>
       <c r="B79" t="n">
-        <v>0.3452311050320049</v>
+        <v>0.3069044774048009</v>
       </c>
       <c r="C79" t="n">
-        <v>-0.7621860182766583</v>
+        <v>-0.6609225081012645</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.617220617036477</v>
+        <v>-1.819747637387264</v>
       </c>
       <c r="E79" t="n">
-        <v>2.873965636035599</v>
+        <v>2.596913143565569</v>
       </c>
       <c r="F79" t="n">
-        <v>-8.632362242156248</v>
+        <v>-6.579368112702569</v>
       </c>
       <c r="G79" t="n">
-        <v>17.26472448431377</v>
+        <v>13.15873622540528</v>
       </c>
       <c r="H79" t="n">
-        <v>-13.7532669521278</v>
+        <v>-8.987339117188931</v>
       </c>
       <c r="I79" t="n">
-        <v>17.75656130806206</v>
+        <v>17.36170272205603</v>
       </c>
       <c r="J79" t="n">
-        <v>-17.96585972630005</v>
+        <v>-12.19807075618779</v>
       </c>
       <c r="K79" t="n">
-        <v>17.99999392329088</v>
+        <v>17.54724090283424</v>
       </c>
       <c r="L79" t="n">
-        <v>39.18132669441793</v>
+        <v>28.52198022251097</v>
       </c>
       <c r="M79" t="n">
-        <v>146.4175850335518</v>
+        <v>106.5148124908946</v>
       </c>
       <c r="N79" t="n">
-        <v>124.454947278519</v>
+        <v>106.5148124908946</v>
       </c>
       <c r="O79" t="n">
-        <v>118.7177225137576</v>
+        <v>59.14845109901044</v>
       </c>
       <c r="P79" t="n">
-        <v>306.5598430344454</v>
+        <v>228.3901834839943</v>
       </c>
       <c r="Q79" t="n">
-        <v>425.277565548203</v>
+        <v>287.5386345830048</v>
       </c>
       <c r="R79" t="n">
-        <v>118.7177225137576</v>
+        <v>59.14845109901044</v>
       </c>
       <c r="S79" t="n">
-        <v>306.5598430344454</v>
+        <v>228.3901834839943</v>
       </c>
       <c r="T79" t="n">
-        <v>425.277565548203</v>
+        <v>287.5386345830048</v>
       </c>
     </row>
     <row r="80">
@@ -5359,61 +5359,61 @@
         <v>0.156</v>
       </c>
       <c r="B80" t="n">
-        <v>0.3515397020904036</v>
+        <v>0.312122447762929</v>
       </c>
       <c r="C80" t="n">
-        <v>-0.7798278047060888</v>
+        <v>-0.6741765831649293</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.581937044177616</v>
+        <v>-1.793239487259935</v>
       </c>
       <c r="E80" t="n">
-        <v>2.937019819532513</v>
+        <v>2.648142975604897</v>
       </c>
       <c r="F80" t="n">
-        <v>-8.93481805005055</v>
+        <v>-6.778158000095613</v>
       </c>
       <c r="G80" t="n">
-        <v>17.86963610010143</v>
+        <v>13.55631600019014</v>
       </c>
       <c r="H80" t="n">
-        <v>-13.63979347940319</v>
+        <v>-9.129922622690575</v>
       </c>
       <c r="I80" t="n">
-        <v>17.74803239852128</v>
+        <v>17.09968361117847</v>
       </c>
       <c r="J80" t="n">
-        <v>-17.99998468782786</v>
+        <v>-12.43766372673723</v>
       </c>
       <c r="K80" t="n">
-        <v>17.99999426753271</v>
+        <v>17.29082766678115</v>
       </c>
       <c r="L80" t="n">
-        <v>37.45910095133461</v>
+        <v>27.99906342370281</v>
       </c>
       <c r="M80" t="n">
-        <v>148.6398419091147</v>
+        <v>106.0338745654922</v>
       </c>
       <c r="N80" t="n">
-        <v>126.3438656227475</v>
+        <v>106.0338745654922</v>
       </c>
       <c r="O80" t="n">
-        <v>121.8391462643559</v>
+        <v>61.89251950868923</v>
       </c>
       <c r="P80" t="n">
-        <v>317.1474217836222</v>
+        <v>231.785845589963</v>
       </c>
       <c r="Q80" t="n">
-        <v>438.9865680479781</v>
+        <v>293.6783650986523</v>
       </c>
       <c r="R80" t="n">
-        <v>121.8391462643559</v>
+        <v>61.89251950868923</v>
       </c>
       <c r="S80" t="n">
-        <v>317.1474217836222</v>
+        <v>231.785845589963</v>
       </c>
       <c r="T80" t="n">
-        <v>438.9865680479781</v>
+        <v>293.6783650986523</v>
       </c>
     </row>
     <row r="81">
@@ -5421,61 +5421,61 @@
         <v>0.158</v>
       </c>
       <c r="B81" t="n">
-        <v>0.3579086411099318</v>
+        <v>0.3174923668879452</v>
       </c>
       <c r="C81" t="n">
-        <v>-0.7977959265154392</v>
+        <v>-0.6880370563838853</v>
       </c>
       <c r="D81" t="n">
-        <v>-1.546000800558915</v>
+        <v>-1.765518540822023</v>
       </c>
       <c r="E81" t="n">
-        <v>3.000035509497093</v>
+        <v>2.698621072312415</v>
       </c>
       <c r="F81" t="n">
-        <v>-9.234527869766815</v>
+        <v>-6.986668332323074</v>
       </c>
       <c r="G81" t="n">
-        <v>18.46905573953153</v>
+        <v>13.97333666464652</v>
       </c>
       <c r="H81" t="n">
-        <v>-13.49353791480907</v>
+        <v>-9.39201784583155</v>
       </c>
       <c r="I81" t="n">
-        <v>17.73958091769081</v>
+        <v>16.74549808359806</v>
       </c>
       <c r="J81" t="n">
-        <v>-17.99998751525527</v>
+        <v>-12.80151199200521</v>
       </c>
       <c r="K81" t="n">
-        <v>17.9999946036182</v>
+        <v>16.94252213056958</v>
       </c>
       <c r="L81" t="n">
-        <v>35.58788253423769</v>
+        <v>26.96017846965582</v>
       </c>
       <c r="M81" t="n">
-        <v>150.7365936179974</v>
+        <v>105.0275648646499</v>
       </c>
       <c r="N81" t="n">
-        <v>128.1261045752978</v>
+        <v>105.0275648646499</v>
       </c>
       <c r="O81" t="n">
-        <v>124.6059448599063</v>
+        <v>65.65244369512858</v>
       </c>
       <c r="P81" t="n">
-        <v>327.6332501568734</v>
+        <v>233.8998599081969</v>
       </c>
       <c r="Q81" t="n">
-        <v>452.2391950167797</v>
+        <v>299.5523036033255</v>
       </c>
       <c r="R81" t="n">
-        <v>124.6059448599063</v>
+        <v>65.65244369512858</v>
       </c>
       <c r="S81" t="n">
-        <v>327.6332501568734</v>
+        <v>233.8998599081969</v>
       </c>
       <c r="T81" t="n">
-        <v>452.2391950167797</v>
+        <v>299.5523036033255</v>
       </c>
     </row>
     <row r="82">
@@ -5483,61 +5483,61 @@
         <v>0.16</v>
       </c>
       <c r="B82" t="n">
-        <v>0.3644247553901814</v>
+        <v>0.322935098171035</v>
       </c>
       <c r="C82" t="n">
-        <v>-0.8167698766227397</v>
+        <v>-0.7022110106758959</v>
       </c>
       <c r="D82" t="n">
-        <v>-1.508052900344314</v>
+        <v>-1.737170632238002</v>
       </c>
       <c r="E82" t="n">
-        <v>3.063015654381504</v>
+        <v>2.748415349424967</v>
       </c>
       <c r="F82" t="n">
-        <v>-9.537372882171189</v>
+        <v>-7.200025519933804</v>
       </c>
       <c r="G82" t="n">
-        <v>19.07474576434285</v>
+        <v>14.40005103986821</v>
       </c>
       <c r="H82" t="n">
-        <v>-13.34574793068564</v>
+        <v>-9.58648250723974</v>
       </c>
       <c r="I82" t="n">
-        <v>17.7310401306996</v>
+        <v>16.34182599708467</v>
       </c>
       <c r="J82" t="n">
-        <v>-17.99998589718518</v>
+        <v>-13.10009496096744</v>
       </c>
       <c r="K82" t="n">
-        <v>17.99999404597683</v>
+        <v>16.54486671674681</v>
       </c>
       <c r="L82" t="n">
-        <v>33.36644842215731</v>
+        <v>26.05874836517716</v>
       </c>
       <c r="M82" t="n">
-        <v>152.3039483676611</v>
+        <v>103.7259088404316</v>
       </c>
       <c r="N82" t="n">
-        <v>129.458356112512</v>
+        <v>103.7259088404316</v>
       </c>
       <c r="O82" t="n">
-        <v>127.2530064593334</v>
+        <v>69.03577580629823</v>
       </c>
       <c r="P82" t="n">
-        <v>338.2115727015666</v>
+        <v>235.2132095516274</v>
       </c>
       <c r="Q82" t="n">
-        <v>465.4645791609</v>
+        <v>304.2489853579256</v>
       </c>
       <c r="R82" t="n">
-        <v>127.2530064593334</v>
+        <v>69.03577580629823</v>
       </c>
       <c r="S82" t="n">
-        <v>338.2115727015666</v>
+        <v>235.2132095516274</v>
       </c>
       <c r="T82" t="n">
-        <v>465.4645791609</v>
+        <v>304.2489853579256</v>
       </c>
     </row>
     <row r="83">
@@ -5545,61 +5545,61 @@
         <v>0.162</v>
       </c>
       <c r="B83" t="n">
-        <v>0.3709797314289706</v>
+        <v>0.3284697833936584</v>
       </c>
       <c r="C83" t="n">
-        <v>-0.8360869184457437</v>
+        <v>-0.7167808579121511</v>
       </c>
       <c r="D83" t="n">
-        <v>-1.469418816698306</v>
+        <v>-1.708030937765491</v>
       </c>
       <c r="E83" t="n">
-        <v>3.126028284318726</v>
+        <v>2.797346035794556</v>
       </c>
       <c r="F83" t="n">
-        <v>-9.846861307848503</v>
+        <v>-7.419503765601767</v>
       </c>
       <c r="G83" t="n">
-        <v>19.69372261569836</v>
+        <v>14.83900753120283</v>
       </c>
       <c r="H83" t="n">
-        <v>-13.19471582187476</v>
+        <v>-9.695537029067822</v>
       </c>
       <c r="I83" t="n">
-        <v>17.72230111397336</v>
+        <v>15.87565769883632</v>
       </c>
       <c r="J83" t="n">
-        <v>-17.99998414010483</v>
+        <v>-13.31625486668148</v>
       </c>
       <c r="K83" t="n">
-        <v>17.99998260285471</v>
+        <v>16.08488770502629</v>
       </c>
       <c r="L83" t="n">
-        <v>31.02292817011894</v>
+        <v>25.33090898043818</v>
       </c>
       <c r="M83" t="n">
-        <v>153.6766027110554</v>
+        <v>102.0512621141149</v>
       </c>
       <c r="N83" t="n">
-        <v>130.6251123043971</v>
+        <v>102.0512621141149</v>
       </c>
       <c r="O83" t="n">
-        <v>129.9040178539308</v>
+        <v>71.94351255215602</v>
       </c>
       <c r="P83" t="n">
-        <v>349.0154700052937</v>
+        <v>235.5154056591458</v>
       </c>
       <c r="Q83" t="n">
-        <v>478.9194878592244</v>
+        <v>307.4589182113018</v>
       </c>
       <c r="R83" t="n">
-        <v>129.9040178539308</v>
+        <v>71.94351255215602</v>
       </c>
       <c r="S83" t="n">
-        <v>349.0154700052937</v>
+        <v>235.5154056591458</v>
       </c>
       <c r="T83" t="n">
-        <v>478.9194878592244</v>
+        <v>307.4589182113018</v>
       </c>
     </row>
     <row r="84">
@@ -5607,61 +5607,61 @@
         <v>0.164</v>
       </c>
       <c r="B84" t="n">
-        <v>0.3776150312338843</v>
+        <v>0.334128680690048</v>
       </c>
       <c r="C84" t="n">
-        <v>-0.8561131000443788</v>
+        <v>-0.7319360365469592</v>
       </c>
       <c r="D84" t="n">
-        <v>-1.429366453501036</v>
+        <v>-1.677720580495875</v>
       </c>
       <c r="E84" t="n">
-        <v>3.189108057943793</v>
+        <v>2.844450375507326</v>
       </c>
       <c r="F84" t="n">
-        <v>-10.17008107235496</v>
+        <v>-7.647791275110617</v>
       </c>
       <c r="G84" t="n">
-        <v>20.34016214470863</v>
+        <v>15.29558255022117</v>
       </c>
       <c r="H84" t="n">
-        <v>-13.03698253239351</v>
+        <v>-9.905459297095753</v>
       </c>
       <c r="I84" t="n">
-        <v>17.7131523741807</v>
+        <v>15.33250392686315</v>
       </c>
       <c r="J84" t="n">
-        <v>-17.99998209570273</v>
+        <v>-13.63758143934973</v>
       </c>
       <c r="K84" t="n">
-        <v>17.99994866042109</v>
+        <v>15.54817164082127</v>
       </c>
       <c r="L84" t="n">
-        <v>28.42706682695294</v>
+        <v>24.14366347740244</v>
       </c>
       <c r="M84" t="n">
-        <v>154.646828793732</v>
+        <v>99.85972966740657</v>
       </c>
       <c r="N84" t="n">
-        <v>131.4498044746722</v>
+        <v>99.85972966740657</v>
       </c>
       <c r="O84" t="n">
-        <v>132.5631931205559</v>
+        <v>75.79243119549919</v>
       </c>
       <c r="P84" t="n">
-        <v>360.285610085187</v>
+        <v>234.3412623007303</v>
       </c>
       <c r="Q84" t="n">
-        <v>492.8488032057429</v>
+        <v>310.1336934962295</v>
       </c>
       <c r="R84" t="n">
-        <v>132.5631931205559</v>
+        <v>75.79243119549919</v>
       </c>
       <c r="S84" t="n">
-        <v>360.285610085187</v>
+        <v>234.3412623007303</v>
       </c>
       <c r="T84" t="n">
-        <v>492.8488032057429</v>
+        <v>310.1336934962295</v>
       </c>
     </row>
     <row r="85">
@@ -5669,61 +5669,61 @@
         <v>0.166</v>
       </c>
       <c r="B85" t="n">
-        <v>0.3843051002153176</v>
+        <v>0.3398406701609119</v>
       </c>
       <c r="C85" t="n">
-        <v>-0.8768452834095309</v>
+        <v>-0.7473516459362551</v>
       </c>
       <c r="D85" t="n">
-        <v>-1.387902086770731</v>
+        <v>-1.646889361717283</v>
       </c>
       <c r="E85" t="n">
-        <v>3.251190369255098</v>
+        <v>2.890656864594956</v>
       </c>
       <c r="F85" t="n">
-        <v>-10.49618085688373</v>
+        <v>-7.879992906918514</v>
       </c>
       <c r="G85" t="n">
-        <v>20.9923617137669</v>
+        <v>15.75998581383784</v>
       </c>
       <c r="H85" t="n">
-        <v>-12.87781879768975</v>
+        <v>-10.12344591406331</v>
       </c>
       <c r="I85" t="n">
-        <v>17.40614908024608</v>
+        <v>14.75495305132489</v>
       </c>
       <c r="J85" t="n">
-        <v>-17.99995505584901</v>
+        <v>-13.96888245263954</v>
       </c>
       <c r="K85" t="n">
-        <v>17.70214138041019</v>
+        <v>14.97716885130001</v>
       </c>
       <c r="L85" t="n">
-        <v>26.39123664161304</v>
+        <v>22.87437107501583</v>
       </c>
       <c r="M85" t="n">
-        <v>155.0574276387297</v>
+        <v>97.4335145616575</v>
       </c>
       <c r="N85" t="n">
-        <v>131.7988134929203</v>
+        <v>97.4335145616575</v>
       </c>
       <c r="O85" t="n">
-        <v>135.1328945553871</v>
+        <v>79.77658830345129</v>
       </c>
       <c r="P85" t="n">
-        <v>365.1900668852797</v>
+        <v>232.4748350911471</v>
       </c>
       <c r="Q85" t="n">
-        <v>500.3229614406667</v>
+        <v>312.2514233945984</v>
       </c>
       <c r="R85" t="n">
-        <v>135.1328945553871</v>
+        <v>79.77658830345129</v>
       </c>
       <c r="S85" t="n">
-        <v>365.1900668852797</v>
+        <v>232.4748350911471</v>
       </c>
       <c r="T85" t="n">
-        <v>500.3229614406667</v>
+        <v>312.2514233945984</v>
       </c>
     </row>
     <row r="86">
@@ -5731,61 +5731,61 @@
         <v>0.168</v>
       </c>
       <c r="B86" t="n">
-        <v>0.3910252668942307</v>
+        <v>0.3456830127527333</v>
       </c>
       <c r="C86" t="n">
-        <v>-0.8979654409773151</v>
+        <v>-0.7634519313932486</v>
       </c>
       <c r="D86" t="n">
-        <v>-1.345661771635163</v>
+        <v>-1.614688790803296</v>
       </c>
       <c r="E86" t="n">
-        <v>3.312724537963663</v>
+        <v>2.934140935160265</v>
       </c>
       <c r="F86" t="n">
-        <v>-10.82386331942369</v>
+        <v>-8.122462012652681</v>
       </c>
       <c r="G86" t="n">
-        <v>21.64772663884938</v>
+        <v>16.24492402530491</v>
       </c>
       <c r="H86" t="n">
-        <v>-12.71786898018714</v>
+        <v>-10.20633732102576</v>
       </c>
       <c r="I86" t="n">
-        <v>16.93546364184089</v>
+        <v>14.08636012872432</v>
       </c>
       <c r="J86" t="n">
-        <v>-17.9999142800659</v>
+        <v>-14.17009878320026</v>
       </c>
       <c r="K86" t="n">
-        <v>17.24069658744867</v>
+        <v>14.31541355748112</v>
       </c>
       <c r="L86" t="n">
-        <v>24.66316438580148</v>
+        <v>21.90883921609037</v>
       </c>
       <c r="M86" t="n">
-        <v>155.160490523328</v>
+        <v>94.37033890277733</v>
       </c>
       <c r="N86" t="n">
-        <v>131.8864169448288</v>
+        <v>94.37033890277733</v>
       </c>
       <c r="O86" t="n">
-        <v>137.6534267951919</v>
+        <v>82.91260279616937</v>
       </c>
       <c r="P86" t="n">
-        <v>366.5963442022358</v>
+        <v>228.6380167948897</v>
       </c>
       <c r="Q86" t="n">
-        <v>504.2497709974277</v>
+        <v>311.550619591059</v>
       </c>
       <c r="R86" t="n">
-        <v>137.6534267951919</v>
+        <v>82.91260279616937</v>
       </c>
       <c r="S86" t="n">
-        <v>366.5963442022358</v>
+        <v>228.6380167948897</v>
       </c>
       <c r="T86" t="n">
-        <v>504.2497709974277</v>
+        <v>311.550619591059</v>
       </c>
     </row>
     <row r="87">
@@ -5793,61 +5793,61 @@
         <v>0.17</v>
       </c>
       <c r="B87" t="n">
-        <v>0.3977599256976097</v>
+        <v>0.3515899317081012</v>
       </c>
       <c r="C87" t="n">
-        <v>-0.9200874342281777</v>
+        <v>-0.779939307039774</v>
       </c>
       <c r="D87" t="n">
-        <v>-1.301417785133438</v>
+        <v>-1.581714039510245</v>
       </c>
       <c r="E87" t="n">
-        <v>3.369897146701912</v>
+        <v>2.975751735343337</v>
       </c>
       <c r="F87" t="n">
-        <v>-11.11542990564873</v>
+        <v>-8.370781409363042</v>
       </c>
       <c r="G87" t="n">
-        <v>22.2308598112972</v>
+        <v>16.74156281872557</v>
       </c>
       <c r="H87" t="n">
-        <v>-12.42972099666061</v>
+        <v>-10.34849364354033</v>
       </c>
       <c r="I87" t="n">
-        <v>16.13890221431551</v>
+        <v>13.37602579193795</v>
       </c>
       <c r="J87" t="n">
-        <v>-17.85405079061719</v>
+        <v>-14.4334349713095</v>
       </c>
       <c r="K87" t="n">
-        <v>16.4523573376548</v>
+        <v>13.61208182768198</v>
       </c>
       <c r="L87" t="n">
-        <v>23.22273598974051</v>
+        <v>20.66381810888616</v>
       </c>
       <c r="M87" t="n">
-        <v>153.9319257775651</v>
+        <v>90.9549243747044</v>
       </c>
       <c r="N87" t="n">
-        <v>130.8421369109303</v>
+        <v>90.9549243747044</v>
       </c>
       <c r="O87" t="n">
-        <v>138.1029815058021</v>
+        <v>86.65471230935077</v>
       </c>
       <c r="P87" t="n">
-        <v>358.4574883372817</v>
+        <v>223.7201575488374</v>
       </c>
       <c r="Q87" t="n">
-        <v>496.5604698430839</v>
+        <v>310.3748698581882</v>
       </c>
       <c r="R87" t="n">
-        <v>138.1029815058021</v>
+        <v>86.65471230935077</v>
       </c>
       <c r="S87" t="n">
-        <v>358.4574883372817</v>
+        <v>223.7201575488374</v>
       </c>
       <c r="T87" t="n">
-        <v>496.5604698430839</v>
+        <v>310.3748698581882</v>
       </c>
     </row>
     <row r="88">
@@ -5855,61 +5855,61 @@
         <v>0.172</v>
       </c>
       <c r="B88" t="n">
-        <v>0.4044699171194528</v>
+        <v>0.3575698078327922</v>
       </c>
       <c r="C88" t="n">
-        <v>-0.9424921087336045</v>
+        <v>-0.7968640099520368</v>
       </c>
       <c r="D88" t="n">
-        <v>-1.256608436122584</v>
+        <v>-1.54786463368572</v>
       </c>
       <c r="E88" t="n">
-        <v>3.424959798925205</v>
+        <v>3.015246149639078</v>
       </c>
       <c r="F88" t="n">
-        <v>-11.38719608431691</v>
+        <v>-8.625710355541656</v>
       </c>
       <c r="G88" t="n">
-        <v>22.77439216863244</v>
+        <v>17.25142071108409</v>
       </c>
       <c r="H88" t="n">
-        <v>-12.09591708846536</v>
+        <v>-10.5576063606458</v>
       </c>
       <c r="I88" t="n">
-        <v>15.25598985669296</v>
+        <v>12.61853278508567</v>
       </c>
       <c r="J88" t="n">
-        <v>-17.65286877761201</v>
+        <v>-14.76695301415012</v>
       </c>
       <c r="K88" t="n">
-        <v>15.57710878627067</v>
+        <v>12.86177781711195</v>
       </c>
       <c r="L88" t="n">
-        <v>21.80573427480795</v>
+        <v>19.1030352695117</v>
       </c>
       <c r="M88" t="n">
-        <v>152.1189666884547</v>
+        <v>87.14155695163112</v>
       </c>
       <c r="N88" t="n">
-        <v>129.3011216851865</v>
+        <v>87.14155695163112</v>
       </c>
       <c r="O88" t="n">
-        <v>137.6995463709591</v>
+        <v>91.08157665549949</v>
       </c>
       <c r="P88" t="n">
-        <v>347.2546897330127</v>
+        <v>217.5809584302983</v>
       </c>
       <c r="Q88" t="n">
-        <v>484.9542361039718</v>
+        <v>308.6625350857977</v>
       </c>
       <c r="R88" t="n">
-        <v>137.6995463709591</v>
+        <v>91.08157665549949</v>
       </c>
       <c r="S88" t="n">
-        <v>347.2546897330127</v>
+        <v>217.5809584302983</v>
       </c>
       <c r="T88" t="n">
-        <v>484.9542361039718</v>
+        <v>308.6625350857977</v>
       </c>
     </row>
     <row r="89">
@@ -5917,61 +5917,61 @@
         <v>0.174</v>
       </c>
       <c r="B89" t="n">
-        <v>0.4111163611430509</v>
+        <v>0.3636494448433579</v>
       </c>
       <c r="C89" t="n">
-        <v>-0.9655170762597286</v>
+        <v>-0.8144932516552462</v>
       </c>
       <c r="D89" t="n">
-        <v>-1.210558501070336</v>
+        <v>-1.512606150279301</v>
       </c>
       <c r="E89" t="n">
-        <v>3.475104520177518</v>
+        <v>3.050784988395899</v>
       </c>
       <c r="F89" t="n">
-        <v>-11.61236611325969</v>
+        <v>-8.891669508790201</v>
       </c>
       <c r="G89" t="n">
-        <v>23.22473222652025</v>
+        <v>17.78333901758059</v>
       </c>
       <c r="H89" t="n">
-        <v>-11.65882327136966</v>
+        <v>-10.64198779647976</v>
       </c>
       <c r="I89" t="n">
-        <v>14.18543002960734</v>
+        <v>11.78844179518981</v>
       </c>
       <c r="J89" t="n">
-        <v>-17.32565793464039</v>
+        <v>-14.98112251676938</v>
       </c>
       <c r="K89" t="n">
-        <v>14.51289875400127</v>
+        <v>12.0391868753377</v>
       </c>
       <c r="L89" t="n">
-        <v>20.42122664757652</v>
+        <v>17.85947096646796</v>
       </c>
       <c r="M89" t="n">
-        <v>148.9553131621154</v>
+        <v>82.67962383722903</v>
       </c>
       <c r="N89" t="n">
-        <v>126.6120161877981</v>
+        <v>82.67962383722903</v>
       </c>
       <c r="O89" t="n">
-        <v>135.336386430001</v>
+        <v>94.63527214757546</v>
       </c>
       <c r="P89" t="n">
-        <v>329.2072119240389</v>
+        <v>209.325629000582</v>
       </c>
       <c r="Q89" t="n">
-        <v>464.5435983540399</v>
+        <v>303.9609011481574</v>
       </c>
       <c r="R89" t="n">
-        <v>135.336386430001</v>
+        <v>94.63527214757546</v>
       </c>
       <c r="S89" t="n">
-        <v>329.2072119240389</v>
+        <v>209.325629000582</v>
       </c>
       <c r="T89" t="n">
-        <v>464.5435983540399</v>
+        <v>303.9609011481574</v>
       </c>
     </row>
     <row r="90">
@@ -5979,61 +5979,61 @@
         <v>0.176</v>
       </c>
       <c r="B90" t="n">
-        <v>0.417640567112089</v>
+        <v>0.3697684145079131</v>
       </c>
       <c r="C90" t="n">
-        <v>-0.9889208942937515</v>
+        <v>-0.8324270107383356</v>
       </c>
       <c r="D90" t="n">
-        <v>-1.163750865002291</v>
+        <v>-1.476738632113122</v>
       </c>
       <c r="E90" t="n">
-        <v>3.520063517401596</v>
+        <v>3.084503900044308</v>
       </c>
       <c r="F90" t="n">
-        <v>-11.79128762717997</v>
+        <v>-9.162507217494788</v>
       </c>
       <c r="G90" t="n">
-        <v>23.58257525436048</v>
+        <v>18.32501443498901</v>
       </c>
       <c r="H90" t="n">
-        <v>-11.17277495949809</v>
+        <v>-10.71717577412539</v>
       </c>
       <c r="I90" t="n">
-        <v>13.00848976922245</v>
+        <v>10.93038330780554</v>
       </c>
       <c r="J90" t="n">
-        <v>-16.92692332156192</v>
+        <v>-15.18847929626284</v>
       </c>
       <c r="K90" t="n">
-        <v>13.34100408030893</v>
+        <v>11.18876601133888</v>
       </c>
       <c r="L90" t="n">
-        <v>19.02184978389315</v>
+        <v>16.59617752181611</v>
       </c>
       <c r="M90" t="n">
-        <v>144.4139855640585</v>
+        <v>77.9341011695593</v>
       </c>
       <c r="N90" t="n">
-        <v>122.7518877294497</v>
+        <v>77.9341011695593</v>
       </c>
       <c r="O90" t="n">
-        <v>131.6913810280296</v>
+        <v>98.20824105587207</v>
       </c>
       <c r="P90" t="n">
-        <v>306.5329811372173</v>
+        <v>200.178317345075</v>
       </c>
       <c r="Q90" t="n">
-        <v>438.224362165247</v>
+        <v>298.386558400947</v>
       </c>
       <c r="R90" t="n">
-        <v>131.6913810280296</v>
+        <v>98.20824105587207</v>
       </c>
       <c r="S90" t="n">
-        <v>306.5329811372173</v>
+        <v>200.178317345075</v>
       </c>
       <c r="T90" t="n">
-        <v>438.224362165247</v>
+        <v>298.386558400947</v>
       </c>
     </row>
     <row r="91">
@@ -6041,61 +6041,61 @@
         <v>0.178</v>
       </c>
       <c r="B91" t="n">
-        <v>0.424084372864918</v>
+        <v>0.375976215244359</v>
       </c>
       <c r="C91" t="n">
-        <v>-1.012573895471729</v>
+        <v>-0.851134325484089</v>
       </c>
       <c r="D91" t="n">
-        <v>-1.116444862646336</v>
+        <v>-1.439324002621615</v>
       </c>
       <c r="E91" t="n">
-        <v>3.561611683730394</v>
+        <v>3.113276978133301</v>
       </c>
       <c r="F91" t="n">
-        <v>-11.93978988565191</v>
+        <v>-9.44606287992568</v>
       </c>
       <c r="G91" t="n">
-        <v>23.87957977130234</v>
+        <v>18.89212575985158</v>
       </c>
       <c r="H91" t="n">
-        <v>-10.6545275752626</v>
+        <v>-10.89992500868468</v>
       </c>
       <c r="I91" t="n">
-        <v>11.76157940117758</v>
+        <v>10.01126570464032</v>
       </c>
       <c r="J91" t="n">
-        <v>-16.48114503946073</v>
+        <v>-15.50960369408841</v>
       </c>
       <c r="K91" t="n">
-        <v>12.09828147595295</v>
+        <v>10.27764467785423</v>
       </c>
       <c r="L91" t="n">
-        <v>17.61269290669507</v>
+        <v>14.82361414487929</v>
       </c>
       <c r="M91" t="n">
-        <v>138.9665138553905</v>
+        <v>72.45862665554573</v>
       </c>
       <c r="N91" t="n">
-        <v>118.1215367770819</v>
+        <v>72.45862665554573</v>
       </c>
       <c r="O91" t="n">
-        <v>127.2032613227143</v>
+        <v>102.9914632014641</v>
       </c>
       <c r="P91" t="n">
-        <v>280.8155741389837</v>
+        <v>188.8314602702758</v>
       </c>
       <c r="Q91" t="n">
-        <v>408.0188354616981</v>
+        <v>291.8229234717399</v>
       </c>
       <c r="R91" t="n">
-        <v>127.2032613227143</v>
+        <v>102.9914632014641</v>
       </c>
       <c r="S91" t="n">
-        <v>280.8155741389837</v>
+        <v>188.8314602702758</v>
       </c>
       <c r="T91" t="n">
-        <v>408.0188354616981</v>
+        <v>291.8229234717399</v>
       </c>
     </row>
     <row r="92">
@@ -6103,61 +6103,61 @@
         <v>0.18</v>
       </c>
       <c r="B92" t="n">
-        <v>0.4302453973850813</v>
+        <v>0.3822257981127314</v>
       </c>
       <c r="C92" t="n">
-        <v>-1.036573167274632</v>
+        <v>-0.8703231535226531</v>
       </c>
       <c r="D92" t="n">
-        <v>-1.06844631904053</v>
+        <v>-1.400946346544487</v>
       </c>
       <c r="E92" t="n">
-        <v>3.594079251038476</v>
+        <v>3.138649439134327</v>
       </c>
       <c r="F92" t="n">
-        <v>-12.02032458505594</v>
+        <v>-9.738191156097459</v>
       </c>
       <c r="G92" t="n">
-        <v>24.04064917011209</v>
+        <v>19.47638231219513</v>
       </c>
       <c r="H92" t="n">
-        <v>-10.11094063587185</v>
+        <v>-11.00951532569292</v>
       </c>
       <c r="I92" t="n">
-        <v>10.4178611799482</v>
+        <v>9.060594298673783</v>
       </c>
       <c r="J92" t="n">
-        <v>-15.97685903337915</v>
+        <v>-15.76175260986848</v>
       </c>
       <c r="K92" t="n">
-        <v>10.75683433324678</v>
+        <v>9.335211289275733</v>
       </c>
       <c r="L92" t="n">
-        <v>16.12032024061394</v>
+        <v>13.26859870237105</v>
       </c>
       <c r="M92" t="n">
-        <v>131.1995419847644</v>
+        <v>66.54791856792481</v>
       </c>
       <c r="N92" t="n">
-        <v>111.5196106870498</v>
+        <v>66.54791856792481</v>
       </c>
       <c r="O92" t="n">
-        <v>121.5082272454817</v>
+        <v>107.2189407196686</v>
       </c>
       <c r="P92" t="n">
-        <v>250.3106425025418</v>
+        <v>176.1266100673719</v>
       </c>
       <c r="Q92" t="n">
-        <v>371.8188697480235</v>
+        <v>283.3455507870405</v>
       </c>
       <c r="R92" t="n">
-        <v>121.5082272454817</v>
+        <v>107.2189407196686</v>
       </c>
       <c r="S92" t="n">
-        <v>250.3106425025418</v>
+        <v>176.1266100673719</v>
       </c>
       <c r="T92" t="n">
-        <v>371.8188697480235</v>
+        <v>283.3455507870405</v>
       </c>
     </row>
     <row r="93">
@@ -6165,61 +6165,61 @@
         <v>0.182</v>
       </c>
       <c r="B93" t="n">
-        <v>0.4362889532226863</v>
+        <v>0.3885176419419719</v>
       </c>
       <c r="C93" t="n">
-        <v>-1.060637854216534</v>
+        <v>-0.889999013062163</v>
       </c>
       <c r="D93" t="n">
-        <v>-1.020316945156725</v>
+        <v>-1.361594627465467</v>
       </c>
       <c r="E93" t="n">
-        <v>3.623165010560625</v>
+        <v>3.160582311510863</v>
       </c>
       <c r="F93" t="n">
-        <v>-12.08058127438222</v>
+        <v>-10.03899028933505</v>
       </c>
       <c r="G93" t="n">
-        <v>24.16116254876568</v>
+        <v>20.0779805786695</v>
       </c>
       <c r="H93" t="n">
-        <v>-9.569879990713178</v>
+        <v>-11.04510831395774</v>
       </c>
       <c r="I93" t="n">
-        <v>9.061061738194612</v>
+        <v>8.078007479013975</v>
       </c>
       <c r="J93" t="n">
-        <v>-15.4652036526117</v>
+        <v>-15.94413557515324</v>
       </c>
       <c r="K93" t="n">
-        <v>9.401734130132208</v>
+        <v>8.361107005173213</v>
       </c>
       <c r="L93" t="n">
-        <v>14.59460631374302</v>
+        <v>11.93362432334803</v>
       </c>
       <c r="M93" t="n">
-        <v>122.6173982562628</v>
+        <v>60.19698907046798</v>
       </c>
       <c r="N93" t="n">
-        <v>104.2247885178234</v>
+        <v>60.19698907046798</v>
       </c>
       <c r="O93" t="n">
-        <v>115.6070431426617</v>
+        <v>110.8843047011128</v>
       </c>
       <c r="P93" t="n">
-        <v>218.9118666212237</v>
+        <v>162.0482039495442</v>
       </c>
       <c r="Q93" t="n">
-        <v>334.5189097638855</v>
+        <v>272.932508650657</v>
       </c>
       <c r="R93" t="n">
-        <v>115.6070431426617</v>
+        <v>110.8843047011128</v>
       </c>
       <c r="S93" t="n">
-        <v>218.9118666212237</v>
+        <v>162.0482039495442</v>
       </c>
       <c r="T93" t="n">
-        <v>334.5189097638855</v>
+        <v>272.932508650657</v>
       </c>
     </row>
     <row r="94">
@@ -6227,61 +6227,61 @@
         <v>0.184</v>
       </c>
       <c r="B94" t="n">
-        <v>0.4420386642412129</v>
+        <v>0.3948594678878951</v>
       </c>
       <c r="C94" t="n">
-        <v>-1.084816463772982</v>
+        <v>-0.910540231243578</v>
       </c>
       <c r="D94" t="n">
-        <v>-0.9719597260438301</v>
+        <v>-1.320512191102637</v>
       </c>
       <c r="E94" t="n">
-        <v>3.6440386714052</v>
+        <v>3.175837355222601</v>
       </c>
       <c r="F94" t="n">
-        <v>-12.09515603829194</v>
+        <v>-10.35673190642436</v>
       </c>
       <c r="G94" t="n">
-        <v>24.19031207658301</v>
+        <v>20.71346381284876</v>
       </c>
       <c r="H94" t="n">
-        <v>-9.043412187646899</v>
+        <v>-11.1936902916434</v>
       </c>
       <c r="I94" t="n">
-        <v>7.688738523727777</v>
+        <v>7.058342639317601</v>
       </c>
       <c r="J94" t="n">
-        <v>-14.94584833433337</v>
+        <v>-16.24777546197849</v>
       </c>
       <c r="K94" t="n">
-        <v>8.029821924007598</v>
+        <v>7.350402479078769</v>
       </c>
       <c r="L94" t="n">
-        <v>12.9862678272077</v>
+        <v>10.08634215490773</v>
       </c>
       <c r="M94" t="n">
-        <v>112.0901622140164</v>
+        <v>52.99764652172973</v>
       </c>
       <c r="N94" t="n">
-        <v>95.27663788191393</v>
+        <v>52.99764652172973</v>
       </c>
       <c r="O94" t="n">
-        <v>109.3772995129606</v>
+        <v>115.9675521397751</v>
       </c>
       <c r="P94" t="n">
-        <v>185.971182170296</v>
+        <v>145.7501243625927</v>
       </c>
       <c r="Q94" t="n">
-        <v>295.3484816832566</v>
+        <v>261.7176765023678</v>
       </c>
       <c r="R94" t="n">
-        <v>109.3772995129606</v>
+        <v>115.9675521397751</v>
       </c>
       <c r="S94" t="n">
-        <v>185.971182170296</v>
+        <v>145.7501243625927</v>
       </c>
       <c r="T94" t="n">
-        <v>295.3484816832566</v>
+        <v>261.7176765023678</v>
       </c>
     </row>
     <row r="95">
@@ -6289,61 +6289,61 @@
         <v>0.186</v>
       </c>
       <c r="B95" t="n">
-        <v>0.4475409935012684</v>
+        <v>0.401216540082471</v>
       </c>
       <c r="C95" t="n">
-        <v>-1.108984059668873</v>
+        <v>-0.9314479770613235</v>
       </c>
       <c r="D95" t="n">
-        <v>-0.923624534252047</v>
+        <v>-1.278696699467146</v>
       </c>
       <c r="E95" t="n">
-        <v>3.658326346986347</v>
+        <v>3.18816365877461</v>
       </c>
       <c r="F95" t="n">
-        <v>-12.08682167074918</v>
+        <v>-10.6821865137738</v>
       </c>
       <c r="G95" t="n">
-        <v>24.1736433414978</v>
+        <v>21.36437302754818</v>
       </c>
       <c r="H95" t="n">
-        <v>-8.544951262975355</v>
+        <v>-11.34005111198459</v>
       </c>
       <c r="I95" t="n">
-        <v>6.339098187769338</v>
+        <v>6.02805336372208</v>
       </c>
       <c r="J95" t="n">
-        <v>-14.44332023830095</v>
+        <v>-16.55295813070621</v>
       </c>
       <c r="K95" t="n">
-        <v>6.679946558884457</v>
+        <v>6.32929102341051</v>
       </c>
       <c r="L95" t="n">
-        <v>11.31496190404837</v>
+        <v>8.229350761936686</v>
       </c>
       <c r="M95" t="n">
-        <v>100.184510888167</v>
+        <v>45.46159934673263</v>
       </c>
       <c r="N95" t="n">
-        <v>85.15683425494198</v>
+        <v>45.46159934673263</v>
       </c>
       <c r="O95" t="n">
-        <v>103.2891618346383</v>
+        <v>121.1402189427829</v>
       </c>
       <c r="P95" t="n">
-        <v>153.2830322418687</v>
+        <v>128.5912059469964</v>
       </c>
       <c r="Q95" t="n">
-        <v>256.5721940765069</v>
+        <v>249.7314248897793</v>
       </c>
       <c r="R95" t="n">
-        <v>103.2891618346383</v>
+        <v>121.1402189427829</v>
       </c>
       <c r="S95" t="n">
-        <v>153.2830322418687</v>
+        <v>128.5912059469964</v>
       </c>
       <c r="T95" t="n">
-        <v>256.5721940765069</v>
+        <v>249.7314248897793</v>
       </c>
     </row>
     <row r="96">
@@ -6351,61 +6351,61 @@
         <v>0.188</v>
       </c>
       <c r="B96" t="n">
-        <v>0.4528498265472807</v>
+        <v>0.407599209025804</v>
       </c>
       <c r="C96" t="n">
-        <v>-1.133143040937585</v>
+        <v>-0.9532591478950855</v>
       </c>
       <c r="D96" t="n">
-        <v>-0.8753065717146237</v>
+        <v>-1.235074357799623</v>
       </c>
       <c r="E96" t="n">
-        <v>3.667462619238105</v>
+        <v>3.193068248288945</v>
       </c>
       <c r="F96" t="n">
-        <v>-12.0605683174636</v>
+        <v>-11.02773826755967</v>
       </c>
       <c r="G96" t="n">
-        <v>24.12113663492888</v>
+        <v>22.05547653511892</v>
       </c>
       <c r="H96" t="n">
-        <v>-8.06839666223831</v>
+        <v>-11.37964278189333</v>
       </c>
       <c r="I96" t="n">
-        <v>5.007199867803127</v>
+        <v>4.981852525717041</v>
       </c>
       <c r="J96" t="n">
-        <v>-13.95395400116054</v>
+        <v>-16.76117905646245</v>
       </c>
       <c r="K96" t="n">
-        <v>5.347307894355623</v>
+        <v>5.292834744862217</v>
       </c>
       <c r="L96" t="n">
-        <v>9.594404327614125</v>
+        <v>6.76770080142403</v>
       </c>
       <c r="M96" t="n">
-        <v>87.2006954308755</v>
+        <v>37.14144127299249</v>
       </c>
       <c r="N96" t="n">
-        <v>74.12059111624417</v>
+        <v>37.14144127299249</v>
       </c>
       <c r="O96" t="n">
-        <v>97.31178501292531</v>
+        <v>125.4994085661356</v>
       </c>
       <c r="P96" t="n">
-        <v>120.7924088987525</v>
+        <v>109.4709093287164</v>
       </c>
       <c r="Q96" t="n">
-        <v>218.1041939116777</v>
+        <v>234.970317894852</v>
       </c>
       <c r="R96" t="n">
-        <v>97.31178501292531</v>
+        <v>125.4994085661356</v>
       </c>
       <c r="S96" t="n">
-        <v>120.7924088987525</v>
+        <v>109.4709093287164</v>
       </c>
       <c r="T96" t="n">
-        <v>218.1041939116777</v>
+        <v>234.970317894852</v>
       </c>
     </row>
     <row r="97">
@@ -6413,61 +6413,61 @@
         <v>0.19</v>
       </c>
       <c r="B97" t="n">
-        <v>0.4577472573317933</v>
+        <v>0.4139813965277028</v>
       </c>
       <c r="C97" t="n">
-        <v>-1.157198880413259</v>
+        <v>-0.97569816999848</v>
       </c>
       <c r="D97" t="n">
-        <v>-0.8271948927632755</v>
+        <v>-1.190196313592834</v>
       </c>
       <c r="E97" t="n">
-        <v>3.66549049606814</v>
+        <v>3.192534797662857</v>
       </c>
       <c r="F97" t="n">
-        <v>-12.01917401220364</v>
+        <v>-11.38942231145032</v>
       </c>
       <c r="G97" t="n">
-        <v>24.0383480244072</v>
+        <v>22.77884462290037</v>
       </c>
       <c r="H97" t="n">
-        <v>-7.670684253133736</v>
+        <v>-11.50039675603567</v>
       </c>
       <c r="I97" t="n">
-        <v>3.7839585214458</v>
+        <v>3.937181228892008</v>
       </c>
       <c r="J97" t="n">
-        <v>-13.53604117108911</v>
+        <v>-17.05843484402342</v>
       </c>
       <c r="K97" t="n">
-        <v>4.12289922858994</v>
+        <v>4.258362938074903</v>
       </c>
       <c r="L97" t="n">
-        <v>7.779366393645399</v>
+        <v>4.975944078761392</v>
       </c>
       <c r="M97" t="n">
-        <v>72.26662825471944</v>
+        <v>28.18198738940326</v>
       </c>
       <c r="N97" t="n">
-        <v>61.42663401651152</v>
+        <v>28.18198738940326</v>
       </c>
       <c r="O97" t="n">
-        <v>92.20713698261544</v>
+        <v>131.0263241367428</v>
       </c>
       <c r="P97" t="n">
-        <v>91.03410761554633</v>
+        <v>89.2177366041258</v>
       </c>
       <c r="Q97" t="n">
-        <v>183.2412445981618</v>
+        <v>220.2440607408686</v>
       </c>
       <c r="R97" t="n">
-        <v>92.20713698261544</v>
+        <v>131.0263241367428</v>
       </c>
       <c r="S97" t="n">
-        <v>91.03410761554633</v>
+        <v>89.2177366041258</v>
       </c>
       <c r="T97" t="n">
-        <v>183.2412445981618</v>
+        <v>220.2440607408686</v>
       </c>
     </row>
     <row r="98">
@@ -6475,61 +6475,61 @@
         <v>0.192</v>
       </c>
       <c r="B98" t="n">
-        <v>0.462494215239381</v>
+        <v>0.4203631480392171</v>
       </c>
       <c r="C98" t="n">
-        <v>-1.181211605650564</v>
+        <v>-0.9987057703275581</v>
       </c>
       <c r="D98" t="n">
-        <v>-0.7791694422886647</v>
+        <v>-1.144181112934677</v>
       </c>
       <c r="E98" t="n">
-        <v>3.659270848484322</v>
+        <v>3.187076691527119</v>
       </c>
       <c r="F98" t="n">
-        <v>-11.97576097081602</v>
+        <v>-11.76571565746016</v>
       </c>
       <c r="G98" t="n">
-        <v>23.95152194163056</v>
+        <v>23.53143131492125</v>
       </c>
       <c r="H98" t="n">
-        <v>-7.29141210529387</v>
+        <v>-11.6946508107951</v>
       </c>
       <c r="I98" t="n">
-        <v>2.597307011684241</v>
+        <v>2.89389507509734</v>
       </c>
       <c r="J98" t="n">
-        <v>-13.13558345905209</v>
+        <v>-17.43632005163566</v>
       </c>
       <c r="K98" t="n">
-        <v>2.935023471061232</v>
+        <v>3.225688256637731</v>
       </c>
       <c r="L98" t="n">
-        <v>5.96399240261559</v>
+        <v>2.885244714445381</v>
       </c>
       <c r="M98" t="n">
-        <v>56.68509131849391</v>
+        <v>18.64359117531009</v>
       </c>
       <c r="N98" t="n">
-        <v>48.18232762071982</v>
+        <v>18.64359117531009</v>
       </c>
       <c r="O98" t="n">
-        <v>87.32466474326435</v>
+        <v>137.6107251012446</v>
       </c>
       <c r="P98" t="n">
-        <v>62.23758246891219</v>
+        <v>67.93863828600684</v>
       </c>
       <c r="Q98" t="n">
-        <v>149.5622472121765</v>
+        <v>205.5493633872514</v>
       </c>
       <c r="R98" t="n">
-        <v>87.32466474326435</v>
+        <v>137.6107251012446</v>
       </c>
       <c r="S98" t="n">
-        <v>62.23758246891219</v>
+        <v>67.93863828600684</v>
       </c>
       <c r="T98" t="n">
-        <v>149.5622472121765</v>
+        <v>205.5493633872514</v>
       </c>
     </row>
     <row r="99">
@@ -6537,185 +6537,61 @@
         <v>0.194</v>
       </c>
       <c r="B99" t="n">
-        <v>0.4668621071719831</v>
+        <v>0.4317255717420492</v>
       </c>
       <c r="C99" t="n">
-        <v>-1.205107697234987</v>
+        <v>-1.042071761806798</v>
       </c>
       <c r="D99" t="n">
-        <v>-0.7313772591198202</v>
+        <v>-1.057449129976197</v>
       </c>
       <c r="E99" t="n">
-        <v>3.64207628423438</v>
+        <v>3.15807345807034</v>
       </c>
       <c r="F99" t="n">
-        <v>-11.93250034819335</v>
+        <v>-12.50658455040448</v>
       </c>
       <c r="G99" t="n">
-        <v>23.86500069638746</v>
+        <v>25.0131691008079</v>
       </c>
       <c r="H99" t="n">
-        <v>-6.943119399932409</v>
+        <v>-11.89678480573713</v>
       </c>
       <c r="I99" t="n">
-        <v>1.498139699094362</v>
+        <v>1.142066292706947</v>
       </c>
       <c r="J99" t="n">
-        <v>-12.76617956985076</v>
+        <v>-17.75518328206118</v>
       </c>
       <c r="K99" t="n">
-        <v>1.834636208913425</v>
+        <v>2.254606304959066</v>
       </c>
       <c r="L99" t="n">
-        <v>4.19870623546511</v>
+        <v>-1.065616518577162e-11</v>
       </c>
       <c r="M99" t="n">
-        <v>39.57047810441688</v>
+        <v>8.284468712912263</v>
       </c>
       <c r="N99" t="n">
-        <v>33.63490638875435</v>
+        <v>8.284468712912263</v>
       </c>
       <c r="O99" t="n">
-        <v>82.85746951741811</v>
+        <v>148.7881450509187</v>
       </c>
       <c r="P99" t="n">
-        <v>35.80798469951063</v>
+        <v>28.56669730381164</v>
       </c>
       <c r="Q99" t="n">
-        <v>118.6654542169287</v>
+        <v>177.3548423547304</v>
       </c>
       <c r="R99" t="n">
-        <v>82.85746951741811</v>
+        <v>148.7881450509187</v>
       </c>
       <c r="S99" t="n">
-        <v>35.80798469951063</v>
+        <v>28.56669730381164</v>
       </c>
       <c r="T99" t="n">
-        <v>118.6654542169287</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="n">
-        <v>0.196</v>
-      </c>
-      <c r="B100" t="n">
-        <v>0.4709886085482775</v>
-      </c>
-      <c r="C100" t="n">
-        <v>-1.228953056004141</v>
-      </c>
-      <c r="D100" t="n">
-        <v>-0.6836865415815115</v>
-      </c>
-      <c r="E100" t="n">
-        <v>3.617321197366421</v>
-      </c>
-      <c r="F100" t="n">
-        <v>-11.90395802519363</v>
-      </c>
-      <c r="G100" t="n">
-        <v>23.80791605038793</v>
-      </c>
-      <c r="H100" t="n">
-        <v>-6.704902850818103</v>
-      </c>
-      <c r="I100" t="n">
-        <v>0.5598346931242471</v>
-      </c>
-      <c r="J100" t="n">
-        <v>-12.51403436711259</v>
-      </c>
-      <c r="K100" t="n">
-        <v>0.8955263094347169</v>
-      </c>
-      <c r="L100" t="n">
-        <v>2.315258047217489</v>
-      </c>
-      <c r="M100" t="n">
-        <v>21.66117568195241</v>
-      </c>
-      <c r="N100" t="n">
-        <v>18.41199932965955</v>
-      </c>
-      <c r="O100" t="n">
-        <v>79.81610571054078</v>
-      </c>
-      <c r="P100" t="n">
-        <v>13.34267829649874</v>
-      </c>
-      <c r="Q100" t="n">
-        <v>93.15878400703951</v>
-      </c>
-      <c r="R100" t="n">
-        <v>79.81610571054078</v>
-      </c>
-      <c r="S100" t="n">
-        <v>18.58430885797517</v>
-      </c>
-      <c r="T100" t="n">
-        <v>93.15878400703951</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="n">
-        <v>0.198</v>
-      </c>
-      <c r="B101" t="n">
-        <v>0.4755225286461454</v>
-      </c>
-      <c r="C101" t="n">
-        <v>-1.256599981439484</v>
-      </c>
-      <c r="D101" t="n">
-        <v>-0.628392690710825</v>
-      </c>
-      <c r="E101" t="n">
-        <v>3.580422390291515</v>
-      </c>
-      <c r="F101" t="n">
-        <v>-11.88664712114061</v>
-      </c>
-      <c r="G101" t="n">
-        <v>23.77329424227928</v>
-      </c>
-      <c r="H101" t="n">
-        <v>-6.546681677367581</v>
-      </c>
-      <c r="I101" t="n">
-        <v>-0.3570094456500732</v>
-      </c>
-      <c r="J101" t="n">
-        <v>-12.37056659476471</v>
-      </c>
-      <c r="K101" t="n">
-        <v>0.1058911301977961</v>
-      </c>
-      <c r="L101" t="n">
-        <v>4.320258442858203e-13</v>
-      </c>
-      <c r="M101" t="n">
-        <v>3.015341206030449</v>
-      </c>
-      <c r="N101" t="n">
-        <v>2.563040025125879</v>
-      </c>
-      <c r="O101" t="n">
-        <v>77.81809491330536</v>
-      </c>
-      <c r="P101" t="n">
-        <v>-8.487290598712203</v>
-      </c>
-      <c r="Q101" t="n">
-        <v>69.33080431459315</v>
-      </c>
-      <c r="R101" t="n">
-        <v>77.81809491330536</v>
-      </c>
-      <c r="S101" t="n">
-        <v>8.487290598712203</v>
-      </c>
-      <c r="T101" t="n">
-        <v>69.33080431459315</v>
+        <v>177.3548423547304</v>
       </c>
     </row>
   </sheetData>

--- a/code/goal19/nlp_demo/task0_vertjump_no_cvt_results.xlsx
+++ b/code/goal19/nlp_demo/task0_vertjump_no_cvt_results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T99"/>
+  <dimension ref="A1:T94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -523,61 +523,61 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.1461830283436809</v>
+        <v>0.146183030211728</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.2967000667403363</v>
+        <v>-0.2967000706471322</v>
       </c>
       <c r="D2" t="n">
-        <v>-2.54819252010912</v>
+        <v>-2.548192512295529</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>-1.988322660278949e-22</v>
       </c>
       <c r="F2" t="n">
-        <v>-4.599527505201061e-24</v>
+        <v>2.125838203772255e-23</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.404616657079581e-24</v>
+        <v>-7.92068183092389e-22</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3457072863789525</v>
+        <v>-0.2112805083367329</v>
       </c>
       <c r="I2" t="n">
-        <v>6.919556354232888</v>
+        <v>7.829397916292395</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3457072863789525</v>
+        <v>-0.2112805083367329</v>
       </c>
       <c r="K2" t="n">
-        <v>6.919556354232888</v>
+        <v>7.829397916292395</v>
       </c>
       <c r="L2" t="n">
-        <v>9.885990242817744</v>
+        <v>9.886212016422888</v>
       </c>
       <c r="M2" t="n">
-        <v>32.9551254</v>
+        <v>32.95512540000989</v>
       </c>
       <c r="N2" t="n">
-        <v>32.9551254</v>
+        <v>32.95512540000989</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.590090172448412e-24</v>
+        <v>-4.491481763346492e-24</v>
       </c>
       <c r="P2" t="n">
-        <v>-9.719324114756371e-24</v>
+        <v>-6.201416982265053e-21</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.130941428720478e-23</v>
+        <v>-6.2059084640284e-21</v>
       </c>
       <c r="R2" t="n">
-        <v>1.590090172448412e-24</v>
+        <v>4.491481763346492e-24</v>
       </c>
       <c r="S2" t="n">
-        <v>9.719324114756371e-24</v>
+        <v>6.201416982265053e-21</v>
       </c>
       <c r="T2" t="n">
-        <v>1.130941428720478e-23</v>
+        <v>6.2059084640284e-21</v>
       </c>
     </row>
     <row r="3">
@@ -585,61 +585,61 @@
         <v>0.002</v>
       </c>
       <c r="B3" t="n">
-        <v>0.1461855631117916</v>
+        <v>0.1462194330518564</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.2967053679101204</v>
+        <v>-0.2967762041930101</v>
       </c>
       <c r="D3" t="n">
-        <v>-2.548181917769553</v>
+        <v>-2.548040245203773</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001529308617205707</v>
+        <v>0.006434934162196993</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.003198369348973506</v>
+        <v>-0.04876164059552055</v>
       </c>
       <c r="G3" t="n">
-        <v>0.006396738697726413</v>
+        <v>0.09752328119029757</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4445539428888974</v>
+        <v>0.2878020836276445</v>
       </c>
       <c r="I3" t="n">
-        <v>7.527807713656079</v>
+        <v>8.689673812225305</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4429931386465984</v>
+        <v>0.2640064030170304</v>
       </c>
       <c r="K3" t="n">
-        <v>7.527897907671718</v>
+        <v>8.691048890490089</v>
       </c>
       <c r="L3" t="n">
-        <v>10.67840558977601</v>
+        <v>11.60745930169393</v>
       </c>
       <c r="M3" t="n">
-        <v>35.59867644853519</v>
+        <v>39.41972408616067</v>
       </c>
       <c r="N3" t="n">
-        <v>35.59867644853519</v>
+        <v>39.41972408616067</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.001629702496527709</v>
+        <v>-0.02769454277037671</v>
       </c>
       <c r="P3" t="n">
-        <v>0.05071148134888846</v>
+        <v>0.8945402818411361</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.04908177885236075</v>
+        <v>0.8668457390707593</v>
       </c>
       <c r="R3" t="n">
-        <v>0.001629702496527709</v>
+        <v>0.02769454277037671</v>
       </c>
       <c r="S3" t="n">
-        <v>0.05071148134888846</v>
+        <v>0.8945402818411361</v>
       </c>
       <c r="T3" t="n">
-        <v>0.04908177885236075</v>
+        <v>0.8668457390707593</v>
       </c>
     </row>
     <row r="4">
@@ -647,61 +647,61 @@
         <v>0.004</v>
       </c>
       <c r="B4" t="n">
-        <v>0.146191561961751</v>
+        <v>0.1462743220336337</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.2967179138731168</v>
+        <v>-0.2968910041208505</v>
       </c>
       <c r="D4" t="n">
-        <v>-2.54815682584356</v>
+        <v>-2.547810645348092</v>
       </c>
       <c r="E4" t="n">
-        <v>0.004100913012282513</v>
+        <v>0.01391589758492553</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.0085766218764697</v>
+        <v>-0.07950866380729645</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01715324375271592</v>
+        <v>0.1590173276143748</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4882552171470146</v>
+        <v>0.581608763139088</v>
       </c>
       <c r="I4" t="n">
-        <v>8.129402397727782</v>
+        <v>9.623809346874438</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4840698256712975</v>
+        <v>0.5428085352011274</v>
       </c>
       <c r="K4" t="n">
-        <v>8.129644258464696</v>
+        <v>9.626051491193801</v>
       </c>
       <c r="L4" t="n">
-        <v>11.40927040326835</v>
+        <v>13.08266699835906</v>
       </c>
       <c r="M4" t="n">
-        <v>38.23289514462546</v>
+        <v>45.19044493970075</v>
       </c>
       <c r="N4" t="n">
-        <v>38.23289514462546</v>
+        <v>45.19044493970075</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.003919932910838871</v>
+        <v>-0.04636085612403242</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1445176509240315</v>
+        <v>1.538147947291516</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.1405977180131927</v>
+        <v>1.491787091167483</v>
       </c>
       <c r="R4" t="n">
-        <v>0.003919932910838871</v>
+        <v>0.04636085612403242</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1445176509240315</v>
+        <v>1.538147947291516</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1405977180131927</v>
+        <v>1.491787091167483</v>
       </c>
     </row>
     <row r="5">
@@ -709,61 +709,61 @@
         <v>0.006</v>
       </c>
       <c r="B5" t="n">
-        <v>0.1462042096611401</v>
+        <v>0.1463528672633533</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.2967443652636758</v>
+        <v>-0.297055284439792</v>
       </c>
       <c r="D5" t="n">
-        <v>-2.548103923062442</v>
+        <v>-2.54748208471021</v>
       </c>
       <c r="E5" t="n">
-        <v>0.008673067045261457</v>
+        <v>0.02273543819763799</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.01813887341465924</v>
+        <v>-0.08720283675376048</v>
       </c>
       <c r="G5" t="n">
-        <v>0.03627774682951001</v>
+        <v>0.1744056735094523</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4261121842150932</v>
+        <v>0.612729049037598</v>
       </c>
       <c r="I5" t="n">
-        <v>8.718220469107786</v>
+        <v>10.65246119323339</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4172604139887395</v>
+        <v>0.5701740647017628</v>
       </c>
       <c r="K5" t="n">
-        <v>8.718731985338081</v>
+        <v>10.65492031322987</v>
       </c>
       <c r="L5" t="n">
-        <v>12.02199706437417</v>
+        <v>14.24302405597652</v>
       </c>
       <c r="M5" t="n">
-        <v>40.84920161781235</v>
+        <v>50.07322787944273</v>
       </c>
       <c r="N5" t="n">
-        <v>40.84920161781235</v>
+        <v>50.07322787944273</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.00747795977487274</v>
+        <v>-0.05347397262254124</v>
       </c>
       <c r="P5" t="n">
-        <v>0.3210384057032233</v>
+        <v>1.860643489785633</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.3135604459283505</v>
+        <v>1.807169517163091</v>
       </c>
       <c r="R5" t="n">
-        <v>0.00747795977487274</v>
+        <v>0.05347397262254124</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3210384057032233</v>
+        <v>1.860643489785633</v>
       </c>
       <c r="T5" t="n">
-        <v>0.3135604459283505</v>
+        <v>1.807169517163091</v>
       </c>
     </row>
     <row r="6">
@@ -771,61 +771,61 @@
         <v>0.008</v>
       </c>
       <c r="B6" t="n">
-        <v>0.1462305835119929</v>
+        <v>0.1464497496150658</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.2967995246439457</v>
+        <v>-0.2972579337810464</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.547993604301902</v>
+        <v>-2.5470767860277</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01526207818565205</v>
+        <v>0.03567345169007406</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.03191978697126585</v>
+        <v>-0.1059709381497009</v>
       </c>
       <c r="G6" t="n">
-        <v>0.06383957394263562</v>
+        <v>0.2119418762987801</v>
       </c>
       <c r="H6" t="n">
-        <v>0.462788107655081</v>
+        <v>0.6131587334278354</v>
       </c>
       <c r="I6" t="n">
-        <v>9.290659351821814</v>
+        <v>11.54875119801284</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4472112516131033</v>
+        <v>0.5614449156107815</v>
       </c>
       <c r="K6" t="n">
-        <v>9.291559489814405</v>
+        <v>11.55173957846865</v>
       </c>
       <c r="L6" t="n">
-        <v>12.76749346581387</v>
+        <v>15.26171981036739</v>
       </c>
       <c r="M6" t="n">
-        <v>43.36708103762538</v>
+        <v>53.57423136699934</v>
       </c>
       <c r="N6" t="n">
-        <v>43.36708103762538</v>
+        <v>53.57423136699934</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.01563187360417112</v>
+        <v>-0.06492992008952653</v>
       </c>
       <c r="P6" t="n">
-        <v>0.6049433329859176</v>
+        <v>2.469068044535844</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.5893114593817466</v>
+        <v>2.404138124446318</v>
       </c>
       <c r="R6" t="n">
-        <v>0.01563187360417112</v>
+        <v>0.06492992008952653</v>
       </c>
       <c r="S6" t="n">
-        <v>0.6049433329859176</v>
+        <v>2.469068044535844</v>
       </c>
       <c r="T6" t="n">
-        <v>0.5893114593817466</v>
+        <v>2.404138124446318</v>
       </c>
     </row>
     <row r="7">
@@ -833,61 +833,61 @@
         <v>0.01</v>
       </c>
       <c r="B7" t="n">
-        <v>0.1462640853394215</v>
+        <v>0.1465626186601401</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.2968695922096074</v>
+        <v>-0.2974940360000979</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.547853469170578</v>
+        <v>-2.546604581589597</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02285671893225538</v>
+        <v>0.05049869971663545</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.04780423560627289</v>
+        <v>-0.1314377066478893</v>
       </c>
       <c r="G7" t="n">
-        <v>0.09560847121234703</v>
+        <v>0.2628754132941847</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5406569983616321</v>
+        <v>0.5919594452320224</v>
       </c>
       <c r="I7" t="n">
-        <v>9.855105866605516</v>
+        <v>12.37095219201948</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5173285313857708</v>
+        <v>0.5278178443878524</v>
       </c>
       <c r="K7" t="n">
-        <v>9.85645394604961</v>
+        <v>12.37465873534693</v>
       </c>
       <c r="L7" t="n">
-        <v>13.56750994744641</v>
+        <v>16.19453127164053</v>
       </c>
       <c r="M7" t="n">
-        <v>45.83884679865808</v>
+        <v>56.83417021982546</v>
       </c>
       <c r="N7" t="n">
-        <v>45.83884679865808</v>
+        <v>56.83417021982546</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.02577630094885529</v>
+        <v>-0.07695956924092626</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9433009257200409</v>
+        <v>3.272245326137675</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.9175246247711856</v>
+        <v>3.195285756896749</v>
       </c>
       <c r="R7" t="n">
-        <v>0.02577630094885529</v>
+        <v>0.07695956924092626</v>
       </c>
       <c r="S7" t="n">
-        <v>0.9433009257200409</v>
+        <v>3.272245326137675</v>
       </c>
       <c r="T7" t="n">
-        <v>0.9175246247711856</v>
+        <v>3.195285756896749</v>
       </c>
     </row>
     <row r="8">
@@ -895,61 +895,61 @@
         <v>0.012</v>
       </c>
       <c r="B8" t="n">
-        <v>0.1463263958071951</v>
+        <v>0.1467045444864743</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.2969999179788634</v>
+        <v>-0.2977909415222333</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.547592817632066</v>
+        <v>-2.546010770545327</v>
       </c>
       <c r="E8" t="n">
-        <v>0.03321548250141316</v>
+        <v>0.06816266973506635</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.06947246685973824</v>
+        <v>-0.1680533741111304</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1389449337195375</v>
+        <v>0.3361067482245406</v>
       </c>
       <c r="H8" t="n">
-        <v>0.4695135943391527</v>
+        <v>0.5332286723962402</v>
       </c>
       <c r="I8" t="n">
-        <v>10.4032478861019</v>
+        <v>13.0728346907051</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4356110305116005</v>
+        <v>0.4512186258300085</v>
       </c>
       <c r="K8" t="n">
-        <v>10.40520700966735</v>
+        <v>13.07757379585507</v>
       </c>
       <c r="L8" t="n">
-        <v>14.13826046327149</v>
+        <v>16.98430509944253</v>
       </c>
       <c r="M8" t="n">
-        <v>48.28004313002036</v>
+        <v>59.99054521180579</v>
       </c>
       <c r="N8" t="n">
-        <v>48.28004313002036</v>
+        <v>59.99054521180579</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.03162051901606956</v>
+        <v>-0.08891650692082587</v>
       </c>
       <c r="P8" t="n">
-        <v>1.460853391719668</v>
+        <v>4.410464593159171</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.429232872703599</v>
+        <v>4.321548086238345</v>
       </c>
       <c r="R8" t="n">
-        <v>0.03162051901606956</v>
+        <v>0.08891650692082587</v>
       </c>
       <c r="S8" t="n">
-        <v>1.460853391719668</v>
+        <v>4.410464593159171</v>
       </c>
       <c r="T8" t="n">
-        <v>1.429232872703599</v>
+        <v>4.321548086238345</v>
       </c>
     </row>
     <row r="9">
@@ -957,61 +957,61 @@
         <v>0.014</v>
       </c>
       <c r="B9" t="n">
-        <v>0.1464030937600296</v>
+        <v>0.1468916986179813</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.2971603427617172</v>
+        <v>-0.2981825185555083</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.547271968066358</v>
+        <v>-2.545227616478777</v>
       </c>
       <c r="E9" t="n">
-        <v>0.04458590054001688</v>
+        <v>0.08839259065123618</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.09325902180184482</v>
+        <v>-0.2100407637886341</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1865180436038421</v>
+        <v>0.4200815275774221</v>
       </c>
       <c r="H9" t="n">
-        <v>0.4515857620985777</v>
+        <v>0.5574462137585413</v>
       </c>
       <c r="I9" t="n">
-        <v>10.94114241926202</v>
+        <v>13.77905490527796</v>
       </c>
       <c r="J9" t="n">
-        <v>0.4060753594592774</v>
+        <v>0.4549463210296878</v>
       </c>
       <c r="K9" t="n">
-        <v>10.94377232367684</v>
+        <v>13.78497805481681</v>
       </c>
       <c r="L9" t="n">
-        <v>14.77949138300558</v>
+        <v>17.89906009157804</v>
       </c>
       <c r="M9" t="n">
-        <v>50.6627092153263</v>
+        <v>63.09347042288817</v>
       </c>
       <c r="N9" t="n">
-        <v>50.6627092153263</v>
+        <v>63.09347042288817</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.04306228775371796</v>
+        <v>-0.1184492372564311</v>
       </c>
       <c r="P9" t="n">
-        <v>2.054306485614064</v>
+        <v>5.826006150674517</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.011244197860345</v>
+        <v>5.707556913418086</v>
       </c>
       <c r="R9" t="n">
-        <v>0.04306228775371796</v>
+        <v>0.1184492372564311</v>
       </c>
       <c r="S9" t="n">
-        <v>2.054306485614064</v>
+        <v>5.826006150674517</v>
       </c>
       <c r="T9" t="n">
-        <v>2.011244197860345</v>
+        <v>5.707556913418086</v>
       </c>
     </row>
     <row r="10">
@@ -1019,61 +1019,61 @@
         <v>0.016</v>
       </c>
       <c r="B10" t="n">
-        <v>0.1465042725824083</v>
+        <v>0.1471068709428772</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.2973719821955112</v>
+        <v>-0.2986327576884184</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.54684868919877</v>
+        <v>-2.544327138212956</v>
       </c>
       <c r="E10" t="n">
-        <v>0.05767768829581212</v>
+        <v>0.110046425151752</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.1206499874977867</v>
+        <v>-0.2547243119515172</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2412999749955307</v>
+        <v>0.5094486239006329</v>
       </c>
       <c r="H10" t="n">
-        <v>0.5242063102734722</v>
+        <v>0.587052833288031</v>
       </c>
       <c r="I10" t="n">
-        <v>11.4616004529163</v>
+        <v>14.46198081479706</v>
       </c>
       <c r="J10" t="n">
-        <v>0.4653291163745523</v>
+        <v>0.4627473690556906</v>
       </c>
       <c r="K10" t="n">
-        <v>11.46500278256373</v>
+        <v>14.46916404039406</v>
       </c>
       <c r="L10" t="n">
-        <v>15.5406474714693</v>
+        <v>18.80457296453402</v>
       </c>
       <c r="M10" t="n">
-        <v>52.94578379370564</v>
+        <v>66.11211089966947</v>
       </c>
       <c r="N10" t="n">
-        <v>52.94578379370564</v>
+        <v>66.11211089966947</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.06402850827361119</v>
+        <v>-0.1487588791998588</v>
       </c>
       <c r="P10" t="n">
-        <v>2.776907471718563</v>
+        <v>7.3825538465333</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.712878963444952</v>
+        <v>7.233794967333441</v>
       </c>
       <c r="R10" t="n">
-        <v>0.06402850827361119</v>
+        <v>0.1487588791998588</v>
       </c>
       <c r="S10" t="n">
-        <v>2.776907471718563</v>
+        <v>7.3825538465333</v>
       </c>
       <c r="T10" t="n">
-        <v>2.712878963444952</v>
+        <v>7.233794967333441</v>
       </c>
     </row>
     <row r="11">
@@ -1081,61 +1081,61 @@
         <v>0.018</v>
       </c>
       <c r="B11" t="n">
-        <v>0.146639470607072</v>
+        <v>0.1473776024117848</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.297654810346023</v>
+        <v>-0.2991993539027906</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.546283032897747</v>
+        <v>-2.543193945784212</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0726333618168406</v>
+        <v>0.1341609806720995</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.1519483991987851</v>
+        <v>-0.3033708978943664</v>
       </c>
       <c r="G11" t="n">
-        <v>0.3038967983974715</v>
+        <v>0.6067417957901236</v>
       </c>
       <c r="H11" t="n">
-        <v>0.4872685700792649</v>
+        <v>0.5265931956581402</v>
       </c>
       <c r="I11" t="n">
-        <v>11.96749515590879</v>
+        <v>15.04180349610569</v>
       </c>
       <c r="J11" t="n">
-        <v>0.4131177512702578</v>
+        <v>0.3785481974856894</v>
       </c>
       <c r="K11" t="n">
-        <v>11.9717801007662</v>
+        <v>15.05035855542633</v>
       </c>
       <c r="L11" t="n">
-        <v>16.13084028120297</v>
+        <v>19.50192059073813</v>
       </c>
       <c r="M11" t="n">
-        <v>55.19657362420181</v>
+        <v>68.85152397064056</v>
       </c>
       <c r="N11" t="n">
-        <v>55.19657362420181</v>
+        <v>68.85152397064056</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.07224449399979578</v>
+        <v>-0.1584613334192558</v>
       </c>
       <c r="P11" t="n">
-        <v>3.659019296286166</v>
+        <v>9.15126663106224</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.58677480228637</v>
+        <v>8.992805297642985</v>
       </c>
       <c r="R11" t="n">
-        <v>0.07224449399979578</v>
+        <v>0.1584613334192558</v>
       </c>
       <c r="S11" t="n">
-        <v>3.659019296286166</v>
+        <v>9.15126663106224</v>
       </c>
       <c r="T11" t="n">
-        <v>3.58677480228637</v>
+        <v>8.992805297642985</v>
       </c>
     </row>
     <row r="12">
@@ -1143,61 +1143,61 @@
         <v>0.02</v>
       </c>
       <c r="B12" t="n">
-        <v>0.1467914864186649</v>
+        <v>0.1476967947147799</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.2979728341035074</v>
+        <v>-0.2998675139680884</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.545646985382778</v>
+        <v>-2.541857625653617</v>
       </c>
       <c r="E12" t="n">
-        <v>0.08847791163207935</v>
+        <v>0.1600171620738814</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.1851107720949886</v>
+        <v>-0.3555817486943277</v>
       </c>
       <c r="G12" t="n">
-        <v>0.3702215441898863</v>
+        <v>0.7111634973893589</v>
       </c>
       <c r="H12" t="n">
-        <v>0.4140763891200559</v>
+        <v>0.5152752149955218</v>
       </c>
       <c r="I12" t="n">
-        <v>12.46577761665373</v>
+        <v>15.60464613838548</v>
       </c>
       <c r="J12" t="n">
-        <v>0.3237423323377015</v>
+        <v>0.3417513216326898</v>
       </c>
       <c r="K12" t="n">
-        <v>12.47099774042681</v>
+        <v>15.61467354369867</v>
       </c>
       <c r="L12" t="n">
-        <v>16.66245818934534</v>
+        <v>20.25927841010021</v>
       </c>
       <c r="M12" t="n">
-        <v>57.42482423060746</v>
+        <v>71.34135183227984</v>
       </c>
       <c r="N12" t="n">
-        <v>57.42482423060746</v>
+        <v>71.34135183227984</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.07685941102981791</v>
+        <v>-0.1837741141251924</v>
       </c>
       <c r="P12" t="n">
-        <v>4.618259178616568</v>
+        <v>11.13271566156091</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.54139976758675</v>
+        <v>10.94894154743572</v>
       </c>
       <c r="R12" t="n">
-        <v>0.07685941102981791</v>
+        <v>0.1837741141251924</v>
       </c>
       <c r="S12" t="n">
-        <v>4.618259178616568</v>
+        <v>11.13271566156091</v>
       </c>
       <c r="T12" t="n">
-        <v>4.54139976758675</v>
+        <v>10.94894154743572</v>
       </c>
     </row>
     <row r="13">
@@ -1205,61 +1205,61 @@
         <v>0.022</v>
       </c>
       <c r="B13" t="n">
-        <v>0.146996591835576</v>
+        <v>0.1480501901537354</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.2984019985269621</v>
+        <v>-0.3006073681650899</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.544788656535869</v>
+        <v>-2.540377917259613</v>
       </c>
       <c r="E13" t="n">
-        <v>0.1066743688287661</v>
+        <v>0.1870550312281796</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.2232126215581611</v>
+        <v>-0.4102358432061031</v>
       </c>
       <c r="G13" t="n">
-        <v>0.4464252431163757</v>
+        <v>0.8204716864100426</v>
       </c>
       <c r="H13" t="n">
-        <v>0.4761754140216274</v>
+        <v>0.5252712316456833</v>
       </c>
       <c r="I13" t="n">
-        <v>12.93427455811989</v>
+        <v>16.14716828865876</v>
       </c>
       <c r="J13" t="n">
-        <v>0.3672476547012448</v>
+        <v>0.325076140161105</v>
       </c>
       <c r="K13" t="n">
-        <v>12.94056915404783</v>
+        <v>16.15873693943714</v>
       </c>
       <c r="L13" t="n">
-        <v>17.37097760672128</v>
+        <v>21.03305882311717</v>
       </c>
       <c r="M13" t="n">
-        <v>59.49017238657576</v>
+        <v>73.6600295947744</v>
       </c>
       <c r="N13" t="n">
-        <v>59.49017238657576</v>
+        <v>73.6600295947744</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.1077919810300174</v>
+        <v>-0.2149455350937296</v>
       </c>
       <c r="P13" t="n">
-        <v>5.796874321169286</v>
+        <v>13.2533696868552</v>
       </c>
       <c r="Q13" t="n">
-        <v>5.689082340139269</v>
+        <v>13.03842415176147</v>
       </c>
       <c r="R13" t="n">
-        <v>0.1077919810300174</v>
+        <v>0.2149455350937296</v>
       </c>
       <c r="S13" t="n">
-        <v>5.796874321169286</v>
+        <v>13.2533696868552</v>
       </c>
       <c r="T13" t="n">
-        <v>5.689082340139269</v>
+        <v>13.03842415176147</v>
       </c>
     </row>
     <row r="14">
@@ -1267,61 +1267,61 @@
         <v>0.024</v>
       </c>
       <c r="B14" t="n">
-        <v>0.147227244014674</v>
+        <v>0.1484822907116984</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.2988846740330924</v>
+        <v>-0.301512322750879</v>
       </c>
       <c r="D14" t="n">
-        <v>-2.543823305523608</v>
+        <v>-2.538568008088035</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1258076919500549</v>
+        <v>0.2162958595746513</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.2632872384476654</v>
+        <v>-0.469726066266362</v>
       </c>
       <c r="G14" t="n">
-        <v>0.5265744768953836</v>
+        <v>0.9394521325333421</v>
       </c>
       <c r="H14" t="n">
-        <v>0.4769182603822887</v>
+        <v>0.4391121234648537</v>
       </c>
       <c r="I14" t="n">
-        <v>13.39315801506353</v>
+        <v>16.55239602027145</v>
       </c>
       <c r="J14" t="n">
-        <v>0.348434088019828</v>
+        <v>0.209885803126869</v>
       </c>
       <c r="K14" t="n">
-        <v>13.40058271518776</v>
+        <v>16.56564229534017</v>
       </c>
       <c r="L14" t="n">
-        <v>17.98226174518442</v>
+        <v>21.56299580317223</v>
       </c>
       <c r="M14" t="n">
-        <v>61.53197522236678</v>
+        <v>75.63922330442053</v>
       </c>
       <c r="N14" t="n">
-        <v>61.53197522236678</v>
+        <v>75.63922330442053</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.1235782226143609</v>
+        <v>-0.2035695128980169</v>
       </c>
       <c r="P14" t="n">
-        <v>7.071669686068279</v>
+        <v>15.57551447430848</v>
       </c>
       <c r="Q14" t="n">
-        <v>6.948091463453918</v>
+        <v>15.37194496141047</v>
       </c>
       <c r="R14" t="n">
-        <v>0.1235782226143609</v>
+        <v>0.2035695128980169</v>
       </c>
       <c r="S14" t="n">
-        <v>7.071669686068279</v>
+        <v>15.57551447430848</v>
       </c>
       <c r="T14" t="n">
-        <v>6.948091463453918</v>
+        <v>15.37194496141047</v>
       </c>
     </row>
     <row r="15">
@@ -1329,61 +1329,61 @@
         <v>0.026</v>
       </c>
       <c r="B15" t="n">
-        <v>0.1474965729589295</v>
+        <v>0.1489610075126416</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.2994483631550714</v>
+        <v>-0.302515178488125</v>
       </c>
       <c r="D15" t="n">
-        <v>-2.542695927279651</v>
+        <v>-2.536562296613543</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1463593922059876</v>
+        <v>0.2465309540672616</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.3063485454664623</v>
+        <v>-0.53132605797511</v>
       </c>
       <c r="G15" t="n">
-        <v>0.6126970909327573</v>
+        <v>1.062652115950931</v>
       </c>
       <c r="H15" t="n">
-        <v>0.3847703329126044</v>
+        <v>0.3954961726246023</v>
       </c>
       <c r="I15" t="n">
-        <v>13.8374870450898</v>
+        <v>16.94215130033776</v>
       </c>
       <c r="J15" t="n">
-        <v>0.2352722427249707</v>
+        <v>0.1362090563327486</v>
       </c>
       <c r="K15" t="n">
-        <v>13.84612607407195</v>
+        <v>16.95713469517267</v>
       </c>
       <c r="L15" t="n">
-        <v>18.44633560235868</v>
+        <v>22.14473551477479</v>
       </c>
       <c r="M15" t="n">
-        <v>63.53813139528927</v>
+        <v>77.429858026548</v>
       </c>
       <c r="N15" t="n">
-        <v>63.53813139528927</v>
+        <v>77.429858026548</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.1164335353062001</v>
+        <v>-0.2100480280287989</v>
       </c>
       <c r="P15" t="n">
-        <v>8.492078019267812</v>
+        <v>18.0291728412785</v>
       </c>
       <c r="Q15" t="n">
-        <v>8.375644483961612</v>
+        <v>17.8191248132497</v>
       </c>
       <c r="R15" t="n">
-        <v>0.1164335353062001</v>
+        <v>0.2100480280287989</v>
       </c>
       <c r="S15" t="n">
-        <v>8.492078019267812</v>
+        <v>18.0291728412785</v>
       </c>
       <c r="T15" t="n">
-        <v>8.375644483961612</v>
+        <v>17.8191248132497</v>
       </c>
     </row>
     <row r="16">
@@ -1391,61 +1391,61 @@
         <v>0.028</v>
       </c>
       <c r="B16" t="n">
-        <v>0.1478190535297194</v>
+        <v>0.149484643022146</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.3001234683821153</v>
+        <v>-0.303612370298142</v>
       </c>
       <c r="D16" t="n">
-        <v>-2.541345716825563</v>
+        <v>-2.534367912993509</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1685495931121893</v>
+        <v>0.2777241084204578</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.3528726552105581</v>
+        <v>-0.594958990929107</v>
       </c>
       <c r="G16" t="n">
-        <v>0.7057453104212078</v>
+        <v>1.189917981856428</v>
       </c>
       <c r="H16" t="n">
-        <v>0.3982054713251305</v>
+        <v>0.3928741664629415</v>
       </c>
       <c r="I16" t="n">
-        <v>14.25560436500383</v>
+        <v>17.31699755948546</v>
       </c>
       <c r="J16" t="n">
-        <v>0.2260036155823781</v>
+        <v>0.1025341788895373</v>
       </c>
       <c r="K16" t="n">
-        <v>14.26555537388077</v>
+        <v>17.33377540302964</v>
       </c>
       <c r="L16" t="n">
-        <v>19.0469980176106</v>
+        <v>22.77639155708731</v>
       </c>
       <c r="M16" t="n">
-        <v>65.40608075314296</v>
+        <v>79.03880015258747</v>
       </c>
       <c r="N16" t="n">
-        <v>65.40608075314296</v>
+        <v>79.03880015258747</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.1421517472786023</v>
+        <v>-0.2337309060037562</v>
       </c>
       <c r="P16" t="n">
-        <v>10.08733519536386</v>
+        <v>20.60955570967733</v>
       </c>
       <c r="Q16" t="n">
-        <v>9.945183448085258</v>
+        <v>20.37582480367357</v>
       </c>
       <c r="R16" t="n">
-        <v>0.1421517472786023</v>
+        <v>0.2337309060037562</v>
       </c>
       <c r="S16" t="n">
-        <v>10.08733519536386</v>
+        <v>20.60955570967733</v>
       </c>
       <c r="T16" t="n">
-        <v>9.945183448085258</v>
+        <v>20.37582480367357</v>
       </c>
     </row>
     <row r="17">
@@ -1453,61 +1453,61 @@
         <v>0.03</v>
       </c>
       <c r="B17" t="n">
-        <v>0.1481667141696819</v>
+        <v>0.150100010280496</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.3008513689859416</v>
+        <v>-0.3049024941852678</v>
       </c>
       <c r="D17" t="n">
-        <v>-2.53988991561791</v>
+        <v>-2.531787665219258</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1914854310646693</v>
+        <v>0.3103532645008382</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.4009743853612133</v>
+        <v>-0.6615207700577137</v>
       </c>
       <c r="G17" t="n">
-        <v>0.8019487707228585</v>
+        <v>1.323041540115556</v>
       </c>
       <c r="H17" t="n">
-        <v>0.4358549273165953</v>
+        <v>0.2917359707693244</v>
       </c>
       <c r="I17" t="n">
-        <v>14.66221318262137</v>
+        <v>17.54299083737594</v>
       </c>
       <c r="J17" t="n">
-        <v>0.2401794272603232</v>
+        <v>-0.0310861650188399</v>
       </c>
       <c r="K17" t="n">
-        <v>14.67352066028856</v>
+        <v>17.56164572309157</v>
       </c>
       <c r="L17" t="n">
-        <v>19.67488434687004</v>
+        <v>23.14958290090297</v>
       </c>
       <c r="M17" t="n">
-        <v>67.21948233612662</v>
+        <v>80.26150850462965</v>
       </c>
       <c r="N17" t="n">
-        <v>67.21948233612662</v>
+        <v>80.26150850462965</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.1740576738115228</v>
+        <v>-0.1888555778949444</v>
       </c>
       <c r="P17" t="n">
-        <v>11.76352532761931</v>
+        <v>23.22700700894136</v>
       </c>
       <c r="Q17" t="n">
-        <v>11.58946765380779</v>
+        <v>23.03815143104641</v>
       </c>
       <c r="R17" t="n">
-        <v>0.1740576738115228</v>
+        <v>0.1888555778949444</v>
       </c>
       <c r="S17" t="n">
-        <v>11.76352532761931</v>
+        <v>23.22700700894136</v>
       </c>
       <c r="T17" t="n">
-        <v>11.58946765380779</v>
+        <v>23.03815143104641</v>
       </c>
     </row>
     <row r="18">
@@ -1515,61 +1515,61 @@
         <v>0.032</v>
       </c>
       <c r="B18" t="n">
-        <v>0.1485867212808347</v>
+        <v>0.1507592437459384</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.301731066523018</v>
+        <v>-0.3062850251757206</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.538130520543757</v>
+        <v>-2.529022603238352</v>
       </c>
       <c r="E18" t="n">
-        <v>0.2163129295867934</v>
+        <v>0.3434644623471864</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4530937935797019</v>
+        <v>-0.7290517547152331</v>
       </c>
       <c r="G18" t="n">
-        <v>0.9061875871592129</v>
+        <v>1.458103509431346</v>
       </c>
       <c r="H18" t="n">
-        <v>0.3315916769364962</v>
+        <v>0.2167435861172136</v>
       </c>
       <c r="I18" t="n">
-        <v>15.04320632554056</v>
+        <v>17.74224905279555</v>
       </c>
       <c r="J18" t="n">
-        <v>0.1104819056696016</v>
+        <v>-0.1390336701838202</v>
       </c>
       <c r="K18" t="n">
-        <v>15.05598357051951</v>
+        <v>17.76280831227853</v>
       </c>
       <c r="L18" t="n">
-        <v>20.07378902320652</v>
+        <v>23.54213764273447</v>
       </c>
       <c r="M18" t="n">
-        <v>68.96570731130252</v>
+        <v>81.28773719102318</v>
       </c>
       <c r="N18" t="n">
-        <v>68.96570731130252</v>
+        <v>81.28773719102318</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.1468609429244618</v>
+        <v>-0.157238497735586</v>
       </c>
       <c r="P18" t="n">
-        <v>13.65667755197943</v>
+        <v>25.88064929071525</v>
       </c>
       <c r="Q18" t="n">
-        <v>13.50981660905497</v>
+        <v>25.72341079297967</v>
       </c>
       <c r="R18" t="n">
-        <v>0.1468609429244618</v>
+        <v>0.157238497735586</v>
       </c>
       <c r="S18" t="n">
-        <v>13.65667755197943</v>
+        <v>25.88064929071525</v>
       </c>
       <c r="T18" t="n">
-        <v>13.50981660905497</v>
+        <v>25.72341079297967</v>
       </c>
     </row>
     <row r="19">
@@ -1577,61 +1577,61 @@
         <v>0.034</v>
       </c>
       <c r="B19" t="n">
-        <v>0.1490430818472378</v>
+        <v>0.1514800854312733</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.3026871314980999</v>
+        <v>-0.3077973647642109</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.536218390593593</v>
+        <v>-2.525997924061371</v>
       </c>
       <c r="E19" t="n">
-        <v>0.2419505026398209</v>
+        <v>0.3772153673468423</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.5069451539142372</v>
+        <v>-0.7978653266648629</v>
       </c>
       <c r="G19" t="n">
-        <v>1.013890307828138</v>
+        <v>1.595730653329127</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2877680509842657</v>
+        <v>0.1918233850373943</v>
       </c>
       <c r="I19" t="n">
-        <v>15.40748494909548</v>
+        <v>17.91205972456804</v>
       </c>
       <c r="J19" t="n">
-        <v>0.04037881587411797</v>
+        <v>-0.1975348943750588</v>
       </c>
       <c r="K19" t="n">
-        <v>15.42178080243585</v>
+        <v>17.93455952677998</v>
       </c>
       <c r="L19" t="n">
-        <v>20.55027338212694</v>
+        <v>23.98794322513082</v>
       </c>
       <c r="M19" t="n">
-        <v>70.62642135807621</v>
+        <v>82.03587114001978</v>
       </c>
       <c r="N19" t="n">
-        <v>70.62642135807621</v>
+        <v>82.03587114001978</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.1469962750368024</v>
+        <v>-0.1526337081260434</v>
       </c>
       <c r="P19" t="n">
-        <v>15.64162625982735</v>
+        <v>28.58848561584456</v>
       </c>
       <c r="Q19" t="n">
-        <v>15.49462998479055</v>
+        <v>28.43585190771852</v>
       </c>
       <c r="R19" t="n">
-        <v>0.1469962750368024</v>
+        <v>0.1526337081260434</v>
       </c>
       <c r="S19" t="n">
-        <v>15.64162625982735</v>
+        <v>28.58848561584456</v>
       </c>
       <c r="T19" t="n">
-        <v>15.49462998479055</v>
+        <v>28.43585190771852</v>
       </c>
     </row>
     <row r="20">
@@ -1639,61 +1639,61 @@
         <v>0.036</v>
       </c>
       <c r="B20" t="n">
-        <v>0.1495485463939887</v>
+        <v>0.1522859474000877</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.3037463488461609</v>
+        <v>-0.3094892282448655</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.534099955897472</v>
+        <v>-2.522614197100062</v>
       </c>
       <c r="E20" t="n">
-        <v>0.2686822738528858</v>
+        <v>0.4114708773608486</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.563135927162468</v>
+        <v>-0.8680827058477849</v>
       </c>
       <c r="G20" t="n">
-        <v>1.126271854325098</v>
+        <v>1.736165411695536</v>
       </c>
       <c r="H20" t="n">
-        <v>0.3255825006898004</v>
+        <v>0.07780963120587932</v>
       </c>
       <c r="I20" t="n">
-        <v>15.74918664221176</v>
+        <v>17.95850754159495</v>
       </c>
       <c r="J20" t="n">
-        <v>0.05077216823451607</v>
+        <v>-0.3458147292478397</v>
       </c>
       <c r="K20" t="n">
-        <v>15.76506707535774</v>
+        <v>17.98298747389986</v>
       </c>
       <c r="L20" t="n">
-        <v>21.13154753840705</v>
+        <v>24.20511037938928</v>
       </c>
       <c r="M20" t="n">
-        <v>72.17163257523194</v>
+        <v>82.44477049652653</v>
       </c>
       <c r="N20" t="n">
-        <v>72.17163257523194</v>
+        <v>82.44477049652653</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.1840500534192869</v>
+        <v>-0.06185332579304463</v>
       </c>
       <c r="P20" t="n">
-        <v>17.75056793313519</v>
+        <v>31.18068088993719</v>
       </c>
       <c r="Q20" t="n">
-        <v>17.5665178797159</v>
+        <v>31.11882756414415</v>
       </c>
       <c r="R20" t="n">
-        <v>0.1840500534192869</v>
+        <v>0.0813056579905634</v>
       </c>
       <c r="S20" t="n">
-        <v>17.75056793313519</v>
+        <v>31.18068088993719</v>
       </c>
       <c r="T20" t="n">
-        <v>17.5665178797159</v>
+        <v>31.11882756414415</v>
       </c>
     </row>
     <row r="21">
@@ -1701,61 +1701,61 @@
         <v>0.038</v>
       </c>
       <c r="B21" t="n">
-        <v>0.1501242714922729</v>
+        <v>0.1531374833145056</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.3049533770027137</v>
+        <v>-0.3112776822437575</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.531685899584366</v>
+        <v>-2.519037289102278</v>
       </c>
       <c r="E21" t="n">
-        <v>0.2967478390227744</v>
+        <v>0.445893007667645</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.6222037167570618</v>
+        <v>-0.9388946573875289</v>
       </c>
       <c r="G21" t="n">
-        <v>1.244407433514205</v>
+        <v>1.87778931477549</v>
       </c>
       <c r="H21" t="n">
-        <v>0.2442827504939239</v>
+        <v>-0.03162331955787295</v>
       </c>
       <c r="I21" t="n">
-        <v>16.06655355782987</v>
+        <v>17.97302548082751</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.05935266328352228</v>
+        <v>-0.489803912362987</v>
       </c>
       <c r="K21" t="n">
-        <v>16.08409970264243</v>
+        <v>17.99950231016584</v>
       </c>
       <c r="L21" t="n">
-        <v>21.51650739723206</v>
+        <v>24.40112943042953</v>
       </c>
       <c r="M21" t="n">
-        <v>73.649564302915</v>
+        <v>82.69566904161837</v>
       </c>
       <c r="N21" t="n">
-        <v>73.649564302915</v>
+        <v>82.69566904161837</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.147191244541638</v>
+        <v>0.03077116938106241</v>
       </c>
       <c r="P21" t="n">
-        <v>20.01872440243642</v>
+        <v>33.7494727996448</v>
       </c>
       <c r="Q21" t="n">
-        <v>19.87153315789478</v>
+        <v>33.78024396902586</v>
       </c>
       <c r="R21" t="n">
-        <v>0.147191244541638</v>
+        <v>0.03077116938106241</v>
       </c>
       <c r="S21" t="n">
-        <v>20.01872440243642</v>
+        <v>33.7494727996448</v>
       </c>
       <c r="T21" t="n">
-        <v>19.87153315789478</v>
+        <v>33.78024396902586</v>
       </c>
     </row>
     <row r="22">
@@ -1763,61 +1763,61 @@
         <v>0.04</v>
       </c>
       <c r="B22" t="n">
-        <v>0.1507319404649332</v>
+        <v>0.1540661975138761</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.3062276466732657</v>
+        <v>-0.3132295144145932</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.529137360243261</v>
+        <v>-2.515133624760607</v>
       </c>
       <c r="E22" t="n">
-        <v>0.325389028825371</v>
+        <v>0.4804818421397629</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.6825175635218678</v>
+        <v>-1.010535862423949</v>
       </c>
       <c r="G22" t="n">
-        <v>1.365035127043598</v>
+        <v>2.021071724847316</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1426368606922963</v>
+        <v>-0.07565893628699312</v>
       </c>
       <c r="I22" t="n">
-        <v>16.37179924657119</v>
+        <v>17.97134587047485</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.1904317103063752</v>
+        <v>-0.5688004371498802</v>
       </c>
       <c r="K22" t="n">
-        <v>16.3910462418625</v>
+        <v>17.99984298179519</v>
       </c>
       <c r="L22" t="n">
-        <v>21.86214512777263</v>
+        <v>24.6732013896092</v>
       </c>
       <c r="M22" t="n">
-        <v>75.08335234172543</v>
+        <v>82.70623333544134</v>
       </c>
       <c r="N22" t="n">
-        <v>75.08335234172543</v>
+        <v>82.70623333544134</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.09761579782010779</v>
+        <v>0.07764202957631627</v>
       </c>
       <c r="P22" t="n">
-        <v>22.35385931991017</v>
+        <v>36.32128852620038</v>
       </c>
       <c r="Q22" t="n">
-        <v>22.25624352209007</v>
+        <v>36.3989305557767</v>
       </c>
       <c r="R22" t="n">
-        <v>0.09761579782010779</v>
+        <v>0.07764202957631627</v>
       </c>
       <c r="S22" t="n">
-        <v>22.35385931991017</v>
+        <v>36.32128852620038</v>
       </c>
       <c r="T22" t="n">
-        <v>22.25624352209007</v>
+        <v>36.3989305557767</v>
       </c>
     </row>
     <row r="23">
@@ -1825,61 +1825,61 @@
         <v>0.042</v>
       </c>
       <c r="B23" t="n">
-        <v>0.1514258576488921</v>
+        <v>0.1550704880403629</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.3076836793447527</v>
+        <v>-0.3153417848831603</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.526225294900288</v>
+        <v>-2.510909083823473</v>
       </c>
       <c r="E23" t="n">
-        <v>0.3554196620970418</v>
+        <v>0.515239923209149</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.7458640918270539</v>
+        <v>-1.084268170120031</v>
       </c>
       <c r="G23" t="n">
-        <v>1.491728183654041</v>
+        <v>2.168536340240026</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1669879963649815</v>
+        <v>-0.1869162289055339</v>
       </c>
       <c r="I23" t="n">
-        <v>16.63865869157774</v>
+        <v>17.96924767088695</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.1969936804466208</v>
+        <v>-0.7160390959241092</v>
       </c>
       <c r="K23" t="n">
-        <v>16.65969205896726</v>
+        <v>17.99982403328434</v>
       </c>
       <c r="L23" t="n">
-        <v>22.36882805041581</v>
+        <v>24.72794902105373</v>
       </c>
       <c r="M23" t="n">
-        <v>76.32541131312928</v>
+        <v>82.77671144298607</v>
       </c>
       <c r="N23" t="n">
-        <v>76.32541131312928</v>
+        <v>82.77671144298607</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.1254873190662198</v>
+        <v>0.2089573467653369</v>
       </c>
       <c r="P23" t="n">
-        <v>24.8408922329319</v>
+        <v>38.96676170213332</v>
       </c>
       <c r="Q23" t="n">
-        <v>24.71540491386568</v>
+        <v>39.17571904889866</v>
       </c>
       <c r="R23" t="n">
-        <v>0.1254873190662198</v>
+        <v>0.2089573467653369</v>
       </c>
       <c r="S23" t="n">
-        <v>24.8408922329319</v>
+        <v>38.96676170213332</v>
       </c>
       <c r="T23" t="n">
-        <v>24.71540491386568</v>
+        <v>39.17571904889866</v>
       </c>
     </row>
     <row r="24">
@@ -1887,61 +1887,61 @@
         <v>0.044</v>
       </c>
       <c r="B24" t="n">
-        <v>0.1521659066372446</v>
+        <v>0.1561222463435204</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.3092371346161183</v>
+        <v>-0.3175549300668522</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.523118384357557</v>
+        <v>-2.506482793456089</v>
       </c>
       <c r="E24" t="n">
-        <v>0.3860742948129997</v>
+        <v>0.5500853093521846</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.8105946425205065</v>
+        <v>-1.158915404035308</v>
       </c>
       <c r="G24" t="n">
-        <v>1.621189285041089</v>
+        <v>2.317830808071447</v>
       </c>
       <c r="H24" t="n">
-        <v>0.1209857811892221</v>
+        <v>-0.3072436265517117</v>
       </c>
       <c r="I24" t="n">
-        <v>16.88947574254042</v>
+        <v>17.96702002911374</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.2745844043607851</v>
+        <v>-0.8727943437209419</v>
       </c>
       <c r="K24" t="n">
-        <v>16.91233451145949</v>
+        <v>17.99970144350755</v>
       </c>
       <c r="L24" t="n">
-        <v>22.75664103215388</v>
+        <v>24.71694875395349</v>
       </c>
       <c r="M24" t="n">
-        <v>77.52106030538</v>
+        <v>82.88040278869521</v>
       </c>
       <c r="N24" t="n">
-        <v>77.52106030538</v>
+        <v>82.88040278869521</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.09332604557642502</v>
+        <v>0.3561058668569647</v>
       </c>
       <c r="P24" t="n">
-        <v>27.39780822346564</v>
+        <v>41.64445440908407</v>
       </c>
       <c r="Q24" t="n">
-        <v>27.30448217788922</v>
+        <v>42.00056027594104</v>
       </c>
       <c r="R24" t="n">
-        <v>0.1112088505456648</v>
+        <v>0.3561058668569647</v>
       </c>
       <c r="S24" t="n">
-        <v>27.39780822346564</v>
+        <v>41.64445440908407</v>
       </c>
       <c r="T24" t="n">
-        <v>27.30448217788922</v>
+        <v>42.00056027594104</v>
       </c>
     </row>
     <row r="25">
@@ -1949,61 +1949,61 @@
         <v>0.046</v>
       </c>
       <c r="B25" t="n">
-        <v>0.1529616560094989</v>
+        <v>0.1572680900885945</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.3109082197154363</v>
+        <v>-0.3199684568984634</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.519776214158921</v>
+        <v>-2.501655739792866</v>
       </c>
       <c r="E25" t="n">
-        <v>0.4174823558645315</v>
+        <v>0.5850258876773597</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.8769962871451082</v>
+        <v>-1.23374298405072</v>
       </c>
       <c r="G25" t="n">
-        <v>1.753992574290521</v>
+        <v>2.467485968101105</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.009962355841224263</v>
+        <v>-0.3096754588772964</v>
       </c>
       <c r="I25" t="n">
-        <v>17.1209229136839</v>
+        <v>17.96508285170603</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.4379365439680371</v>
+        <v>-0.9117420350940478</v>
       </c>
       <c r="K25" t="n">
-        <v>17.14565420898139</v>
+        <v>17.99987440385626</v>
       </c>
       <c r="L25" t="n">
-        <v>23.00092827433268</v>
+        <v>24.86560778672411</v>
       </c>
       <c r="M25" t="n">
-        <v>78.66067304043932</v>
+        <v>83.03182070178563</v>
       </c>
       <c r="N25" t="n">
-        <v>78.66067304043932</v>
+        <v>83.03182070178563</v>
       </c>
       <c r="O25" t="n">
-        <v>0.01131992166079682</v>
+        <v>0.382147168488945</v>
       </c>
       <c r="P25" t="n">
-        <v>30.0391023192312</v>
+        <v>44.32845085704081</v>
       </c>
       <c r="Q25" t="n">
-        <v>30.050422240892</v>
+        <v>44.71059802552976</v>
       </c>
       <c r="R25" t="n">
-        <v>0.04603771389039353</v>
+        <v>0.382147168488945</v>
       </c>
       <c r="S25" t="n">
-        <v>30.0391023192312</v>
+        <v>44.32845085704081</v>
       </c>
       <c r="T25" t="n">
-        <v>30.050422240892</v>
+        <v>44.71059802552976</v>
       </c>
     </row>
     <row r="26">
@@ -2011,61 +2011,61 @@
         <v>0.048</v>
       </c>
       <c r="B26" t="n">
-        <v>0.1538417983883552</v>
+        <v>0.158477365676419</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.3127579653429182</v>
+        <v>-0.322517608336336</v>
       </c>
       <c r="D26" t="n">
-        <v>-2.516076722903956</v>
+        <v>-2.496557436917121</v>
       </c>
       <c r="E26" t="n">
-        <v>0.4498336295291155</v>
+        <v>0.6200347760811267</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.9455369948708091</v>
+        <v>-1.308651797223437</v>
       </c>
       <c r="G26" t="n">
-        <v>1.891073989741656</v>
+        <v>2.61730359444657</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.02842663000741689</v>
+        <v>-0.3941965937409387</v>
       </c>
       <c r="I26" t="n">
-        <v>17.31500954167881</v>
+        <v>17.96299063021303</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.4898486835043717</v>
+        <v>-1.032818670785976</v>
       </c>
       <c r="K26" t="n">
-        <v>17.34167368493417</v>
+        <v>17.99989461089473</v>
       </c>
       <c r="L26" t="n">
-        <v>23.38898533793781</v>
+        <v>24.90340227353398</v>
       </c>
       <c r="M26" t="n">
-        <v>79.61698559988005</v>
+        <v>83.16975260633015</v>
       </c>
       <c r="N26" t="n">
-        <v>79.61698559988005</v>
+        <v>83.16975260633015</v>
       </c>
       <c r="O26" t="n">
-        <v>0.02638375172694456</v>
+        <v>0.5220097539427384</v>
       </c>
       <c r="P26" t="n">
-        <v>32.76144413083021</v>
+        <v>47.01441182283894</v>
       </c>
       <c r="Q26" t="n">
-        <v>32.78782788255715</v>
+        <v>47.53642157678169</v>
       </c>
       <c r="R26" t="n">
-        <v>0.02638375172694456</v>
+        <v>0.5220097539427384</v>
       </c>
       <c r="S26" t="n">
-        <v>32.76144413083021</v>
+        <v>47.01441182283894</v>
       </c>
       <c r="T26" t="n">
-        <v>32.78782788255715</v>
+        <v>47.53642157678169</v>
       </c>
     </row>
     <row r="27">
@@ -2073,61 +2073,61 @@
         <v>0.05</v>
       </c>
       <c r="B27" t="n">
-        <v>0.1547587739321581</v>
+        <v>0.1597346293195021</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.3146857786548042</v>
+        <v>-0.3251693825644477</v>
       </c>
       <c r="D27" t="n">
-        <v>-2.512221096280185</v>
+        <v>-2.491253888460898</v>
       </c>
       <c r="E27" t="n">
-        <v>0.4825630768437127</v>
+        <v>0.6550960473122407</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.014945453879386</v>
+        <v>-1.383635163395342</v>
       </c>
       <c r="G27" t="n">
-        <v>2.029890907758505</v>
+        <v>2.767270326791255</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.03942219204684674</v>
+        <v>-0.5357459650565041</v>
       </c>
       <c r="I27" t="n">
-        <v>17.49409998934578</v>
+        <v>17.96078904916994</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.5347155735399871</v>
+        <v>-1.210959924793431</v>
       </c>
       <c r="K27" t="n">
-        <v>17.52272145114518</v>
+        <v>17.99980756077769</v>
       </c>
       <c r="L27" t="n">
-        <v>23.77671066208134</v>
+        <v>24.86390187074185</v>
       </c>
       <c r="M27" t="n">
-        <v>80.50991021175621</v>
+        <v>83.29797749923431</v>
       </c>
       <c r="N27" t="n">
-        <v>80.50991021175621</v>
+        <v>83.29797749923431</v>
       </c>
       <c r="O27" t="n">
-        <v>0.042180326309015</v>
+        <v>0.7413034889598886</v>
       </c>
       <c r="P27" t="n">
-        <v>35.51547115033173</v>
+        <v>49.70234971139919</v>
       </c>
       <c r="Q27" t="n">
-        <v>35.55765147664075</v>
+        <v>50.44365320035907</v>
       </c>
       <c r="R27" t="n">
-        <v>0.042180326309015</v>
+        <v>0.7413034889598886</v>
       </c>
       <c r="S27" t="n">
-        <v>35.51547115033173</v>
+        <v>49.70234971139919</v>
       </c>
       <c r="T27" t="n">
-        <v>35.55765147664075</v>
+        <v>50.44365320035907</v>
       </c>
     </row>
     <row r="28">
@@ -2135,61 +2135,61 @@
         <v>0.052</v>
       </c>
       <c r="B28" t="n">
-        <v>0.1557702787238894</v>
+        <v>0.1610994933106331</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.316814282939907</v>
+        <v>-0.3280522129318574</v>
       </c>
       <c r="D28" t="n">
-        <v>-2.507964087709979</v>
+        <v>-2.485488227726079</v>
       </c>
       <c r="E28" t="n">
-        <v>0.516140006117625</v>
+        <v>0.6903104640769153</v>
       </c>
       <c r="F28" t="n">
-        <v>-1.086338977621626</v>
+        <v>-1.4594494882456</v>
       </c>
       <c r="G28" t="n">
-        <v>2.172677955243238</v>
+        <v>2.91889897649116</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.1842138594540767</v>
+        <v>-0.5479779240914036</v>
       </c>
       <c r="I28" t="n">
-        <v>17.6395171360479</v>
+        <v>17.95874444863944</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.71434728053343</v>
+        <v>-1.260189274355256</v>
       </c>
       <c r="K28" t="n">
-        <v>17.67015189521683</v>
+        <v>17.99990092420796</v>
       </c>
       <c r="L28" t="n">
-        <v>23.93177643991894</v>
+        <v>24.98443150562016</v>
       </c>
       <c r="M28" t="n">
-        <v>81.30120527598719</v>
+        <v>83.42955155637718</v>
       </c>
       <c r="N28" t="n">
-        <v>81.30120527598719</v>
+        <v>83.42955155637718</v>
       </c>
       <c r="O28" t="n">
-        <v>0.2062288551921539</v>
+        <v>0.8002588017059037</v>
       </c>
       <c r="P28" t="n">
-        <v>38.33726313155465</v>
+        <v>52.41958939191989</v>
       </c>
       <c r="Q28" t="n">
-        <v>38.54349198674681</v>
+        <v>53.21984819362579</v>
       </c>
       <c r="R28" t="n">
-        <v>0.2062288551921539</v>
+        <v>0.8002588017059037</v>
       </c>
       <c r="S28" t="n">
-        <v>38.33726313155465</v>
+        <v>52.41958939191989</v>
       </c>
       <c r="T28" t="n">
-        <v>38.54349198674681</v>
+        <v>53.21984819362579</v>
       </c>
     </row>
     <row r="29">
@@ -2197,61 +2197,61 @@
         <v>0.054</v>
       </c>
       <c r="B29" t="n">
-        <v>0.1568358972682814</v>
+        <v>0.1625148188379719</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.3190580542593901</v>
+        <v>-0.3310439138332614</v>
       </c>
       <c r="D29" t="n">
-        <v>-2.503476545071013</v>
+        <v>-2.47950482592327</v>
       </c>
       <c r="E29" t="n">
-        <v>0.5500888774072863</v>
+        <v>0.7256026518704385</v>
       </c>
       <c r="F29" t="n">
-        <v>-1.158648080352863</v>
+        <v>-1.535667412537955</v>
       </c>
       <c r="G29" t="n">
-        <v>2.317296160705709</v>
+        <v>3.071334825075669</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.2610547597314152</v>
+        <v>-0.6243448748835057</v>
       </c>
       <c r="I29" t="n">
-        <v>17.76057781132135</v>
+        <v>17.95660754208639</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.8264750229436122</v>
+        <v>-1.373750572202028</v>
       </c>
       <c r="K29" t="n">
-        <v>17.7932516871873</v>
+        <v>17.99991336311995</v>
       </c>
       <c r="L29" t="n">
-        <v>24.1741016290527</v>
+        <v>25.03488052290027</v>
       </c>
       <c r="M29" t="n">
-        <v>81.97439886028698</v>
+        <v>83.57475173768304</v>
       </c>
       <c r="N29" t="n">
-        <v>81.97439886028698</v>
+        <v>83.57475173768304</v>
       </c>
       <c r="O29" t="n">
-        <v>0.3026121931021309</v>
+        <v>0.9646908857421792</v>
       </c>
       <c r="P29" t="n">
-        <v>41.16437465728276</v>
+        <v>55.15058012519803</v>
       </c>
       <c r="Q29" t="n">
-        <v>41.46698685038489</v>
+        <v>56.11527101094021</v>
       </c>
       <c r="R29" t="n">
-        <v>0.3026121931021309</v>
+        <v>0.9646908857421792</v>
       </c>
       <c r="S29" t="n">
-        <v>41.16437465728276</v>
+        <v>55.15058012519803</v>
       </c>
       <c r="T29" t="n">
-        <v>41.46698685038489</v>
+        <v>56.11527101094021</v>
       </c>
     </row>
     <row r="30">
@@ -2259,61 +2259,61 @@
         <v>0.056</v>
       </c>
       <c r="B30" t="n">
-        <v>0.1579599895334822</v>
+        <v>0.163990052609984</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.3214263797274102</v>
+        <v>-0.3341648664990467</v>
       </c>
       <c r="D30" t="n">
-        <v>-2.498739894134973</v>
+        <v>-2.4732629205917</v>
       </c>
       <c r="E30" t="n">
-        <v>0.5844396582396528</v>
+        <v>0.7609871699054666</v>
       </c>
       <c r="F30" t="n">
-        <v>-1.231946530663016</v>
+        <v>-1.612364492558497</v>
       </c>
       <c r="G30" t="n">
-        <v>2.463893061325736</v>
+        <v>3.224728985117044</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.2644700705694382</v>
+        <v>-0.7768532804756497</v>
       </c>
       <c r="I30" t="n">
-        <v>17.85531960386767</v>
+        <v>17.95436104925833</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.86565997753299</v>
+        <v>-1.563687152844196</v>
       </c>
       <c r="K30" t="n">
-        <v>17.89006049603236</v>
+        <v>17.99982972794848</v>
       </c>
       <c r="L30" t="n">
-        <v>24.51071675749356</v>
+        <v>25.00212940198731</v>
       </c>
       <c r="M30" t="n">
-        <v>82.51997547801119</v>
+        <v>83.73612893700407</v>
       </c>
       <c r="N30" t="n">
-        <v>82.51997547801119</v>
+        <v>83.73612893700407</v>
       </c>
       <c r="O30" t="n">
-        <v>0.3258785267223554</v>
+        <v>1.254345638303236</v>
       </c>
       <c r="P30" t="n">
-        <v>43.99723432548728</v>
+        <v>57.89789619248337</v>
       </c>
       <c r="Q30" t="n">
-        <v>44.32311285220964</v>
+        <v>59.15224183078661</v>
       </c>
       <c r="R30" t="n">
-        <v>0.3258785267223554</v>
+        <v>1.254345638303236</v>
       </c>
       <c r="S30" t="n">
-        <v>43.99723432548728</v>
+        <v>57.89789619248337</v>
       </c>
       <c r="T30" t="n">
-        <v>44.32311285220964</v>
+        <v>59.15224183078661</v>
       </c>
     </row>
     <row r="31">
@@ -2321,61 +2321,61 @@
         <v>0.058</v>
       </c>
       <c r="B31" t="n">
-        <v>0.1591785716899572</v>
+        <v>0.1655646826286682</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.3239967452592443</v>
+        <v>-0.3375013926197561</v>
       </c>
       <c r="D31" t="n">
-        <v>-2.493599163071305</v>
+        <v>-2.466589868350281</v>
       </c>
       <c r="E31" t="n">
-        <v>0.6192457219904247</v>
+        <v>0.7965312342077778</v>
       </c>
       <c r="F31" t="n">
-        <v>-1.306467133850382</v>
+        <v>-1.689710797908598</v>
       </c>
       <c r="G31" t="n">
-        <v>2.612934267700758</v>
+        <v>3.379421595817313</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.3953536116528379</v>
+        <v>-0.8091800746626198</v>
       </c>
       <c r="I31" t="n">
-        <v>17.91498952345574</v>
+        <v>17.95224759885231</v>
       </c>
       <c r="J31" t="n">
-        <v>-1.032909572971824</v>
+        <v>-1.633758944042015</v>
       </c>
       <c r="K31" t="n">
-        <v>17.95183189663032</v>
+        <v>17.99989744335334</v>
       </c>
       <c r="L31" t="n">
-        <v>24.61834315891178</v>
+        <v>25.11906976507473</v>
       </c>
       <c r="M31" t="n">
-        <v>82.955174781319</v>
+        <v>83.91165335086002</v>
       </c>
       <c r="N31" t="n">
-        <v>82.955174781319</v>
+        <v>83.91165335086002</v>
       </c>
       <c r="O31" t="n">
-        <v>0.5246446835394629</v>
+        <v>1.368127600497884</v>
       </c>
       <c r="P31" t="n">
-        <v>46.81604529098314</v>
+        <v>60.6680195552776</v>
       </c>
       <c r="Q31" t="n">
-        <v>47.3406899745226</v>
+        <v>62.03614715577548</v>
       </c>
       <c r="R31" t="n">
-        <v>0.5246446835394629</v>
+        <v>1.368127600497884</v>
       </c>
       <c r="S31" t="n">
-        <v>46.81604529098314</v>
+        <v>60.6680195552776</v>
       </c>
       <c r="T31" t="n">
-        <v>47.3406899745226</v>
+        <v>62.03614715577548</v>
       </c>
     </row>
     <row r="32">
@@ -2383,61 +2383,61 @@
         <v>0.06</v>
       </c>
       <c r="B32" t="n">
-        <v>0.1604367152051878</v>
+        <v>0.1671881557764255</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.3266518821503147</v>
+        <v>-0.3409443204525214</v>
       </c>
       <c r="D32" t="n">
-        <v>-2.488288889289164</v>
+        <v>-2.45970401268475</v>
       </c>
       <c r="E32" t="n">
-        <v>0.6542041176679407</v>
+        <v>0.8321604015362443</v>
       </c>
       <c r="F32" t="n">
-        <v>-1.381425722791013</v>
+        <v>-1.767432159449864</v>
       </c>
       <c r="G32" t="n">
-        <v>2.762851445582323</v>
+        <v>3.534864318899769</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.5300550005825861</v>
+        <v>-0.8759136132163781</v>
       </c>
       <c r="I32" t="n">
-        <v>17.95841447528031</v>
+        <v>17.95008987353706</v>
       </c>
       <c r="J32" t="n">
-        <v>-1.2041907533046</v>
+        <v>-1.738420507027912</v>
       </c>
       <c r="K32" t="n">
-        <v>17.99737068066302</v>
+        <v>17.99993146043355</v>
       </c>
       <c r="L32" t="n">
-        <v>24.70699135645055</v>
+        <v>25.20088199809446</v>
       </c>
       <c r="M32" t="n">
-        <v>83.324379242398</v>
+        <v>84.09328947159577</v>
       </c>
       <c r="N32" t="n">
-        <v>83.324379242398</v>
+        <v>84.09328947159577</v>
       </c>
       <c r="O32" t="n">
-        <v>0.7325330224477017</v>
+        <v>1.553356001346685</v>
       </c>
       <c r="P32" t="n">
-        <v>49.61641522130546</v>
+        <v>63.45098587126019</v>
       </c>
       <c r="Q32" t="n">
-        <v>50.34894824375316</v>
+        <v>65.00434187260689</v>
       </c>
       <c r="R32" t="n">
-        <v>0.7325330224477017</v>
+        <v>1.553356001346685</v>
       </c>
       <c r="S32" t="n">
-        <v>49.61641522130546</v>
+        <v>63.45098587126019</v>
       </c>
       <c r="T32" t="n">
-        <v>50.34894824375316</v>
+        <v>65.00434187260689</v>
       </c>
     </row>
     <row r="33">
@@ -2445,61 +2445,61 @@
         <v>0.062</v>
       </c>
       <c r="B33" t="n">
-        <v>0.1617918432411418</v>
+        <v>0.1688858095673897</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.3295153019621189</v>
+        <v>-0.3445490670470338</v>
       </c>
       <c r="D33" t="n">
-        <v>-2.482562049665555</v>
+        <v>-2.452494519495726</v>
       </c>
       <c r="E33" t="n">
-        <v>0.6894370622525022</v>
+        <v>0.8679219733167681</v>
       </c>
       <c r="F33" t="n">
-        <v>-1.457267649050029</v>
+        <v>-1.845749504542511</v>
       </c>
       <c r="G33" t="n">
-        <v>2.914535298100112</v>
+        <v>3.691499009084751</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.5461313402671381</v>
+        <v>-1.038884978029804</v>
       </c>
       <c r="I33" t="n">
-        <v>17.9579831892049</v>
+        <v>17.94781330531634</v>
       </c>
       <c r="J33" t="n">
-        <v>-1.257277953003552</v>
+        <v>-1.939610736246549</v>
       </c>
       <c r="K33" t="n">
-        <v>17.99907813690811</v>
+        <v>17.99986344134443</v>
       </c>
       <c r="L33" t="n">
-        <v>24.94772698679971</v>
+        <v>25.17819735286879</v>
       </c>
       <c r="M33" t="n">
-        <v>83.4807038056998</v>
+        <v>84.28381237705085</v>
       </c>
       <c r="N33" t="n">
-        <v>83.4807038056998</v>
+        <v>84.28381237705085</v>
       </c>
       <c r="O33" t="n">
-        <v>0.7965584550604252</v>
+        <v>1.921384868385144</v>
       </c>
       <c r="P33" t="n">
-        <v>52.3391383872005</v>
+        <v>66.2542270941625</v>
       </c>
       <c r="Q33" t="n">
-        <v>53.13569684226092</v>
+        <v>68.17561196254765</v>
       </c>
       <c r="R33" t="n">
-        <v>0.7965584550604252</v>
+        <v>1.921384868385144</v>
       </c>
       <c r="S33" t="n">
-        <v>52.3391383872005</v>
+        <v>66.2542270941625</v>
       </c>
       <c r="T33" t="n">
-        <v>53.13569684226092</v>
+        <v>68.17561196254765</v>
       </c>
     </row>
     <row r="34">
@@ -2507,61 +2507,61 @@
         <v>0.064</v>
       </c>
       <c r="B34" t="n">
-        <v>0.1632065038610029</v>
+        <v>0.1706701628437135</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.3325072110236712</v>
+        <v>-0.3483441397190177</v>
       </c>
       <c r="D34" t="n">
-        <v>-2.47657823154245</v>
+        <v>-2.444904374151758</v>
       </c>
       <c r="E34" t="n">
-        <v>0.724773187642365</v>
+        <v>0.9038532897937969</v>
       </c>
       <c r="F34" t="n">
-        <v>-1.533536977930622</v>
+        <v>-1.924858919391639</v>
       </c>
       <c r="G34" t="n">
-        <v>3.067073955861193</v>
+        <v>3.849717838783245</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.6384089591233365</v>
+        <v>-1.096993673692128</v>
       </c>
       <c r="I34" t="n">
-        <v>17.95667493906252</v>
+        <v>17.94562087277671</v>
       </c>
       <c r="J34" t="n">
-        <v>-1.38677500435348</v>
+        <v>-2.036324826355248</v>
       </c>
       <c r="K34" t="n">
-        <v>17.99992068184016</v>
+        <v>17.99990189430356</v>
       </c>
       <c r="L34" t="n">
-        <v>25.05647777811547</v>
+        <v>25.28300395302254</v>
       </c>
       <c r="M34" t="n">
-        <v>83.65712749506473</v>
+        <v>84.48769052060037</v>
       </c>
       <c r="N34" t="n">
-        <v>83.65712749506473</v>
+        <v>84.48769052060037</v>
       </c>
       <c r="O34" t="n">
-        <v>0.9864589753113882</v>
+        <v>2.112880261515585</v>
       </c>
       <c r="P34" t="n">
-        <v>55.07425684163188</v>
+        <v>69.08536718001297</v>
       </c>
       <c r="Q34" t="n">
-        <v>56.06071581694327</v>
+        <v>71.19824744152855</v>
       </c>
       <c r="R34" t="n">
-        <v>0.9864589753113882</v>
+        <v>2.112880261515585</v>
       </c>
       <c r="S34" t="n">
-        <v>55.07425684163188</v>
+        <v>69.08536718001297</v>
       </c>
       <c r="T34" t="n">
-        <v>56.06071581694327</v>
+        <v>71.19824744152855</v>
       </c>
     </row>
     <row r="35">
@@ -2569,61 +2569,61 @@
         <v>0.066</v>
       </c>
       <c r="B35" t="n">
-        <v>0.1646787627805698</v>
+        <v>0.1725038621031199</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.3356234345669789</v>
+        <v>-0.3522479017174796</v>
       </c>
       <c r="D35" t="n">
-        <v>-2.470345784455836</v>
+        <v>-2.437096850154834</v>
       </c>
       <c r="E35" t="n">
-        <v>0.7602091413708882</v>
+        <v>0.9398848868501759</v>
       </c>
       <c r="F35" t="n">
-        <v>-1.610219822615114</v>
+        <v>-2.004437882826385</v>
       </c>
       <c r="G35" t="n">
-        <v>3.22043964523021</v>
+        <v>4.008875765653003</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.8044119872872363</v>
+        <v>-1.155320426882534</v>
       </c>
       <c r="I35" t="n">
-        <v>17.95451821845495</v>
+        <v>17.94341927264086</v>
       </c>
       <c r="J35" t="n">
-        <v>-1.590199260723412</v>
+        <v>-2.13348611370181</v>
       </c>
       <c r="K35" t="n">
-        <v>17.99992641745269</v>
+        <v>17.99994442093657</v>
       </c>
       <c r="L35" t="n">
-        <v>25.03753207422897</v>
+        <v>25.39281677056784</v>
       </c>
       <c r="M35" t="n">
-        <v>83.85299726606817</v>
+        <v>84.69986788751319</v>
       </c>
       <c r="N35" t="n">
-        <v>83.85299726606817</v>
+        <v>84.69986788751319</v>
       </c>
       <c r="O35" t="n">
-        <v>1.29814475243275</v>
+        <v>2.319760984934784</v>
       </c>
       <c r="P35" t="n">
-        <v>57.82136784698581</v>
+        <v>71.93283159792009</v>
       </c>
       <c r="Q35" t="n">
-        <v>59.11951259941856</v>
+        <v>74.25259258285486</v>
       </c>
       <c r="R35" t="n">
-        <v>1.29814475243275</v>
+        <v>2.319760984934784</v>
       </c>
       <c r="S35" t="n">
-        <v>57.82136784698581</v>
+        <v>71.93283159792009</v>
       </c>
       <c r="T35" t="n">
-        <v>59.11951259941856</v>
+        <v>74.25259258285486</v>
       </c>
     </row>
     <row r="36">
@@ -2631,61 +2631,61 @@
         <v>0.068</v>
       </c>
       <c r="B36" t="n">
-        <v>0.1662512364863071</v>
+        <v>0.1744265268822422</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.3389571614208728</v>
+        <v>-0.3563483152342957</v>
       </c>
       <c r="D36" t="n">
-        <v>-2.463678330748048</v>
+        <v>-2.428896023121202</v>
       </c>
       <c r="E36" t="n">
-        <v>0.7958103676021192</v>
+        <v>0.9761043138702293</v>
       </c>
       <c r="F36" t="n">
-        <v>-1.687646504484327</v>
+        <v>-2.084899315566663</v>
       </c>
       <c r="G36" t="n">
-        <v>3.375293008968464</v>
+        <v>4.169798631133316</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.8343064736808632</v>
+        <v>-1.328910321594601</v>
       </c>
       <c r="I36" t="n">
-        <v>17.95234375174523</v>
+        <v>17.94109173469925</v>
       </c>
       <c r="J36" t="n">
-        <v>-1.657877967869215</v>
+        <v>-2.346341187591133</v>
       </c>
       <c r="K36" t="n">
-        <v>17.99993538317168</v>
+        <v>17.99988589539823</v>
       </c>
       <c r="L36" t="n">
-        <v>25.13664322389383</v>
+        <v>25.38210567282481</v>
       </c>
       <c r="M36" t="n">
-        <v>84.00023719326546</v>
+        <v>84.92834626115911</v>
       </c>
       <c r="N36" t="n">
-        <v>84.00023719326546</v>
+        <v>84.92834626115911</v>
       </c>
       <c r="O36" t="n">
-        <v>1.408335118035227</v>
+        <v>2.776559908475885</v>
       </c>
       <c r="P36" t="n">
-        <v>60.59418854366722</v>
+        <v>74.81058111824036</v>
       </c>
       <c r="Q36" t="n">
-        <v>62.00252366170245</v>
+        <v>77.58714102671625</v>
       </c>
       <c r="R36" t="n">
-        <v>1.408335118035227</v>
+        <v>2.776559908475885</v>
       </c>
       <c r="S36" t="n">
-        <v>60.59418854366722</v>
+        <v>74.81058111824036</v>
       </c>
       <c r="T36" t="n">
-        <v>62.00252366170245</v>
+        <v>77.58714102671625</v>
       </c>
     </row>
     <row r="37">
@@ -2693,61 +2693,61 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B37" t="n">
-        <v>0.1678641885426003</v>
+        <v>0.1764231239881939</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.3423790493108133</v>
+        <v>-0.3606133840730509</v>
       </c>
       <c r="D37" t="n">
-        <v>-2.456834554968167</v>
+        <v>-2.420365885443692</v>
       </c>
       <c r="E37" t="n">
-        <v>0.8314819430664161</v>
+        <v>1.012491831556619</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.765391706497334</v>
+        <v>-2.166138115029735</v>
       </c>
       <c r="G37" t="n">
-        <v>3.53078341299446</v>
+        <v>4.332276230059374</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.8732969043186132</v>
+        <v>-1.413448703991473</v>
       </c>
       <c r="I37" t="n">
-        <v>17.950157737078</v>
+        <v>17.93881948029174</v>
       </c>
       <c r="J37" t="n">
-        <v>-1.734808057089313</v>
+        <v>-2.470524104125984</v>
       </c>
       <c r="K37" t="n">
-        <v>17.99994178320123</v>
+        <v>17.99990457513558</v>
       </c>
       <c r="L37" t="n">
-        <v>25.23185856204685</v>
+        <v>25.4780489622613</v>
       </c>
       <c r="M37" t="n">
-        <v>84.15711880030666</v>
+        <v>85.16858652585957</v>
       </c>
       <c r="N37" t="n">
-        <v>84.15711880030666</v>
+        <v>85.16858652585957</v>
       </c>
       <c r="O37" t="n">
-        <v>1.545635299446565</v>
+        <v>3.063500368227731</v>
       </c>
       <c r="P37" t="n">
-        <v>63.37802044648489</v>
+        <v>77.71570423326322</v>
       </c>
       <c r="Q37" t="n">
-        <v>64.92365574593146</v>
+        <v>80.77920460149096</v>
       </c>
       <c r="R37" t="n">
-        <v>1.545635299446565</v>
+        <v>3.063500368227731</v>
       </c>
       <c r="S37" t="n">
-        <v>63.37802044648489</v>
+        <v>77.71570423326322</v>
       </c>
       <c r="T37" t="n">
-        <v>64.92365574593146</v>
+        <v>80.77920460149096</v>
       </c>
     </row>
     <row r="38">
@@ -2755,61 +2755,61 @@
         <v>0.07200000000000001</v>
       </c>
       <c r="B38" t="n">
-        <v>0.1695727027279887</v>
+        <v>0.1784696521829398</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.3460096275091304</v>
+        <v>-0.3649898414480554</v>
       </c>
       <c r="D38" t="n">
-        <v>-2.449573398571532</v>
+        <v>-2.411612970693683</v>
       </c>
       <c r="E38" t="n">
-        <v>0.8673261092571445</v>
+        <v>1.048994725787652</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.84392161579142</v>
+        <v>-2.247915129393308</v>
       </c>
       <c r="G38" t="n">
-        <v>3.687843231583407</v>
+        <v>4.495830258786538</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.049828642001179</v>
+        <v>-1.463438061581086</v>
       </c>
       <c r="I38" t="n">
-        <v>17.94793652531688</v>
+        <v>17.93656365457574</v>
       </c>
       <c r="J38" t="n">
-        <v>-1.949662390507392</v>
+        <v>-2.56042064472502</v>
       </c>
       <c r="K38" t="n">
-        <v>17.99993511488221</v>
+        <v>17.99995486122463</v>
       </c>
       <c r="L38" t="n">
-        <v>25.22443758873218</v>
+        <v>25.61780457460451</v>
       </c>
       <c r="M38" t="n">
-        <v>84.38981089674192</v>
+        <v>85.41707120531676</v>
       </c>
       <c r="N38" t="n">
-        <v>84.38981089674192</v>
+        <v>85.41707120531676</v>
       </c>
       <c r="O38" t="n">
-        <v>1.943479838195915</v>
+        <v>3.29170923579522</v>
       </c>
       <c r="P38" t="n">
-        <v>66.18898301597969</v>
+        <v>80.63969350504391</v>
       </c>
       <c r="Q38" t="n">
-        <v>68.1324628541756</v>
+        <v>83.93140274083913</v>
       </c>
       <c r="R38" t="n">
-        <v>1.943479838195915</v>
+        <v>3.29170923579522</v>
       </c>
       <c r="S38" t="n">
-        <v>66.18898301597969</v>
+        <v>80.63969350504391</v>
       </c>
       <c r="T38" t="n">
-        <v>68.1324628541756</v>
+        <v>83.93140274083913</v>
       </c>
     </row>
     <row r="39">
@@ -2817,61 +2817,61 @@
         <v>0.074</v>
       </c>
       <c r="B39" t="n">
-        <v>0.1713450994863427</v>
+        <v>0.1806204723788814</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.3497806659038762</v>
+        <v>-0.3696004745119985</v>
       </c>
       <c r="D39" t="n">
-        <v>-2.442031321782041</v>
+        <v>-2.402391704565797</v>
       </c>
       <c r="E39" t="n">
-        <v>0.9032966348467867</v>
+        <v>1.085753681004612</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.923031103716295</v>
+        <v>-2.330923691420451</v>
       </c>
       <c r="G39" t="n">
-        <v>3.846062207432854</v>
+        <v>4.661847382841053</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.139870044055133</v>
+        <v>-1.649264392609751</v>
       </c>
       <c r="I39" t="n">
-        <v>17.9457077703966</v>
+        <v>17.93417222195158</v>
       </c>
       <c r="J39" t="n">
-        <v>-2.078309222668685</v>
+        <v>-2.786755154022931</v>
       </c>
       <c r="K39" t="n">
-        <v>17.9999372475214</v>
+        <v>17.99990427004964</v>
       </c>
       <c r="L39" t="n">
-        <v>25.29027848598</v>
+        <v>25.61973752395835</v>
       </c>
       <c r="M39" t="n">
-        <v>84.59076775903212</v>
+        <v>85.68522146811142</v>
       </c>
       <c r="N39" t="n">
-        <v>84.59076775903212</v>
+        <v>85.68522146811142</v>
       </c>
       <c r="O39" t="n">
-        <v>2.192729596962083</v>
+        <v>3.85224232688691</v>
       </c>
       <c r="P39" t="n">
-        <v>69.02009452920301</v>
+        <v>83.6061696569751</v>
       </c>
       <c r="Q39" t="n">
-        <v>71.21282412616509</v>
+        <v>87.45841198386201</v>
       </c>
       <c r="R39" t="n">
-        <v>2.192729596962083</v>
+        <v>3.85224232688691</v>
       </c>
       <c r="S39" t="n">
-        <v>69.02009452920301</v>
+        <v>83.6061696569751</v>
       </c>
       <c r="T39" t="n">
-        <v>71.21282412616509</v>
+        <v>87.45841198386201</v>
       </c>
     </row>
     <row r="40">
@@ -2879,61 +2879,61 @@
         <v>0.076</v>
       </c>
       <c r="B40" t="n">
-        <v>0.1731728250549343</v>
+        <v>0.1828322163568664</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.3536733571249462</v>
+        <v>-0.3743491226246394</v>
       </c>
       <c r="D40" t="n">
-        <v>-2.434245939339901</v>
+        <v>-2.392894408340514</v>
       </c>
       <c r="E40" t="n">
-        <v>0.9393766005369087</v>
+        <v>1.122673166493576</v>
       </c>
       <c r="F40" t="n">
-        <v>-2.002642565725683</v>
+        <v>-2.414700662573769</v>
       </c>
       <c r="G40" t="n">
-        <v>4.005285131450394</v>
+        <v>4.829401325147654</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.15500201235856</v>
+        <v>-1.761899588540458</v>
       </c>
       <c r="I40" t="n">
-        <v>17.94347248233273</v>
+        <v>17.931813352636</v>
       </c>
       <c r="J40" t="n">
-        <v>-2.132291584432693</v>
+        <v>-2.940273511876457</v>
       </c>
       <c r="K40" t="n">
-        <v>17.99994700268618</v>
+        <v>17.99990791132058</v>
       </c>
       <c r="L40" t="n">
-        <v>25.41957161982109</v>
+        <v>25.7078698970128</v>
       </c>
       <c r="M40" t="n">
-        <v>84.76423867850029</v>
+        <v>85.96439681616933</v>
       </c>
       <c r="N40" t="n">
-        <v>84.76423867850029</v>
+        <v>85.96439681616933</v>
       </c>
       <c r="O40" t="n">
-        <v>2.313281152097487</v>
+        <v>4.25663301312805</v>
       </c>
       <c r="P40" t="n">
-        <v>71.86865707848034</v>
+        <v>86.59970847594168</v>
       </c>
       <c r="Q40" t="n">
-        <v>74.18193823057781</v>
+        <v>90.85634148906972</v>
       </c>
       <c r="R40" t="n">
-        <v>2.313281152097487</v>
+        <v>4.25663301312805</v>
       </c>
       <c r="S40" t="n">
-        <v>71.86865707848034</v>
+        <v>86.59970847594168</v>
       </c>
       <c r="T40" t="n">
-        <v>74.18193823057781</v>
+        <v>90.85634148906972</v>
       </c>
     </row>
     <row r="41">
@@ -2941,61 +2941,61 @@
         <v>0.078</v>
       </c>
       <c r="B41" t="n">
-        <v>0.1751059863280901</v>
+        <v>0.1850984623327255</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.3577996100939366</v>
+        <v>-0.3792212380539573</v>
       </c>
       <c r="D41" t="n">
-        <v>-2.42599343340192</v>
+        <v>-2.383150177481879</v>
       </c>
       <c r="E41" t="n">
-        <v>0.9756829208085245</v>
+        <v>1.159736261263677</v>
       </c>
       <c r="F41" t="n">
-        <v>-2.083305469654087</v>
+        <v>-2.49916504726506</v>
       </c>
       <c r="G41" t="n">
-        <v>4.166610939308234</v>
+        <v>4.998330094529964</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.322215504752047</v>
+        <v>-1.809058496629027</v>
       </c>
       <c r="I41" t="n">
-        <v>17.94119269021671</v>
+        <v>17.92948361423309</v>
       </c>
       <c r="J41" t="n">
-        <v>-2.338868573943242</v>
+        <v>-3.028651039694376</v>
       </c>
       <c r="K41" t="n">
-        <v>17.99994190446096</v>
+        <v>17.99996006856596</v>
       </c>
       <c r="L41" t="n">
-        <v>25.44012477487976</v>
+        <v>25.87311568374083</v>
       </c>
       <c r="M41" t="n">
-        <v>85.02586502391969</v>
+        <v>86.25343512994317</v>
       </c>
       <c r="N41" t="n">
-        <v>85.02586502391969</v>
+        <v>86.25343512994317</v>
       </c>
       <c r="O41" t="n">
-        <v>2.764989615579162</v>
+        <v>4.5213397741141</v>
       </c>
       <c r="P41" t="n">
-        <v>74.75371690456848</v>
+        <v>89.61745737136371</v>
       </c>
       <c r="Q41" t="n">
-        <v>77.51870652014765</v>
+        <v>94.13879714547781</v>
       </c>
       <c r="R41" t="n">
-        <v>2.764989615579162</v>
+        <v>4.5213397741141</v>
       </c>
       <c r="S41" t="n">
-        <v>74.75371690456848</v>
+        <v>89.61745737136371</v>
       </c>
       <c r="T41" t="n">
-        <v>77.51870652014765</v>
+        <v>94.13879714547781</v>
       </c>
     </row>
     <row r="42">
@@ -3003,61 +3003,61 @@
         <v>0.08</v>
       </c>
       <c r="B42" t="n">
-        <v>0.177080460133252</v>
+        <v>0.1874772323022216</v>
       </c>
       <c r="C42" t="n">
-        <v>-0.3620178645843435</v>
+        <v>-0.3843507200764378</v>
       </c>
       <c r="D42" t="n">
-        <v>-2.417556924421106</v>
+        <v>-2.372891213436918</v>
       </c>
       <c r="E42" t="n">
-        <v>1.012082919347145</v>
+        <v>1.197117443371895</v>
       </c>
       <c r="F42" t="n">
-        <v>-2.164406752247467</v>
+        <v>-2.585200578628985</v>
       </c>
       <c r="G42" t="n">
-        <v>4.328813504495732</v>
+        <v>5.170401157258066</v>
       </c>
       <c r="H42" t="n">
-        <v>-1.474457458607505</v>
+        <v>-2.003424684747953</v>
       </c>
       <c r="I42" t="n">
-        <v>17.93890226541279</v>
+        <v>17.92701634011581</v>
       </c>
       <c r="J42" t="n">
-        <v>-2.530687953704268</v>
+        <v>-3.265002567118898</v>
       </c>
       <c r="K42" t="n">
-        <v>17.99993853582618</v>
+        <v>17.99991899643314</v>
       </c>
       <c r="L42" t="n">
-        <v>25.47542053194223</v>
+        <v>25.89441869914923</v>
       </c>
       <c r="M42" t="n">
-        <v>85.28608640311217</v>
+        <v>86.56643862342692</v>
       </c>
       <c r="N42" t="n">
-        <v>85.28608640311217</v>
+        <v>86.56643862342692</v>
       </c>
       <c r="O42" t="n">
-        <v>3.191983620625801</v>
+        <v>5.189127547133326</v>
       </c>
       <c r="P42" t="n">
-        <v>77.65404213907631</v>
+        <v>92.68962132301807</v>
       </c>
       <c r="Q42" t="n">
-        <v>80.84602575970212</v>
+        <v>97.87874887015138</v>
       </c>
       <c r="R42" t="n">
-        <v>3.191983620625801</v>
+        <v>5.189127547133326</v>
       </c>
       <c r="S42" t="n">
-        <v>77.65404213907631</v>
+        <v>92.68962132301807</v>
       </c>
       <c r="T42" t="n">
-        <v>80.84602575970212</v>
+        <v>97.87874887015138</v>
       </c>
     </row>
     <row r="43">
@@ -3065,61 +3065,61 @@
         <v>0.082</v>
       </c>
       <c r="B43" t="n">
-        <v>0.1791491391234832</v>
+        <v>0.18990751077316</v>
       </c>
       <c r="C43" t="n">
-        <v>-0.3664465156535064</v>
+        <v>-0.3895991488271101</v>
       </c>
       <c r="D43" t="n">
-        <v>-2.40869962228278</v>
+        <v>-2.362394355935573</v>
       </c>
       <c r="E43" t="n">
-        <v>1.048702743496206</v>
+        <v>1.234653542787162</v>
       </c>
       <c r="F43" t="n">
-        <v>-2.246540547181997</v>
+        <v>-2.671999177931301</v>
       </c>
       <c r="G43" t="n">
-        <v>4.49308109436339</v>
+        <v>5.343998355862698</v>
       </c>
       <c r="H43" t="n">
-        <v>-1.499695309313993</v>
+        <v>-2.145954642560747</v>
       </c>
       <c r="I43" t="n">
-        <v>17.93659607056423</v>
+        <v>17.92456083364075</v>
       </c>
       <c r="J43" t="n">
-        <v>-2.596007096338808</v>
+        <v>-3.449890241391222</v>
       </c>
       <c r="K43" t="n">
-        <v>17.99994851399475</v>
+        <v>17.99991121045841</v>
       </c>
       <c r="L43" t="n">
-        <v>25.61576199869195</v>
+        <v>25.97665662441869</v>
       </c>
       <c r="M43" t="n">
-        <v>85.49833323030856</v>
+        <v>86.88976581147469</v>
       </c>
       <c r="N43" t="n">
-        <v>85.49833323030856</v>
+        <v>86.88976581147469</v>
       </c>
       <c r="O43" t="n">
-        <v>3.370231067144434</v>
+        <v>5.736413388642438</v>
       </c>
       <c r="P43" t="n">
-        <v>80.59037880193894</v>
+        <v>95.78862355643483</v>
       </c>
       <c r="Q43" t="n">
-        <v>83.96060986908338</v>
+        <v>101.5250369450773</v>
       </c>
       <c r="R43" t="n">
-        <v>3.370231067144434</v>
+        <v>5.736413388642438</v>
       </c>
       <c r="S43" t="n">
-        <v>80.59037880193894</v>
+        <v>95.78862355643483</v>
       </c>
       <c r="T43" t="n">
-        <v>83.96060986908338</v>
+        <v>101.5250369450773</v>
       </c>
     </row>
     <row r="44">
@@ -3127,61 +3127,61 @@
         <v>0.08400000000000001</v>
       </c>
       <c r="B44" t="n">
-        <v>0.181286508391177</v>
+        <v>0.1924076887508429</v>
       </c>
       <c r="C44" t="n">
-        <v>-0.3710299539402925</v>
+        <v>-0.3950091203494533</v>
       </c>
       <c r="D44" t="n">
-        <v>-2.399532745709208</v>
+        <v>-2.351574412890887</v>
       </c>
       <c r="E44" t="n">
-        <v>1.085495415316881</v>
+        <v>1.272400908353551</v>
       </c>
       <c r="F44" t="n">
-        <v>-2.329498415636278</v>
+        <v>-2.759838177582542</v>
       </c>
       <c r="G44" t="n">
-        <v>4.658996831272174</v>
+        <v>5.519676355164784</v>
       </c>
       <c r="H44" t="n">
-        <v>-1.624226631208478</v>
+        <v>-2.204875889538667</v>
       </c>
       <c r="I44" t="n">
-        <v>17.93425673987975</v>
+        <v>17.92212961031177</v>
       </c>
       <c r="J44" t="n">
-        <v>-2.761021858038982</v>
+        <v>-3.551676920198947</v>
       </c>
       <c r="K44" t="n">
-        <v>17.99994859520069</v>
+        <v>17.99995704691959</v>
       </c>
       <c r="L44" t="n">
-        <v>25.68824661122432</v>
+        <v>26.15569665722477</v>
       </c>
       <c r="M44" t="n">
-        <v>85.77141017487824</v>
+        <v>87.22703081867503</v>
       </c>
       <c r="N44" t="n">
-        <v>85.77141017487824</v>
+        <v>87.22703081867503</v>
       </c>
       <c r="O44" t="n">
-        <v>3.794014446447593</v>
+        <v>6.086236641520587</v>
       </c>
       <c r="P44" t="n">
-        <v>83.55540157406246</v>
+        <v>98.9242612976597</v>
       </c>
       <c r="Q44" t="n">
-        <v>87.34941602051005</v>
+        <v>105.0104979391803</v>
       </c>
       <c r="R44" t="n">
-        <v>3.794014446447593</v>
+        <v>6.086236641520587</v>
       </c>
       <c r="S44" t="n">
-        <v>83.55540157406246</v>
+        <v>98.9242612976597</v>
       </c>
       <c r="T44" t="n">
-        <v>87.34941602051005</v>
+        <v>105.0104979391803</v>
       </c>
     </row>
     <row r="45">
@@ -3189,61 +3189,61 @@
         <v>0.08600000000000001</v>
       </c>
       <c r="B45" t="n">
-        <v>0.1834770875926986</v>
+        <v>0.1950080022803408</v>
       </c>
       <c r="C45" t="n">
-        <v>-0.3757332959152188</v>
+        <v>-0.4006531188185006</v>
       </c>
       <c r="D45" t="n">
-        <v>-2.390126061759356</v>
+        <v>-2.340286415952792</v>
       </c>
       <c r="E45" t="n">
-        <v>1.122421981096186</v>
+        <v>1.310472181385222</v>
       </c>
       <c r="F45" t="n">
-        <v>-2.413094640770352</v>
+        <v>-2.849329388429416</v>
       </c>
       <c r="G45" t="n">
-        <v>4.826189281541804</v>
+        <v>5.698658776858915</v>
       </c>
       <c r="H45" t="n">
-        <v>-1.825674210055424</v>
+        <v>-2.395556816269898</v>
       </c>
       <c r="I45" t="n">
-        <v>17.93189174099737</v>
+        <v>17.91958005035762</v>
       </c>
       <c r="J45" t="n">
-        <v>-3.003264394751355</v>
+        <v>-3.786029557823453</v>
       </c>
       <c r="K45" t="n">
-        <v>17.99994100986711</v>
+        <v>17.99993113911133</v>
       </c>
       <c r="L45" t="n">
-        <v>25.70816688923881</v>
+        <v>26.21112825238867</v>
       </c>
       <c r="M45" t="n">
-        <v>86.0916082935025</v>
+        <v>87.58820611609625</v>
       </c>
       <c r="N45" t="n">
-        <v>86.0916082935025</v>
+        <v>87.58820611609625</v>
       </c>
       <c r="O45" t="n">
-        <v>4.407998698689914</v>
+        <v>6.837423648813147</v>
       </c>
       <c r="P45" t="n">
-        <v>86.54264562744925</v>
+        <v>102.1172925170808</v>
       </c>
       <c r="Q45" t="n">
-        <v>90.95064432613917</v>
+        <v>108.9547161658939</v>
       </c>
       <c r="R45" t="n">
-        <v>4.407998698689914</v>
+        <v>6.837423648813147</v>
       </c>
       <c r="S45" t="n">
-        <v>86.54264562744925</v>
+        <v>102.1172925170808</v>
       </c>
       <c r="T45" t="n">
-        <v>90.95064432613917</v>
+        <v>108.9547161658939</v>
       </c>
     </row>
     <row r="46">
@@ -3251,61 +3251,61 @@
         <v>0.08799999999999999</v>
       </c>
       <c r="B46" t="n">
-        <v>0.1857790756189425</v>
+        <v>0.197660728261047</v>
       </c>
       <c r="C46" t="n">
-        <v>-0.3806901403764877</v>
+        <v>-0.4064205724453691</v>
       </c>
       <c r="D46" t="n">
-        <v>-2.380212372836818</v>
+        <v>-2.328751508699055</v>
       </c>
       <c r="E46" t="n">
-        <v>1.159651558105925</v>
+        <v>1.348720244671483</v>
       </c>
       <c r="F46" t="n">
-        <v>-2.498154872160081</v>
+        <v>-2.939721675524104</v>
       </c>
       <c r="G46" t="n">
-        <v>4.996309744320117</v>
+        <v>5.879443351048499</v>
       </c>
       <c r="H46" t="n">
-        <v>-1.877721380468068</v>
+        <v>-2.570304522302199</v>
       </c>
       <c r="I46" t="n">
-        <v>17.92950157215829</v>
+        <v>17.91701435841808</v>
       </c>
       <c r="J46" t="n">
-        <v>-3.096820958082188</v>
+        <v>-4.004888699957962</v>
       </c>
       <c r="K46" t="n">
-        <v>17.99994953955321</v>
+        <v>17.99991450966786</v>
       </c>
       <c r="L46" t="n">
-        <v>25.84860995133353</v>
+        <v>26.28953912931131</v>
       </c>
       <c r="M46" t="n">
-        <v>86.35359161640231</v>
+        <v>87.96142246618592</v>
       </c>
       <c r="N46" t="n">
-        <v>86.35359161640231</v>
+        <v>87.96142246618592</v>
       </c>
       <c r="O46" t="n">
-        <v>4.692959394503596</v>
+        <v>7.558380374615175</v>
       </c>
       <c r="P46" t="n">
-        <v>89.5810657871003</v>
+        <v>105.3419015609342</v>
       </c>
       <c r="Q46" t="n">
-        <v>94.27402518160389</v>
+        <v>112.9002819355494</v>
       </c>
       <c r="R46" t="n">
-        <v>4.692959394503596</v>
+        <v>7.558380374615175</v>
       </c>
       <c r="S46" t="n">
-        <v>89.5810657871003</v>
+        <v>105.3419015609342</v>
       </c>
       <c r="T46" t="n">
-        <v>94.27402518160389</v>
+        <v>112.9002819355494</v>
       </c>
     </row>
     <row r="47">
@@ -3313,61 +3313,61 @@
         <v>0.09</v>
       </c>
       <c r="B47" t="n">
-        <v>0.1881234704523109</v>
+        <v>0.2003995106463281</v>
       </c>
       <c r="C47" t="n">
-        <v>-0.3857442245868294</v>
+        <v>-0.412391592334505</v>
       </c>
       <c r="D47" t="n">
-        <v>-2.370104204416134</v>
+        <v>-2.316809468920783</v>
       </c>
       <c r="E47" t="n">
-        <v>1.197002645564076</v>
+        <v>1.387265097283684</v>
       </c>
       <c r="F47" t="n">
-        <v>-2.583809638506757</v>
+        <v>-3.031626047524063</v>
       </c>
       <c r="G47" t="n">
-        <v>5.167619277012728</v>
+        <v>6.063252095047812</v>
       </c>
       <c r="H47" t="n">
-        <v>-1.958991092482435</v>
+        <v>-2.642611112255426</v>
       </c>
       <c r="I47" t="n">
-        <v>17.92709178821987</v>
+        <v>17.91446333656473</v>
       </c>
       <c r="J47" t="n">
-        <v>-3.219890196073733</v>
+        <v>-4.122044623447168</v>
       </c>
       <c r="K47" t="n">
-        <v>17.99995522002575</v>
+        <v>17.99995519110491</v>
       </c>
       <c r="L47" t="n">
-        <v>25.97255075497577</v>
+        <v>26.48445752877259</v>
       </c>
       <c r="M47" t="n">
-        <v>86.63866355715638</v>
+        <v>88.35398327120674</v>
       </c>
       <c r="N47" t="n">
-        <v>86.63866355715638</v>
+        <v>88.35398327120674</v>
       </c>
       <c r="O47" t="n">
-        <v>5.068254319469885</v>
+        <v>8.013785433400077</v>
       </c>
       <c r="P47" t="n">
-        <v>92.64023513945372</v>
+        <v>108.6197396504795</v>
       </c>
       <c r="Q47" t="n">
-        <v>97.70848945892359</v>
+        <v>116.6335250838796</v>
       </c>
       <c r="R47" t="n">
-        <v>5.068254319469885</v>
+        <v>8.013785433400077</v>
       </c>
       <c r="S47" t="n">
-        <v>92.64023513945372</v>
+        <v>108.6197396504795</v>
       </c>
       <c r="T47" t="n">
-        <v>97.70848945892359</v>
+        <v>116.6335250838796</v>
       </c>
     </row>
     <row r="48">
@@ -3375,61 +3375,61 @@
         <v>0.092</v>
       </c>
       <c r="B48" t="n">
-        <v>0.1905611305190694</v>
+        <v>0.2032257586446186</v>
       </c>
       <c r="C48" t="n">
-        <v>-0.3910127826455627</v>
+        <v>-0.4185722202520644</v>
       </c>
       <c r="D48" t="n">
-        <v>-2.359567088298668</v>
+        <v>-2.304448213085664</v>
       </c>
       <c r="E48" t="n">
-        <v>1.234626054047546</v>
+        <v>1.42613211292312</v>
       </c>
       <c r="F48" t="n">
-        <v>-2.670802664135263</v>
+        <v>-3.12523223600335</v>
       </c>
       <c r="G48" t="n">
-        <v>5.341605328271057</v>
+        <v>6.250464472006618</v>
       </c>
       <c r="H48" t="n">
-        <v>-2.175435912524906</v>
+        <v>-2.830838433478394</v>
       </c>
       <c r="I48" t="n">
-        <v>17.9246306002937</v>
+        <v>17.91180977167138</v>
       </c>
       <c r="J48" t="n">
-        <v>-3.478787612622915</v>
+        <v>-4.355951764648029</v>
       </c>
       <c r="K48" t="n">
-        <v>17.99994723542232</v>
+        <v>17.99994132072667</v>
       </c>
       <c r="L48" t="n">
-        <v>26.00882211647424</v>
+        <v>26.57578615415111</v>
       </c>
       <c r="M48" t="n">
-        <v>87.01178114708516</v>
+        <v>88.77020572453362</v>
       </c>
       <c r="N48" t="n">
-        <v>87.01178114708516</v>
+        <v>88.77020572453362</v>
       </c>
       <c r="O48" t="n">
-        <v>5.819772769968922</v>
+        <v>8.860338627890213</v>
       </c>
       <c r="P48" t="n">
-        <v>95.74608370944952</v>
+        <v>111.9568229618943</v>
       </c>
       <c r="Q48" t="n">
-        <v>101.5658564794184</v>
+        <v>120.8171615897845</v>
       </c>
       <c r="R48" t="n">
-        <v>5.819772769968922</v>
+        <v>8.860338627890213</v>
       </c>
       <c r="S48" t="n">
-        <v>95.74608370944952</v>
+        <v>111.9568229618943</v>
       </c>
       <c r="T48" t="n">
-        <v>101.5658564794184</v>
+        <v>120.8171615897845</v>
       </c>
     </row>
     <row r="49">
@@ -3437,61 +3437,61 @@
         <v>0.094</v>
       </c>
       <c r="B49" t="n">
-        <v>0.1930728997830606</v>
+        <v>0.2061054468151419</v>
       </c>
       <c r="C49" t="n">
-        <v>-0.396453730482542</v>
+        <v>-0.4248815778812293</v>
       </c>
       <c r="D49" t="n">
-        <v>-2.348685192624709</v>
+        <v>-2.291829497827335</v>
       </c>
       <c r="E49" t="n">
-        <v>1.272482409858371</v>
+        <v>1.465200601783598</v>
       </c>
       <c r="F49" t="n">
-        <v>-2.758958240283518</v>
+        <v>-3.219903106647363</v>
       </c>
       <c r="G49" t="n">
-        <v>5.517916480567364</v>
+        <v>6.439806213295034</v>
       </c>
       <c r="H49" t="n">
-        <v>-2.293140395092862</v>
+        <v>-3.040683107536504</v>
       </c>
       <c r="I49" t="n">
-        <v>17.92214751012715</v>
+        <v>17.90911649286591</v>
       </c>
       <c r="J49" t="n">
-        <v>-3.639512016351219</v>
+        <v>-4.611995823580417</v>
       </c>
       <c r="K49" t="n">
-        <v>17.99995013250315</v>
+        <v>17.99991776047337</v>
       </c>
       <c r="L49" t="n">
-        <v>26.12262432627346</v>
+        <v>26.6529490747394</v>
       </c>
       <c r="M49" t="n">
-        <v>87.34512570828254</v>
+        <v>89.200573739893</v>
       </c>
       <c r="N49" t="n">
-        <v>87.34512570828254</v>
+        <v>89.200573739893</v>
       </c>
       <c r="O49" t="n">
-        <v>6.32944888834623</v>
+        <v>9.792607542910517</v>
       </c>
       <c r="P49" t="n">
-        <v>98.89263293942948</v>
+        <v>115.3311228799124</v>
       </c>
       <c r="Q49" t="n">
-        <v>105.2220818277757</v>
+        <v>125.1237304228229</v>
       </c>
       <c r="R49" t="n">
-        <v>6.32944888834623</v>
+        <v>9.792607542910517</v>
       </c>
       <c r="S49" t="n">
-        <v>98.89263293942948</v>
+        <v>115.3311228799124</v>
       </c>
       <c r="T49" t="n">
-        <v>105.2220818277757</v>
+        <v>125.1237304228229</v>
       </c>
     </row>
     <row r="50">
@@ -3499,61 +3499,61 @@
         <v>0.096</v>
       </c>
       <c r="B50" t="n">
-        <v>0.1956359316245929</v>
+        <v>0.2090882795213425</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.4020139232270987</v>
+        <v>-0.4314416007904185</v>
       </c>
       <c r="D50" t="n">
-        <v>-2.337564807135596</v>
+        <v>-2.278709452008956</v>
       </c>
       <c r="E50" t="n">
-        <v>1.310499899251498</v>
+        <v>1.504673386753452</v>
       </c>
       <c r="F50" t="n">
-        <v>-2.847917972169379</v>
+        <v>-3.316711794145934</v>
       </c>
       <c r="G50" t="n">
-        <v>5.695835944337837</v>
+        <v>6.633423588291715</v>
       </c>
       <c r="H50" t="n">
-        <v>-2.342544526351665</v>
+        <v>-3.128445400265368</v>
       </c>
       <c r="I50" t="n">
-        <v>17.91964926981274</v>
+        <v>17.90642291998974</v>
       </c>
       <c r="J50" t="n">
-        <v>-3.732328496770322</v>
+        <v>-4.747000755808584</v>
       </c>
       <c r="K50" t="n">
-        <v>17.9999605566279</v>
+        <v>17.99995419258466</v>
       </c>
       <c r="L50" t="n">
-        <v>26.29005592717744</v>
+        <v>26.86630252364281</v>
       </c>
       <c r="M50" t="n">
-        <v>87.65095859690045</v>
+        <v>89.65720759200101</v>
       </c>
       <c r="N50" t="n">
-        <v>87.65095859690045</v>
+        <v>89.65720759200101</v>
       </c>
       <c r="O50" t="n">
-        <v>6.671838600095626</v>
+        <v>10.38010865414069</v>
       </c>
       <c r="P50" t="n">
-        <v>102.0673355001204</v>
+        <v>118.7806452916484</v>
       </c>
       <c r="Q50" t="n">
-        <v>108.739174100216</v>
+        <v>129.1607539457891</v>
       </c>
       <c r="R50" t="n">
-        <v>6.671838600095626</v>
+        <v>10.38010865414069</v>
       </c>
       <c r="S50" t="n">
-        <v>102.0673355001204</v>
+        <v>118.7806452916484</v>
       </c>
       <c r="T50" t="n">
-        <v>108.739174100216</v>
+        <v>129.1607539457891</v>
       </c>
     </row>
     <row r="51">
@@ -3561,61 +3561,61 @@
         <v>0.098</v>
       </c>
       <c r="B51" t="n">
-        <v>0.1983172871436097</v>
+        <v>0.2121455230649009</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.4078528014164143</v>
+        <v>-0.4381851993833585</v>
       </c>
       <c r="D51" t="n">
-        <v>-2.325887050756965</v>
+        <v>-2.265222254823076</v>
       </c>
       <c r="E51" t="n">
-        <v>1.34891547599</v>
+        <v>1.544457340547202</v>
       </c>
       <c r="F51" t="n">
-        <v>-2.938902306094756</v>
+        <v>-3.415229433817077</v>
       </c>
       <c r="G51" t="n">
-        <v>5.877804612189685</v>
+        <v>6.83045886763408</v>
       </c>
       <c r="H51" t="n">
-        <v>-2.564038243223639</v>
+        <v>-3.315735610772023</v>
       </c>
       <c r="I51" t="n">
-        <v>17.91707640075553</v>
+        <v>17.90364052079338</v>
       </c>
       <c r="J51" t="n">
-        <v>-3.99822256859788</v>
+        <v>-4.982367574474756</v>
       </c>
       <c r="K51" t="n">
-        <v>17.9999534457874</v>
+        <v>17.99994999082702</v>
       </c>
       <c r="L51" t="n">
-        <v>26.35262205024016</v>
+        <v>26.99571951715933</v>
       </c>
       <c r="M51" t="n">
-        <v>88.07670347841074</v>
+        <v>90.13684957787912</v>
       </c>
       <c r="N51" t="n">
-        <v>88.07670347841074</v>
+        <v>90.13684957787912</v>
       </c>
       <c r="O51" t="n">
-        <v>7.549851223163643</v>
+        <v>11.33858953066803</v>
       </c>
       <c r="P51" t="n">
-        <v>105.312756762162</v>
+        <v>122.2897537246797</v>
       </c>
       <c r="Q51" t="n">
-        <v>112.8626079853256</v>
+        <v>133.6283432553477</v>
       </c>
       <c r="R51" t="n">
-        <v>7.549851223163643</v>
+        <v>11.33858953066803</v>
       </c>
       <c r="S51" t="n">
-        <v>105.312756762162</v>
+        <v>122.2897537246797</v>
       </c>
       <c r="T51" t="n">
-        <v>112.8626079853256</v>
+        <v>133.6283432553477</v>
       </c>
     </row>
     <row r="52">
@@ -3623,61 +3623,61 @@
         <v>0.1</v>
       </c>
       <c r="B52" t="n">
-        <v>0.2010424604509816</v>
+        <v>0.2152573741995857</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.413796013566191</v>
+        <v>-0.4450637057824844</v>
       </c>
       <c r="D52" t="n">
-        <v>-2.314000626457411</v>
+        <v>-2.251465242024824</v>
       </c>
       <c r="E52" t="n">
-        <v>1.387487224730425</v>
+        <v>1.584470879041191</v>
       </c>
       <c r="F52" t="n">
-        <v>-3.030692390126656</v>
+        <v>-3.515008307171086</v>
       </c>
       <c r="G52" t="n">
-        <v>6.061384780253988</v>
+        <v>7.03001661434251</v>
       </c>
       <c r="H52" t="n">
-        <v>-2.750945543189495</v>
+        <v>-3.564315716465118</v>
       </c>
       <c r="I52" t="n">
-        <v>17.91448481231057</v>
+        <v>17.90079767582139</v>
       </c>
       <c r="J52" t="n">
-        <v>-4.229923429571303</v>
+        <v>-5.279639770364608</v>
       </c>
       <c r="K52" t="n">
-        <v>17.99995033771215</v>
+        <v>17.99992091008362</v>
       </c>
       <c r="L52" t="n">
-        <v>26.44340111376487</v>
+        <v>27.07481733652727</v>
       </c>
       <c r="M52" t="n">
-        <v>88.49143430919106</v>
+        <v>90.63329417213127</v>
       </c>
       <c r="N52" t="n">
-        <v>88.49143430919106</v>
+        <v>90.63329417213127</v>
       </c>
       <c r="O52" t="n">
-        <v>8.339561160382944</v>
+        <v>12.52921438194473</v>
       </c>
       <c r="P52" t="n">
-        <v>108.5863981451976</v>
+        <v>125.842871789372</v>
       </c>
       <c r="Q52" t="n">
-        <v>116.9259593055806</v>
+        <v>138.3720861713167</v>
       </c>
       <c r="R52" t="n">
-        <v>8.339561160382944</v>
+        <v>12.52921438194473</v>
       </c>
       <c r="S52" t="n">
-        <v>108.5863981451976</v>
+        <v>125.842871789372</v>
       </c>
       <c r="T52" t="n">
-        <v>116.9259593055806</v>
+        <v>138.3720861713167</v>
       </c>
     </row>
     <row r="53">
@@ -3685,61 +3685,61 @@
         <v>0.102</v>
       </c>
       <c r="B53" t="n">
-        <v>0.2038604297275334</v>
+        <v>0.2184906009195993</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.4199607496024361</v>
+        <v>-0.4522465289237959</v>
       </c>
       <c r="D53" t="n">
-        <v>-2.301671154384921</v>
+        <v>-2.237099595742202</v>
       </c>
       <c r="E53" t="n">
-        <v>1.426394110642261</v>
+        <v>1.625023873950495</v>
       </c>
       <c r="F53" t="n">
-        <v>-3.124217025462469</v>
+        <v>-3.617758852295373</v>
       </c>
       <c r="G53" t="n">
-        <v>6.248434050924131</v>
+        <v>7.235517704590623</v>
       </c>
       <c r="H53" t="n">
-        <v>-2.815168282076192</v>
+        <v>-3.670190763039898</v>
       </c>
       <c r="I53" t="n">
-        <v>17.91185806462927</v>
+        <v>17.89793301927946</v>
       </c>
       <c r="J53" t="n">
-        <v>-4.339786190501877</v>
+        <v>-5.43565708296004</v>
       </c>
       <c r="K53" t="n">
-        <v>17.9999609847473</v>
+        <v>17.99995381891419</v>
       </c>
       <c r="L53" t="n">
-        <v>26.62764379271374</v>
+        <v>27.30981617216799</v>
       </c>
       <c r="M53" t="n">
-        <v>88.85497146771841</v>
+        <v>91.1651324806412</v>
       </c>
       <c r="N53" t="n">
-        <v>88.85497146771841</v>
+        <v>91.1651324806412</v>
       </c>
       <c r="O53" t="n">
-        <v>8.798119205742497</v>
+        <v>13.28377982956571</v>
       </c>
       <c r="P53" t="n">
-        <v>111.9208247800221</v>
+        <v>129.5004911686341</v>
       </c>
       <c r="Q53" t="n">
-        <v>120.7189439857646</v>
+        <v>142.7842709981998</v>
       </c>
       <c r="R53" t="n">
-        <v>8.798119205742497</v>
+        <v>13.28377982956571</v>
       </c>
       <c r="S53" t="n">
-        <v>111.9208247800221</v>
+        <v>129.5004911686341</v>
       </c>
       <c r="T53" t="n">
-        <v>120.7189439857646</v>
+        <v>142.7842709981998</v>
       </c>
     </row>
     <row r="54">
@@ -3747,61 +3747,61 @@
         <v>0.104</v>
       </c>
       <c r="B54" t="n">
-        <v>0.2067587128854623</v>
+        <v>0.2217846762228637</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.4263200241686995</v>
+        <v>-0.4595845807871305</v>
       </c>
       <c r="D54" t="n">
-        <v>-2.288952605252395</v>
+        <v>-2.222423492015532</v>
       </c>
       <c r="E54" t="n">
-        <v>1.465610887558237</v>
+        <v>1.66586529810283</v>
       </c>
       <c r="F54" t="n">
-        <v>-3.219379197077927</v>
+        <v>-3.722162492391913</v>
       </c>
       <c r="G54" t="n">
-        <v>6.438758394155546</v>
+        <v>7.4443249847837</v>
       </c>
       <c r="H54" t="n">
-        <v>-2.996748961543883</v>
+        <v>-3.858423685519957</v>
       </c>
       <c r="I54" t="n">
-        <v>17.90917316480046</v>
+        <v>17.89499253245718</v>
       </c>
       <c r="J54" t="n">
-        <v>-4.567806009717911</v>
+        <v>-5.674838981807212</v>
       </c>
       <c r="K54" t="n">
-        <v>17.99995965815805</v>
+        <v>17.99995751474263</v>
       </c>
       <c r="L54" t="n">
-        <v>26.74564354642349</v>
+        <v>27.48010873505415</v>
       </c>
       <c r="M54" t="n">
-        <v>89.30655045624236</v>
+        <v>91.7186799676866</v>
       </c>
       <c r="N54" t="n">
-        <v>89.30655045624236</v>
+        <v>91.7186799676866</v>
       </c>
       <c r="O54" t="n">
-        <v>9.663364324064919</v>
+        <v>14.37698573360471</v>
       </c>
       <c r="P54" t="n">
-        <v>115.3125027166075</v>
+        <v>133.2158082005764</v>
       </c>
       <c r="Q54" t="n">
-        <v>124.9758670406724</v>
+        <v>147.5927939341811</v>
       </c>
       <c r="R54" t="n">
-        <v>9.663364324064919</v>
+        <v>14.37698573360471</v>
       </c>
       <c r="S54" t="n">
-        <v>115.3125027166075</v>
+        <v>133.2158082005764</v>
       </c>
       <c r="T54" t="n">
-        <v>124.9758670406724</v>
+        <v>147.5927939341811</v>
       </c>
     </row>
     <row r="55">
@@ -3809,61 +3809,61 @@
         <v>0.106</v>
       </c>
       <c r="B55" t="n">
-        <v>0.2097064855212306</v>
+        <v>0.2251458034140133</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.4327991735325095</v>
+        <v>-0.4670936864089849</v>
       </c>
       <c r="D55" t="n">
-        <v>-2.275994306524774</v>
+        <v>-2.207405280771824</v>
       </c>
       <c r="E55" t="n">
-        <v>1.505018619558429</v>
+        <v>1.707024555871548</v>
       </c>
       <c r="F55" t="n">
-        <v>-3.315550419856559</v>
+        <v>-3.82838775483069</v>
       </c>
       <c r="G55" t="n">
-        <v>6.631100839714533</v>
+        <v>7.656775509661753</v>
       </c>
       <c r="H55" t="n">
-        <v>-3.250645697714069</v>
+        <v>-4.13741058724879</v>
       </c>
       <c r="I55" t="n">
-        <v>17.9064524315719</v>
+        <v>17.89196848471721</v>
       </c>
       <c r="J55" t="n">
-        <v>-4.86863430260407</v>
+        <v>-6.005663811606166</v>
       </c>
       <c r="K55" t="n">
-        <v>17.99995095341188</v>
+        <v>17.99992901940344</v>
       </c>
       <c r="L55" t="n">
-        <v>26.82282435670242</v>
+        <v>27.57909844232045</v>
       </c>
       <c r="M55" t="n">
-        <v>89.81238089071626</v>
+        <v>92.29614980965752</v>
       </c>
       <c r="N55" t="n">
-        <v>89.81238089071626</v>
+        <v>92.29614980965752</v>
       </c>
       <c r="O55" t="n">
-        <v>10.77921034150807</v>
+        <v>15.84335532862939</v>
       </c>
       <c r="P55" t="n">
-        <v>118.7394589510562</v>
+        <v>136.9947049632545</v>
       </c>
       <c r="Q55" t="n">
-        <v>129.5186692925643</v>
+        <v>152.8380602918838</v>
       </c>
       <c r="R55" t="n">
-        <v>10.77921034150807</v>
+        <v>15.84335532862939</v>
       </c>
       <c r="S55" t="n">
-        <v>118.7394589510562</v>
+        <v>136.9947049632545</v>
       </c>
       <c r="T55" t="n">
-        <v>129.5186692925643</v>
+        <v>152.8380602918838</v>
       </c>
     </row>
     <row r="56">
@@ -3871,61 +3871,61 @@
         <v>0.108</v>
       </c>
       <c r="B56" t="n">
-        <v>0.2127806992059331</v>
+        <v>0.2286257077906817</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.4395894462628536</v>
+        <v>-0.4749114871467938</v>
       </c>
       <c r="D56" t="n">
-        <v>-2.262413761064086</v>
+        <v>-2.191769679296206</v>
       </c>
       <c r="E56" t="n">
-        <v>1.544949055165115</v>
+        <v>1.748781786577644</v>
       </c>
       <c r="F56" t="n">
-        <v>-3.414538606310624</v>
+        <v>-3.938057977013033</v>
       </c>
       <c r="G56" t="n">
-        <v>6.829077212621051</v>
+        <v>7.876115954026145</v>
       </c>
       <c r="H56" t="n">
-        <v>-3.338907341587689</v>
+        <v>-4.277818661680626</v>
       </c>
       <c r="I56" t="n">
-        <v>17.90367107482087</v>
+        <v>17.88890070268357</v>
       </c>
       <c r="J56" t="n">
-        <v>-5.005202181467274</v>
+        <v>-6.199590954462987</v>
       </c>
       <c r="K56" t="n">
-        <v>17.99996106351883</v>
+        <v>17.99995393763534</v>
       </c>
       <c r="L56" t="n">
-        <v>27.02185865716892</v>
+        <v>27.82590237103336</v>
       </c>
       <c r="M56" t="n">
-        <v>90.24647094931468</v>
+        <v>92.91365041780556</v>
       </c>
       <c r="N56" t="n">
-        <v>90.24647094931468</v>
+        <v>92.91365041780556</v>
       </c>
       <c r="O56" t="n">
-        <v>11.40623911386878</v>
+        <v>16.85458986813603</v>
       </c>
       <c r="P56" t="n">
-        <v>122.2651829086693</v>
+        <v>140.8946564669301</v>
       </c>
       <c r="Q56" t="n">
-        <v>133.6714220225381</v>
+        <v>157.7492463350662</v>
       </c>
       <c r="R56" t="n">
-        <v>11.40623911386878</v>
+        <v>16.85458986813603</v>
       </c>
       <c r="S56" t="n">
-        <v>122.2651829086693</v>
+        <v>140.8946564669301</v>
       </c>
       <c r="T56" t="n">
-        <v>133.6714220225381</v>
+        <v>157.7492463350662</v>
       </c>
     </row>
     <row r="57">
@@ -3933,61 +3933,61 @@
         <v>0.11</v>
       </c>
       <c r="B57" t="n">
-        <v>0.2159005390617524</v>
+        <v>0.2321633561465508</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.4464936943672051</v>
+        <v>-0.482881799879383</v>
       </c>
       <c r="D57" t="n">
-        <v>-2.248605264855383</v>
+        <v>-2.175829053831027</v>
       </c>
       <c r="E57" t="n">
-        <v>1.585079412778483</v>
+        <v>1.790845412902974</v>
       </c>
       <c r="F57" t="n">
-        <v>-3.514626293723851</v>
+        <v>-4.049554677912577</v>
       </c>
       <c r="G57" t="n">
-        <v>7.029252587446795</v>
+        <v>8.099109355825117</v>
       </c>
       <c r="H57" t="n">
-        <v>-3.48010840122848</v>
+        <v>-4.469332450209203</v>
       </c>
       <c r="I57" t="n">
-        <v>17.9008534250698</v>
+        <v>17.88576664464371</v>
       </c>
       <c r="J57" t="n">
-        <v>-5.195246032565719</v>
+        <v>-6.445515133030541</v>
       </c>
       <c r="K57" t="n">
-        <v>17.9999658865528</v>
+        <v>17.99996408656084</v>
       </c>
       <c r="L57" t="n">
-        <v>27.19527082025824</v>
+        <v>28.04041617025858</v>
       </c>
       <c r="M57" t="n">
-        <v>90.72613695129439</v>
+        <v>93.55426072887401</v>
       </c>
       <c r="N57" t="n">
-        <v>90.72613695129439</v>
+        <v>93.55426072887401</v>
       </c>
       <c r="O57" t="n">
-        <v>12.24297341351812</v>
+        <v>18.11386318033663</v>
       </c>
       <c r="P57" t="n">
-        <v>125.8293765303613</v>
+        <v>144.8584633505909</v>
       </c>
       <c r="Q57" t="n">
-        <v>138.0723499438795</v>
+        <v>162.9723265309275</v>
       </c>
       <c r="R57" t="n">
-        <v>12.24297341351812</v>
+        <v>18.11386318033663</v>
       </c>
       <c r="S57" t="n">
-        <v>125.8293765303613</v>
+        <v>144.8584633505909</v>
       </c>
       <c r="T57" t="n">
-        <v>138.0723499438795</v>
+        <v>162.9723265309275</v>
       </c>
     </row>
     <row r="58">
@@ -3995,61 +3995,61 @@
         <v>0.112</v>
       </c>
       <c r="B58" t="n">
-        <v>0.2191132582629193</v>
+        <v>0.2357864383156767</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.4536303941273538</v>
+        <v>-0.4910786186724299</v>
       </c>
       <c r="D58" t="n">
-        <v>-2.234331865335086</v>
+        <v>-2.159435416244933</v>
       </c>
       <c r="E58" t="n">
-        <v>1.625619635498717</v>
+        <v>1.833367894883905</v>
       </c>
       <c r="F58" t="n">
-        <v>-3.616973424121486</v>
+        <v>-4.163807222394317</v>
       </c>
       <c r="G58" t="n">
-        <v>7.233946848243728</v>
+        <v>8.327614444788949</v>
       </c>
       <c r="H58" t="n">
-        <v>-3.757909319297936</v>
+        <v>-4.7782559254822</v>
       </c>
       <c r="I58" t="n">
-        <v>17.89795820695216</v>
+        <v>17.88251864874657</v>
       </c>
       <c r="J58" t="n">
-        <v>-5.52299235026922</v>
+        <v>-6.810193850010627</v>
       </c>
       <c r="K58" t="n">
-        <v>17.99995685751239</v>
+        <v>17.99993801241809</v>
       </c>
       <c r="L58" t="n">
-        <v>27.29872172907009</v>
+        <v>28.17041245856105</v>
       </c>
       <c r="M58" t="n">
-        <v>91.31686187900944</v>
+        <v>94.23034967486676</v>
       </c>
       <c r="N58" t="n">
-        <v>91.31686187900944</v>
+        <v>94.23034967486676</v>
       </c>
       <c r="O58" t="n">
-        <v>13.60536785555876</v>
+        <v>19.9056830235311</v>
       </c>
       <c r="P58" t="n">
-        <v>129.4726051044056</v>
+        <v>148.9185114553497</v>
       </c>
       <c r="Q58" t="n">
-        <v>143.0779729599644</v>
+        <v>168.8241944788808</v>
       </c>
       <c r="R58" t="n">
-        <v>13.60536785555876</v>
+        <v>19.9056830235311</v>
       </c>
       <c r="S58" t="n">
-        <v>129.4726051044056</v>
+        <v>148.9185114553497</v>
       </c>
       <c r="T58" t="n">
-        <v>143.0779729599644</v>
+        <v>168.8241944788808</v>
       </c>
     </row>
     <row r="59">
@@ -4057,61 +4057,61 @@
         <v>0.114</v>
       </c>
       <c r="B59" t="n">
-        <v>0.2224135247539797</v>
+        <v>0.2395159284765573</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.4609902458324831</v>
+        <v>-0.4995636408191138</v>
       </c>
       <c r="D59" t="n">
-        <v>-2.219612161924827</v>
+        <v>-2.142465371951566</v>
       </c>
       <c r="E59" t="n">
-        <v>1.666573293523972</v>
+        <v>1.876497345314272</v>
       </c>
       <c r="F59" t="n">
-        <v>-3.72165037180679</v>
+        <v>-4.281733258970556</v>
       </c>
       <c r="G59" t="n">
-        <v>7.443300743613964</v>
+        <v>8.563466517941057</v>
       </c>
       <c r="H59" t="n">
-        <v>-3.922273654727352</v>
+        <v>-4.964218775158766</v>
       </c>
       <c r="I59" t="n">
-        <v>17.89501028857083</v>
+        <v>17.87920947113025</v>
       </c>
       <c r="J59" t="n">
-        <v>-5.738439036169065</v>
+        <v>-7.053704605536398</v>
       </c>
       <c r="K59" t="n">
-        <v>17.99996082905579</v>
+        <v>17.99995434903322</v>
       </c>
       <c r="L59" t="n">
-        <v>27.48221541754556</v>
+        <v>28.42833468257144</v>
       </c>
       <c r="M59" t="n">
-        <v>91.85650446840896</v>
+        <v>94.94841199369728</v>
       </c>
       <c r="N59" t="n">
-        <v>91.85650446840896</v>
+        <v>94.94841199369728</v>
       </c>
       <c r="O59" t="n">
-        <v>14.60441467019106</v>
+        <v>21.26658923378677</v>
       </c>
       <c r="P59" t="n">
-        <v>133.1975311499882</v>
+        <v>153.1075298812121</v>
       </c>
       <c r="Q59" t="n">
-        <v>147.8019458201792</v>
+        <v>174.3741191149989</v>
       </c>
       <c r="R59" t="n">
-        <v>14.60441467019106</v>
+        <v>21.26658923378677</v>
       </c>
       <c r="S59" t="n">
-        <v>133.1975311499882</v>
+        <v>153.1075298812121</v>
       </c>
       <c r="T59" t="n">
-        <v>147.8019458201792</v>
+        <v>174.3741191149989</v>
       </c>
     </row>
     <row r="60">
@@ -4119,61 +4119,61 @@
         <v>0.116</v>
       </c>
       <c r="B60" t="n">
-        <v>0.2257616917439517</v>
+        <v>0.2433049615120707</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.4684721925734574</v>
+        <v>-0.5082119097227276</v>
       </c>
       <c r="D60" t="n">
-        <v>-2.204648268442878</v>
+        <v>-2.125168834144338</v>
       </c>
       <c r="E60" t="n">
-        <v>1.707753157950386</v>
+        <v>1.91997869794387</v>
       </c>
       <c r="F60" t="n">
-        <v>-3.827602052388887</v>
+        <v>-4.401841038738195</v>
       </c>
       <c r="G60" t="n">
-        <v>7.655204104776674</v>
+        <v>8.803682077476067</v>
       </c>
       <c r="H60" t="n">
-        <v>-4.024572460659477</v>
+        <v>-5.162079872643679</v>
       </c>
       <c r="I60" t="n">
-        <v>17.89203353584266</v>
+        <v>17.87583811004778</v>
       </c>
       <c r="J60" t="n">
-        <v>-5.892442262225254</v>
+        <v>-7.310178299547919</v>
       </c>
       <c r="K60" t="n">
-        <v>17.99997191372001</v>
+        <v>17.99997002734019</v>
       </c>
       <c r="L60" t="n">
-        <v>27.70950359794452</v>
+        <v>28.69152621762725</v>
       </c>
       <c r="M60" t="n">
-        <v>92.36819794032164</v>
+        <v>95.69299263575181</v>
       </c>
       <c r="N60" t="n">
-        <v>92.36819794032164</v>
+        <v>95.69299263575181</v>
       </c>
       <c r="O60" t="n">
-        <v>15.40465998391564</v>
+        <v>22.73581575294271</v>
       </c>
       <c r="P60" t="n">
-        <v>136.9671570332387</v>
+        <v>157.3729271431763</v>
       </c>
       <c r="Q60" t="n">
-        <v>152.3718170171543</v>
+        <v>180.108742896119</v>
       </c>
       <c r="R60" t="n">
-        <v>15.40465998391564</v>
+        <v>22.73581575294271</v>
       </c>
       <c r="S60" t="n">
-        <v>136.9671570332387</v>
+        <v>157.3729271431763</v>
       </c>
       <c r="T60" t="n">
-        <v>152.3718170171543</v>
+        <v>180.108742896119</v>
       </c>
     </row>
     <row r="61">
@@ -4181,61 +4181,61 @@
         <v>0.118</v>
       </c>
       <c r="B61" t="n">
-        <v>0.2292459881389137</v>
+        <v>0.2471993919839365</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.4763080296261935</v>
+        <v>-0.5171522471282879</v>
       </c>
       <c r="D61" t="n">
-        <v>-2.188976594337406</v>
+        <v>-2.107288159333217</v>
       </c>
       <c r="E61" t="n">
-        <v>1.749619280025643</v>
+        <v>1.964102209678074</v>
       </c>
       <c r="F61" t="n">
-        <v>-3.937517311122787</v>
+        <v>-4.526008872998011</v>
       </c>
       <c r="G61" t="n">
-        <v>7.875034622245757</v>
+        <v>9.052017745996409</v>
       </c>
       <c r="H61" t="n">
-        <v>-4.328889430738734</v>
+        <v>-5.507741831278778</v>
       </c>
       <c r="I61" t="n">
-        <v>17.88892482342521</v>
+        <v>17.87231278697949</v>
       </c>
       <c r="J61" t="n">
-        <v>-6.250397878566653</v>
+        <v>-7.716434161301808</v>
       </c>
       <c r="K61" t="n">
-        <v>17.99996281159887</v>
+        <v>17.99994623719804</v>
       </c>
       <c r="L61" t="n">
-        <v>27.84579941528192</v>
+        <v>28.8599025338543</v>
       </c>
       <c r="M61" t="n">
-        <v>93.05910420141112</v>
+        <v>96.48927396511259</v>
       </c>
       <c r="N61" t="n">
-        <v>93.05910420141112</v>
+        <v>96.48927396511259</v>
       </c>
       <c r="O61" t="n">
-        <v>17.06736551759598</v>
+        <v>24.94556556919685</v>
       </c>
       <c r="P61" t="n">
-        <v>140.8754501237571</v>
+        <v>161.7801360188283</v>
       </c>
       <c r="Q61" t="n">
-        <v>157.9428156413531</v>
+        <v>186.7257015880251</v>
       </c>
       <c r="R61" t="n">
-        <v>17.06736551759598</v>
+        <v>24.94556556919685</v>
       </c>
       <c r="S61" t="n">
-        <v>140.8754501237571</v>
+        <v>161.7801360188283</v>
       </c>
       <c r="T61" t="n">
-        <v>157.9428156413531</v>
+        <v>186.7257015880251</v>
       </c>
     </row>
     <row r="62">
@@ -4243,61 +4243,61 @@
         <v>0.12</v>
       </c>
       <c r="B62" t="n">
-        <v>0.2327782340461729</v>
+        <v>0.2511872940142748</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.4842711071782292</v>
+        <v>-0.5263580291049628</v>
       </c>
       <c r="D62" t="n">
-        <v>-2.173050439233335</v>
+        <v>-2.088876595379868</v>
       </c>
       <c r="E62" t="n">
-        <v>1.791743417890679</v>
+        <v>2.008830638729323</v>
       </c>
       <c r="F62" t="n">
-        <v>-4.048958750747323</v>
+        <v>-4.654039645171742</v>
       </c>
       <c r="G62" t="n">
-        <v>8.09791750149526</v>
+        <v>9.308079290343546</v>
       </c>
       <c r="H62" t="n">
-        <v>-4.576109508409083</v>
+        <v>-5.746490958301777</v>
       </c>
       <c r="I62" t="n">
-        <v>17.88577968085818</v>
+        <v>17.86871128928507</v>
       </c>
       <c r="J62" t="n">
-        <v>-6.552001378773777</v>
+        <v>-8.017662305145588</v>
       </c>
       <c r="K62" t="n">
-        <v>17.99996031762926</v>
+        <v>17.99995520727892</v>
       </c>
       <c r="L62" t="n">
-        <v>28.02085430512791</v>
+        <v>29.13567774379267</v>
       </c>
       <c r="M62" t="n">
-        <v>93.72419463208357</v>
+        <v>97.32903810781148</v>
       </c>
       <c r="N62" t="n">
-        <v>93.72419463208357</v>
+        <v>97.32903810781148</v>
       </c>
       <c r="O62" t="n">
-        <v>18.5348891457732</v>
+        <v>26.758814738529</v>
       </c>
       <c r="P62" t="n">
-        <v>144.8372448701074</v>
+        <v>166.3228168902971</v>
       </c>
       <c r="Q62" t="n">
-        <v>163.3721340158806</v>
+        <v>193.0816316288261</v>
       </c>
       <c r="R62" t="n">
-        <v>18.5348891457732</v>
+        <v>26.758814738529</v>
       </c>
       <c r="S62" t="n">
-        <v>144.8372448701074</v>
+        <v>166.3228168902971</v>
       </c>
       <c r="T62" t="n">
-        <v>163.3721340158806</v>
+        <v>193.0816316288261</v>
       </c>
     </row>
     <row r="63">
@@ -4305,61 +4305,61 @@
         <v>0.122</v>
       </c>
       <c r="B63" t="n">
-        <v>0.2364041193936856</v>
+        <v>0.2552368055834768</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.4924828360640586</v>
+        <v>-0.535739932331652</v>
       </c>
       <c r="D63" t="n">
-        <v>-2.156626981461676</v>
+        <v>-2.07011278892649</v>
       </c>
       <c r="E63" t="n">
-        <v>1.834372476346292</v>
+        <v>2.053964719190867</v>
       </c>
       <c r="F63" t="n">
-        <v>-4.163388997467816</v>
+        <v>-4.784693275425826</v>
       </c>
       <c r="G63" t="n">
-        <v>8.326777994934897</v>
+        <v>9.569386550851089</v>
       </c>
       <c r="H63" t="n">
-        <v>-4.703577817901772</v>
+        <v>-5.954472836122693</v>
       </c>
       <c r="I63" t="n">
-        <v>17.88256404113671</v>
+        <v>17.86504691103214</v>
       </c>
       <c r="J63" t="n">
-        <v>-6.735311648666066</v>
+        <v>-8.289403154530497</v>
       </c>
       <c r="K63" t="n">
-        <v>17.99997161086529</v>
+        <v>17.99997526139914</v>
       </c>
       <c r="L63" t="n">
-        <v>28.27615493783026</v>
+        <v>29.45230706459286</v>
       </c>
       <c r="M63" t="n">
-        <v>94.33314977449317</v>
+        <v>98.19924964492779</v>
       </c>
       <c r="N63" t="n">
-        <v>94.33314977449317</v>
+        <v>98.19924964492779</v>
       </c>
       <c r="O63" t="n">
-        <v>19.58915575750528</v>
+        <v>28.49869027447289</v>
       </c>
       <c r="P63" t="n">
-        <v>148.903821295439</v>
+        <v>170.957374033092</v>
       </c>
       <c r="Q63" t="n">
-        <v>168.4929770529443</v>
+        <v>199.4560643075649</v>
       </c>
       <c r="R63" t="n">
-        <v>19.58915575750528</v>
+        <v>28.49869027447289</v>
       </c>
       <c r="S63" t="n">
-        <v>148.903821295439</v>
+        <v>170.957374033092</v>
       </c>
       <c r="T63" t="n">
-        <v>168.4929770529443</v>
+        <v>199.4560643075649</v>
       </c>
     </row>
     <row r="64">
@@ -4367,61 +4367,61 @@
         <v>0.124</v>
       </c>
       <c r="B64" t="n">
-        <v>0.2401261635662746</v>
+        <v>0.2594136709194655</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.5009558041767358</v>
+        <v>-0.5454931090556934</v>
       </c>
       <c r="D64" t="n">
-        <v>-2.139681045236322</v>
+        <v>-2.050606435478407</v>
       </c>
       <c r="E64" t="n">
-        <v>1.877555546576614</v>
+        <v>2.099980443103902</v>
       </c>
       <c r="F64" t="n">
-        <v>-4.281187396384329</v>
+        <v>-4.921245504334394</v>
       </c>
       <c r="G64" t="n">
-        <v>8.5623747927685</v>
+        <v>9.842491008669334</v>
       </c>
       <c r="H64" t="n">
-        <v>-4.975557435355064</v>
+        <v>-6.345705214770168</v>
       </c>
       <c r="I64" t="n">
-        <v>17.87923933705325</v>
+        <v>17.8611737629965</v>
       </c>
       <c r="J64" t="n">
-        <v>-7.064776884790617</v>
+        <v>-8.747273020885352</v>
       </c>
       <c r="K64" t="n">
-        <v>17.99996882163128</v>
+        <v>17.99995288621874</v>
       </c>
       <c r="L64" t="n">
-        <v>28.47703661131223</v>
+        <v>29.66726065418184</v>
       </c>
       <c r="M64" t="n">
-        <v>95.08296943431422</v>
+        <v>99.143508564228</v>
       </c>
       <c r="N64" t="n">
-        <v>95.08296943431422</v>
+        <v>99.143508564228</v>
       </c>
       <c r="O64" t="n">
-        <v>21.32835806734216</v>
+        <v>31.25561840420698</v>
       </c>
       <c r="P64" t="n">
-        <v>153.0882134804474</v>
+        <v>175.7979106399253</v>
       </c>
       <c r="Q64" t="n">
-        <v>174.4165715477896</v>
+        <v>207.0535290441323</v>
       </c>
       <c r="R64" t="n">
-        <v>21.32835806734216</v>
+        <v>31.25561840420698</v>
       </c>
       <c r="S64" t="n">
-        <v>153.0882134804474</v>
+        <v>175.7979106399253</v>
       </c>
       <c r="T64" t="n">
-        <v>174.4165715477896</v>
+        <v>207.0535290441323</v>
       </c>
     </row>
     <row r="65">
@@ -4429,61 +4429,61 @@
         <v>0.126</v>
       </c>
       <c r="B65" t="n">
-        <v>0.2438971264457182</v>
+        <v>0.2636703128811954</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.5095618344354428</v>
+        <v>-0.5554854833525908</v>
       </c>
       <c r="D65" t="n">
-        <v>-2.122468984718908</v>
+        <v>-2.030621686884612</v>
       </c>
       <c r="E65" t="n">
-        <v>1.92102142416103</v>
+        <v>2.146583743219497</v>
       </c>
       <c r="F65" t="n">
-        <v>-4.40070765500038</v>
+        <v>-5.06178365082444</v>
       </c>
       <c r="G65" t="n">
-        <v>8.801415310002056</v>
+        <v>10.12356730164925</v>
       </c>
       <c r="H65" t="n">
-        <v>-5.314417422622745</v>
+        <v>-6.647211200459318</v>
       </c>
       <c r="I65" t="n">
-        <v>17.87585961259723</v>
+        <v>17.85721347356249</v>
       </c>
       <c r="J65" t="n">
-        <v>-7.46196275826293</v>
+        <v>-9.117361622061644</v>
       </c>
       <c r="K65" t="n">
-        <v>17.99995956846826</v>
+        <v>17.99995577251574</v>
       </c>
       <c r="L65" t="n">
-        <v>28.65349027932221</v>
+        <v>29.97033321678285</v>
       </c>
       <c r="M65" t="n">
-        <v>95.89945331547469</v>
+        <v>100.1326117970862</v>
       </c>
       <c r="N65" t="n">
-        <v>95.89945331547469</v>
+        <v>100.1326117970862</v>
       </c>
       <c r="O65" t="n">
-        <v>23.38773514693633</v>
+        <v>33.66485340445526</v>
       </c>
       <c r="P65" t="n">
-        <v>157.3328406586595</v>
+        <v>180.7780590505614</v>
       </c>
       <c r="Q65" t="n">
-        <v>180.7205758055958</v>
+        <v>214.4429124550166</v>
       </c>
       <c r="R65" t="n">
-        <v>23.38773514693633</v>
+        <v>33.66485340445526</v>
       </c>
       <c r="S65" t="n">
-        <v>157.3328406586595</v>
+        <v>180.7780590505614</v>
       </c>
       <c r="T65" t="n">
-        <v>180.7205758055958</v>
+        <v>214.4429124550166</v>
       </c>
     </row>
     <row r="66">
@@ -4491,61 +4491,61 @@
         <v>0.128</v>
       </c>
       <c r="B66" t="n">
-        <v>0.2478112095923255</v>
+        <v>0.267993192174944</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.5185663569798002</v>
+        <v>-0.5656764597952193</v>
       </c>
       <c r="D66" t="n">
-        <v>-2.104459939630193</v>
+        <v>-2.010239733999355</v>
       </c>
       <c r="E66" t="n">
-        <v>1.965369404788651</v>
+        <v>2.193674899015298</v>
       </c>
       <c r="F66" t="n">
-        <v>-4.525740392415602</v>
+        <v>-5.205631244709531</v>
       </c>
       <c r="G66" t="n">
-        <v>9.051480784830961</v>
+        <v>10.41126248941819</v>
       </c>
       <c r="H66" t="n">
-        <v>-5.473119946686923</v>
+        <v>-6.874218712115209</v>
       </c>
       <c r="I66" t="n">
-        <v>17.87234517801681</v>
+        <v>17.85318083193653</v>
       </c>
       <c r="J66" t="n">
-        <v>-7.681681258185737</v>
+        <v>-9.414566759533459</v>
       </c>
       <c r="K66" t="n">
-        <v>17.99997105708292</v>
+        <v>17.99997963303733</v>
       </c>
       <c r="L66" t="n">
-        <v>28.9428868395614</v>
+        <v>30.34656963682125</v>
       </c>
       <c r="M66" t="n">
-        <v>96.6279674195077</v>
+        <v>101.1589485887556</v>
       </c>
       <c r="N66" t="n">
-        <v>96.6279674195077</v>
+        <v>101.1589485887556</v>
       </c>
       <c r="O66" t="n">
-        <v>24.78284834800041</v>
+        <v>35.78540403074712</v>
       </c>
       <c r="P66" t="n">
-        <v>161.7706163681746</v>
+        <v>185.8741250412696</v>
       </c>
       <c r="Q66" t="n">
-        <v>186.553464716175</v>
+        <v>221.6595290720167</v>
       </c>
       <c r="R66" t="n">
-        <v>24.78284834800041</v>
+        <v>35.78540403074712</v>
       </c>
       <c r="S66" t="n">
-        <v>161.7706163681746</v>
+        <v>185.8741250412696</v>
       </c>
       <c r="T66" t="n">
-        <v>186.553464716175</v>
+        <v>221.6595290720167</v>
       </c>
     </row>
     <row r="67">
@@ -4553,61 +4553,61 @@
         <v>0.13</v>
       </c>
       <c r="B67" t="n">
-        <v>0.2517786608169751</v>
+        <v>0.2724634657393942</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.527723452115786</v>
+        <v>-0.5763228584823117</v>
       </c>
       <c r="D67" t="n">
-        <v>-2.086145749358221</v>
+        <v>-1.98894693662517</v>
       </c>
       <c r="E67" t="n">
-        <v>2.01006948095291</v>
+        <v>2.241931454030099</v>
       </c>
       <c r="F67" t="n">
-        <v>-4.653038235192041</v>
+        <v>-5.357779336241483</v>
       </c>
       <c r="G67" t="n">
-        <v>9.306076470383392</v>
+        <v>10.71555867248318</v>
       </c>
       <c r="H67" t="n">
-        <v>-5.713465514385737</v>
+        <v>-7.3212038668066</v>
       </c>
       <c r="I67" t="n">
-        <v>17.86875920786461</v>
+        <v>17.84887094536127</v>
       </c>
       <c r="J67" t="n">
-        <v>-7.984148173159452</v>
+        <v>-9.935800182892443</v>
       </c>
       <c r="K67" t="n">
-        <v>17.99997488609702</v>
+        <v>17.99996032264329</v>
       </c>
       <c r="L67" t="n">
-        <v>29.20882531795879</v>
+        <v>30.62593900098624</v>
       </c>
       <c r="M67" t="n">
-        <v>97.44456072230498</v>
+        <v>102.2906557301089</v>
       </c>
       <c r="N67" t="n">
-        <v>97.44456072230498</v>
+        <v>102.2906557301089</v>
       </c>
       <c r="O67" t="n">
-        <v>26.60861395207813</v>
+        <v>39.26432317577608</v>
       </c>
       <c r="P67" t="n">
-        <v>166.287584836049</v>
+        <v>191.2598779951271</v>
       </c>
       <c r="Q67" t="n">
-        <v>192.8961987881271</v>
+        <v>230.5242011709032</v>
       </c>
       <c r="R67" t="n">
-        <v>26.60861395207813</v>
+        <v>39.26432317577608</v>
       </c>
       <c r="S67" t="n">
-        <v>166.287584836049</v>
+        <v>191.2598779951271</v>
       </c>
       <c r="T67" t="n">
-        <v>192.8961987881271</v>
+        <v>230.5242011709032</v>
       </c>
     </row>
     <row r="68">
@@ -4615,61 +4615,61 @@
         <v>0.132</v>
       </c>
       <c r="B68" t="n">
-        <v>0.2558413793257311</v>
+        <v>0.2770010498367131</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.5371529043792284</v>
+        <v>-0.5871838250864831</v>
       </c>
       <c r="D68" t="n">
-        <v>-2.067286844831337</v>
+        <v>-1.967225003416827</v>
       </c>
       <c r="E68" t="n">
-        <v>2.055398082384556</v>
+        <v>2.290753031679256</v>
       </c>
       <c r="F68" t="n">
-        <v>-4.784379514492583</v>
+        <v>-5.514012254515513</v>
       </c>
       <c r="G68" t="n">
-        <v>9.568759028985996</v>
+        <v>11.02802450903143</v>
       </c>
       <c r="H68" t="n">
-        <v>-6.099551969119632</v>
+        <v>-7.699038091910988</v>
       </c>
       <c r="I68" t="n">
-        <v>17.86504553965977</v>
+        <v>17.84446265140642</v>
       </c>
       <c r="J68" t="n">
-        <v>-8.434329172192014</v>
+        <v>-10.38987607211456</v>
       </c>
       <c r="K68" t="n">
-        <v>17.99996504196847</v>
+        <v>17.99995779698376</v>
       </c>
       <c r="L68" t="n">
-        <v>29.43288880611125</v>
+        <v>30.96958331770144</v>
       </c>
       <c r="M68" t="n">
-        <v>98.41838408397527</v>
+        <v>103.4677178215242</v>
       </c>
       <c r="N68" t="n">
-        <v>98.41838408397527</v>
+        <v>103.4677178215242</v>
       </c>
       <c r="O68" t="n">
-        <v>29.2031365797165</v>
+        <v>42.47434182379691</v>
       </c>
       <c r="P68" t="n">
-        <v>170.9459201900197</v>
+        <v>196.788464691195</v>
       </c>
       <c r="Q68" t="n">
-        <v>200.1490567697362</v>
+        <v>239.2628065149919</v>
       </c>
       <c r="R68" t="n">
-        <v>29.2031365797165</v>
+        <v>42.47434182379691</v>
       </c>
       <c r="S68" t="n">
-        <v>170.9459201900197</v>
+        <v>196.788464691195</v>
       </c>
       <c r="T68" t="n">
-        <v>200.1490567697362</v>
+        <v>239.2628065149919</v>
       </c>
     </row>
     <row r="69">
@@ -4677,61 +4677,61 @@
         <v>0.134</v>
       </c>
       <c r="B69" t="n">
-        <v>0.2600107685586289</v>
+        <v>0.2816271454605752</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.5468961070871764</v>
+        <v>-0.5983272411765047</v>
       </c>
       <c r="D69" t="n">
-        <v>-2.047800439415441</v>
+        <v>-1.944938171236784</v>
       </c>
       <c r="E69" t="n">
-        <v>2.101480116783733</v>
+        <v>2.340319085273565</v>
       </c>
       <c r="F69" t="n">
-        <v>-4.920720324679545</v>
+        <v>-5.675629936079697</v>
       </c>
       <c r="G69" t="n">
-        <v>9.841440649359345</v>
+        <v>11.35125987215873</v>
       </c>
       <c r="H69" t="n">
-        <v>-6.353944193891852</v>
+        <v>-7.978258738709688</v>
       </c>
       <c r="I69" t="n">
-        <v>17.86120551742054</v>
+        <v>17.83992623175669</v>
       </c>
       <c r="J69" t="n">
-        <v>-8.755255712335471</v>
+        <v>-10.74796614751658</v>
       </c>
       <c r="K69" t="n">
-        <v>17.99996983057651</v>
+        <v>17.99997899595413</v>
       </c>
       <c r="L69" t="n">
-        <v>29.73239409196513</v>
+        <v>31.40266220283263</v>
       </c>
       <c r="M69" t="n">
-        <v>99.32522222792917</v>
+        <v>104.704295230951</v>
       </c>
       <c r="N69" t="n">
-        <v>99.32522222792917</v>
+        <v>104.704295230951</v>
       </c>
       <c r="O69" t="n">
-        <v>31.28440387809092</v>
+        <v>45.29048828633353</v>
       </c>
       <c r="P69" t="n">
-        <v>175.7792708737789</v>
+        <v>202.5053513799188</v>
       </c>
       <c r="Q69" t="n">
-        <v>207.0636747518698</v>
+        <v>247.7958396662523</v>
       </c>
       <c r="R69" t="n">
-        <v>31.28440387809092</v>
+        <v>45.29048828633353</v>
       </c>
       <c r="S69" t="n">
-        <v>175.7792708737789</v>
+        <v>202.5053513799188</v>
       </c>
       <c r="T69" t="n">
-        <v>207.0636747518698</v>
+        <v>247.7958396662523</v>
       </c>
     </row>
     <row r="70">
@@ -4739,61 +4739,61 @@
         <v>0.136</v>
       </c>
       <c r="B70" t="n">
-        <v>0.2642324012215275</v>
+        <v>0.2863894365399632</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.5567936019810198</v>
+        <v>-0.6099205570731305</v>
       </c>
       <c r="D70" t="n">
-        <v>-2.028005449627754</v>
+        <v>-1.921751539443532</v>
       </c>
       <c r="E70" t="n">
-        <v>2.147933831286381</v>
+        <v>2.391117067683831</v>
       </c>
       <c r="F70" t="n">
-        <v>-5.059542436798075</v>
+        <v>-5.84665838571227</v>
       </c>
       <c r="G70" t="n">
-        <v>10.11908487359507</v>
+        <v>11.69331677142465</v>
       </c>
       <c r="H70" t="n">
-        <v>-6.562484196337905</v>
+        <v>-8.469815430514767</v>
       </c>
       <c r="I70" t="n">
-        <v>17.85730084241752</v>
+        <v>17.83508831252694</v>
       </c>
       <c r="J70" t="n">
-        <v>-9.031540905495365</v>
+        <v>-11.32298472274235</v>
       </c>
       <c r="K70" t="n">
-        <v>17.99997993913521</v>
+        <v>17.99996407900403</v>
       </c>
       <c r="L70" t="n">
-        <v>30.05954459202049</v>
+        <v>31.7643862075635</v>
       </c>
       <c r="M70" t="n">
-        <v>100.2149778072988</v>
+        <v>106.056692496295</v>
       </c>
       <c r="N70" t="n">
-        <v>100.2149778072988</v>
+        <v>106.056692496295</v>
       </c>
       <c r="O70" t="n">
-        <v>33.20763836721963</v>
+        <v>49.57476318739342</v>
       </c>
       <c r="P70" t="n">
-        <v>180.6994564433617</v>
+        <v>208.5503210113045</v>
       </c>
       <c r="Q70" t="n">
-        <v>213.9070948105813</v>
+        <v>258.1250841986979</v>
       </c>
       <c r="R70" t="n">
-        <v>33.20763836721963</v>
+        <v>49.57476318739342</v>
       </c>
       <c r="S70" t="n">
-        <v>180.6994564433617</v>
+        <v>208.5503210113045</v>
       </c>
       <c r="T70" t="n">
-        <v>213.9070948105813</v>
+        <v>258.1250841986979</v>
       </c>
     </row>
     <row r="71">
@@ -4801,61 +4801,61 @@
         <v>0.138</v>
       </c>
       <c r="B71" t="n">
-        <v>0.2686029047039588</v>
+        <v>0.2912224647320235</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.5671425863227728</v>
+        <v>-0.6217536517991264</v>
       </c>
       <c r="D71" t="n">
-        <v>-2.007307480944247</v>
+        <v>-1.89808534999154</v>
       </c>
       <c r="E71" t="n">
-        <v>2.195497005902095</v>
+        <v>2.442586018347777</v>
       </c>
       <c r="F71" t="n">
-        <v>-5.206050488528364</v>
+        <v>-6.022899436638778</v>
       </c>
       <c r="G71" t="n">
-        <v>10.41210097705703</v>
+        <v>12.04579887327805</v>
       </c>
       <c r="H71" t="n">
-        <v>-6.991093746946468</v>
+        <v>-8.943122385615609</v>
       </c>
       <c r="I71" t="n">
-        <v>17.8531598501339</v>
+        <v>17.83011065011423</v>
       </c>
       <c r="J71" t="n">
-        <v>-9.53164638534831</v>
+        <v>-11.88229731069533</v>
       </c>
       <c r="K71" t="n">
-        <v>17.9999704739104</v>
+        <v>17.99995641422744</v>
       </c>
       <c r="L71" t="n">
-        <v>30.29048344335562</v>
+        <v>32.16413549309836</v>
       </c>
       <c r="M71" t="n">
-        <v>101.351815271988</v>
+        <v>107.4700172437928</v>
       </c>
       <c r="N71" t="n">
-        <v>101.351815271988</v>
+        <v>107.4700172437928</v>
       </c>
       <c r="O71" t="n">
-        <v>36.43620045834862</v>
+        <v>53.88822651085236</v>
       </c>
       <c r="P71" t="n">
-        <v>185.8881260783449</v>
+        <v>214.7771987944739</v>
       </c>
       <c r="Q71" t="n">
-        <v>222.3243265366935</v>
+        <v>268.6654253053263</v>
       </c>
       <c r="R71" t="n">
-        <v>36.43620045834862</v>
+        <v>53.88822651085236</v>
       </c>
       <c r="S71" t="n">
-        <v>185.8881260783449</v>
+        <v>214.7771987944739</v>
       </c>
       <c r="T71" t="n">
-        <v>222.3243265366935</v>
+        <v>268.6654253053263</v>
       </c>
     </row>
     <row r="72">
@@ -4863,61 +4863,61 @@
         <v>0.14</v>
       </c>
       <c r="B72" t="n">
-        <v>0.27303518038335</v>
+        <v>0.2961692736330625</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.5776852063905418</v>
+        <v>-0.6339767921971268</v>
       </c>
       <c r="D72" t="n">
-        <v>-1.98622224080871</v>
+        <v>-1.87363906919554</v>
       </c>
       <c r="E72" t="n">
-        <v>2.243546557863991</v>
+        <v>2.495156441446564</v>
       </c>
       <c r="F72" t="n">
-        <v>-5.356083834001315</v>
+        <v>-6.207756822746853</v>
       </c>
       <c r="G72" t="n">
-        <v>10.71216766800321</v>
+        <v>12.41551364549297</v>
       </c>
       <c r="H72" t="n">
-        <v>-7.345048248090936</v>
+        <v>-9.295332372741889</v>
       </c>
       <c r="I72" t="n">
-        <v>17.84892236379875</v>
+        <v>17.8249202372534</v>
       </c>
       <c r="J72" t="n">
-        <v>-9.958817159083578</v>
+        <v>-12.32471770224235</v>
       </c>
       <c r="K72" t="n">
-        <v>17.9999639279176</v>
+        <v>17.99997897965485</v>
       </c>
       <c r="L72" t="n">
-        <v>30.55965394073177</v>
+        <v>32.67864196561803</v>
       </c>
       <c r="M72" t="n">
-        <v>102.4486182552849</v>
+        <v>108.9818956674771</v>
       </c>
       <c r="N72" t="n">
-        <v>102.4486182552849</v>
+        <v>108.9818956674771</v>
       </c>
       <c r="O72" t="n">
-        <v>39.35870609749221</v>
+        <v>57.72521552258744</v>
       </c>
       <c r="P72" t="n">
-        <v>191.1999775566806</v>
+        <v>221.3048904713517</v>
       </c>
       <c r="Q72" t="n">
-        <v>230.5586836541728</v>
+        <v>279.0301059939392</v>
       </c>
       <c r="R72" t="n">
-        <v>39.35870609749221</v>
+        <v>57.72521552258744</v>
       </c>
       <c r="S72" t="n">
-        <v>191.1999775566806</v>
+        <v>221.3048904713517</v>
       </c>
       <c r="T72" t="n">
-        <v>230.5586836541728</v>
+        <v>279.0301059939392</v>
       </c>
     </row>
     <row r="73">
@@ -4925,61 +4925,61 @@
         <v>0.142</v>
       </c>
       <c r="B73" t="n">
-        <v>0.2775654368380163</v>
+        <v>0.3012404985341504</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.5885349642887536</v>
+        <v>-0.6466437138612746</v>
       </c>
       <c r="D73" t="n">
-        <v>-1.964522725012286</v>
+        <v>-1.848305225867244</v>
       </c>
       <c r="E73" t="n">
-        <v>2.29236758359241</v>
+        <v>2.549031357908133</v>
       </c>
       <c r="F73" t="n">
-        <v>-5.511708870088769</v>
+        <v>-6.403382431387074</v>
       </c>
       <c r="G73" t="n">
-        <v>11.02341774017664</v>
+        <v>12.80676486277417</v>
       </c>
       <c r="H73" t="n">
-        <v>-7.580587669560865</v>
+        <v>-9.854146915380047</v>
       </c>
       <c r="I73" t="n">
-        <v>17.8445318221662</v>
+        <v>17.81939631682003</v>
       </c>
       <c r="J73" t="n">
-        <v>-10.27030159816418</v>
+        <v>-12.97899754189694</v>
       </c>
       <c r="K73" t="n">
-        <v>17.99996201230269</v>
+        <v>17.99997170138515</v>
       </c>
       <c r="L73" t="n">
-        <v>30.88946606174268</v>
+        <v>33.15656072907996</v>
       </c>
       <c r="M73" t="n">
-        <v>103.4819200241584</v>
+        <v>110.6335027375913</v>
       </c>
       <c r="N73" t="n">
-        <v>103.4819200241584</v>
+        <v>110.6335027375913</v>
       </c>
       <c r="O73" t="n">
-        <v>41.7957563065354</v>
+        <v>63.17641179642891</v>
       </c>
       <c r="P73" t="n">
-        <v>196.7072155212587</v>
+        <v>228.2074511981774</v>
       </c>
       <c r="Q73" t="n">
-        <v>238.5029718277941</v>
+        <v>291.3838629946063</v>
       </c>
       <c r="R73" t="n">
-        <v>41.7957563065354</v>
+        <v>63.17641179642891</v>
       </c>
       <c r="S73" t="n">
-        <v>196.7072155212587</v>
+        <v>228.2074511981774</v>
       </c>
       <c r="T73" t="n">
-        <v>238.5029718277941</v>
+        <v>291.3838629946063</v>
       </c>
     </row>
     <row r="74">
@@ -4987,61 +4987,61 @@
         <v>0.144</v>
       </c>
       <c r="B74" t="n">
-        <v>0.2822150886314985</v>
+        <v>0.3063865701262865</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.5997728127039509</v>
+        <v>-0.6595824645495582</v>
       </c>
       <c r="D74" t="n">
-        <v>-1.942047028181892</v>
+        <v>-1.822427724490677</v>
       </c>
       <c r="E74" t="n">
-        <v>2.342021868161566</v>
+        <v>2.60371313953693</v>
       </c>
       <c r="F74" t="n">
-        <v>-5.67451400704358</v>
+        <v>-6.605736999751234</v>
       </c>
       <c r="G74" t="n">
-        <v>11.34902801408699</v>
+        <v>13.21147399950342</v>
       </c>
       <c r="H74" t="n">
-        <v>-7.885097058103835</v>
+        <v>-10.45285127364045</v>
       </c>
       <c r="I74" t="n">
-        <v>17.83993729334982</v>
+        <v>17.81367792591061</v>
       </c>
       <c r="J74" t="n">
-        <v>-10.6542598935411</v>
+        <v>-13.67645092951905</v>
       </c>
       <c r="K74" t="n">
-        <v>17.99995858834845</v>
+        <v>17.9999597093036</v>
       </c>
       <c r="L74" t="n">
-        <v>30.73478400627228</v>
+        <v>33.64738431726707</v>
       </c>
       <c r="M74" t="n">
-        <v>104.4560039834401</v>
+        <v>112.3665696827789</v>
       </c>
       <c r="N74" t="n">
-        <v>104.4560039834401</v>
+        <v>112.3665696827789</v>
       </c>
       <c r="O74" t="n">
-        <v>44.78106918699799</v>
+        <v>69.07260901467856</v>
       </c>
       <c r="P74" t="n">
-        <v>202.4649019142433</v>
+        <v>235.3442959913846</v>
       </c>
       <c r="Q74" t="n">
-        <v>247.2459711012413</v>
+        <v>304.4169050060631</v>
       </c>
       <c r="R74" t="n">
-        <v>44.78106918699799</v>
+        <v>69.07260901467856</v>
       </c>
       <c r="S74" t="n">
-        <v>202.4649019142433</v>
+        <v>235.3442959913846</v>
       </c>
       <c r="T74" t="n">
-        <v>247.2459711012413</v>
+        <v>304.4169050060631</v>
       </c>
     </row>
     <row r="75">
@@ -5049,61 +5049,61 @@
         <v>0.146</v>
       </c>
       <c r="B75" t="n">
-        <v>0.2869210756940344</v>
+        <v>0.3116757438339903</v>
       </c>
       <c r="C75" t="n">
-        <v>-0.6111953926006399</v>
+        <v>-0.6730540304099469</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.919201868388513</v>
+        <v>-1.795484592769899</v>
       </c>
       <c r="E75" t="n">
-        <v>2.392054791537294</v>
+        <v>2.659997185724519</v>
       </c>
       <c r="F75" t="n">
-        <v>-5.840745136447814</v>
+        <v>-6.821633530813628</v>
       </c>
       <c r="G75" t="n">
-        <v>11.68149027289679</v>
+        <v>13.64326706162667</v>
       </c>
       <c r="H75" t="n">
-        <v>-8.20170270742285</v>
+        <v>-10.90027615582301</v>
       </c>
       <c r="I75" t="n">
-        <v>17.83316866267809</v>
+        <v>17.8076043338487</v>
       </c>
       <c r="J75" t="n">
-        <v>-11.05198633400938</v>
+        <v>-14.22923331886006</v>
       </c>
       <c r="K75" t="n">
-        <v>17.99787767552594</v>
+        <v>17.99997439941764</v>
       </c>
       <c r="L75" t="n">
-        <v>30.41065187730083</v>
+        <v>34.25701442525022</v>
       </c>
       <c r="M75" t="n">
-        <v>105.3907929401546</v>
+        <v>114.24837663893</v>
       </c>
       <c r="N75" t="n">
-        <v>105.3907929401546</v>
+        <v>114.24837663893</v>
       </c>
       <c r="O75" t="n">
-        <v>47.90689500193633</v>
+        <v>74.40128600666357</v>
       </c>
       <c r="P75" t="n">
-        <v>208.3166275277965</v>
+        <v>242.9527180435418</v>
       </c>
       <c r="Q75" t="n">
-        <v>256.2235225297328</v>
+        <v>317.3540040502053</v>
       </c>
       <c r="R75" t="n">
-        <v>47.90689500193633</v>
+        <v>74.40128600666357</v>
       </c>
       <c r="S75" t="n">
-        <v>208.3166275277965</v>
+        <v>242.9527180435418</v>
       </c>
       <c r="T75" t="n">
-        <v>256.2235225297328</v>
+        <v>317.3540040502053</v>
       </c>
     </row>
     <row r="76">
@@ -5111,61 +5111,61 @@
         <v>0.148</v>
       </c>
       <c r="B76" t="n">
-        <v>0.2917822884648186</v>
+        <v>0.3170751456713932</v>
       </c>
       <c r="C76" t="n">
-        <v>-0.6231434288766046</v>
+        <v>-0.686957162964714</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.895305795836584</v>
+        <v>-1.767678327660365</v>
       </c>
       <c r="E76" t="n">
-        <v>2.44298313473042</v>
+        <v>2.717401540451726</v>
       </c>
       <c r="F76" t="n">
-        <v>-6.016804606114369</v>
+        <v>-7.047531598729933</v>
       </c>
       <c r="G76" t="n">
-        <v>12.03360921222838</v>
+        <v>14.0950631974596</v>
       </c>
       <c r="H76" t="n">
-        <v>-8.343466829461718</v>
+        <v>-11.40120780238367</v>
       </c>
       <c r="I76" t="n">
-        <v>17.79925423011689</v>
+        <v>17.80123497336697</v>
       </c>
       <c r="J76" t="n">
-        <v>-11.27966747724553</v>
+        <v>-14.84040322256388</v>
       </c>
       <c r="K76" t="n">
-        <v>17.96892812000931</v>
+        <v>17.99997536445115</v>
       </c>
       <c r="L76" t="n">
-        <v>30.22187184852764</v>
+        <v>34.44884814613605</v>
       </c>
       <c r="M76" t="n">
-        <v>106.1017121980121</v>
+        <v>116.039984691508</v>
       </c>
       <c r="N76" t="n">
-        <v>106.1017121980121</v>
+        <v>116.039984691508</v>
       </c>
       <c r="O76" t="n">
-        <v>50.21667719712582</v>
+        <v>80.42260915226025</v>
       </c>
       <c r="P76" t="n">
-        <v>214.1817733353844</v>
+        <v>250.9077595282666</v>
       </c>
       <c r="Q76" t="n">
-        <v>264.3984505325103</v>
+        <v>331.3303686805268</v>
       </c>
       <c r="R76" t="n">
-        <v>50.21667719712582</v>
+        <v>80.42260915226025</v>
       </c>
       <c r="S76" t="n">
-        <v>214.1817733353844</v>
+        <v>250.9077595282666</v>
       </c>
       <c r="T76" t="n">
-        <v>264.3984505325103</v>
+        <v>331.3303686805268</v>
       </c>
     </row>
     <row r="77">
@@ -5173,61 +5173,61 @@
         <v>0.15</v>
       </c>
       <c r="B77" t="n">
-        <v>0.2967137973622002</v>
+        <v>0.3225531479023258</v>
       </c>
       <c r="C77" t="n">
-        <v>-0.6353407106303997</v>
+        <v>-0.70117033652674</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.870911232328994</v>
+        <v>-1.739251980536313</v>
       </c>
       <c r="E77" t="n">
-        <v>2.494124947636833</v>
+        <v>2.77559963462054</v>
       </c>
       <c r="F77" t="n">
-        <v>-6.197361715264774</v>
+        <v>-7.280789500170473</v>
       </c>
       <c r="G77" t="n">
-        <v>12.39472343052894</v>
+        <v>14.56157900034197</v>
       </c>
       <c r="H77" t="n">
-        <v>-8.54220595720564</v>
+        <v>-11.92538029282074</v>
       </c>
       <c r="I77" t="n">
-        <v>17.72263033693865</v>
+        <v>17.79465036380624</v>
       </c>
       <c r="J77" t="n">
-        <v>-11.56651847425485</v>
+        <v>-15.47840556890393</v>
       </c>
       <c r="K77" t="n">
-        <v>17.89739593730911</v>
+        <v>17.99996862771106</v>
       </c>
       <c r="L77" t="n">
-        <v>29.80219395036853</v>
+        <v>34.38026599241492</v>
       </c>
       <c r="M77" t="n">
-        <v>106.5972957577541</v>
+        <v>117.7644869455732</v>
       </c>
       <c r="N77" t="n">
-        <v>106.5972957577541</v>
+        <v>117.7644869455732</v>
       </c>
       <c r="O77" t="n">
-        <v>52.96602666988287</v>
+        <v>86.83369770294857</v>
       </c>
       <c r="P77" t="n">
-        <v>219.6407231511955</v>
+        <v>259.1179054351184</v>
       </c>
       <c r="Q77" t="n">
-        <v>272.6067498210784</v>
+        <v>345.951603138067</v>
       </c>
       <c r="R77" t="n">
-        <v>52.96602666988287</v>
+        <v>86.83369770294857</v>
       </c>
       <c r="S77" t="n">
-        <v>219.6407231511955</v>
+        <v>259.1179054351184</v>
       </c>
       <c r="T77" t="n">
-        <v>272.6067498210784</v>
+        <v>345.951603138067</v>
       </c>
     </row>
     <row r="78">
@@ -5235,61 +5235,61 @@
         <v>0.152</v>
       </c>
       <c r="B78" t="n">
-        <v>0.3017446875606784</v>
+        <v>0.3282037763724318</v>
       </c>
       <c r="C78" t="n">
-        <v>-0.6478903637178401</v>
+        <v>-0.7160984813066574</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.845811926154113</v>
+        <v>-1.709395690976478</v>
       </c>
       <c r="E78" t="n">
-        <v>2.54556855381235</v>
+        <v>2.835465329796885</v>
       </c>
       <c r="F78" t="n">
-        <v>-6.384277371968276</v>
+        <v>-7.533581324694957</v>
       </c>
       <c r="G78" t="n">
-        <v>12.76855474393747</v>
+        <v>15.06716264938955</v>
       </c>
       <c r="H78" t="n">
-        <v>-8.821493622557909</v>
+        <v>-12.28021002521488</v>
       </c>
       <c r="I78" t="n">
-        <v>17.58562585139063</v>
+        <v>17.7875287969372</v>
       </c>
       <c r="J78" t="n">
-        <v>-11.93702098007843</v>
+        <v>-15.95659771166602</v>
       </c>
       <c r="K78" t="n">
-        <v>17.76566247328015</v>
+        <v>17.99997579029359</v>
       </c>
       <c r="L78" t="n">
-        <v>29.0560836897065</v>
+        <v>34.29394793246161</v>
       </c>
       <c r="M78" t="n">
-        <v>106.788448008303</v>
+        <v>119.3004125321324</v>
       </c>
       <c r="N78" t="n">
-        <v>106.788448008303</v>
+        <v>119.3004125321324</v>
       </c>
       <c r="O78" t="n">
-        <v>56.3368153325163</v>
+        <v>92.56184536728995</v>
       </c>
       <c r="P78" t="n">
-        <v>224.5254125046316</v>
+        <v>268.0056673958045</v>
       </c>
       <c r="Q78" t="n">
-        <v>280.8622278371479</v>
+        <v>360.5675127630944</v>
       </c>
       <c r="R78" t="n">
-        <v>56.3368153325163</v>
+        <v>92.56184536728995</v>
       </c>
       <c r="S78" t="n">
-        <v>224.5254125046316</v>
+        <v>268.0056673958045</v>
       </c>
       <c r="T78" t="n">
-        <v>280.8622278371479</v>
+        <v>360.5675127630944</v>
       </c>
     </row>
     <row r="79">
@@ -5297,61 +5297,61 @@
         <v>0.154</v>
       </c>
       <c r="B79" t="n">
-        <v>0.3069044774048009</v>
+        <v>0.3339471010812366</v>
       </c>
       <c r="C79" t="n">
-        <v>-0.6609225081012645</v>
+        <v>-0.7314347190260486</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.819747637387264</v>
+        <v>-1.678723215537696</v>
       </c>
       <c r="E79" t="n">
-        <v>2.596913143565569</v>
+        <v>2.89607203212537</v>
       </c>
       <c r="F79" t="n">
-        <v>-6.579368112702569</v>
+        <v>-7.797839206442196</v>
       </c>
       <c r="G79" t="n">
-        <v>13.15873622540528</v>
+        <v>15.59567841288402</v>
       </c>
       <c r="H79" t="n">
-        <v>-8.987339117188931</v>
+        <v>-12.62938329967758</v>
       </c>
       <c r="I79" t="n">
-        <v>17.36170272205603</v>
+        <v>17.78007562465758</v>
       </c>
       <c r="J79" t="n">
-        <v>-12.19807075618779</v>
+        <v>-16.43472883242137</v>
       </c>
       <c r="K79" t="n">
-        <v>17.54724090283424</v>
+        <v>17.99997469027924</v>
       </c>
       <c r="L79" t="n">
-        <v>28.52198022251097</v>
+        <v>33.76030837437818</v>
       </c>
       <c r="M79" t="n">
-        <v>106.5148124908946</v>
+        <v>120.7097019346107</v>
       </c>
       <c r="N79" t="n">
-        <v>106.5148124908946</v>
+        <v>120.7097019346107</v>
       </c>
       <c r="O79" t="n">
-        <v>59.14845109901044</v>
+        <v>98.53188565741273</v>
       </c>
       <c r="P79" t="n">
-        <v>228.3901834839943</v>
+        <v>277.2900729701941</v>
       </c>
       <c r="Q79" t="n">
-        <v>287.5386345830048</v>
+        <v>375.8219586276069</v>
       </c>
       <c r="R79" t="n">
-        <v>59.14845109901044</v>
+        <v>98.53188565741273</v>
       </c>
       <c r="S79" t="n">
-        <v>228.3901834839943</v>
+        <v>277.2900729701941</v>
       </c>
       <c r="T79" t="n">
-        <v>287.5386345830048</v>
+        <v>375.8219586276069</v>
       </c>
     </row>
     <row r="80">
@@ -5359,61 +5359,61 @@
         <v>0.156</v>
       </c>
       <c r="B80" t="n">
-        <v>0.312122447762929</v>
+        <v>0.339785261889143</v>
       </c>
       <c r="C80" t="n">
-        <v>-0.6741765831649293</v>
+        <v>-0.7471884703683652</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.793239487259935</v>
+        <v>-1.647215712853063</v>
       </c>
       <c r="E80" t="n">
-        <v>2.648142975604897</v>
+        <v>2.957436847498158</v>
       </c>
       <c r="F80" t="n">
-        <v>-6.778158000095613</v>
+        <v>-8.073827835351873</v>
       </c>
       <c r="G80" t="n">
-        <v>13.55631600019014</v>
+        <v>16.14765567070478</v>
       </c>
       <c r="H80" t="n">
-        <v>-9.129922622690575</v>
+        <v>-12.97276953884651</v>
       </c>
       <c r="I80" t="n">
-        <v>17.09968361117847</v>
+        <v>17.77228319197192</v>
       </c>
       <c r="J80" t="n">
-        <v>-12.43766372673723</v>
+        <v>-16.91279752249822</v>
       </c>
       <c r="K80" t="n">
-        <v>17.29082766678115</v>
+        <v>17.99996513692885</v>
       </c>
       <c r="L80" t="n">
-        <v>27.99906342370281</v>
+        <v>32.76902105709181</v>
       </c>
       <c r="M80" t="n">
-        <v>106.0338745654922</v>
+        <v>121.9894318007804</v>
       </c>
       <c r="N80" t="n">
-        <v>106.0338745654922</v>
+        <v>121.9894318007804</v>
       </c>
       <c r="O80" t="n">
-        <v>61.89251950868923</v>
+        <v>104.7494025803809</v>
       </c>
       <c r="P80" t="n">
-        <v>231.785845589963</v>
+        <v>286.9802785380389</v>
       </c>
       <c r="Q80" t="n">
-        <v>293.6783650986523</v>
+        <v>391.7296811184198</v>
       </c>
       <c r="R80" t="n">
-        <v>61.89251950868923</v>
+        <v>104.7494025803809</v>
       </c>
       <c r="S80" t="n">
-        <v>231.785845589963</v>
+        <v>286.9802785380389</v>
       </c>
       <c r="T80" t="n">
-        <v>293.6783650986523</v>
+        <v>391.7296811184198</v>
       </c>
     </row>
     <row r="81">
@@ -5421,61 +5421,61 @@
         <v>0.158</v>
       </c>
       <c r="B81" t="n">
-        <v>0.3174923668879452</v>
+        <v>0.3458021576925666</v>
       </c>
       <c r="C81" t="n">
-        <v>-0.6880370563838853</v>
+        <v>-0.7637856441206574</v>
       </c>
       <c r="D81" t="n">
-        <v>-1.765518540822023</v>
+        <v>-1.614021365348479</v>
       </c>
       <c r="E81" t="n">
-        <v>2.698621072312415</v>
+        <v>3.019961931630582</v>
       </c>
       <c r="F81" t="n">
-        <v>-6.986668332323074</v>
+        <v>-8.375038263890877</v>
       </c>
       <c r="G81" t="n">
-        <v>13.97333666464652</v>
+        <v>16.75007652778148</v>
       </c>
       <c r="H81" t="n">
-        <v>-9.39201784583155</v>
+        <v>-13.15691287358171</v>
       </c>
       <c r="I81" t="n">
-        <v>16.74549808359806</v>
+        <v>17.76379852274266</v>
       </c>
       <c r="J81" t="n">
-        <v>-12.80151199200521</v>
+        <v>-17.24393154636046</v>
       </c>
       <c r="K81" t="n">
-        <v>16.94252213056958</v>
+        <v>17.99997460178438</v>
       </c>
       <c r="L81" t="n">
-        <v>26.96017846965582</v>
+        <v>31.79284740279424</v>
       </c>
       <c r="M81" t="n">
-        <v>105.0275648646499</v>
+        <v>123.0219623767225</v>
       </c>
       <c r="N81" t="n">
-        <v>105.0275648646499</v>
+        <v>123.0219623767225</v>
       </c>
       <c r="O81" t="n">
-        <v>65.65244369512858</v>
+        <v>110.2203286470074</v>
       </c>
       <c r="P81" t="n">
-        <v>233.8998599081969</v>
+        <v>297.5419524173894</v>
       </c>
       <c r="Q81" t="n">
-        <v>299.5523036033255</v>
+        <v>407.7622810643969</v>
       </c>
       <c r="R81" t="n">
-        <v>65.65244369512858</v>
+        <v>110.2203286470074</v>
       </c>
       <c r="S81" t="n">
-        <v>233.8998599081969</v>
+        <v>297.5419524173894</v>
       </c>
       <c r="T81" t="n">
-        <v>299.5523036033255</v>
+        <v>407.7622810643969</v>
       </c>
     </row>
     <row r="82">
@@ -5483,61 +5483,61 @@
         <v>0.16</v>
       </c>
       <c r="B82" t="n">
-        <v>0.322935098171035</v>
+        <v>0.3519041980765052</v>
       </c>
       <c r="C82" t="n">
-        <v>-0.7022110106758959</v>
+        <v>-0.78081293455309</v>
       </c>
       <c r="D82" t="n">
-        <v>-1.737170632238002</v>
+        <v>-1.579966784483613</v>
       </c>
       <c r="E82" t="n">
-        <v>2.748415349424967</v>
+        <v>3.082894074320513</v>
       </c>
       <c r="F82" t="n">
-        <v>-7.200025519933804</v>
+        <v>-8.689505262775297</v>
       </c>
       <c r="G82" t="n">
-        <v>14.40005103986821</v>
+        <v>17.37901052555</v>
       </c>
       <c r="H82" t="n">
-        <v>-9.58648250723974</v>
+        <v>-13.31446243883952</v>
       </c>
       <c r="I82" t="n">
-        <v>16.34182599708467</v>
+        <v>17.75493717969912</v>
       </c>
       <c r="J82" t="n">
-        <v>-13.10009496096744</v>
+        <v>-17.55494100707386</v>
       </c>
       <c r="K82" t="n">
-        <v>16.54486671674681</v>
+        <v>17.99998122810937</v>
       </c>
       <c r="L82" t="n">
-        <v>26.05874836517716</v>
+        <v>30.46123765103686</v>
       </c>
       <c r="M82" t="n">
-        <v>103.7259088404316</v>
+        <v>123.9100283742976</v>
       </c>
       <c r="N82" t="n">
-        <v>103.7259088404316</v>
+        <v>123.9100283742976</v>
       </c>
       <c r="O82" t="n">
-        <v>69.03577580629823</v>
+        <v>115.7155628506544</v>
       </c>
       <c r="P82" t="n">
-        <v>235.2132095516274</v>
+        <v>308.5604613043429</v>
       </c>
       <c r="Q82" t="n">
-        <v>304.2489853579256</v>
+        <v>424.2760241549972</v>
       </c>
       <c r="R82" t="n">
-        <v>69.03577580629823</v>
+        <v>115.7155628506544</v>
       </c>
       <c r="S82" t="n">
-        <v>235.2132095516274</v>
+        <v>308.5604613043429</v>
       </c>
       <c r="T82" t="n">
-        <v>304.2489853579256</v>
+        <v>424.2760241549972</v>
       </c>
     </row>
     <row r="83">
@@ -5545,61 +5545,61 @@
         <v>0.162</v>
       </c>
       <c r="B83" t="n">
-        <v>0.3284697833936584</v>
+        <v>0.3581284955879506</v>
       </c>
       <c r="C83" t="n">
-        <v>-0.7167808579121511</v>
+        <v>-0.7984650471165374</v>
       </c>
       <c r="D83" t="n">
-        <v>-1.708030937765491</v>
+        <v>-1.544662559356718</v>
       </c>
       <c r="E83" t="n">
-        <v>2.797346035794556</v>
+        <v>3.146373545042457</v>
       </c>
       <c r="F83" t="n">
-        <v>-7.419503765601767</v>
+        <v>-9.023323784931538</v>
       </c>
       <c r="G83" t="n">
-        <v>14.83900753120283</v>
+        <v>18.04664756986416</v>
       </c>
       <c r="H83" t="n">
-        <v>-9.695537029067822</v>
+        <v>-13.44639400253986</v>
       </c>
       <c r="I83" t="n">
-        <v>15.87565769883632</v>
+        <v>17.74552301271281</v>
       </c>
       <c r="J83" t="n">
-        <v>-13.31625486668148</v>
+        <v>-17.84977600958645</v>
       </c>
       <c r="K83" t="n">
-        <v>16.08488770502629</v>
+        <v>17.99998074344789</v>
       </c>
       <c r="L83" t="n">
-        <v>25.33090898043818</v>
+        <v>28.52675854395662</v>
       </c>
       <c r="M83" t="n">
-        <v>102.0512621141149</v>
+        <v>124.5838485892484</v>
       </c>
       <c r="N83" t="n">
-        <v>102.0512621141149</v>
+        <v>124.5838485892484</v>
       </c>
       <c r="O83" t="n">
-        <v>71.94351255215602</v>
+        <v>121.342627819182</v>
       </c>
       <c r="P83" t="n">
-        <v>235.5154056591458</v>
+        <v>320.2455641217607</v>
       </c>
       <c r="Q83" t="n">
-        <v>307.4589182113018</v>
+        <v>441.5881919409426</v>
       </c>
       <c r="R83" t="n">
-        <v>71.94351255215602</v>
+        <v>121.342627819182</v>
       </c>
       <c r="S83" t="n">
-        <v>235.5154056591458</v>
+        <v>320.2455641217607</v>
       </c>
       <c r="T83" t="n">
-        <v>307.4589182113018</v>
+        <v>441.5881919409426</v>
       </c>
     </row>
     <row r="84">
@@ -5607,61 +5607,61 @@
         <v>0.164</v>
       </c>
       <c r="B84" t="n">
-        <v>0.334128680690048</v>
+        <v>0.3645110240156804</v>
       </c>
       <c r="C84" t="n">
-        <v>-0.7319360365469592</v>
+        <v>-0.8170060326798407</v>
       </c>
       <c r="D84" t="n">
-        <v>-1.677720580495875</v>
+        <v>-1.507580588230112</v>
       </c>
       <c r="E84" t="n">
-        <v>2.844450375507326</v>
+        <v>3.210120434704351</v>
       </c>
       <c r="F84" t="n">
-        <v>-7.647791275110617</v>
+        <v>-9.385475792507556</v>
       </c>
       <c r="G84" t="n">
-        <v>15.29558255022117</v>
+        <v>18.77095158501497</v>
       </c>
       <c r="H84" t="n">
-        <v>-9.905459297095753</v>
+        <v>-13.37431839868264</v>
       </c>
       <c r="I84" t="n">
-        <v>15.33250392686315</v>
+        <v>17.7353112872143</v>
       </c>
       <c r="J84" t="n">
-        <v>-13.63758143934973</v>
+        <v>-17.95443058542633</v>
       </c>
       <c r="K84" t="n">
-        <v>15.54817164082127</v>
+        <v>17.99998170456301</v>
       </c>
       <c r="L84" t="n">
-        <v>24.14366347740244</v>
+        <v>26.44352461995735</v>
       </c>
       <c r="M84" t="n">
-        <v>99.85972966740657</v>
+        <v>124.8083008331095</v>
       </c>
       <c r="N84" t="n">
-        <v>99.85972966740657</v>
+        <v>124.8083008331095</v>
       </c>
       <c r="O84" t="n">
-        <v>75.79243119549919</v>
+        <v>125.4974445593809</v>
       </c>
       <c r="P84" t="n">
-        <v>234.3412623007303</v>
+        <v>332.9040020076716</v>
       </c>
       <c r="Q84" t="n">
-        <v>310.1336934962295</v>
+        <v>458.4014465670525</v>
       </c>
       <c r="R84" t="n">
-        <v>75.79243119549919</v>
+        <v>125.4974445593809</v>
       </c>
       <c r="S84" t="n">
-        <v>234.3412623007303</v>
+        <v>332.9040020076716</v>
       </c>
       <c r="T84" t="n">
-        <v>310.1336934962295</v>
+        <v>458.4014465670525</v>
       </c>
     </row>
     <row r="85">
@@ -5669,61 +5669,61 @@
         <v>0.166</v>
       </c>
       <c r="B85" t="n">
-        <v>0.3398406701609119</v>
+        <v>0.3709783235102522</v>
       </c>
       <c r="C85" t="n">
-        <v>-0.7473516459362551</v>
+        <v>-0.8360565669550328</v>
       </c>
       <c r="D85" t="n">
-        <v>-1.646889361717283</v>
+        <v>-1.469479519679728</v>
       </c>
       <c r="E85" t="n">
-        <v>2.890656864594956</v>
+        <v>3.273751368396582</v>
       </c>
       <c r="F85" t="n">
-        <v>-7.879992906918514</v>
+        <v>-9.763706844325391</v>
       </c>
       <c r="G85" t="n">
-        <v>15.75998581383784</v>
+        <v>19.52741368864974</v>
       </c>
       <c r="H85" t="n">
-        <v>-10.12344591406331</v>
+        <v>-13.23494139328619</v>
       </c>
       <c r="I85" t="n">
-        <v>14.75495305132489</v>
+        <v>17.70012770041068</v>
       </c>
       <c r="J85" t="n">
-        <v>-13.96888245263954</v>
+        <v>-17.99963033331698</v>
       </c>
       <c r="K85" t="n">
-        <v>14.97716885130001</v>
+        <v>17.97546423342064</v>
       </c>
       <c r="L85" t="n">
-        <v>22.87437107501583</v>
+        <v>24.06750774749651</v>
       </c>
       <c r="M85" t="n">
-        <v>97.4335145616575</v>
+        <v>124.6565260953838</v>
       </c>
       <c r="N85" t="n">
-        <v>97.4335145616575</v>
+        <v>124.6565260953838</v>
       </c>
       <c r="O85" t="n">
-        <v>79.77658830345129</v>
+        <v>129.1957369510516</v>
       </c>
       <c r="P85" t="n">
-        <v>232.4748350911471</v>
+        <v>345.6084922673953</v>
       </c>
       <c r="Q85" t="n">
-        <v>312.2514233945984</v>
+        <v>474.8042292184469</v>
       </c>
       <c r="R85" t="n">
-        <v>79.77658830345129</v>
+        <v>129.1957369510516</v>
       </c>
       <c r="S85" t="n">
-        <v>232.4748350911471</v>
+        <v>345.6084922673953</v>
       </c>
       <c r="T85" t="n">
-        <v>312.2514233945984</v>
+        <v>474.8042292184469</v>
       </c>
     </row>
     <row r="86">
@@ -5731,61 +5731,61 @@
         <v>0.168</v>
       </c>
       <c r="B86" t="n">
-        <v>0.3456830127527333</v>
+        <v>0.3775896049177391</v>
       </c>
       <c r="C86" t="n">
-        <v>-0.7634519313932486</v>
+        <v>-0.8560165265338128</v>
       </c>
       <c r="D86" t="n">
-        <v>-1.614688790803296</v>
+        <v>-1.429559600522168</v>
       </c>
       <c r="E86" t="n">
-        <v>2.934140935160265</v>
+        <v>3.336843515401926</v>
       </c>
       <c r="F86" t="n">
-        <v>-8.122462012652681</v>
+        <v>-10.17043410271913</v>
       </c>
       <c r="G86" t="n">
-        <v>16.24492402530491</v>
+        <v>20.34086820543936</v>
       </c>
       <c r="H86" t="n">
-        <v>-10.20633732102576</v>
+        <v>-13.03663170073652</v>
       </c>
       <c r="I86" t="n">
-        <v>14.08636012872432</v>
+        <v>17.59016303457598</v>
       </c>
       <c r="J86" t="n">
-        <v>-14.17009878320026</v>
+        <v>-17.99980354286346</v>
       </c>
       <c r="K86" t="n">
-        <v>14.31541355748112</v>
+        <v>17.87696927627267</v>
       </c>
       <c r="L86" t="n">
-        <v>21.90883921609037</v>
+        <v>20.91320546938304</v>
       </c>
       <c r="M86" t="n">
-        <v>94.37033890277733</v>
+        <v>123.68707856484</v>
       </c>
       <c r="N86" t="n">
-        <v>94.37033890277733</v>
+        <v>123.68707856484</v>
       </c>
       <c r="O86" t="n">
-        <v>82.91260279616937</v>
+        <v>132.5567326370335</v>
       </c>
       <c r="P86" t="n">
-        <v>228.6380167948897</v>
+        <v>357.7642860469725</v>
       </c>
       <c r="Q86" t="n">
-        <v>311.550619591059</v>
+        <v>490.321018684006</v>
       </c>
       <c r="R86" t="n">
-        <v>82.91260279616937</v>
+        <v>132.5567326370335</v>
       </c>
       <c r="S86" t="n">
-        <v>228.6380167948897</v>
+        <v>357.7642860469725</v>
       </c>
       <c r="T86" t="n">
-        <v>311.550619591059</v>
+        <v>490.321018684006</v>
       </c>
     </row>
     <row r="87">
@@ -5793,61 +5793,61 @@
         <v>0.17</v>
       </c>
       <c r="B87" t="n">
-        <v>0.3515899317081012</v>
+        <v>0.3843271538244094</v>
       </c>
       <c r="C87" t="n">
-        <v>-0.779939307039774</v>
+        <v>-0.8768987371868765</v>
       </c>
       <c r="D87" t="n">
-        <v>-1.581714039510245</v>
+        <v>-1.38779517921604</v>
       </c>
       <c r="E87" t="n">
-        <v>2.975751735343337</v>
+        <v>3.398506094800714</v>
       </c>
       <c r="F87" t="n">
-        <v>-8.370781409363042</v>
+        <v>-10.60851697420623</v>
       </c>
       <c r="G87" t="n">
-        <v>16.74156281872557</v>
+        <v>21.21703394841251</v>
       </c>
       <c r="H87" t="n">
-        <v>-10.34849364354033</v>
+        <v>-12.80579928012862</v>
       </c>
       <c r="I87" t="n">
-        <v>13.37602579193795</v>
+        <v>17.37255537110962</v>
       </c>
       <c r="J87" t="n">
-        <v>-14.4334349713095</v>
+        <v>-17.98275556354126</v>
       </c>
       <c r="K87" t="n">
-        <v>13.61208182768198</v>
+        <v>17.67171554978224</v>
       </c>
       <c r="L87" t="n">
-        <v>20.66381810888616</v>
+        <v>17.89458564091353</v>
       </c>
       <c r="M87" t="n">
-        <v>90.9549243747044</v>
+        <v>121.6767117063404</v>
       </c>
       <c r="N87" t="n">
-        <v>90.9549243747044</v>
+        <v>121.6767117063404</v>
       </c>
       <c r="O87" t="n">
-        <v>86.65471230935077</v>
+        <v>135.7837943218172</v>
       </c>
       <c r="P87" t="n">
-        <v>223.7201575488374</v>
+        <v>368.4492449073927</v>
       </c>
       <c r="Q87" t="n">
-        <v>310.3748698581882</v>
+        <v>504.2330392292099</v>
       </c>
       <c r="R87" t="n">
-        <v>86.65471230935077</v>
+        <v>135.7837943218172</v>
       </c>
       <c r="S87" t="n">
-        <v>223.7201575488374</v>
+        <v>368.4492449073927</v>
       </c>
       <c r="T87" t="n">
-        <v>310.3748698581882</v>
+        <v>504.2330392292099</v>
       </c>
     </row>
     <row r="88">
@@ -5855,61 +5855,61 @@
         <v>0.172</v>
       </c>
       <c r="B88" t="n">
-        <v>0.3575698078327922</v>
+        <v>0.3911434201887119</v>
       </c>
       <c r="C88" t="n">
-        <v>-0.7968640099520368</v>
+        <v>-0.8983881380400884</v>
       </c>
       <c r="D88" t="n">
-        <v>-1.54786463368572</v>
+        <v>-1.344816377509616</v>
       </c>
       <c r="E88" t="n">
-        <v>3.015246149639078</v>
+        <v>3.458976459578697</v>
       </c>
       <c r="F88" t="n">
-        <v>-8.625710355541656</v>
+        <v>-11.06714637487147</v>
       </c>
       <c r="G88" t="n">
-        <v>17.25142071108409</v>
+        <v>22.13429274974115</v>
       </c>
       <c r="H88" t="n">
-        <v>-10.5576063606458</v>
+        <v>-12.56340546529826</v>
       </c>
       <c r="I88" t="n">
-        <v>12.61853278508567</v>
+        <v>17.06658827138471</v>
       </c>
       <c r="J88" t="n">
-        <v>-14.76695301415012</v>
+        <v>-17.96417289623554</v>
       </c>
       <c r="K88" t="n">
-        <v>12.86177781711195</v>
+        <v>17.37868179915606</v>
       </c>
       <c r="L88" t="n">
-        <v>19.1030352695117</v>
+        <v>14.84822728213995</v>
       </c>
       <c r="M88" t="n">
-        <v>87.14155695163112</v>
+        <v>118.9067693670368</v>
       </c>
       <c r="N88" t="n">
-        <v>87.14155695163112</v>
+        <v>118.9067693670368</v>
       </c>
       <c r="O88" t="n">
-        <v>91.08157665549949</v>
+        <v>139.0210159028784</v>
       </c>
       <c r="P88" t="n">
-        <v>217.5809584302983</v>
+        <v>377.6514897427152</v>
       </c>
       <c r="Q88" t="n">
-        <v>308.6625350857977</v>
+        <v>516.6725056455937</v>
       </c>
       <c r="R88" t="n">
-        <v>91.08157665549949</v>
+        <v>139.0210159028784</v>
       </c>
       <c r="S88" t="n">
-        <v>217.5809584302983</v>
+        <v>377.6514897427152</v>
       </c>
       <c r="T88" t="n">
-        <v>308.6625350857977</v>
+        <v>516.6725056455937</v>
       </c>
     </row>
     <row r="89">
@@ -5917,61 +5917,61 @@
         <v>0.174</v>
       </c>
       <c r="B89" t="n">
-        <v>0.3636494448433579</v>
+        <v>0.3981074272171243</v>
       </c>
       <c r="C89" t="n">
-        <v>-0.8144932516552462</v>
+        <v>-0.9211797713649198</v>
       </c>
       <c r="D89" t="n">
-        <v>-1.512606150279301</v>
+        <v>-1.299233110859954</v>
       </c>
       <c r="E89" t="n">
-        <v>3.050784988395899</v>
+        <v>3.515690995204713</v>
       </c>
       <c r="F89" t="n">
-        <v>-8.891669508790201</v>
+        <v>-11.56937677209502</v>
       </c>
       <c r="G89" t="n">
-        <v>17.78333901758059</v>
+        <v>23.13875354419111</v>
       </c>
       <c r="H89" t="n">
-        <v>-10.64198779647976</v>
+        <v>-12.34326540565226</v>
       </c>
       <c r="I89" t="n">
-        <v>11.78844179518981</v>
+        <v>16.48758473277497</v>
       </c>
       <c r="J89" t="n">
-        <v>-14.98112251676938</v>
+        <v>-17.98912127043462</v>
       </c>
       <c r="K89" t="n">
-        <v>12.0391868753377</v>
+        <v>16.81384115774807</v>
       </c>
       <c r="L89" t="n">
-        <v>17.85947096646796</v>
+        <v>11.18323859026769</v>
       </c>
       <c r="M89" t="n">
-        <v>82.67962383722903</v>
+        <v>114.1531142544775</v>
       </c>
       <c r="N89" t="n">
-        <v>82.67962383722903</v>
+        <v>114.1531142544775</v>
       </c>
       <c r="O89" t="n">
-        <v>94.63527214757546</v>
+        <v>142.7497107670378</v>
       </c>
       <c r="P89" t="n">
-        <v>209.325629000582</v>
+        <v>381.2171697090095</v>
       </c>
       <c r="Q89" t="n">
-        <v>303.9609011481574</v>
+        <v>523.9668804760473</v>
       </c>
       <c r="R89" t="n">
-        <v>94.63527214757546</v>
+        <v>142.7497107670378</v>
       </c>
       <c r="S89" t="n">
-        <v>209.325629000582</v>
+        <v>381.2171697090095</v>
       </c>
       <c r="T89" t="n">
-        <v>303.9609011481574</v>
+        <v>523.9668804760473</v>
       </c>
     </row>
     <row r="90">
@@ -5979,61 +5979,61 @@
         <v>0.176</v>
       </c>
       <c r="B90" t="n">
-        <v>0.3697684145079131</v>
+        <v>0.4051478764542007</v>
       </c>
       <c r="C90" t="n">
-        <v>-0.8324270107383356</v>
+        <v>-0.9448892774050301</v>
       </c>
       <c r="D90" t="n">
-        <v>-1.476738632113122</v>
+        <v>-1.251814098779733</v>
       </c>
       <c r="E90" t="n">
-        <v>3.084503900044308</v>
+        <v>3.567381320894809</v>
       </c>
       <c r="F90" t="n">
-        <v>-9.162507217494788</v>
+        <v>-12.09205364159889</v>
       </c>
       <c r="G90" t="n">
-        <v>18.32501443498901</v>
+        <v>24.18410728319843</v>
       </c>
       <c r="H90" t="n">
-        <v>-10.71717577412539</v>
+        <v>-12.09905778713141</v>
       </c>
       <c r="I90" t="n">
-        <v>10.93038330780554</v>
+        <v>15.49109980086078</v>
       </c>
       <c r="J90" t="n">
-        <v>-15.18847929626284</v>
+        <v>-17.99997996423167</v>
       </c>
       <c r="K90" t="n">
-        <v>11.18876601133888</v>
+        <v>15.83209571355388</v>
       </c>
       <c r="L90" t="n">
-        <v>16.59617752181611</v>
+        <v>7.88954192130735</v>
       </c>
       <c r="M90" t="n">
-        <v>77.9341011695593</v>
+        <v>106.6932530636951</v>
       </c>
       <c r="N90" t="n">
-        <v>77.9341011695593</v>
+        <v>106.6932530636951</v>
       </c>
       <c r="O90" t="n">
-        <v>98.20824105587207</v>
+        <v>146.2228243698289</v>
       </c>
       <c r="P90" t="n">
-        <v>200.178317345075</v>
+        <v>373.8394950414244</v>
       </c>
       <c r="Q90" t="n">
-        <v>298.386558400947</v>
+        <v>520.0623194112533</v>
       </c>
       <c r="R90" t="n">
-        <v>98.20824105587207</v>
+        <v>146.2228243698289</v>
       </c>
       <c r="S90" t="n">
-        <v>200.178317345075</v>
+        <v>373.8394950414244</v>
       </c>
       <c r="T90" t="n">
-        <v>298.386558400947</v>
+        <v>520.0623194112533</v>
       </c>
     </row>
     <row r="91">
@@ -6041,61 +6041,61 @@
         <v>0.178</v>
       </c>
       <c r="B91" t="n">
-        <v>0.375976215244359</v>
+        <v>0.4122474056006779</v>
       </c>
       <c r="C91" t="n">
-        <v>-0.851134325484089</v>
+        <v>-0.969311629652711</v>
       </c>
       <c r="D91" t="n">
-        <v>-1.439324002621615</v>
+        <v>-1.202969394284371</v>
       </c>
       <c r="E91" t="n">
-        <v>3.113276978133301</v>
+        <v>3.615134475981959</v>
       </c>
       <c r="F91" t="n">
-        <v>-9.44606287992568</v>
+        <v>-12.63041668965986</v>
       </c>
       <c r="G91" t="n">
-        <v>18.89212575985158</v>
+        <v>25.26083337931748</v>
       </c>
       <c r="H91" t="n">
-        <v>-10.89992500868468</v>
+        <v>-11.83634344855729</v>
       </c>
       <c r="I91" t="n">
-        <v>10.01126570464032</v>
+        <v>14.16714958573338</v>
       </c>
       <c r="J91" t="n">
-        <v>-15.50960369408841</v>
+        <v>-17.9999867931113</v>
       </c>
       <c r="K91" t="n">
-        <v>10.27764467785423</v>
+        <v>14.52332733638175</v>
       </c>
       <c r="L91" t="n">
-        <v>14.82361414487929</v>
+        <v>4.882446940038314</v>
       </c>
       <c r="M91" t="n">
-        <v>72.45862665554573</v>
+        <v>97.11022545819398</v>
       </c>
       <c r="N91" t="n">
-        <v>72.45862665554573</v>
+        <v>97.11022545819398</v>
       </c>
       <c r="O91" t="n">
-        <v>102.9914632014641</v>
+        <v>149.4972133663346</v>
       </c>
       <c r="P91" t="n">
-        <v>188.8314602702758</v>
+        <v>357.856756922975</v>
       </c>
       <c r="Q91" t="n">
-        <v>291.8229234717399</v>
+        <v>507.3539702893097</v>
       </c>
       <c r="R91" t="n">
-        <v>102.9914632014641</v>
+        <v>149.4972133663346</v>
       </c>
       <c r="S91" t="n">
-        <v>188.8314602702758</v>
+        <v>357.856756922975</v>
       </c>
       <c r="T91" t="n">
-        <v>291.8229234717399</v>
+        <v>507.3539702893097</v>
       </c>
     </row>
     <row r="92">
@@ -6103,61 +6103,61 @@
         <v>0.18</v>
       </c>
       <c r="B92" t="n">
-        <v>0.3822257981127314</v>
+        <v>0.4194039704312614</v>
       </c>
       <c r="C92" t="n">
-        <v>-0.8703231535226531</v>
+        <v>-0.9953824152826226</v>
       </c>
       <c r="D92" t="n">
-        <v>-1.400946346544487</v>
+        <v>-1.150827823024548</v>
       </c>
       <c r="E92" t="n">
-        <v>3.138649439134327</v>
+        <v>3.644025175550604</v>
       </c>
       <c r="F92" t="n">
-        <v>-9.738191156097459</v>
+        <v>-13.15155227972224</v>
       </c>
       <c r="G92" t="n">
-        <v>19.47638231219513</v>
+        <v>26.30310455944519</v>
       </c>
       <c r="H92" t="n">
-        <v>-11.00951532569292</v>
+        <v>-11.58203438624101</v>
       </c>
       <c r="I92" t="n">
-        <v>9.060594298673783</v>
+        <v>11.18917763115144</v>
       </c>
       <c r="J92" t="n">
-        <v>-15.76175260986848</v>
+        <v>-17.99999189874547</v>
       </c>
       <c r="K92" t="n">
-        <v>9.335211289275733</v>
+        <v>11.56005140543961</v>
       </c>
       <c r="L92" t="n">
-        <v>13.26859870237105</v>
+        <v>2.052141243442719</v>
       </c>
       <c r="M92" t="n">
-        <v>66.54791856792481</v>
+        <v>76.67571060917123</v>
       </c>
       <c r="N92" t="n">
-        <v>66.54791856792481</v>
+        <v>76.67571060917123</v>
       </c>
       <c r="O92" t="n">
-        <v>107.2189407196686</v>
+        <v>152.247545574278</v>
       </c>
       <c r="P92" t="n">
-        <v>176.1266100673719</v>
+        <v>292.5726851862323</v>
       </c>
       <c r="Q92" t="n">
-        <v>283.3455507870405</v>
+        <v>444.8202307605104</v>
       </c>
       <c r="R92" t="n">
-        <v>107.2189407196686</v>
+        <v>152.247545574278</v>
       </c>
       <c r="S92" t="n">
-        <v>176.1266100673719</v>
+        <v>292.5726851862323</v>
       </c>
       <c r="T92" t="n">
-        <v>283.3455507870405</v>
+        <v>444.8202307605104</v>
       </c>
     </row>
     <row r="93">
@@ -6165,61 +6165,61 @@
         <v>0.182</v>
       </c>
       <c r="B93" t="n">
-        <v>0.3885176419419719</v>
+        <v>0.4265171475388796</v>
       </c>
       <c r="C93" t="n">
-        <v>-0.889999013062163</v>
+        <v>-1.022079265241949</v>
       </c>
       <c r="D93" t="n">
-        <v>-1.361594627465467</v>
+        <v>-1.097434123105895</v>
       </c>
       <c r="E93" t="n">
-        <v>3.160582311510863</v>
+        <v>3.656010183514855</v>
       </c>
       <c r="F93" t="n">
-        <v>-10.03899028933505</v>
+        <v>-13.61274669282574</v>
       </c>
       <c r="G93" t="n">
-        <v>20.0779805786695</v>
+        <v>27.22549338565245</v>
       </c>
       <c r="H93" t="n">
-        <v>-11.04510831395774</v>
+        <v>-11.35697521137212</v>
       </c>
       <c r="I93" t="n">
-        <v>8.078007479013975</v>
+        <v>6.874100716880684</v>
       </c>
       <c r="J93" t="n">
-        <v>-15.94413557515324</v>
+        <v>-17.99999559747108</v>
       </c>
       <c r="K93" t="n">
-        <v>8.361107005173213</v>
+        <v>7.257980173618384</v>
       </c>
       <c r="L93" t="n">
-        <v>11.93362432334803</v>
+        <v>0.3393677009441385</v>
       </c>
       <c r="M93" t="n">
-        <v>60.19698907046798</v>
+        <v>46.78889876380667</v>
       </c>
       <c r="N93" t="n">
-        <v>60.19698907046798</v>
+        <v>46.78889876380667</v>
       </c>
       <c r="O93" t="n">
-        <v>110.8843047011128</v>
+        <v>154.5637188968108</v>
       </c>
       <c r="P93" t="n">
-        <v>162.0482039495442</v>
+        <v>184.8602330609555</v>
       </c>
       <c r="Q93" t="n">
-        <v>272.932508650657</v>
+        <v>339.4239519577663</v>
       </c>
       <c r="R93" t="n">
-        <v>110.8843047011128</v>
+        <v>154.5637188968108</v>
       </c>
       <c r="S93" t="n">
-        <v>162.0482039495442</v>
+        <v>184.8602330609555</v>
       </c>
       <c r="T93" t="n">
-        <v>272.932508650657</v>
+        <v>339.4239519577663</v>
       </c>
     </row>
     <row r="94">
@@ -6227,371 +6227,61 @@
         <v>0.184</v>
       </c>
       <c r="B94" t="n">
-        <v>0.3948594678878951</v>
+        <v>0.4344163648302988</v>
       </c>
       <c r="C94" t="n">
-        <v>-0.910540231243578</v>
+        <v>-1.052839802733387</v>
       </c>
       <c r="D94" t="n">
-        <v>-1.320512191102637</v>
+        <v>-1.035913048123018</v>
       </c>
       <c r="E94" t="n">
-        <v>3.175837355222601</v>
+        <v>3.645560011554255</v>
       </c>
       <c r="F94" t="n">
-        <v>-10.35673190642436</v>
+        <v>-14.04426773748821</v>
       </c>
       <c r="G94" t="n">
-        <v>20.71346381284876</v>
+        <v>28.08853547497387</v>
       </c>
       <c r="H94" t="n">
-        <v>-11.1936902916434</v>
+        <v>-11.14639509499104</v>
       </c>
       <c r="I94" t="n">
-        <v>7.058342639317601</v>
+        <v>0.1576812131287555</v>
       </c>
       <c r="J94" t="n">
-        <v>-16.24777546197849</v>
+        <v>-17.99999752168357</v>
       </c>
       <c r="K94" t="n">
-        <v>7.350402479078769</v>
+        <v>1.267306059272364</v>
       </c>
       <c r="L94" t="n">
-        <v>10.08634215490773</v>
+        <v>-8.98846820296097e-09</v>
       </c>
       <c r="M94" t="n">
-        <v>52.99764652172973</v>
+        <v>4.980043313999673</v>
       </c>
       <c r="N94" t="n">
-        <v>52.99764652172973</v>
+        <v>4.980043313999673</v>
       </c>
       <c r="O94" t="n">
-        <v>115.9675521397751</v>
+        <v>156.5429570218796</v>
       </c>
       <c r="P94" t="n">
-        <v>145.7501243625927</v>
+        <v>4.429034348703966</v>
       </c>
       <c r="Q94" t="n">
-        <v>261.7176765023678</v>
+        <v>160.9719913705836</v>
       </c>
       <c r="R94" t="n">
-        <v>115.9675521397751</v>
+        <v>156.5429570218796</v>
       </c>
       <c r="S94" t="n">
-        <v>145.7501243625927</v>
+        <v>4.429034348703966</v>
       </c>
       <c r="T94" t="n">
-        <v>261.7176765023678</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="n">
-        <v>0.186</v>
-      </c>
-      <c r="B95" t="n">
-        <v>0.401216540082471</v>
-      </c>
-      <c r="C95" t="n">
-        <v>-0.9314479770613235</v>
-      </c>
-      <c r="D95" t="n">
-        <v>-1.278696699467146</v>
-      </c>
-      <c r="E95" t="n">
-        <v>3.18816365877461</v>
-      </c>
-      <c r="F95" t="n">
-        <v>-10.6821865137738</v>
-      </c>
-      <c r="G95" t="n">
-        <v>21.36437302754818</v>
-      </c>
-      <c r="H95" t="n">
-        <v>-11.34005111198459</v>
-      </c>
-      <c r="I95" t="n">
-        <v>6.02805336372208</v>
-      </c>
-      <c r="J95" t="n">
-        <v>-16.55295813070621</v>
-      </c>
-      <c r="K95" t="n">
-        <v>6.32929102341051</v>
-      </c>
-      <c r="L95" t="n">
-        <v>8.229350761936686</v>
-      </c>
-      <c r="M95" t="n">
-        <v>45.46159934673263</v>
-      </c>
-      <c r="N95" t="n">
-        <v>45.46159934673263</v>
-      </c>
-      <c r="O95" t="n">
-        <v>121.1402189427829</v>
-      </c>
-      <c r="P95" t="n">
-        <v>128.5912059469964</v>
-      </c>
-      <c r="Q95" t="n">
-        <v>249.7314248897793</v>
-      </c>
-      <c r="R95" t="n">
-        <v>121.1402189427829</v>
-      </c>
-      <c r="S95" t="n">
-        <v>128.5912059469964</v>
-      </c>
-      <c r="T95" t="n">
-        <v>249.7314248897793</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="n">
-        <v>0.188</v>
-      </c>
-      <c r="B96" t="n">
-        <v>0.407599209025804</v>
-      </c>
-      <c r="C96" t="n">
-        <v>-0.9532591478950855</v>
-      </c>
-      <c r="D96" t="n">
-        <v>-1.235074357799623</v>
-      </c>
-      <c r="E96" t="n">
-        <v>3.193068248288945</v>
-      </c>
-      <c r="F96" t="n">
-        <v>-11.02773826755967</v>
-      </c>
-      <c r="G96" t="n">
-        <v>22.05547653511892</v>
-      </c>
-      <c r="H96" t="n">
-        <v>-11.37964278189333</v>
-      </c>
-      <c r="I96" t="n">
-        <v>4.981852525717041</v>
-      </c>
-      <c r="J96" t="n">
-        <v>-16.76117905646245</v>
-      </c>
-      <c r="K96" t="n">
-        <v>5.292834744862217</v>
-      </c>
-      <c r="L96" t="n">
-        <v>6.76770080142403</v>
-      </c>
-      <c r="M96" t="n">
-        <v>37.14144127299249</v>
-      </c>
-      <c r="N96" t="n">
-        <v>37.14144127299249</v>
-      </c>
-      <c r="O96" t="n">
-        <v>125.4994085661356</v>
-      </c>
-      <c r="P96" t="n">
-        <v>109.4709093287164</v>
-      </c>
-      <c r="Q96" t="n">
-        <v>234.970317894852</v>
-      </c>
-      <c r="R96" t="n">
-        <v>125.4994085661356</v>
-      </c>
-      <c r="S96" t="n">
-        <v>109.4709093287164</v>
-      </c>
-      <c r="T96" t="n">
-        <v>234.970317894852</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="B97" t="n">
-        <v>0.4139813965277028</v>
-      </c>
-      <c r="C97" t="n">
-        <v>-0.97569816999848</v>
-      </c>
-      <c r="D97" t="n">
-        <v>-1.190196313592834</v>
-      </c>
-      <c r="E97" t="n">
-        <v>3.192534797662857</v>
-      </c>
-      <c r="F97" t="n">
-        <v>-11.38942231145032</v>
-      </c>
-      <c r="G97" t="n">
-        <v>22.77884462290037</v>
-      </c>
-      <c r="H97" t="n">
-        <v>-11.50039675603567</v>
-      </c>
-      <c r="I97" t="n">
-        <v>3.937181228892008</v>
-      </c>
-      <c r="J97" t="n">
-        <v>-17.05843484402342</v>
-      </c>
-      <c r="K97" t="n">
-        <v>4.258362938074903</v>
-      </c>
-      <c r="L97" t="n">
-        <v>4.975944078761392</v>
-      </c>
-      <c r="M97" t="n">
-        <v>28.18198738940326</v>
-      </c>
-      <c r="N97" t="n">
-        <v>28.18198738940326</v>
-      </c>
-      <c r="O97" t="n">
-        <v>131.0263241367428</v>
-      </c>
-      <c r="P97" t="n">
-        <v>89.2177366041258</v>
-      </c>
-      <c r="Q97" t="n">
-        <v>220.2440607408686</v>
-      </c>
-      <c r="R97" t="n">
-        <v>131.0263241367428</v>
-      </c>
-      <c r="S97" t="n">
-        <v>89.2177366041258</v>
-      </c>
-      <c r="T97" t="n">
-        <v>220.2440607408686</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="n">
-        <v>0.192</v>
-      </c>
-      <c r="B98" t="n">
-        <v>0.4203631480392171</v>
-      </c>
-      <c r="C98" t="n">
-        <v>-0.9987057703275581</v>
-      </c>
-      <c r="D98" t="n">
-        <v>-1.144181112934677</v>
-      </c>
-      <c r="E98" t="n">
-        <v>3.187076691527119</v>
-      </c>
-      <c r="F98" t="n">
-        <v>-11.76571565746016</v>
-      </c>
-      <c r="G98" t="n">
-        <v>23.53143131492125</v>
-      </c>
-      <c r="H98" t="n">
-        <v>-11.6946508107951</v>
-      </c>
-      <c r="I98" t="n">
-        <v>2.89389507509734</v>
-      </c>
-      <c r="J98" t="n">
-        <v>-17.43632005163566</v>
-      </c>
-      <c r="K98" t="n">
-        <v>3.225688256637731</v>
-      </c>
-      <c r="L98" t="n">
-        <v>2.885244714445381</v>
-      </c>
-      <c r="M98" t="n">
-        <v>18.64359117531009</v>
-      </c>
-      <c r="N98" t="n">
-        <v>18.64359117531009</v>
-      </c>
-      <c r="O98" t="n">
-        <v>137.6107251012446</v>
-      </c>
-      <c r="P98" t="n">
-        <v>67.93863828600684</v>
-      </c>
-      <c r="Q98" t="n">
-        <v>205.5493633872514</v>
-      </c>
-      <c r="R98" t="n">
-        <v>137.6107251012446</v>
-      </c>
-      <c r="S98" t="n">
-        <v>67.93863828600684</v>
-      </c>
-      <c r="T98" t="n">
-        <v>205.5493633872514</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="n">
-        <v>0.194</v>
-      </c>
-      <c r="B99" t="n">
-        <v>0.4317255717420492</v>
-      </c>
-      <c r="C99" t="n">
-        <v>-1.042071761806798</v>
-      </c>
-      <c r="D99" t="n">
-        <v>-1.057449129976197</v>
-      </c>
-      <c r="E99" t="n">
-        <v>3.15807345807034</v>
-      </c>
-      <c r="F99" t="n">
-        <v>-12.50658455040448</v>
-      </c>
-      <c r="G99" t="n">
-        <v>25.0131691008079</v>
-      </c>
-      <c r="H99" t="n">
-        <v>-11.89678480573713</v>
-      </c>
-      <c r="I99" t="n">
-        <v>1.142066292706947</v>
-      </c>
-      <c r="J99" t="n">
-        <v>-17.75518328206118</v>
-      </c>
-      <c r="K99" t="n">
-        <v>2.254606304959066</v>
-      </c>
-      <c r="L99" t="n">
-        <v>-1.065616518577162e-11</v>
-      </c>
-      <c r="M99" t="n">
-        <v>8.284468712912263</v>
-      </c>
-      <c r="N99" t="n">
-        <v>8.284468712912263</v>
-      </c>
-      <c r="O99" t="n">
-        <v>148.7881450509187</v>
-      </c>
-      <c r="P99" t="n">
-        <v>28.56669730381164</v>
-      </c>
-      <c r="Q99" t="n">
-        <v>177.3548423547304</v>
-      </c>
-      <c r="R99" t="n">
-        <v>148.7881450509187</v>
-      </c>
-      <c r="S99" t="n">
-        <v>28.56669730381164</v>
-      </c>
-      <c r="T99" t="n">
-        <v>177.3548423547304</v>
+        <v>160.9719913705836</v>
       </c>
     </row>
   </sheetData>
